--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1,19 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ResearchInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
   <si>
     <t>id</t>
   </si>
@@ -147,81 +161,87 @@
     <t>终焉议会议案：魔王重命名</t>
   </si>
   <si>
-    <t>ui_research_8</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>100200001</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>ui_research_57</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>开启孕育功能</t>
+  </si>
+  <si>
+    <t>孕育可跳过</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：R</t>
+  </si>
+  <si>
+    <t>-396</t>
+  </si>
+  <si>
+    <t>-596</t>
+  </si>
+  <si>
+    <t>100*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：R 概率+1%</t>
+  </si>
+  <si>
+    <t>-800</t>
+  </si>
+  <si>
+    <t>100401000,100401001,</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：SR</t>
+  </si>
+  <si>
+    <t>1000*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：SR 概率+1%</t>
+  </si>
+  <si>
+    <t>-1000</t>
+  </si>
+  <si>
+    <t>100402000,100402001,</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：SSR</t>
+  </si>
+  <si>
+    <t>10000*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：SSR 概率+1%</t>
+  </si>
+  <si>
+    <t>ui_research_5</t>
+  </si>
+  <si>
+    <t>100,200,300,400,500,600,700,800,900,1000,</t>
+  </si>
+  <si>
+    <t>阵容上限+1</t>
+  </si>
+  <si>
+    <t>ui_research_6</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>100,200,300,400,500,600,700,800,900,1000,</t>
-  </si>
-  <si>
-    <t>传送门可选择世界+1</t>
-  </si>
-  <si>
-    <t>ui_research_57</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>开启孕育功能</t>
-  </si>
-  <si>
-    <t>孕育可跳过</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：R</t>
-  </si>
-  <si>
-    <t>100*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：R 概率+1%</t>
-  </si>
-  <si>
-    <t>-800</t>
-  </si>
-  <si>
-    <t>100401000,100401001,</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：SR</t>
-  </si>
-  <si>
-    <t>1000*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：SR 概率+1%</t>
-  </si>
-  <si>
-    <t>-1000</t>
-  </si>
-  <si>
-    <t>100402000,100402001,</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：SSR</t>
-  </si>
-  <si>
-    <t>10000*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：SSR 概率+1%</t>
-  </si>
-  <si>
-    <t>ui_research_5</t>
-  </si>
-  <si>
-    <t>阵容上限+1</t>
-  </si>
-  <si>
-    <t>ui_research_6</t>
-  </si>
-  <si>
     <t>100,200,300,400,</t>
   </si>
   <si>
@@ -315,7 +335,10 @@
     <t>解锁种族：骷髅</t>
   </si>
   <si>
-    <t>-225</t>
+    <t>-223</t>
+  </si>
+  <si>
+    <t>204</t>
   </si>
   <si>
     <t>10</t>
@@ -660,8 +683,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="19">
     <font>
       <sz val="11"/>
@@ -1444,74 +1472,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1800,13 +1765,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K86"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1" style="50"/>
     <col min="2" max="2" width="23.75" customWidth="1" style="50"/>
@@ -2130,34 +2092,34 @@
     </row>
     <row r="10">
       <c r="A10" s="50">
-        <v>100300001</v>
+        <v>100200001</v>
       </c>
       <c r="B10" s="50">
         <v>1</v>
       </c>
       <c r="C10" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="50">
-        <v>10</v>
-      </c>
       <c r="E10" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="I10" s="50" t="s">
         <v>46</v>
-      </c>
-      <c r="G10" s="50">
-        <v>100300001</v>
-      </c>
-      <c r="I10" s="50" t="s">
-        <v>47</v>
       </c>
       <c r="J10" s="50">
         <v>100300001</v>
       </c>
       <c r="K10" s="50" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -2168,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" s="50">
         <v>1</v>
@@ -2183,13 +2145,13 @@
         <v>100400000</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J11" s="50">
         <v>100400000</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -2200,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" s="50">
         <v>1</v>
@@ -2224,7 +2186,7 @@
         <v>100400001</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -2235,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="50">
         <v>1</v>
@@ -2259,7 +2221,7 @@
         <v>100401000</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -2270,16 +2232,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" s="50">
         <v>50</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F14" s="50" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G14" s="50">
         <v>100401001</v>
@@ -2305,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15" s="50">
         <v>1</v>
@@ -2340,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" s="50">
         <v>40</v>
@@ -2375,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" s="50">
         <v>1</v>
@@ -2410,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D18" s="50">
         <v>30</v>
@@ -2460,13 +2422,13 @@
         <v>200000001</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="J19" s="50">
         <v>200000001</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2477,7 +2439,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" s="50">
         <v>4</v>
@@ -2486,19 +2448,19 @@
         <v>28</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G20" s="50">
         <v>200100001</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J20" s="50">
         <v>200100001</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -2509,16 +2471,16 @@
         <v>3</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D21" s="50">
         <v>1</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G21" s="50">
         <v>300100000</v>
@@ -2533,7 +2495,7 @@
         <v>300100000</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
@@ -2544,13 +2506,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" s="50">
         <v>1</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F22" s="50" t="s">
         <v>28</v>
@@ -2568,7 +2530,7 @@
         <v>300100001</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
@@ -2579,13 +2541,13 @@
         <v>3</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D23" s="50">
         <v>1</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F23" s="50" t="s">
         <v>28</v>
@@ -2603,7 +2565,7 @@
         <v>300100002</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
@@ -2614,13 +2576,13 @@
         <v>3</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D24" s="50">
         <v>1</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F24" s="50" t="s">
         <v>28</v>
@@ -2638,7 +2600,7 @@
         <v>300100003</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -2649,13 +2611,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D25" s="50">
         <v>1</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>28</v>
@@ -2673,7 +2635,7 @@
         <v>300100004</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
@@ -2684,22 +2646,22 @@
         <v>3</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D26" s="50">
         <v>1</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G26" s="50">
         <v>300100101</v>
       </c>
       <c r="H26" s="50" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I26" s="50">
         <v>100</v>
@@ -2708,7 +2670,7 @@
         <v>300100101</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
@@ -2719,16 +2681,16 @@
         <v>3</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D27" s="50">
         <v>1</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G27" s="50">
         <v>300100102</v>
@@ -2743,7 +2705,7 @@
         <v>300100102</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
@@ -2754,13 +2716,13 @@
         <v>3</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D28" s="50">
         <v>1</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F28" s="50" t="s">
         <v>27</v>
@@ -2769,7 +2731,7 @@
         <v>300100201</v>
       </c>
       <c r="H28" s="50" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I28" s="50">
         <v>100</v>
@@ -2778,7 +2740,7 @@
         <v>300100201</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
@@ -2789,13 +2751,13 @@
         <v>3</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F29" s="50" t="s">
         <v>27</v>
@@ -2804,7 +2766,7 @@
         <v>300100301</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I29" s="50">
         <v>100</v>
@@ -2813,7 +2775,7 @@
         <v>300100301</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
@@ -2824,28 +2786,28 @@
         <v>3</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D30" s="50">
         <v>1</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G30" s="50">
         <v>300200000</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J30" s="50">
         <v>300200000</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31">
@@ -2856,16 +2818,16 @@
         <v>3</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="G31" s="50">
         <v>300200001</v>
@@ -2874,13 +2836,13 @@
         <v>300200000</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J31" s="50">
         <v>300200001</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
@@ -2891,13 +2853,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D32" s="50">
         <v>1</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>28</v>
@@ -2909,13 +2871,13 @@
         <v>300200000</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J32" s="50">
         <v>300200002</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
@@ -2926,13 +2888,13 @@
         <v>3</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D33" s="50">
         <v>1</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F33" s="50" t="s">
         <v>28</v>
@@ -2950,7 +2912,7 @@
         <v>300200003</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34">
@@ -2961,13 +2923,13 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D34" s="50">
         <v>1</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F34" s="50" t="s">
         <v>28</v>
@@ -2985,7 +2947,7 @@
         <v>300200004</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
@@ -2996,22 +2958,22 @@
         <v>3</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D35" s="50">
         <v>1</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G35" s="50">
         <v>300200101</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I35" s="50">
         <v>100</v>
@@ -3020,7 +2982,7 @@
         <v>300200101</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36">
@@ -3031,16 +2993,16 @@
         <v>3</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D36" s="50">
         <v>1</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F36" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G36" s="50">
         <v>300200102</v>
@@ -3055,7 +3017,7 @@
         <v>300200102</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37">
@@ -3066,13 +3028,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D37" s="50">
         <v>1</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F37" s="50" t="s">
         <v>27</v>
@@ -3081,7 +3043,7 @@
         <v>300200201</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I37" s="50">
         <v>100</v>
@@ -3090,7 +3052,7 @@
         <v>300200201</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38">
@@ -3101,13 +3063,13 @@
         <v>3</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D38" s="50">
         <v>1</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F38" s="50" t="s">
         <v>27</v>
@@ -3116,7 +3078,7 @@
         <v>300200301</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I38" s="50">
         <v>100</v>
@@ -3125,7 +3087,7 @@
         <v>300200301</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39">
@@ -3136,7 +3098,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D39" s="50">
         <v>1</v>
@@ -3145,7 +3107,7 @@
         <v>56</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G39" s="50">
         <v>300300000</v>
@@ -3160,7 +3122,7 @@
         <v>300300000</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40">
@@ -3171,13 +3133,13 @@
         <v>3</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D40" s="50">
         <v>1</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F40" s="50" t="s">
         <v>28</v>
@@ -3195,7 +3157,7 @@
         <v>300300001</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41">
@@ -3206,13 +3168,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D41" s="50">
         <v>1</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>28</v>
@@ -3230,7 +3192,7 @@
         <v>300300002</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42">
@@ -3241,13 +3203,13 @@
         <v>3</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D42" s="50">
         <v>1</v>
       </c>
       <c r="E42" s="50" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F42" s="50" t="s">
         <v>28</v>
@@ -3265,7 +3227,7 @@
         <v>300300003</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43">
@@ -3276,13 +3238,13 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F43" s="50" t="s">
         <v>28</v>
@@ -3300,7 +3262,7 @@
         <v>300300004</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44">
@@ -3311,7 +3273,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
@@ -3320,13 +3282,13 @@
         <v>56</v>
       </c>
       <c r="F44" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G44" s="50">
         <v>300300101</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I44" s="50">
         <v>100</v>
@@ -3335,7 +3297,7 @@
         <v>300300101</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45">
@@ -3346,7 +3308,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
@@ -3355,7 +3317,7 @@
         <v>56</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G45" s="50">
         <v>300300102</v>
@@ -3370,7 +3332,7 @@
         <v>300300102</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46">
@@ -3381,7 +3343,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
@@ -3396,7 +3358,7 @@
         <v>300300201</v>
       </c>
       <c r="H46" s="50" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I46" s="50">
         <v>100</v>
@@ -3405,7 +3367,7 @@
         <v>300300201</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47">
@@ -3416,13 +3378,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>27</v>
@@ -3431,7 +3393,7 @@
         <v>300300301</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I47" s="50">
         <v>100</v>
@@ -3440,7 +3402,7 @@
         <v>300300301</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48">
@@ -3451,16 +3413,16 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G48" s="50">
         <v>300400000</v>
@@ -3475,7 +3437,7 @@
         <v>300400000</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49">
@@ -3486,13 +3448,13 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F49" s="50" t="s">
         <v>28</v>
@@ -3510,7 +3472,7 @@
         <v>300400001</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50">
@@ -3521,13 +3483,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>28</v>
@@ -3545,7 +3507,7 @@
         <v>300400002</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51">
@@ -3556,13 +3518,13 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F51" s="50" t="s">
         <v>28</v>
@@ -3580,7 +3542,7 @@
         <v>300400003</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52">
@@ -3591,13 +3553,13 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F52" s="50" t="s">
         <v>28</v>
@@ -3615,7 +3577,7 @@
         <v>300400004</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53">
@@ -3626,13 +3588,13 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F53" s="50" t="s">
         <v>28</v>
@@ -3650,7 +3612,7 @@
         <v>300400005</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54">
@@ -3661,22 +3623,22 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F54" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G54" s="50">
         <v>300400101</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I54" s="50">
         <v>100</v>
@@ -3685,7 +3647,7 @@
         <v>300400101</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55">
@@ -3696,16 +3658,16 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G55" s="50">
         <v>300400102</v>
@@ -3720,7 +3682,7 @@
         <v>300400102</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56">
@@ -3731,13 +3693,13 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>27</v>
@@ -3746,7 +3708,7 @@
         <v>300400201</v>
       </c>
       <c r="H56" s="50" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I56" s="50">
         <v>100</v>
@@ -3755,7 +3717,7 @@
         <v>300400201</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57">
@@ -3766,13 +3728,13 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F57" s="50" t="s">
         <v>27</v>
@@ -3781,7 +3743,7 @@
         <v>300400301</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I57" s="50">
         <v>100</v>
@@ -3790,7 +3752,7 @@
         <v>300400301</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3801,16 +3763,16 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F58" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G58" s="50">
         <v>300500000</v>
@@ -3825,7 +3787,7 @@
         <v>300500000</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3836,13 +3798,13 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F59" s="50" t="s">
         <v>28</v>
@@ -3860,7 +3822,7 @@
         <v>300500001</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3871,13 +3833,13 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>28</v>
@@ -3895,7 +3857,7 @@
         <v>300500002</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3906,13 +3868,13 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F61" s="50" t="s">
         <v>28</v>
@@ -3930,7 +3892,7 @@
         <v>300500003</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3941,13 +3903,13 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>28</v>
@@ -3965,7 +3927,7 @@
         <v>300500004</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3976,22 +3938,22 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G63" s="50">
         <v>300500101</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I63" s="50">
         <v>100</v>
@@ -4000,7 +3962,7 @@
         <v>300500101</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4011,16 +3973,16 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G64" s="50">
         <v>300500102</v>
@@ -4035,7 +3997,7 @@
         <v>300500102</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65">
@@ -4046,13 +4008,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>27</v>
@@ -4061,7 +4023,7 @@
         <v>300500201</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I65" s="50">
         <v>100</v>
@@ -4070,7 +4032,7 @@
         <v>300500201</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="66">
@@ -4081,13 +4043,13 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F66" s="50" t="s">
         <v>27</v>
@@ -4096,7 +4058,7 @@
         <v>300500301</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I66" s="50">
         <v>100</v>
@@ -4105,7 +4067,7 @@
         <v>300500301</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4116,16 +4078,16 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G67" s="50">
         <v>300600000</v>
@@ -4140,7 +4102,7 @@
         <v>300600000</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4151,13 +4113,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>28</v>
@@ -4175,7 +4137,7 @@
         <v>300600001</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4186,13 +4148,13 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>28</v>
@@ -4210,7 +4172,7 @@
         <v>300600002</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4221,13 +4183,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>28</v>
@@ -4245,7 +4207,7 @@
         <v>300600003</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4256,13 +4218,13 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>28</v>
@@ -4280,7 +4242,7 @@
         <v>300600004</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4291,13 +4253,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>28</v>
@@ -4315,7 +4277,7 @@
         <v>300600005</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4326,22 +4288,22 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G73" s="50">
         <v>300600101</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I73" s="50">
         <v>100</v>
@@ -4350,7 +4312,7 @@
         <v>300600101</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4361,16 +4323,16 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F74" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G74" s="50">
         <v>300600102</v>
@@ -4385,7 +4347,7 @@
         <v>300600102</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75">
@@ -4396,13 +4358,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>27</v>
@@ -4411,7 +4373,7 @@
         <v>300600201</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I75" s="50">
         <v>100</v>
@@ -4420,7 +4382,7 @@
         <v>300600201</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76">
@@ -4431,13 +4393,13 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>27</v>
@@ -4446,7 +4408,7 @@
         <v>300600301</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
@@ -4455,7 +4417,7 @@
         <v>300600301</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="77">
@@ -4466,16 +4428,16 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G77" s="50">
         <v>300700000</v>
@@ -4490,7 +4452,7 @@
         <v>300700000</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4501,13 +4463,13 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>28</v>
@@ -4525,7 +4487,7 @@
         <v>300700001</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4536,13 +4498,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>28</v>
@@ -4560,7 +4522,7 @@
         <v>300700002</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4571,13 +4533,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>28</v>
@@ -4595,7 +4557,7 @@
         <v>300700003</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4606,13 +4568,13 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>28</v>
@@ -4630,7 +4592,7 @@
         <v>300700004</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4641,22 +4603,22 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F82" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G82" s="50">
         <v>300700101</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I82" s="50">
         <v>100</v>
@@ -4665,7 +4627,7 @@
         <v>300700101</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4676,16 +4638,16 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F83" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G83" s="50">
         <v>300700102</v>
@@ -4700,7 +4662,7 @@
         <v>300700102</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84">
@@ -4711,13 +4673,13 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>27</v>
@@ -4726,7 +4688,7 @@
         <v>300700201</v>
       </c>
       <c r="H84" s="50" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I84" s="50">
         <v>100</v>
@@ -4735,7 +4697,7 @@
         <v>300700201</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85">
@@ -4746,13 +4708,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>27</v>
@@ -4761,7 +4723,7 @@
         <v>300700301</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
@@ -4770,7 +4732,7 @@
         <v>300700301</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="86">
@@ -4787,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>42</v>
@@ -4802,7 +4764,7 @@
         <v>100500001</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="50" customFormat="1"/>
@@ -4816,7 +4778,7 @@
     <row r="123" ht="12" customHeight="1" s="50" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
   <si>
     <t>id</t>
   </si>
@@ -164,9 +164,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>100200001</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -230,7 +227,7 @@
     <t>ui_research_5</t>
   </si>
   <si>
-    <t>100,200,300,400,500,600,700,800,900,1000,</t>
+    <t>50,100,200,500,1000,2000,5000,10000,20000,50000,</t>
   </si>
   <si>
     <t>阵容上限+1</t>
@@ -2092,7 +2089,7 @@
     </row>
     <row r="10">
       <c r="A10" s="50">
-        <v>100200001</v>
+        <v>100300001</v>
       </c>
       <c r="B10" s="50">
         <v>1</v>
@@ -2109,11 +2106,11 @@
       <c r="F10" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="50">
+        <v>100300001</v>
+      </c>
+      <c r="I10" s="50" t="s">
         <v>45</v>
-      </c>
-      <c r="I10" s="50" t="s">
-        <v>46</v>
       </c>
       <c r="J10" s="50">
         <v>100300001</v>
@@ -2130,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="50">
         <v>1</v>
@@ -2145,13 +2142,13 @@
         <v>100400000</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J11" s="50">
         <v>100400000</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -2162,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="50">
         <v>1</v>
@@ -2186,7 +2183,7 @@
         <v>100400001</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -2197,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="50">
         <v>1</v>
@@ -2221,7 +2218,7 @@
         <v>100401000</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -2232,16 +2229,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="50">
         <v>50</v>
       </c>
       <c r="E14" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="50" t="s">
         <v>52</v>
-      </c>
-      <c r="F14" s="50" t="s">
-        <v>53</v>
       </c>
       <c r="G14" s="50">
         <v>100401001</v>
@@ -2250,13 +2247,13 @@
         <v>100401000</v>
       </c>
       <c r="I14" s="50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J14" s="50">
         <v>100401001</v>
       </c>
       <c r="K14" s="50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2267,7 +2264,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" s="50">
         <v>1</v>
@@ -2276,13 +2273,13 @@
         <v>27</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" s="50">
         <v>100402000</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I15" s="50">
         <v>1000</v>
@@ -2291,7 +2288,7 @@
         <v>100402000</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
@@ -2302,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="50">
         <v>40</v>
@@ -2311,7 +2308,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" s="50">
         <v>100402001</v>
@@ -2320,13 +2317,13 @@
         <v>100402000</v>
       </c>
       <c r="I16" s="50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J16" s="50">
         <v>100402001</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -2337,7 +2334,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="50">
         <v>1</v>
@@ -2346,13 +2343,13 @@
         <v>27</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" s="50">
         <v>100403000</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I17" s="50">
         <v>10000</v>
@@ -2361,7 +2358,7 @@
         <v>100403000</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -2372,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" s="50">
         <v>30</v>
@@ -2381,7 +2378,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G18" s="50">
         <v>100403001</v>
@@ -2390,13 +2387,13 @@
         <v>100403000</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J18" s="50">
         <v>100403001</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
@@ -2407,7 +2404,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="50">
         <v>30</v>
@@ -2422,13 +2419,13 @@
         <v>200000001</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J19" s="50">
         <v>200000001</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -2439,7 +2436,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20" s="50">
         <v>4</v>
@@ -2448,19 +2445,19 @@
         <v>28</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G20" s="50">
         <v>200100001</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J20" s="50">
         <v>200100001</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -2471,16 +2468,16 @@
         <v>3</v>
       </c>
       <c r="C21" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="50">
+        <v>1</v>
+      </c>
+      <c r="E21" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="50">
-        <v>1</v>
-      </c>
-      <c r="E21" s="50" t="s">
-        <v>74</v>
-      </c>
       <c r="F21" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G21" s="50">
         <v>300100000</v>
@@ -2495,7 +2492,7 @@
         <v>300100000</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
@@ -2506,13 +2503,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="50">
+        <v>1</v>
+      </c>
+      <c r="E22" s="50" t="s">
         <v>76</v>
-      </c>
-      <c r="D22" s="50">
-        <v>1</v>
-      </c>
-      <c r="E22" s="50" t="s">
-        <v>77</v>
       </c>
       <c r="F22" s="50" t="s">
         <v>28</v>
@@ -2530,7 +2527,7 @@
         <v>300100001</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
@@ -2541,13 +2538,13 @@
         <v>3</v>
       </c>
       <c r="C23" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="50">
+        <v>1</v>
+      </c>
+      <c r="E23" s="50" t="s">
         <v>79</v>
-      </c>
-      <c r="D23" s="50">
-        <v>1</v>
-      </c>
-      <c r="E23" s="50" t="s">
-        <v>80</v>
       </c>
       <c r="F23" s="50" t="s">
         <v>28</v>
@@ -2565,7 +2562,7 @@
         <v>300100002</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
@@ -2576,13 +2573,13 @@
         <v>3</v>
       </c>
       <c r="C24" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="50">
+        <v>1</v>
+      </c>
+      <c r="E24" s="50" t="s">
         <v>82</v>
-      </c>
-      <c r="D24" s="50">
-        <v>1</v>
-      </c>
-      <c r="E24" s="50" t="s">
-        <v>83</v>
       </c>
       <c r="F24" s="50" t="s">
         <v>28</v>
@@ -2600,7 +2597,7 @@
         <v>300100003</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
@@ -2611,13 +2608,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="50">
+        <v>1</v>
+      </c>
+      <c r="E25" s="50" t="s">
         <v>85</v>
-      </c>
-      <c r="D25" s="50">
-        <v>1</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>86</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>28</v>
@@ -2635,7 +2632,7 @@
         <v>300100004</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
@@ -2646,22 +2643,22 @@
         <v>3</v>
       </c>
       <c r="C26" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="50">
+        <v>1</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="50" t="s">
         <v>88</v>
-      </c>
-      <c r="D26" s="50">
-        <v>1</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="50" t="s">
-        <v>89</v>
       </c>
       <c r="G26" s="50">
         <v>300100101</v>
       </c>
       <c r="H26" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I26" s="50">
         <v>100</v>
@@ -2670,7 +2667,7 @@
         <v>300100101</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
@@ -2681,16 +2678,16 @@
         <v>3</v>
       </c>
       <c r="C27" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="50">
+        <v>1</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="50" t="s">
         <v>92</v>
-      </c>
-      <c r="D27" s="50">
-        <v>1</v>
-      </c>
-      <c r="E27" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="50" t="s">
-        <v>93</v>
       </c>
       <c r="G27" s="50">
         <v>300100102</v>
@@ -2705,7 +2702,7 @@
         <v>300100102</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28">
@@ -2716,13 +2713,13 @@
         <v>3</v>
       </c>
       <c r="C28" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="50">
+        <v>1</v>
+      </c>
+      <c r="E28" s="50" t="s">
         <v>73</v>
-      </c>
-      <c r="D28" s="50">
-        <v>1</v>
-      </c>
-      <c r="E28" s="50" t="s">
-        <v>74</v>
       </c>
       <c r="F28" s="50" t="s">
         <v>27</v>
@@ -2731,7 +2728,7 @@
         <v>300100201</v>
       </c>
       <c r="H28" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I28" s="50">
         <v>100</v>
@@ -2740,7 +2737,7 @@
         <v>300100201</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29">
@@ -2751,13 +2748,13 @@
         <v>3</v>
       </c>
       <c r="C29" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="50">
+        <v>1</v>
+      </c>
+      <c r="E29" s="50" t="s">
         <v>97</v>
-      </c>
-      <c r="D29" s="50">
-        <v>1</v>
-      </c>
-      <c r="E29" s="50" t="s">
-        <v>98</v>
       </c>
       <c r="F29" s="50" t="s">
         <v>27</v>
@@ -2766,7 +2763,7 @@
         <v>300100301</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I29" s="50">
         <v>100</v>
@@ -2775,7 +2772,7 @@
         <v>300100301</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
@@ -2786,28 +2783,28 @@
         <v>3</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D30" s="50">
         <v>1</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G30" s="50">
         <v>300200000</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J30" s="50">
         <v>300200000</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -2818,16 +2815,16 @@
         <v>3</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="50" t="s">
         <v>102</v>
-      </c>
-      <c r="F31" s="50" t="s">
-        <v>103</v>
       </c>
       <c r="G31" s="50">
         <v>300200001</v>
@@ -2836,13 +2833,13 @@
         <v>300200000</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J31" s="50">
         <v>300200001</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32">
@@ -2853,13 +2850,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" s="50">
         <v>1</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>28</v>
@@ -2871,13 +2868,13 @@
         <v>300200000</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J32" s="50">
         <v>300200002</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33">
@@ -2888,13 +2885,13 @@
         <v>3</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D33" s="50">
         <v>1</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F33" s="50" t="s">
         <v>28</v>
@@ -2912,7 +2909,7 @@
         <v>300200003</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34">
@@ -2923,13 +2920,13 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D34" s="50">
         <v>1</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F34" s="50" t="s">
         <v>28</v>
@@ -2947,7 +2944,7 @@
         <v>300200004</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35">
@@ -2958,22 +2955,22 @@
         <v>3</v>
       </c>
       <c r="C35" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="50">
+        <v>1</v>
+      </c>
+      <c r="E35" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" s="50" t="s">
         <v>88</v>
-      </c>
-      <c r="D35" s="50">
-        <v>1</v>
-      </c>
-      <c r="E35" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="50" t="s">
-        <v>89</v>
       </c>
       <c r="G35" s="50">
         <v>300200101</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I35" s="50">
         <v>100</v>
@@ -2982,7 +2979,7 @@
         <v>300200101</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36">
@@ -2993,16 +2990,16 @@
         <v>3</v>
       </c>
       <c r="C36" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="50">
+        <v>1</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="50" t="s">
         <v>92</v>
-      </c>
-      <c r="D36" s="50">
-        <v>1</v>
-      </c>
-      <c r="E36" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="50" t="s">
-        <v>93</v>
       </c>
       <c r="G36" s="50">
         <v>300200102</v>
@@ -3017,7 +3014,7 @@
         <v>300200102</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37">
@@ -3028,13 +3025,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D37" s="50">
         <v>1</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F37" s="50" t="s">
         <v>27</v>
@@ -3043,7 +3040,7 @@
         <v>300200201</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I37" s="50">
         <v>100</v>
@@ -3052,7 +3049,7 @@
         <v>300200201</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38">
@@ -3063,13 +3060,13 @@
         <v>3</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D38" s="50">
         <v>1</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F38" s="50" t="s">
         <v>27</v>
@@ -3078,7 +3075,7 @@
         <v>300200301</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I38" s="50">
         <v>100</v>
@@ -3087,7 +3084,7 @@
         <v>300200301</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39">
@@ -3098,16 +3095,16 @@
         <v>3</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D39" s="50">
         <v>1</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G39" s="50">
         <v>300300000</v>
@@ -3122,7 +3119,7 @@
         <v>300300000</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40">
@@ -3133,13 +3130,13 @@
         <v>3</v>
       </c>
       <c r="C40" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="50">
+        <v>1</v>
+      </c>
+      <c r="E40" s="50" t="s">
         <v>122</v>
-      </c>
-      <c r="D40" s="50">
-        <v>1</v>
-      </c>
-      <c r="E40" s="50" t="s">
-        <v>123</v>
       </c>
       <c r="F40" s="50" t="s">
         <v>28</v>
@@ -3157,7 +3154,7 @@
         <v>300300001</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41">
@@ -3168,13 +3165,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" s="50">
+        <v>1</v>
+      </c>
+      <c r="E41" s="50" t="s">
         <v>125</v>
-      </c>
-      <c r="D41" s="50">
-        <v>1</v>
-      </c>
-      <c r="E41" s="50" t="s">
-        <v>126</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>28</v>
@@ -3192,7 +3189,7 @@
         <v>300300002</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42">
@@ -3203,13 +3200,13 @@
         <v>3</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D42" s="50">
         <v>1</v>
       </c>
       <c r="E42" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F42" s="50" t="s">
         <v>28</v>
@@ -3227,7 +3224,7 @@
         <v>300300003</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43">
@@ -3238,13 +3235,13 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="50">
+        <v>1</v>
+      </c>
+      <c r="E43" s="50" t="s">
         <v>130</v>
-      </c>
-      <c r="D43" s="50">
-        <v>1</v>
-      </c>
-      <c r="E43" s="50" t="s">
-        <v>131</v>
       </c>
       <c r="F43" s="50" t="s">
         <v>28</v>
@@ -3262,7 +3259,7 @@
         <v>300300004</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44">
@@ -3273,22 +3270,22 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="50">
+        <v>1</v>
+      </c>
+      <c r="E44" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" s="50" t="s">
         <v>88</v>
-      </c>
-      <c r="D44" s="50">
-        <v>1</v>
-      </c>
-      <c r="E44" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="F44" s="50" t="s">
-        <v>89</v>
       </c>
       <c r="G44" s="50">
         <v>300300101</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I44" s="50">
         <v>100</v>
@@ -3297,7 +3294,7 @@
         <v>300300101</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45">
@@ -3308,16 +3305,16 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="50">
+        <v>1</v>
+      </c>
+      <c r="E45" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" s="50" t="s">
         <v>92</v>
-      </c>
-      <c r="D45" s="50">
-        <v>1</v>
-      </c>
-      <c r="E45" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="F45" s="50" t="s">
-        <v>93</v>
       </c>
       <c r="G45" s="50">
         <v>300300102</v>
@@ -3332,7 +3329,7 @@
         <v>300300102</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46">
@@ -3343,13 +3340,13 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F46" s="50" t="s">
         <v>27</v>
@@ -3358,7 +3355,7 @@
         <v>300300201</v>
       </c>
       <c r="H46" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I46" s="50">
         <v>100</v>
@@ -3367,7 +3364,7 @@
         <v>300300201</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47">
@@ -3378,13 +3375,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>27</v>
@@ -3393,7 +3390,7 @@
         <v>300300301</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I47" s="50">
         <v>100</v>
@@ -3402,7 +3399,7 @@
         <v>300300301</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48">
@@ -3413,16 +3410,16 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" s="50">
+        <v>1</v>
+      </c>
+      <c r="E48" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="50">
-        <v>1</v>
-      </c>
-      <c r="E48" s="50" t="s">
-        <v>141</v>
-      </c>
       <c r="F48" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G48" s="50">
         <v>300400000</v>
@@ -3437,7 +3434,7 @@
         <v>300400000</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49">
@@ -3448,13 +3445,13 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F49" s="50" t="s">
         <v>28</v>
@@ -3472,7 +3469,7 @@
         <v>300400001</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50">
@@ -3483,13 +3480,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" s="50">
+        <v>1</v>
+      </c>
+      <c r="E50" s="50" t="s">
         <v>145</v>
-      </c>
-      <c r="D50" s="50">
-        <v>1</v>
-      </c>
-      <c r="E50" s="50" t="s">
-        <v>146</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>28</v>
@@ -3507,7 +3504,7 @@
         <v>300400002</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51">
@@ -3518,13 +3515,13 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F51" s="50" t="s">
         <v>28</v>
@@ -3542,7 +3539,7 @@
         <v>300400003</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52">
@@ -3553,13 +3550,13 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="D52" s="50">
+        <v>1</v>
+      </c>
+      <c r="E52" s="50" t="s">
         <v>150</v>
-      </c>
-      <c r="D52" s="50">
-        <v>1</v>
-      </c>
-      <c r="E52" s="50" t="s">
-        <v>151</v>
       </c>
       <c r="F52" s="50" t="s">
         <v>28</v>
@@ -3577,7 +3574,7 @@
         <v>300400004</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53">
@@ -3588,13 +3585,13 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F53" s="50" t="s">
         <v>28</v>
@@ -3612,7 +3609,7 @@
         <v>300400005</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54">
@@ -3623,22 +3620,22 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" s="50">
+        <v>1</v>
+      </c>
+      <c r="E54" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="F54" s="50" t="s">
         <v>88</v>
-      </c>
-      <c r="D54" s="50">
-        <v>1</v>
-      </c>
-      <c r="E54" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="F54" s="50" t="s">
-        <v>89</v>
       </c>
       <c r="G54" s="50">
         <v>300400101</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I54" s="50">
         <v>100</v>
@@ -3647,7 +3644,7 @@
         <v>300400101</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55">
@@ -3658,16 +3655,16 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="50">
+        <v>1</v>
+      </c>
+      <c r="E55" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="F55" s="50" t="s">
         <v>92</v>
-      </c>
-      <c r="D55" s="50">
-        <v>1</v>
-      </c>
-      <c r="E55" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="F55" s="50" t="s">
-        <v>93</v>
       </c>
       <c r="G55" s="50">
         <v>300400102</v>
@@ -3682,7 +3679,7 @@
         <v>300400102</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56">
@@ -3693,13 +3690,13 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D56" s="50">
+        <v>1</v>
+      </c>
+      <c r="E56" s="50" t="s">
         <v>140</v>
-      </c>
-      <c r="D56" s="50">
-        <v>1</v>
-      </c>
-      <c r="E56" s="50" t="s">
-        <v>141</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>27</v>
@@ -3708,7 +3705,7 @@
         <v>300400201</v>
       </c>
       <c r="H56" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I56" s="50">
         <v>100</v>
@@ -3717,7 +3714,7 @@
         <v>300400201</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57">
@@ -3728,13 +3725,13 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F57" s="50" t="s">
         <v>27</v>
@@ -3743,7 +3740,7 @@
         <v>300400301</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I57" s="50">
         <v>100</v>
@@ -3752,7 +3749,7 @@
         <v>300400301</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3763,16 +3760,16 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" s="50">
+        <v>1</v>
+      </c>
+      <c r="E58" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="D58" s="50">
-        <v>1</v>
-      </c>
-      <c r="E58" s="50" t="s">
-        <v>162</v>
-      </c>
       <c r="F58" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G58" s="50">
         <v>300500000</v>
@@ -3787,7 +3784,7 @@
         <v>300500000</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3798,13 +3795,13 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F59" s="50" t="s">
         <v>28</v>
@@ -3822,7 +3819,7 @@
         <v>300500001</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3833,13 +3830,13 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>28</v>
@@ -3857,7 +3854,7 @@
         <v>300500002</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3868,13 +3865,13 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F61" s="50" t="s">
         <v>28</v>
@@ -3892,7 +3889,7 @@
         <v>300500003</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3903,13 +3900,13 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>28</v>
@@ -3927,7 +3924,7 @@
         <v>300500004</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3938,22 +3935,22 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D63" s="50">
+        <v>1</v>
+      </c>
+      <c r="E63" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="F63" s="50" t="s">
         <v>88</v>
-      </c>
-      <c r="D63" s="50">
-        <v>1</v>
-      </c>
-      <c r="E63" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="F63" s="50" t="s">
-        <v>89</v>
       </c>
       <c r="G63" s="50">
         <v>300500101</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I63" s="50">
         <v>100</v>
@@ -3962,7 +3959,7 @@
         <v>300500101</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="50" customFormat="1">
@@ -3973,16 +3970,16 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="50">
+        <v>1</v>
+      </c>
+      <c r="E64" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="F64" s="50" t="s">
         <v>92</v>
-      </c>
-      <c r="D64" s="50">
-        <v>1</v>
-      </c>
-      <c r="E64" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="F64" s="50" t="s">
-        <v>93</v>
       </c>
       <c r="G64" s="50">
         <v>300500102</v>
@@ -3997,7 +3994,7 @@
         <v>300500102</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65">
@@ -4008,13 +4005,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="D65" s="50">
+        <v>1</v>
+      </c>
+      <c r="E65" s="50" t="s">
         <v>161</v>
-      </c>
-      <c r="D65" s="50">
-        <v>1</v>
-      </c>
-      <c r="E65" s="50" t="s">
-        <v>162</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>27</v>
@@ -4023,7 +4020,7 @@
         <v>300500201</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I65" s="50">
         <v>100</v>
@@ -4032,7 +4029,7 @@
         <v>300500201</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66">
@@ -4043,13 +4040,13 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F66" s="50" t="s">
         <v>27</v>
@@ -4058,7 +4055,7 @@
         <v>300500301</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I66" s="50">
         <v>100</v>
@@ -4067,7 +4064,7 @@
         <v>300500301</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4078,16 +4075,16 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="D67" s="50">
+        <v>1</v>
+      </c>
+      <c r="E67" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="D67" s="50">
-        <v>1</v>
-      </c>
-      <c r="E67" s="50" t="s">
-        <v>180</v>
-      </c>
       <c r="F67" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G67" s="50">
         <v>300600000</v>
@@ -4102,7 +4099,7 @@
         <v>300600000</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4113,13 +4110,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" s="50">
+        <v>1</v>
+      </c>
+      <c r="E68" s="50" t="s">
         <v>182</v>
-      </c>
-      <c r="D68" s="50">
-        <v>1</v>
-      </c>
-      <c r="E68" s="50" t="s">
-        <v>183</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>28</v>
@@ -4137,7 +4134,7 @@
         <v>300600001</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4148,13 +4145,13 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>28</v>
@@ -4172,7 +4169,7 @@
         <v>300600002</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4183,13 +4180,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>28</v>
@@ -4207,7 +4204,7 @@
         <v>300600003</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4218,13 +4215,13 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>28</v>
@@ -4242,7 +4239,7 @@
         <v>300600004</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4253,13 +4250,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>28</v>
@@ -4277,7 +4274,7 @@
         <v>300600005</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4288,22 +4285,22 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D73" s="50">
+        <v>1</v>
+      </c>
+      <c r="E73" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="F73" s="50" t="s">
         <v>88</v>
-      </c>
-      <c r="D73" s="50">
-        <v>1</v>
-      </c>
-      <c r="E73" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="F73" s="50" t="s">
-        <v>89</v>
       </c>
       <c r="G73" s="50">
         <v>300600101</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I73" s="50">
         <v>100</v>
@@ -4312,7 +4309,7 @@
         <v>300600101</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="50" customFormat="1">
@@ -4323,16 +4320,16 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D74" s="50">
+        <v>1</v>
+      </c>
+      <c r="E74" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="F74" s="50" t="s">
         <v>92</v>
-      </c>
-      <c r="D74" s="50">
-        <v>1</v>
-      </c>
-      <c r="E74" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="F74" s="50" t="s">
-        <v>93</v>
       </c>
       <c r="G74" s="50">
         <v>300600102</v>
@@ -4347,7 +4344,7 @@
         <v>300600102</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75">
@@ -4358,13 +4355,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="D75" s="50">
+        <v>1</v>
+      </c>
+      <c r="E75" s="50" t="s">
         <v>179</v>
-      </c>
-      <c r="D75" s="50">
-        <v>1</v>
-      </c>
-      <c r="E75" s="50" t="s">
-        <v>180</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>27</v>
@@ -4373,7 +4370,7 @@
         <v>300600201</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I75" s="50">
         <v>100</v>
@@ -4382,7 +4379,7 @@
         <v>300600201</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76">
@@ -4393,13 +4390,13 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>27</v>
@@ -4408,7 +4405,7 @@
         <v>300600301</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
@@ -4417,7 +4414,7 @@
         <v>300600301</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77">
@@ -4428,16 +4425,16 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="D77" s="50">
+        <v>1</v>
+      </c>
+      <c r="E77" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="D77" s="50">
-        <v>1</v>
-      </c>
-      <c r="E77" s="50" t="s">
-        <v>199</v>
-      </c>
       <c r="F77" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G77" s="50">
         <v>300700000</v>
@@ -4452,7 +4449,7 @@
         <v>300700000</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4463,13 +4460,13 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>28</v>
@@ -4487,7 +4484,7 @@
         <v>300700001</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4498,13 +4495,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>28</v>
@@ -4522,7 +4519,7 @@
         <v>300700002</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4533,13 +4530,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>28</v>
@@ -4557,7 +4554,7 @@
         <v>300700003</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4568,13 +4565,13 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>28</v>
@@ -4592,7 +4589,7 @@
         <v>300700004</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4603,22 +4600,22 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" s="50">
+        <v>1</v>
+      </c>
+      <c r="E82" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" s="50" t="s">
         <v>88</v>
-      </c>
-      <c r="D82" s="50">
-        <v>1</v>
-      </c>
-      <c r="E82" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="F82" s="50" t="s">
-        <v>89</v>
       </c>
       <c r="G82" s="50">
         <v>300700101</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I82" s="50">
         <v>100</v>
@@ -4627,7 +4624,7 @@
         <v>300700101</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="50" customFormat="1">
@@ -4638,16 +4635,16 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D83" s="50">
+        <v>1</v>
+      </c>
+      <c r="E83" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="F83" s="50" t="s">
         <v>92</v>
-      </c>
-      <c r="D83" s="50">
-        <v>1</v>
-      </c>
-      <c r="E83" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="F83" s="50" t="s">
-        <v>93</v>
       </c>
       <c r="G83" s="50">
         <v>300700102</v>
@@ -4662,7 +4659,7 @@
         <v>300700102</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84">
@@ -4673,13 +4670,13 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="D84" s="50">
+        <v>1</v>
+      </c>
+      <c r="E84" s="50" t="s">
         <v>198</v>
-      </c>
-      <c r="D84" s="50">
-        <v>1</v>
-      </c>
-      <c r="E84" s="50" t="s">
-        <v>199</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>27</v>
@@ -4688,7 +4685,7 @@
         <v>300700201</v>
       </c>
       <c r="H84" s="50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I84" s="50">
         <v>100</v>
@@ -4697,7 +4694,7 @@
         <v>300700201</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85">
@@ -4708,13 +4705,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>27</v>
@@ -4723,7 +4720,7 @@
         <v>300700301</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
@@ -4732,7 +4729,7 @@
         <v>300700301</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86">
@@ -4749,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>42</v>
@@ -4764,7 +4761,7 @@
         <v>100500001</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="50" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -123,6 +123,9 @@
     <t>ui_research_3</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
     <t>开启献祭设施</t>
   </si>
   <si>
@@ -213,7 +216,7 @@
     <t>ui_research_5</t>
   </si>
   <si>
-    <t>50,100,200,500,1000,2000,5000,10000,20000,50000,</t>
+    <t>100,250,500,1000,2000,5000,10000,20000,50000,100000,</t>
   </si>
   <si>
     <t>阵容上限+1</t>
@@ -331,9 +334,6 @@
   </si>
   <si>
     <t>-75</t>
-  </si>
-  <si>
-    <t>50</t>
   </si>
   <si>
     <t>解锁职业：骷髅投手</t>
@@ -2036,14 +2036,14 @@
       <c r="G6" s="50">
         <v>100100001</v>
       </c>
-      <c r="I6" s="50">
-        <v>100</v>
+      <c r="I6" s="50" t="s">
+        <v>36</v>
       </c>
       <c r="J6" s="50">
         <v>100100001</v>
       </c>
       <c r="K6" s="50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -2054,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="50">
         <v>1</v>
@@ -2075,7 +2075,7 @@
         <v>100200001</v>
       </c>
       <c r="K7" s="50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -2086,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="50">
         <v>1</v>
@@ -2095,7 +2095,7 @@
         <v>28</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="50">
         <v>100200002</v>
@@ -2110,7 +2110,7 @@
         <v>100200002</v>
       </c>
       <c r="K8" s="50" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="50">
         <v>1</v>
@@ -2130,7 +2130,7 @@
         <v>28</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" s="50">
         <v>100200003</v>
@@ -2145,7 +2145,7 @@
         <v>100200003</v>
       </c>
       <c r="K9" s="50" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -2156,10 +2156,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="50" t="s">
         <v>28</v>
@@ -2171,13 +2171,13 @@
         <v>100300001</v>
       </c>
       <c r="I10" s="50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J10" s="50">
         <v>100300001</v>
       </c>
       <c r="K10" s="50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -2188,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" s="50">
         <v>1</v>
@@ -2203,13 +2203,13 @@
         <v>100400000</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J11" s="50">
         <v>100400000</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -2220,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="50">
         <v>1</v>
@@ -2229,7 +2229,7 @@
         <v>27</v>
       </c>
       <c r="F12" s="50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" s="50">
         <v>100400001</v>
@@ -2244,7 +2244,7 @@
         <v>100400001</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -2255,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="50">
         <v>1</v>
@@ -2264,7 +2264,7 @@
         <v>27</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" s="50">
         <v>100401000</v>
@@ -2279,7 +2279,7 @@
         <v>100401000</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -2290,16 +2290,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="50">
         <v>50</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14" s="50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G14" s="50">
         <v>100401001</v>
@@ -2308,13 +2308,13 @@
         <v>100401000</v>
       </c>
       <c r="I14" s="50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J14" s="50">
         <v>100401001</v>
       </c>
       <c r="K14" s="50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2325,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="50">
         <v>1</v>
@@ -2334,13 +2334,13 @@
         <v>27</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15" s="50">
         <v>100402000</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I15" s="50">
         <v>1000</v>
@@ -2349,7 +2349,7 @@
         <v>100402000</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -2360,16 +2360,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="50">
         <v>40</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" s="50">
         <v>100402001</v>
@@ -2378,13 +2378,13 @@
         <v>100402000</v>
       </c>
       <c r="I16" s="50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J16" s="50">
         <v>100402001</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
@@ -2395,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="50">
         <v>1</v>
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G17" s="50">
         <v>100403000</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I17" s="50">
         <v>10000</v>
@@ -2419,7 +2419,7 @@
         <v>100403000</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -2430,16 +2430,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="50">
         <v>30</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G18" s="50">
         <v>100403001</v>
@@ -2448,13 +2448,13 @@
         <v>100403000</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J18" s="50">
         <v>100403001</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -2465,7 +2465,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" s="50">
         <v>30</v>
@@ -2480,13 +2480,13 @@
         <v>200000001</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J19" s="50">
         <v>200000001</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2497,7 +2497,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" s="50">
         <v>4</v>
@@ -2506,19 +2506,19 @@
         <v>28</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="50">
         <v>200100001</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J20" s="50">
         <v>200100001</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -2529,16 +2529,16 @@
         <v>3</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D21" s="50">
         <v>1</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="50">
         <v>300100000</v>
@@ -2553,7 +2553,7 @@
         <v>300100000</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
@@ -2564,13 +2564,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D22" s="50">
         <v>1</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F22" s="50" t="s">
         <v>28</v>
@@ -2588,7 +2588,7 @@
         <v>300100001</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
@@ -2599,13 +2599,13 @@
         <v>3</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D23" s="50">
         <v>1</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" s="50" t="s">
         <v>28</v>
@@ -2623,7 +2623,7 @@
         <v>300100002</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
@@ -2634,13 +2634,13 @@
         <v>3</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="50">
         <v>1</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F24" s="50" t="s">
         <v>28</v>
@@ -2658,7 +2658,7 @@
         <v>300100003</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -2669,13 +2669,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D25" s="50">
         <v>1</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>28</v>
@@ -2693,7 +2693,7 @@
         <v>300100004</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
@@ -2704,22 +2704,22 @@
         <v>3</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D26" s="50">
         <v>1</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G26" s="50">
         <v>300100101</v>
       </c>
       <c r="H26" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I26" s="50">
         <v>100</v>
@@ -2728,7 +2728,7 @@
         <v>300100101</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
@@ -2739,16 +2739,16 @@
         <v>3</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D27" s="50">
         <v>1</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G27" s="50">
         <v>300100102</v>
@@ -2763,7 +2763,7 @@
         <v>300100102</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
@@ -2774,13 +2774,13 @@
         <v>3</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D28" s="50">
         <v>1</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F28" s="50" t="s">
         <v>27</v>
@@ -2789,7 +2789,7 @@
         <v>300100201</v>
       </c>
       <c r="H28" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="50">
         <v>100</v>
@@ -2798,7 +2798,7 @@
         <v>300100201</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
@@ -2809,13 +2809,13 @@
         <v>3</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F29" s="50" t="s">
         <v>27</v>
@@ -2824,7 +2824,7 @@
         <v>300100301</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I29" s="50">
         <v>100</v>
@@ -2833,7 +2833,7 @@
         <v>300100301</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
@@ -2844,28 +2844,28 @@
         <v>3</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D30" s="50">
         <v>1</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="50">
         <v>300200000</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J30" s="50">
         <v>300200000</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31">
@@ -2876,16 +2876,16 @@
         <v>3</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G31" s="50">
         <v>300200001</v>
@@ -2894,13 +2894,13 @@
         <v>300200000</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J31" s="50">
         <v>300200001</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
@@ -2911,13 +2911,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D32" s="50">
         <v>1</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>28</v>
@@ -2929,7 +2929,7 @@
         <v>300200000</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="J32" s="50">
         <v>300200002</v>
@@ -2946,7 +2946,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D33" s="50">
         <v>1</v>
@@ -2981,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D34" s="50">
         <v>1</v>
@@ -3016,16 +3016,16 @@
         <v>3</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D35" s="50">
         <v>1</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G35" s="50">
         <v>300200101</v>
@@ -3051,16 +3051,16 @@
         <v>3</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D36" s="50">
         <v>1</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F36" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G36" s="50">
         <v>300200102</v>
@@ -3086,13 +3086,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D37" s="50">
         <v>1</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F37" s="50" t="s">
         <v>27</v>
@@ -3121,7 +3121,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D38" s="50">
         <v>1</v>
@@ -3162,10 +3162,10 @@
         <v>1</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G39" s="50">
         <v>300300000</v>
@@ -3331,16 +3331,16 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F44" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G44" s="50">
         <v>300300101</v>
@@ -3366,16 +3366,16 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G45" s="50">
         <v>300300102</v>
@@ -3407,7 +3407,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F46" s="50" t="s">
         <v>27</v>
@@ -3436,7 +3436,7 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>141</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G48" s="50">
         <v>300400000</v>
@@ -3506,7 +3506,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
@@ -3690,7 +3690,7 @@
         <v>141</v>
       </c>
       <c r="F54" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G54" s="50">
         <v>300400101</v>
@@ -3716,7 +3716,7 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         <v>141</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G55" s="50">
         <v>300400102</v>
@@ -3786,7 +3786,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
@@ -3830,7 +3830,7 @@
         <v>162</v>
       </c>
       <c r="F58" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G58" s="50">
         <v>300500000</v>
@@ -3856,7 +3856,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
@@ -3891,7 +3891,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
@@ -3926,7 +3926,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
@@ -3961,7 +3961,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
@@ -3996,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
@@ -4005,7 +4005,7 @@
         <v>162</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G63" s="50">
         <v>300500101</v>
@@ -4031,7 +4031,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
@@ -4040,7 +4040,7 @@
         <v>162</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G64" s="50">
         <v>300500102</v>
@@ -4101,7 +4101,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
@@ -4145,7 +4145,7 @@
         <v>180</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G67" s="50">
         <v>300600000</v>
@@ -4206,7 +4206,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
@@ -4241,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
@@ -4276,7 +4276,7 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
@@ -4311,7 +4311,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
@@ -4346,7 +4346,7 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
@@ -4355,7 +4355,7 @@
         <v>180</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G73" s="50">
         <v>300600101</v>
@@ -4381,7 +4381,7 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
@@ -4390,7 +4390,7 @@
         <v>180</v>
       </c>
       <c r="F74" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G74" s="50">
         <v>300600102</v>
@@ -4451,7 +4451,7 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
@@ -4495,7 +4495,7 @@
         <v>199</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G77" s="50">
         <v>300700000</v>
@@ -4521,7 +4521,7 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
@@ -4556,7 +4556,7 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
@@ -4591,7 +4591,7 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
@@ -4626,7 +4626,7 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
@@ -4661,7 +4661,7 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
@@ -4670,7 +4670,7 @@
         <v>199</v>
       </c>
       <c r="F82" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G82" s="50">
         <v>300700101</v>
@@ -4696,7 +4696,7 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
@@ -4705,7 +4705,7 @@
         <v>199</v>
       </c>
       <c r="F83" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G83" s="50">
         <v>300700102</v>
@@ -4766,7 +4766,7 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
@@ -4807,16 +4807,16 @@
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G86" s="50">
         <v>100500001</v>
       </c>
       <c r="I86" s="50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J86" s="50">
         <v>100500001</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -1478,139 +1478,142 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="50" t="n">
         <v>100100002</v>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>ui_research_3</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="50" t="n">
         <v>350</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="50" t="n">
         <v>350</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="50" t="n">
         <v>100100002</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="50" t="n">
         <v>100100001</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="50" t="inlineStr">
         <is>
           <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="50" t="n">
         <v>100100002</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="50" t="inlineStr">
         <is>
           <t>献祭祭品数量+1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="n">
-        <v>100200001</v>
-      </c>
-      <c r="B8" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_7</t>
-        </is>
-      </c>
-      <c r="D8" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F8" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
-      </c>
-      <c r="G8" s="50" t="n">
-        <v>100200001</v>
-      </c>
-      <c r="I8" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J8" s="50" t="n">
-        <v>100200001</v>
-      </c>
-      <c r="K8" s="50" t="inlineStr">
-        <is>
-          <t>开启终焉议会</t>
+      <c r="A8" t="n">
+        <v>100100003</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ui_research_3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>350</v>
+      </c>
+      <c r="F8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" t="n">
+        <v>100100003</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>100100001</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100,500,1000,5000,10000,20000,30000,40000,50000,100000</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>100100003</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>献祭失败保底概率提升</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="n">
-        <v>100200002</v>
-      </c>
-      <c r="B9" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_59</t>
-        </is>
-      </c>
-      <c r="D9" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F9" s="50" t="inlineStr">
-        <is>
-          <t>-400</t>
-        </is>
-      </c>
-      <c r="G9" s="50" t="n">
-        <v>100200002</v>
-      </c>
-      <c r="H9" s="50" t="n">
-        <v>100200001</v>
-      </c>
-      <c r="I9" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J9" s="50" t="n">
-        <v>100200002</v>
-      </c>
-      <c r="K9" s="50" t="inlineStr">
-        <is>
-          <t>终焉议会议案：魔物重命名</t>
+      <c r="A9" t="n">
+        <v>100100004</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ui_research_3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>500</v>
+      </c>
+      <c r="F9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100100004</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>100100001</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100,500,1000,5000,10000,20000,30000,40000,50000,100000</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>100100004</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>不同魔物献祭成功率提升</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="50" t="n">
-        <v>100200003</v>
+        <v>100200001</v>
       </c>
       <c r="B10" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="50" t="inlineStr">
         <is>
-          <t>ui_research_59</t>
+          <t>ui_research_7</t>
         </is>
       </c>
       <c r="D10" s="50" t="n">
@@ -1623,43 +1626,38 @@
       </c>
       <c r="F10" s="50" t="inlineStr">
         <is>
-          <t>-600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G10" s="50" t="n">
-        <v>100200003</v>
-      </c>
-      <c r="H10" s="50" t="n">
         <v>100200001</v>
       </c>
       <c r="I10" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>100200003</v>
+        <v>100200001</v>
       </c>
       <c r="K10" s="50" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="50" t="n">
-        <v>100300001</v>
+        <v>100200002</v>
       </c>
       <c r="B11" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="50" t="inlineStr">
         <is>
-          <t>ui_research_7</t>
-        </is>
-      </c>
-      <c r="D11" s="50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>ui_research_59</t>
+        </is>
+      </c>
+      <c r="D11" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="E11" s="50" t="inlineStr">
         <is>
@@ -1668,36 +1666,37 @@
       </c>
       <c r="F11" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="G11" s="50" t="n">
-        <v>100300001</v>
-      </c>
-      <c r="I11" s="50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+        <v>100200002</v>
+      </c>
+      <c r="H11" s="50" t="n">
+        <v>100200001</v>
+      </c>
+      <c r="I11" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>100300001</v>
+        <v>100200002</v>
       </c>
       <c r="K11" s="50" t="inlineStr">
         <is>
-          <t>开启终焉议会</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="50" t="n">
-        <v>100400000</v>
+        <v>100200003</v>
       </c>
       <c r="B12" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="50" t="inlineStr">
         <is>
-          <t>ui_research_57</t>
+          <t>ui_research_59</t>
         </is>
       </c>
       <c r="D12" s="50" t="n">
@@ -1705,77 +1704,79 @@
       </c>
       <c r="E12" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F12" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>-600</t>
         </is>
       </c>
       <c r="G12" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="I12" s="50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+        <v>100200003</v>
+      </c>
+      <c r="H12" s="50" t="n">
+        <v>100200001</v>
+      </c>
+      <c r="I12" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>100400000</v>
+        <v>100200003</v>
       </c>
       <c r="K12" s="50" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>终焉议会议案：魔王重命名</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="50" t="n">
-        <v>100400001</v>
+        <v>100300001</v>
       </c>
       <c r="B13" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="50" t="inlineStr">
         <is>
-          <t>ui_research_57</t>
-        </is>
-      </c>
-      <c r="D13" s="50" t="n">
-        <v>1</v>
+          <t>ui_research_7</t>
+        </is>
+      </c>
+      <c r="D13" s="50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="E13" s="50" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F13" s="50" t="inlineStr">
+        <is>
           <t>-200</t>
         </is>
       </c>
-      <c r="F13" s="50" t="inlineStr">
-        <is>
-          <t>-400</t>
-        </is>
-      </c>
       <c r="G13" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="H13" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="I13" s="50" t="n">
-        <v>100</v>
+        <v>100300001</v>
+      </c>
+      <c r="I13" s="50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="J13" s="50" t="n">
-        <v>100400001</v>
+        <v>100300001</v>
       </c>
       <c r="K13" s="50" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="50" t="n">
-        <v>100401000</v>
+        <v>100400000</v>
       </c>
       <c r="B14" s="50" t="n">
         <v>1</v>
@@ -1795,30 +1796,29 @@
       </c>
       <c r="F14" s="50" t="inlineStr">
         <is>
-          <t>-600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G14" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="H14" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="I14" s="50" t="n">
-        <v>100</v>
+        <v>100400000</v>
+      </c>
+      <c r="I14" s="50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J14" s="50" t="n">
-        <v>100401000</v>
+        <v>100400000</v>
       </c>
       <c r="K14" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="50" t="n">
-        <v>100401001</v>
+        <v>100400001</v>
       </c>
       <c r="B15" s="50" t="n">
         <v>1</v>
@@ -1829,41 +1829,39 @@
         </is>
       </c>
       <c r="D15" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E15" s="50" t="inlineStr">
         <is>
-          <t>-396</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="F15" s="50" t="inlineStr">
         <is>
-          <t>-596</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="G15" s="50" t="n">
-        <v>100401001</v>
+        <v>100400001</v>
       </c>
       <c r="H15" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="I15" s="50" t="inlineStr">
-        <is>
-          <t>100*1</t>
-        </is>
+        <v>100400000</v>
+      </c>
+      <c r="I15" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>100401001</v>
+        <v>100400001</v>
       </c>
       <c r="K15" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="50" t="n">
-        <v>100402000</v>
+        <v>100401000</v>
       </c>
       <c r="B16" s="50" t="n">
         <v>1</v>
@@ -1883,32 +1881,30 @@
       </c>
       <c r="F16" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-600</t>
         </is>
       </c>
       <c r="G16" s="50" t="n">
-        <v>100402000</v>
-      </c>
-      <c r="H16" s="50" t="inlineStr">
-        <is>
-          <t>100401000,100401001,</t>
-        </is>
+        <v>100401000</v>
+      </c>
+      <c r="H16" s="50" t="n">
+        <v>100400001</v>
       </c>
       <c r="I16" s="50" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>100402000</v>
+        <v>100401000</v>
       </c>
       <c r="K16" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="50" t="n">
-        <v>100402001</v>
+        <v>100401001</v>
       </c>
       <c r="B17" s="50" t="n">
         <v>1</v>
@@ -1919,41 +1915,41 @@
         </is>
       </c>
       <c r="D17" s="50" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E17" s="50" t="inlineStr">
         <is>
-          <t>-400</t>
+          <t>-396</t>
         </is>
       </c>
       <c r="F17" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-596</t>
         </is>
       </c>
       <c r="G17" s="50" t="n">
-        <v>100402001</v>
+        <v>100401001</v>
       </c>
       <c r="H17" s="50" t="n">
-        <v>100402000</v>
+        <v>100401000</v>
       </c>
       <c r="I17" s="50" t="inlineStr">
         <is>
-          <t>1000*1</t>
+          <t>100*1</t>
         </is>
       </c>
       <c r="J17" s="50" t="n">
-        <v>100402001</v>
+        <v>100401001</v>
       </c>
       <c r="K17" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="50" t="n">
-        <v>100403000</v>
+        <v>100402000</v>
       </c>
       <c r="B18" s="50" t="n">
         <v>1</v>
@@ -1973,32 +1969,32 @@
       </c>
       <c r="F18" s="50" t="inlineStr">
         <is>
-          <t>-1000</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="G18" s="50" t="n">
-        <v>100403000</v>
+        <v>100402000</v>
       </c>
       <c r="H18" s="50" t="inlineStr">
         <is>
-          <t>100402000,100402001,</t>
+          <t>100401000,100401001,</t>
         </is>
       </c>
       <c r="I18" s="50" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>100403000</v>
+        <v>100402000</v>
       </c>
       <c r="K18" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="50" t="n">
-        <v>100403001</v>
+        <v>100402001</v>
       </c>
       <c r="B19" s="50" t="n">
         <v>1</v>
@@ -2009,7 +2005,7 @@
         </is>
       </c>
       <c r="D19" s="50" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E19" s="50" t="inlineStr">
         <is>
@@ -2018,205 +2014,209 @@
       </c>
       <c r="F19" s="50" t="inlineStr">
         <is>
-          <t>-1000</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="G19" s="50" t="n">
-        <v>100403001</v>
+        <v>100402001</v>
       </c>
       <c r="H19" s="50" t="n">
-        <v>100403000</v>
+        <v>100402000</v>
       </c>
       <c r="I19" s="50" t="inlineStr">
         <is>
-          <t>10000*1</t>
+          <t>1000*1</t>
         </is>
       </c>
       <c r="J19" s="50" t="n">
-        <v>100403001</v>
+        <v>100402001</v>
       </c>
       <c r="K19" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="n">
-        <v>200000001</v>
+        <v>100403000</v>
       </c>
       <c r="B20" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="50" t="inlineStr">
         <is>
-          <t>ui_research_5</t>
+          <t>ui_research_57</t>
         </is>
       </c>
       <c r="D20" s="50" t="n">
-        <v>30</v>
-      </c>
-      <c r="E20" s="50" t="n">
-        <v>-200</v>
-      </c>
-      <c r="F20" s="50" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E20" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F20" s="50" t="inlineStr">
+        <is>
+          <t>-1000</t>
+        </is>
       </c>
       <c r="G20" s="50" t="n">
-        <v>200000001</v>
-      </c>
-      <c r="I20" s="50" t="inlineStr">
-        <is>
-          <t>100,250,500,1000,2000,5000,10000,20000,50000,100000,</t>
-        </is>
+        <v>100403000</v>
+      </c>
+      <c r="H20" s="50" t="inlineStr">
+        <is>
+          <t>100402000,100402001,</t>
+        </is>
+      </c>
+      <c r="I20" s="50" t="n">
+        <v>10000</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>200000001</v>
+        <v>100403000</v>
       </c>
       <c r="K20" s="50" t="inlineStr">
         <is>
-          <t>阵容上限+1</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="50" t="n">
-        <v>200100001</v>
+        <v>100403001</v>
       </c>
       <c r="B21" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="50" t="inlineStr">
         <is>
-          <t>ui_research_6</t>
+          <t>ui_research_57</t>
         </is>
       </c>
       <c r="D21" s="50" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E21" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="F21" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1000</t>
         </is>
       </c>
       <c r="G21" s="50" t="n">
-        <v>200100001</v>
+        <v>100403001</v>
+      </c>
+      <c r="H21" s="50" t="n">
+        <v>100403000</v>
       </c>
       <c r="I21" s="50" t="inlineStr">
         <is>
-          <t>100,200,300,400,</t>
+          <t>10000*1</t>
         </is>
       </c>
       <c r="J21" s="50" t="n">
-        <v>200100001</v>
+        <v>100403001</v>
       </c>
       <c r="K21" s="50" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="50" t="n">
-        <v>300100000</v>
+        <v>200000001</v>
       </c>
       <c r="B22" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_5</t>
         </is>
       </c>
       <c r="D22" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="50" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="F22" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="E22" s="50" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F22" s="50" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="H22" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I22" s="50" t="n">
-        <v>100</v>
+        <v>200000001</v>
+      </c>
+      <c r="I22" s="50" t="inlineStr">
+        <is>
+          <t>100,250,500,1000,2000,5000,10000,20000,50000,100000,</t>
+        </is>
       </c>
       <c r="J22" s="50" t="n">
-        <v>300100000</v>
+        <v>200000001</v>
       </c>
       <c r="K22" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>阵容上限+1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="50" t="n">
-        <v>300100001</v>
+        <v>200100001</v>
       </c>
       <c r="B23" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_6</t>
         </is>
       </c>
       <c r="D23" s="50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="50" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F23" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" s="50" t="n">
-        <v>300100001</v>
-      </c>
-      <c r="H23" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="I23" s="50" t="n">
-        <v>100</v>
+        <v>200100001</v>
+      </c>
+      <c r="I23" s="50" t="inlineStr">
+        <is>
+          <t>100,200,300,400,</t>
+        </is>
       </c>
       <c r="J23" s="50" t="n">
-        <v>300100001</v>
+        <v>200100001</v>
       </c>
       <c r="K23" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50" t="n">
-        <v>300100002</v>
+        <v>300100000</v>
       </c>
       <c r="B24" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D24" s="50" t="n">
@@ -2224,42 +2224,42 @@
       </c>
       <c r="E24" s="50" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F24" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G24" s="50" t="n">
-        <v>300100002</v>
+        <v>300100000</v>
       </c>
       <c r="H24" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="I24" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" s="50" t="n">
         <v>300100000</v>
       </c>
-      <c r="I24" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J24" s="50" t="n">
-        <v>300100002</v>
-      </c>
       <c r="K24" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="B25" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D25" s="50" t="n">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="E25" s="50" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F25" s="50" t="inlineStr">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="G25" s="50" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="H25" s="50" t="n">
         <v>300100000</v>
@@ -2285,24 +2285,24 @@
         <v>100</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="K25" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="50" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="B26" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D26" s="50" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="E26" s="50" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F26" s="50" t="inlineStr">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="G26" s="50" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="H26" s="50" t="n">
         <v>300100000</v>
@@ -2328,24 +2328,24 @@
         <v>100</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="K26" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="50" t="n">
-        <v>300100101</v>
+        <v>300100003</v>
       </c>
       <c r="B27" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C27" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D27" s="50" t="n">
@@ -2353,44 +2353,42 @@
       </c>
       <c r="E27" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F27" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G27" s="50" t="n">
-        <v>300100101</v>
-      </c>
-      <c r="H27" s="50" t="inlineStr">
-        <is>
-          <t>300100001|300100002|300100003|300100004|</t>
-        </is>
+        <v>300100003</v>
+      </c>
+      <c r="H27" s="50" t="n">
+        <v>300100000</v>
       </c>
       <c r="I27" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>300100101</v>
+        <v>300100003</v>
       </c>
       <c r="K27" s="50" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="50" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="B28" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C28" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D28" s="50" t="n">
@@ -2398,42 +2396,42 @@
       </c>
       <c r="E28" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F28" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G28" s="50" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="H28" s="50" t="n">
-        <v>300100101</v>
+        <v>300100000</v>
       </c>
       <c r="I28" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="K28" s="50" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="50" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="B29" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C29" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D29" s="50" t="n">
@@ -2446,39 +2444,39 @@
       </c>
       <c r="F29" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G29" s="50" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="H29" s="50" t="inlineStr">
         <is>
-          <t>100200001,300100000,</t>
+          <t>300100001|300100002|300100003|300100004|</t>
         </is>
       </c>
       <c r="I29" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="K29" s="50" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="50" t="n">
-        <v>300100301</v>
+        <v>300100102</v>
       </c>
       <c r="B30" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C30" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D30" s="50" t="n">
@@ -2486,44 +2484,42 @@
       </c>
       <c r="E30" s="50" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F30" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G30" s="50" t="n">
-        <v>300100301</v>
-      </c>
-      <c r="H30" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300100000,</t>
-        </is>
+        <v>300100102</v>
+      </c>
+      <c r="H30" s="50" t="n">
+        <v>300100101</v>
       </c>
       <c r="I30" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>300100301</v>
+        <v>300100102</v>
       </c>
       <c r="K30" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="50" t="n">
-        <v>300200000</v>
+        <v>300100201</v>
       </c>
       <c r="B31" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D31" s="50" t="n">
@@ -2531,41 +2527,44 @@
       </c>
       <c r="E31" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F31" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G31" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I31" s="50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+        <v>300100201</v>
+      </c>
+      <c r="H31" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300100000,</t>
+        </is>
+      </c>
+      <c r="I31" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>300200000</v>
+        <v>300100201</v>
       </c>
       <c r="K31" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50" t="n">
-        <v>300200001</v>
+        <v>300100301</v>
       </c>
       <c r="B32" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D32" s="50" t="n">
@@ -2573,44 +2572,44 @@
       </c>
       <c r="E32" s="50" t="inlineStr">
         <is>
-          <t>-223</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F32" s="50" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G32" s="50" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="H32" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I32" s="50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>300100301</v>
+      </c>
+      <c r="H32" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300100000,</t>
+        </is>
+      </c>
+      <c r="I32" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>300200001</v>
+        <v>300100301</v>
       </c>
       <c r="K32" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="50" t="n">
-        <v>300200002</v>
+        <v>300200000</v>
       </c>
       <c r="B33" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D33" s="50" t="n">
@@ -2618,44 +2617,41 @@
       </c>
       <c r="E33" s="50" t="inlineStr">
         <is>
-          <t>-75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F33" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G33" s="50" t="n">
-        <v>300200002</v>
-      </c>
-      <c r="H33" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I33" s="50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" s="50" t="n">
-        <v>300200002</v>
+        <v>300200000</v>
       </c>
       <c r="K33" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="50" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="B34" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D34" s="50" t="n">
@@ -2663,44 +2659,44 @@
       </c>
       <c r="E34" s="50" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-223</t>
         </is>
       </c>
       <c r="F34" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G34" s="50" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="H34" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I34" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" s="50" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="K34" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="50" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="B35" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C35" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D35" s="50" t="n">
@@ -2708,7 +2704,7 @@
       </c>
       <c r="E35" s="50" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-75</t>
         </is>
       </c>
       <c r="F35" s="50" t="inlineStr">
@@ -2717,35 +2713,35 @@
         </is>
       </c>
       <c r="G35" s="50" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="H35" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I35" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J35" s="50" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="K35" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="50" t="n">
-        <v>300200101</v>
+        <v>300200003</v>
       </c>
       <c r="B36" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D36" s="50" t="n">
@@ -2753,46 +2749,44 @@
       </c>
       <c r="E36" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F36" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G36" s="50" t="n">
-        <v>300200101</v>
-      </c>
-      <c r="H36" s="50" t="inlineStr">
-        <is>
-          <t>300200001|300200002|300200003|300200004|</t>
-        </is>
+        <v>300200003</v>
+      </c>
+      <c r="H36" s="50" t="n">
+        <v>300200000</v>
       </c>
       <c r="I36" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J36" s="50" t="n">
-        <v>300200101</v>
+        <v>300200003</v>
       </c>
       <c r="K36" s="50" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="50" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="B37" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D37" s="50" t="n">
@@ -2800,42 +2794,44 @@
       </c>
       <c r="E37" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F37" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G37" s="50" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="H37" s="50" t="n">
-        <v>300200101</v>
-      </c>
-      <c r="I37" s="50" t="n">
-        <v>100</v>
+        <v>300200000</v>
+      </c>
+      <c r="I37" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="J37" s="50" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="K37" s="50" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="50" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="B38" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D38" s="50" t="n">
@@ -2848,39 +2844,41 @@
       </c>
       <c r="F38" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G38" s="50" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="H38" s="50" t="inlineStr">
         <is>
-          <t>100200001,300200000,</t>
-        </is>
-      </c>
-      <c r="I38" s="50" t="n">
-        <v>100</v>
+          <t>300200001|300200002|300200003|300200004|</t>
+        </is>
+      </c>
+      <c r="I38" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="J38" s="50" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="K38" s="50" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50" t="n">
-        <v>300200301</v>
+        <v>300200102</v>
       </c>
       <c r="B39" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D39" s="50" t="n">
@@ -2888,44 +2886,42 @@
       </c>
       <c r="E39" s="50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F39" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G39" s="50" t="n">
-        <v>300200301</v>
-      </c>
-      <c r="H39" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300200000,</t>
-        </is>
+        <v>300200102</v>
+      </c>
+      <c r="H39" s="50" t="n">
+        <v>300200101</v>
       </c>
       <c r="I39" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J39" s="50" t="n">
-        <v>300200301</v>
+        <v>300200102</v>
       </c>
       <c r="K39" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="50" t="n">
-        <v>300300000</v>
+        <v>300200201</v>
       </c>
       <c r="B40" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C40" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D40" s="50" t="n">
@@ -2933,42 +2929,44 @@
       </c>
       <c r="E40" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F40" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G40" s="50" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="H40" s="50" t="n">
-        <v>300200000</v>
+        <v>300200201</v>
+      </c>
+      <c r="H40" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300200000,</t>
+        </is>
       </c>
       <c r="I40" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J40" s="50" t="n">
-        <v>300300000</v>
+        <v>300200201</v>
       </c>
       <c r="K40" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="50" t="n">
-        <v>300300001</v>
+        <v>300200301</v>
       </c>
       <c r="B41" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C41" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D41" s="50" t="n">
@@ -2976,42 +2974,44 @@
       </c>
       <c r="E41" s="50" t="inlineStr">
         <is>
-          <t>-1025</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F41" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G41" s="50" t="n">
-        <v>300300001</v>
-      </c>
-      <c r="H41" s="50" t="n">
-        <v>300300000</v>
+        <v>300200301</v>
+      </c>
+      <c r="H41" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300200000,</t>
+        </is>
       </c>
       <c r="I41" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J41" s="50" t="n">
-        <v>300300001</v>
+        <v>300200301</v>
       </c>
       <c r="K41" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="50" t="n">
-        <v>300300002</v>
+        <v>300300000</v>
       </c>
       <c r="B42" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>ui_research_54</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D42" s="50" t="n">
@@ -3019,42 +3019,42 @@
       </c>
       <c r="E42" s="50" t="inlineStr">
         <is>
-          <t>-875</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F42" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G42" s="50" t="n">
-        <v>300300002</v>
+        <v>300300000</v>
       </c>
       <c r="H42" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="I42" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" s="50" t="n">
         <v>300300000</v>
       </c>
-      <c r="I42" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J42" s="50" t="n">
-        <v>300300002</v>
-      </c>
       <c r="K42" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="50" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="B43" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C43" s="50" t="inlineStr">
         <is>
-          <t>ui_research_54</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D43" s="50" t="n">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E43" s="50" t="inlineStr">
         <is>
-          <t>-725</t>
+          <t>-1025</t>
         </is>
       </c>
       <c r="F43" s="50" t="inlineStr">
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="G43" s="50" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="H43" s="50" t="n">
         <v>300300000</v>
@@ -3080,24 +3080,24 @@
         <v>100</v>
       </c>
       <c r="J43" s="50" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="K43" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="50" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="B44" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="50" t="inlineStr">
         <is>
-          <t>ui_research_53</t>
+          <t>ui_research_54</t>
         </is>
       </c>
       <c r="D44" s="50" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="E44" s="50" t="inlineStr">
         <is>
-          <t>-575</t>
+          <t>-875</t>
         </is>
       </c>
       <c r="F44" s="50" t="inlineStr">
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="G44" s="50" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="H44" s="50" t="n">
         <v>300300000</v>
@@ -3123,24 +3123,24 @@
         <v>100</v>
       </c>
       <c r="J44" s="50" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="K44" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="50" t="n">
-        <v>300300101</v>
+        <v>300300003</v>
       </c>
       <c r="B45" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C45" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_54</t>
         </is>
       </c>
       <c r="D45" s="50" t="n">
@@ -3148,44 +3148,42 @@
       </c>
       <c r="E45" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-725</t>
         </is>
       </c>
       <c r="F45" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G45" s="50" t="n">
-        <v>300300101</v>
-      </c>
-      <c r="H45" s="50" t="inlineStr">
-        <is>
-          <t>300300001|300300002|300300003|300300004|</t>
-        </is>
+        <v>300300003</v>
+      </c>
+      <c r="H45" s="50" t="n">
+        <v>300300000</v>
       </c>
       <c r="I45" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J45" s="50" t="n">
-        <v>300300101</v>
+        <v>300300003</v>
       </c>
       <c r="K45" s="50" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="50" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="B46" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C46" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_53</t>
         </is>
       </c>
       <c r="D46" s="50" t="n">
@@ -3193,42 +3191,42 @@
       </c>
       <c r="E46" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-575</t>
         </is>
       </c>
       <c r="F46" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G46" s="50" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="H46" s="50" t="n">
-        <v>300300101</v>
+        <v>300300000</v>
       </c>
       <c r="I46" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J46" s="50" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="K46" s="50" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="50" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="B47" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C47" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D47" s="50" t="n">
@@ -3241,39 +3239,39 @@
       </c>
       <c r="F47" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G47" s="50" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="H47" s="50" t="inlineStr">
         <is>
-          <t>100200001,300300000,</t>
+          <t>300300001|300300002|300300003|300300004|</t>
         </is>
       </c>
       <c r="I47" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J47" s="50" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="K47" s="50" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="50" t="n">
-        <v>300300301</v>
+        <v>300300102</v>
       </c>
       <c r="B48" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D48" s="50" t="n">
@@ -3281,44 +3279,42 @@
       </c>
       <c r="E48" s="50" t="inlineStr">
         <is>
-          <t>-650</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G48" s="50" t="n">
-        <v>300300301</v>
-      </c>
-      <c r="H48" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300300000,</t>
-        </is>
+        <v>300300102</v>
+      </c>
+      <c r="H48" s="50" t="n">
+        <v>300300101</v>
       </c>
       <c r="I48" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J48" s="50" t="n">
-        <v>300300301</v>
+        <v>300300102</v>
       </c>
       <c r="K48" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="50" t="n">
-        <v>300400000</v>
+        <v>300300201</v>
       </c>
       <c r="B49" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D49" s="50" t="n">
@@ -3326,42 +3322,44 @@
       </c>
       <c r="E49" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F49" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G49" s="50" t="n">
-        <v>300400000</v>
-      </c>
-      <c r="H49" s="50" t="n">
-        <v>300600000</v>
+        <v>300300201</v>
+      </c>
+      <c r="H49" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300300000,</t>
+        </is>
       </c>
       <c r="I49" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J49" s="50" t="n">
-        <v>300400000</v>
+        <v>300300201</v>
       </c>
       <c r="K49" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="50" t="n">
-        <v>300400001</v>
+        <v>300300301</v>
       </c>
       <c r="B50" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C50" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D50" s="50" t="n">
@@ -3369,42 +3367,44 @@
       </c>
       <c r="E50" s="50" t="inlineStr">
         <is>
-          <t>-2700</t>
+          <t>-650</t>
         </is>
       </c>
       <c r="F50" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G50" s="50" t="n">
-        <v>300400001</v>
-      </c>
-      <c r="H50" s="50" t="n">
-        <v>300400000</v>
+        <v>300300301</v>
+      </c>
+      <c r="H50" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300300000,</t>
+        </is>
       </c>
       <c r="I50" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J50" s="50" t="n">
-        <v>300400001</v>
+        <v>300300301</v>
       </c>
       <c r="K50" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="50" t="n">
-        <v>300400002</v>
+        <v>300400000</v>
       </c>
       <c r="B51" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C51" s="50" t="inlineStr">
         <is>
-          <t>ui_research_45</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D51" s="50" t="n">
@@ -3412,42 +3412,42 @@
       </c>
       <c r="E51" s="50" t="inlineStr">
         <is>
-          <t>-2550</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F51" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G51" s="50" t="n">
-        <v>300400002</v>
+        <v>300400000</v>
       </c>
       <c r="H51" s="50" t="n">
+        <v>300600000</v>
+      </c>
+      <c r="I51" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="I51" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J51" s="50" t="n">
-        <v>300400002</v>
-      </c>
       <c r="K51" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="50" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="B52" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C52" s="50" t="inlineStr">
         <is>
-          <t>ui_research_52</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D52" s="50" t="n">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="E52" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2700</t>
         </is>
       </c>
       <c r="F52" s="50" t="inlineStr">
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="G52" s="50" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="H52" s="50" t="n">
         <v>300400000</v>
@@ -3473,24 +3473,24 @@
         <v>100</v>
       </c>
       <c r="J52" s="50" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="K52" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="50" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="B53" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C53" s="50" t="inlineStr">
         <is>
-          <t>ui_research_49</t>
+          <t>ui_research_45</t>
         </is>
       </c>
       <c r="D53" s="50" t="n">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="E53" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2550</t>
         </is>
       </c>
       <c r="F53" s="50" t="inlineStr">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="G53" s="50" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="H53" s="50" t="n">
         <v>300400000</v>
@@ -3516,24 +3516,24 @@
         <v>100</v>
       </c>
       <c r="J53" s="50" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="K53" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="50" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="B54" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_52</t>
         </is>
       </c>
       <c r="D54" s="50" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="E54" s="50" t="inlineStr">
         <is>
-          <t>-2100</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F54" s="50" t="inlineStr">
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="G54" s="50" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="H54" s="50" t="n">
         <v>300400000</v>
@@ -3559,24 +3559,24 @@
         <v>100</v>
       </c>
       <c r="J54" s="50" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="K54" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="50" t="n">
-        <v>300400101</v>
+        <v>300400004</v>
       </c>
       <c r="B55" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C55" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_49</t>
         </is>
       </c>
       <c r="D55" s="50" t="n">
@@ -3584,44 +3584,42 @@
       </c>
       <c r="E55" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F55" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G55" s="50" t="n">
-        <v>300400101</v>
-      </c>
-      <c r="H55" s="50" t="inlineStr">
-        <is>
-          <t>300400001|300400002|300400003|300400004|300400005|</t>
-        </is>
+        <v>300400004</v>
+      </c>
+      <c r="H55" s="50" t="n">
+        <v>300400000</v>
       </c>
       <c r="I55" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J55" s="50" t="n">
-        <v>300400101</v>
+        <v>300400004</v>
       </c>
       <c r="K55" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="50" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="B56" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C56" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D56" s="50" t="n">
@@ -3629,42 +3627,42 @@
       </c>
       <c r="E56" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2100</t>
         </is>
       </c>
       <c r="F56" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G56" s="50" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="H56" s="50" t="n">
-        <v>300400101</v>
+        <v>300400000</v>
       </c>
       <c r="I56" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J56" s="50" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="K56" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="50" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="B57" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C57" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D57" s="50" t="n">
@@ -3677,39 +3675,39 @@
       </c>
       <c r="F57" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G57" s="50" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="H57" s="50" t="inlineStr">
         <is>
-          <t>100200001,300400000,</t>
+          <t>300400001|300400002|300400003|300400004|300400005|</t>
         </is>
       </c>
       <c r="I57" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J57" s="50" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="K57" s="50" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51">
       <c r="A58" s="50" t="n">
-        <v>300400301</v>
+        <v>300400102</v>
       </c>
       <c r="B58" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C58" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D58" s="50" t="n">
@@ -3717,44 +3715,42 @@
       </c>
       <c r="E58" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F58" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G58" s="50" t="n">
-        <v>300400301</v>
-      </c>
-      <c r="H58" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300400000,</t>
-        </is>
+        <v>300400102</v>
+      </c>
+      <c r="H58" s="50" t="n">
+        <v>300400101</v>
       </c>
       <c r="I58" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J58" s="50" t="n">
-        <v>300400301</v>
+        <v>300400102</v>
       </c>
       <c r="K58" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51">
       <c r="A59" s="50" t="n">
-        <v>300500000</v>
+        <v>300400201</v>
       </c>
       <c r="B59" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C59" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D59" s="50" t="n">
@@ -3762,42 +3758,44 @@
       </c>
       <c r="E59" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F59" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G59" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="H59" s="50" t="n">
-        <v>300700000</v>
+        <v>300400201</v>
+      </c>
+      <c r="H59" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300400000,</t>
+        </is>
       </c>
       <c r="I59" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J59" s="50" t="n">
-        <v>300500000</v>
+        <v>300400201</v>
       </c>
       <c r="K59" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51">
       <c r="A60" s="50" t="n">
-        <v>300500001</v>
+        <v>300400301</v>
       </c>
       <c r="B60" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D60" s="50" t="n">
@@ -3805,42 +3803,44 @@
       </c>
       <c r="E60" s="50" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F60" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G60" s="50" t="n">
-        <v>300500001</v>
-      </c>
-      <c r="H60" s="50" t="n">
-        <v>300500000</v>
+        <v>300400301</v>
+      </c>
+      <c r="H60" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300400000,</t>
+        </is>
       </c>
       <c r="I60" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J60" s="50" t="n">
-        <v>300500001</v>
+        <v>300400301</v>
       </c>
       <c r="K60" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51">
       <c r="A61" s="50" t="n">
-        <v>300500002</v>
+        <v>300500000</v>
       </c>
       <c r="B61" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C61" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D61" s="50" t="n">
@@ -3848,42 +3848,42 @@
       </c>
       <c r="E61" s="50" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F61" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" s="50" t="n">
-        <v>300500002</v>
+        <v>300500000</v>
       </c>
       <c r="H61" s="50" t="n">
+        <v>300700000</v>
+      </c>
+      <c r="I61" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J61" s="50" t="n">
         <v>300500000</v>
       </c>
-      <c r="I61" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J61" s="50" t="n">
-        <v>300500002</v>
-      </c>
       <c r="K61" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51">
       <c r="A62" s="50" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="B62" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D62" s="50" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="E62" s="50" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F62" s="50" t="inlineStr">
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="G62" s="50" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="H62" s="50" t="n">
         <v>300500000</v>
@@ -3909,24 +3909,24 @@
         <v>100</v>
       </c>
       <c r="J62" s="50" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="K62" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51">
       <c r="A63" s="50" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="B63" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C63" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D63" s="50" t="n">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="E63" s="50" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F63" s="50" t="inlineStr">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="G63" s="50" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="H63" s="50" t="n">
         <v>300500000</v>
@@ -3952,24 +3952,24 @@
         <v>100</v>
       </c>
       <c r="J63" s="50" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="K63" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51">
       <c r="A64" s="50" t="n">
-        <v>300500101</v>
+        <v>300500003</v>
       </c>
       <c r="B64" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C64" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D64" s="50" t="n">
@@ -3977,44 +3977,42 @@
       </c>
       <c r="E64" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F64" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G64" s="50" t="n">
-        <v>300500101</v>
-      </c>
-      <c r="H64" s="50" t="inlineStr">
-        <is>
-          <t>300500001|300500002|300500003|300500004|</t>
-        </is>
+        <v>300500003</v>
+      </c>
+      <c r="H64" s="50" t="n">
+        <v>300500000</v>
       </c>
       <c r="I64" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J64" s="50" t="n">
-        <v>300500101</v>
+        <v>300500003</v>
       </c>
       <c r="K64" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="50" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="B65" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C65" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D65" s="50" t="n">
@@ -4022,42 +4020,42 @@
       </c>
       <c r="E65" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="F65" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G65" s="50" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="H65" s="50" t="n">
-        <v>300500101</v>
+        <v>300500000</v>
       </c>
       <c r="I65" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J65" s="50" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="K65" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="50" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="B66" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C66" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D66" s="50" t="n">
@@ -4070,39 +4068,39 @@
       </c>
       <c r="F66" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G66" s="50" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="H66" s="50" t="inlineStr">
         <is>
-          <t>100200001,300500000,</t>
+          <t>300500001|300500002|300500003|300500004|</t>
         </is>
       </c>
       <c r="I66" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J66" s="50" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="K66" s="50" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51">
       <c r="A67" s="50" t="n">
-        <v>300500301</v>
+        <v>300500102</v>
       </c>
       <c r="B67" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D67" s="50" t="n">
@@ -4110,44 +4108,42 @@
       </c>
       <c r="E67" s="50" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F67" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G67" s="50" t="n">
-        <v>300500301</v>
-      </c>
-      <c r="H67" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300500000,</t>
-        </is>
+        <v>300500102</v>
+      </c>
+      <c r="H67" s="50" t="n">
+        <v>300500101</v>
       </c>
       <c r="I67" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J67" s="50" t="n">
-        <v>300500301</v>
+        <v>300500102</v>
       </c>
       <c r="K67" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51">
       <c r="A68" s="50" t="n">
-        <v>300600000</v>
+        <v>300500201</v>
       </c>
       <c r="B68" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C68" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D68" s="50" t="n">
@@ -4155,42 +4151,44 @@
       </c>
       <c r="E68" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F68" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G68" s="50" t="n">
-        <v>300600000</v>
-      </c>
-      <c r="H68" s="50" t="n">
-        <v>300300000</v>
+        <v>300500201</v>
+      </c>
+      <c r="H68" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300500000,</t>
+        </is>
       </c>
       <c r="I68" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J68" s="50" t="n">
-        <v>300600000</v>
+        <v>300500201</v>
       </c>
       <c r="K68" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51">
       <c r="A69" s="50" t="n">
-        <v>300600001</v>
+        <v>300500301</v>
       </c>
       <c r="B69" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="50" t="inlineStr">
         <is>
-          <t>ui_research_44</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D69" s="50" t="n">
@@ -4198,42 +4196,44 @@
       </c>
       <c r="E69" s="50" t="inlineStr">
         <is>
-          <t>-1900</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="F69" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G69" s="50" t="n">
-        <v>300600001</v>
-      </c>
-      <c r="H69" s="50" t="n">
-        <v>300600000</v>
+        <v>300500301</v>
+      </c>
+      <c r="H69" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300500000,</t>
+        </is>
       </c>
       <c r="I69" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J69" s="50" t="n">
-        <v>300600001</v>
+        <v>300500301</v>
       </c>
       <c r="K69" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51">
       <c r="A70" s="50" t="n">
-        <v>300600002</v>
+        <v>300600000</v>
       </c>
       <c r="B70" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D70" s="50" t="n">
@@ -4241,42 +4241,42 @@
       </c>
       <c r="E70" s="50" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F70" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G70" s="50" t="n">
-        <v>300600002</v>
+        <v>300600000</v>
       </c>
       <c r="H70" s="50" t="n">
+        <v>300300000</v>
+      </c>
+      <c r="I70" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J70" s="50" t="n">
         <v>300600000</v>
       </c>
-      <c r="I70" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J70" s="50" t="n">
-        <v>300600002</v>
-      </c>
       <c r="K70" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51">
       <c r="A71" s="50" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="B71" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C71" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_44</t>
         </is>
       </c>
       <c r="D71" s="50" t="n">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="E71" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1900</t>
         </is>
       </c>
       <c r="F71" s="50" t="inlineStr">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="G71" s="50" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="H71" s="50" t="n">
         <v>300600000</v>
@@ -4302,24 +4302,24 @@
         <v>100</v>
       </c>
       <c r="J71" s="50" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="K71" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51">
       <c r="A72" s="50" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="B72" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C72" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D72" s="50" t="n">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="E72" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="F72" s="50" t="inlineStr">
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="G72" s="50" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="H72" s="50" t="n">
         <v>300600000</v>
@@ -4345,24 +4345,24 @@
         <v>100</v>
       </c>
       <c r="J72" s="50" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="K72" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51">
       <c r="A73" s="50" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="B73" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C73" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D73" s="50" t="n">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="E73" s="50" t="inlineStr">
         <is>
-          <t>-1300</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F73" s="50" t="inlineStr">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="G73" s="50" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="H73" s="50" t="n">
         <v>300600000</v>
@@ -4388,24 +4388,24 @@
         <v>100</v>
       </c>
       <c r="J73" s="50" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="K73" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51">
       <c r="A74" s="50" t="n">
-        <v>300600101</v>
+        <v>300600004</v>
       </c>
       <c r="B74" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C74" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D74" s="50" t="n">
@@ -4413,44 +4413,42 @@
       </c>
       <c r="E74" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F74" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G74" s="50" t="n">
-        <v>300600101</v>
-      </c>
-      <c r="H74" s="50" t="inlineStr">
-        <is>
-          <t>300600001|300600002|300600003|300600004|</t>
-        </is>
+        <v>300600004</v>
+      </c>
+      <c r="H74" s="50" t="n">
+        <v>300600000</v>
       </c>
       <c r="I74" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J74" s="50" t="n">
-        <v>300600101</v>
+        <v>300600004</v>
       </c>
       <c r="K74" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="50" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="B75" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C75" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D75" s="50" t="n">
@@ -4458,42 +4456,42 @@
       </c>
       <c r="E75" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1300</t>
         </is>
       </c>
       <c r="F75" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G75" s="50" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="H75" s="50" t="n">
-        <v>300600101</v>
+        <v>300600000</v>
       </c>
       <c r="I75" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J75" s="50" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="K75" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="50" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="B76" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C76" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D76" s="50" t="n">
@@ -4506,39 +4504,39 @@
       </c>
       <c r="F76" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G76" s="50" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="H76" s="50" t="inlineStr">
         <is>
-          <t>100200001,300600000,</t>
+          <t>300600001|300600002|300600003|300600004|</t>
         </is>
       </c>
       <c r="I76" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J76" s="50" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="K76" s="50" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="50" t="n">
-        <v>300600301</v>
+        <v>300600102</v>
       </c>
       <c r="B77" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C77" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D77" s="50" t="n">
@@ -4546,44 +4544,42 @@
       </c>
       <c r="E77" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F77" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G77" s="50" t="n">
-        <v>300600301</v>
-      </c>
-      <c r="H77" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300600000,</t>
-        </is>
+        <v>300600102</v>
+      </c>
+      <c r="H77" s="50" t="n">
+        <v>300600101</v>
       </c>
       <c r="I77" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J77" s="50" t="n">
-        <v>300600301</v>
+        <v>300600102</v>
       </c>
       <c r="K77" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51">
       <c r="A78" s="50" t="n">
-        <v>300700000</v>
+        <v>300600201</v>
       </c>
       <c r="B78" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C78" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D78" s="50" t="n">
@@ -4591,42 +4587,44 @@
       </c>
       <c r="E78" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F78" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G78" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="H78" s="50" t="n">
-        <v>300100000</v>
+        <v>300600201</v>
+      </c>
+      <c r="H78" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300600000,</t>
+        </is>
       </c>
       <c r="I78" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J78" s="50" t="n">
-        <v>300700000</v>
+        <v>300600201</v>
       </c>
       <c r="K78" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51">
       <c r="A79" s="50" t="n">
-        <v>300700001</v>
+        <v>300600301</v>
       </c>
       <c r="B79" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C79" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D79" s="50" t="n">
@@ -4634,42 +4632,44 @@
       </c>
       <c r="E79" s="50" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F79" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G79" s="50" t="n">
-        <v>300700001</v>
-      </c>
-      <c r="H79" s="50" t="n">
-        <v>300700000</v>
+        <v>300600301</v>
+      </c>
+      <c r="H79" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300600000,</t>
+        </is>
       </c>
       <c r="I79" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J79" s="50" t="n">
-        <v>300700001</v>
+        <v>300600301</v>
       </c>
       <c r="K79" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51">
       <c r="A80" s="50" t="n">
-        <v>300700002</v>
+        <v>300700000</v>
       </c>
       <c r="B80" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C80" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_38</t>
         </is>
       </c>
       <c r="D80" s="50" t="n">
@@ -4677,42 +4677,42 @@
       </c>
       <c r="E80" s="50" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F80" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G80" s="50" t="n">
-        <v>300700002</v>
+        <v>300700000</v>
       </c>
       <c r="H80" s="50" t="n">
+        <v>300100000</v>
+      </c>
+      <c r="I80" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J80" s="50" t="n">
         <v>300700000</v>
       </c>
-      <c r="I80" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J80" s="50" t="n">
-        <v>300700002</v>
-      </c>
       <c r="K80" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51">
       <c r="A81" s="50" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="B81" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C81" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D81" s="50" t="n">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E81" s="50" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="F81" s="50" t="inlineStr">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="G81" s="50" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="H81" s="50" t="n">
         <v>300700000</v>
@@ -4738,24 +4738,24 @@
         <v>100</v>
       </c>
       <c r="J81" s="50" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="K81" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51">
       <c r="A82" s="50" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="B82" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C82" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D82" s="50" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="E82" s="50" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F82" s="50" t="inlineStr">
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="G82" s="50" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="H82" s="50" t="n">
         <v>300700000</v>
@@ -4781,24 +4781,24 @@
         <v>100</v>
       </c>
       <c r="J82" s="50" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="K82" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51">
       <c r="A83" s="50" t="n">
-        <v>300700101</v>
+        <v>300700003</v>
       </c>
       <c r="B83" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C83" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D83" s="50" t="n">
@@ -4806,44 +4806,42 @@
       </c>
       <c r="E83" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="F83" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G83" s="50" t="n">
-        <v>300700101</v>
-      </c>
-      <c r="H83" s="50" t="inlineStr">
-        <is>
-          <t>300700001|300700002|300700003|300700004|</t>
-        </is>
+        <v>300700003</v>
+      </c>
+      <c r="H83" s="50" t="n">
+        <v>300700000</v>
       </c>
       <c r="I83" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J83" s="50" t="n">
-        <v>300700101</v>
+        <v>300700003</v>
       </c>
       <c r="K83" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="50" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="B84" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C84" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D84" s="50" t="n">
@@ -4851,42 +4849,42 @@
       </c>
       <c r="E84" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F84" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G84" s="50" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="H84" s="50" t="n">
-        <v>300700101</v>
+        <v>300700000</v>
       </c>
       <c r="I84" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J84" s="50" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="K84" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="50" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="B85" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C85" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D85" s="50" t="n">
@@ -4899,39 +4897,39 @@
       </c>
       <c r="F85" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G85" s="50" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="H85" s="50" t="inlineStr">
         <is>
-          <t>100200001,300700000,</t>
+          <t>300700001|300700002|300700003|300700004|</t>
         </is>
       </c>
       <c r="I85" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J85" s="50" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="K85" s="50" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="50" t="n">
-        <v>300700301</v>
+        <v>300700102</v>
       </c>
       <c r="B86" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C86" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D86" s="50" t="n">
@@ -4939,71 +4937,159 @@
       </c>
       <c r="E86" s="50" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F86" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G86" s="50" t="n">
-        <v>300700301</v>
-      </c>
-      <c r="H86" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300700000,</t>
-        </is>
+        <v>300700102</v>
+      </c>
+      <c r="H86" s="50" t="n">
+        <v>300700101</v>
       </c>
       <c r="I86" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J86" s="50" t="n">
-        <v>300700301</v>
+        <v>300700102</v>
       </c>
       <c r="K86" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B87" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_38</t>
+        </is>
+      </c>
+      <c r="D87" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="50" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="F87" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="G87" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="H87" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300700000,</t>
+        </is>
+      </c>
+      <c r="I87" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J87" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="K87" s="50" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B88" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_58</t>
+        </is>
+      </c>
+      <c r="D88" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="50" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="F88" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="G88" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="H88" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300700000,</t>
+        </is>
+      </c>
+      <c r="I88" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J88" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="K88" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="B87" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" s="50" t="inlineStr">
+      <c r="B89" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="50" t="inlineStr">
         <is>
           <t>ui_research_18</t>
         </is>
       </c>
-      <c r="D87" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="50" t="inlineStr">
+      <c r="D89" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F87" s="50" t="inlineStr">
+      <c r="F89" s="50" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="G87" s="50" t="n">
+      <c r="G89" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="I87" s="50" t="inlineStr">
+      <c r="I89" s="50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J87" s="50" t="n">
+      <c r="J89" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="K87" s="50" t="inlineStr">
+      <c r="K89" s="50" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -234,7 +234,7 @@
     <t>ui_research_5</t>
   </si>
   <si>
-    <t>100,250,500,1000,2000,5000,10000,20000,50000,100000,</t>
+    <t>50,100,200,500,1000,2000,5000,10000,50000,100000,</t>
   </si>
   <si>
     <t>阵容上限+1</t>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
   <si>
     <t>id</t>
   </si>
@@ -168,12 +168,33 @@
     <t>终焉议会议案：魔王重命名</t>
   </si>
   <si>
+    <t>ui_research_9</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
+    <t>ui_research_11</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>200,400,800,1600,3200,6400,12800,25600,51200,</t>
+  </si>
+  <si>
+    <t>剑与魔法：征服难度+1</t>
+  </si>
+  <si>
     <t>ui_research_57</t>
   </si>
   <si>
@@ -243,9 +264,6 @@
     <t>ui_research_6</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>100,200,300,400,</t>
   </si>
   <si>
@@ -300,9 +318,6 @@
     <t>ui_research_33</t>
   </si>
   <si>
-    <t>400</t>
-  </si>
-  <si>
     <t>300100001|300100002|300100003|300100004|</t>
   </si>
   <si>
@@ -310,9 +325,6 @@
   </si>
   <si>
     <t>ui_research_34</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>孕育人类x10</t>
@@ -1838,7 +1850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1" style="51"/>
@@ -2274,22 +2286,22 @@
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="G13" s="50">
         <v>100300001</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J13" s="50">
         <v>100300001</v>
@@ -2299,46 +2311,46 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50">
-        <v>100400000</v>
-      </c>
-      <c r="B14" s="50">
-        <v>1</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="50">
-        <v>1</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="50">
-        <v>100400000</v>
-      </c>
-      <c r="I14" s="50" t="s">
+      <c r="A14" s="51">
+        <v>100310112</v>
+      </c>
+      <c r="B14" s="51">
+        <v>1</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="51">
+        <v>9</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="50">
-        <v>100400000</v>
-      </c>
-      <c r="K14" s="50" t="s">
-        <v>55</v>
+      <c r="G14" s="51">
+        <v>100310112</v>
+      </c>
+      <c r="I14" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="51">
+        <v>100310112</v>
+      </c>
+      <c r="K14" s="51" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="50">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B15" s="50">
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D15" s="50">
         <v>1</v>
@@ -2347,33 +2359,30 @@
         <v>27</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G15" s="50">
-        <v>100400001</v>
-      </c>
-      <c r="H15" s="50">
         <v>100400000</v>
       </c>
-      <c r="I15" s="50">
-        <v>100</v>
+      <c r="I15" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="J15" s="50">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="50">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B16" s="50">
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -2382,354 +2391,354 @@
         <v>27</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G16" s="50">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="H16" s="50">
+        <v>100400000</v>
+      </c>
+      <c r="I16" s="50">
+        <v>100</v>
+      </c>
+      <c r="J16" s="50">
         <v>100400001</v>
       </c>
-      <c r="I16" s="50">
-        <v>100</v>
-      </c>
-      <c r="J16" s="50">
-        <v>100401000</v>
-      </c>
       <c r="K16" s="50" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="50">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B17" s="50">
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D17" s="50">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G17" s="50">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="H17" s="50">
+        <v>100400001</v>
+      </c>
+      <c r="I17" s="50">
+        <v>100</v>
+      </c>
+      <c r="J17" s="50">
         <v>100401000</v>
       </c>
-      <c r="I17" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="50">
-        <v>100401001</v>
-      </c>
       <c r="K17" s="50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="50">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B18" s="50">
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D18" s="50">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G18" s="50">
-        <v>100402000</v>
-      </c>
-      <c r="H18" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="I18" s="50">
-        <v>1000</v>
+        <v>100401001</v>
+      </c>
+      <c r="H18" s="50">
+        <v>100401000</v>
+      </c>
+      <c r="I18" s="50" t="s">
+        <v>67</v>
       </c>
       <c r="J18" s="50">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="50">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B19" s="50">
         <v>1</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D19" s="50">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G19" s="50">
-        <v>100402001</v>
-      </c>
-      <c r="H19" s="50">
         <v>100402000</v>
       </c>
-      <c r="I19" s="50" t="s">
-        <v>65</v>
+      <c r="H19" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="50">
+        <v>1000</v>
       </c>
       <c r="J19" s="50">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B20" s="50">
         <v>1</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D20" s="50">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E20" s="50" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G20" s="50">
-        <v>100403000</v>
-      </c>
-      <c r="H20" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="I20" s="50">
-        <v>10000</v>
+        <v>100402001</v>
+      </c>
+      <c r="H20" s="50">
+        <v>100402000</v>
+      </c>
+      <c r="I20" s="50" t="s">
+        <v>72</v>
       </c>
       <c r="J20" s="50">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="50">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B21" s="50">
         <v>1</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D21" s="50">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G21" s="50">
-        <v>100403001</v>
-      </c>
-      <c r="H21" s="50">
         <v>100403000</v>
       </c>
-      <c r="I21" s="50" t="s">
-        <v>70</v>
+      <c r="H21" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="50">
+        <v>10000</v>
       </c>
       <c r="J21" s="50">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="50">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B22" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D22" s="50">
         <v>30</v>
       </c>
-      <c r="E22" s="50">
-        <v>-200</v>
-      </c>
-      <c r="F22" s="50">
-        <v>0</v>
+      <c r="E22" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>74</v>
       </c>
       <c r="G22" s="50">
-        <v>200000001</v>
+        <v>100403001</v>
+      </c>
+      <c r="H22" s="50">
+        <v>100403000</v>
       </c>
       <c r="I22" s="50" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J22" s="50">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="50">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="B23" s="50">
         <v>2</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D23" s="50">
-        <v>4</v>
-      </c>
-      <c r="E23" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="50" t="s">
-        <v>76</v>
+        <v>30</v>
+      </c>
+      <c r="E23" s="50">
+        <v>-200</v>
+      </c>
+      <c r="F23" s="50">
+        <v>0</v>
       </c>
       <c r="G23" s="50">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J23" s="50">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50">
-        <v>300100000</v>
+        <v>200100001</v>
       </c>
       <c r="B24" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D24" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="G24" s="50">
-        <v>300100000</v>
-      </c>
-      <c r="H24" s="50">
-        <v>300200000</v>
-      </c>
-      <c r="I24" s="50">
-        <v>100</v>
+        <v>200100001</v>
+      </c>
+      <c r="I24" s="50" t="s">
+        <v>83</v>
       </c>
       <c r="J24" s="50">
-        <v>300100000</v>
+        <v>200100001</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="B25" s="50">
         <v>3</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D25" s="50">
         <v>1</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G25" s="50">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="H25" s="50">
+        <v>300200000</v>
+      </c>
+      <c r="I25" s="50">
+        <v>100</v>
+      </c>
+      <c r="J25" s="50">
         <v>300100000</v>
       </c>
-      <c r="I25" s="50">
-        <v>100</v>
-      </c>
-      <c r="J25" s="50">
-        <v>300100001</v>
-      </c>
       <c r="K25" s="50" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="50">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="B26" s="50">
         <v>3</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D26" s="50">
         <v>1</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F26" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G26" s="50">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="H26" s="50">
         <v>300100000</v>
@@ -2738,33 +2747,33 @@
         <v>100</v>
       </c>
       <c r="J26" s="50">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="50">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="B27" s="50">
         <v>3</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D27" s="50">
         <v>1</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F27" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G27" s="50">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="H27" s="50">
         <v>300100000</v>
@@ -2773,33 +2782,33 @@
         <v>100</v>
       </c>
       <c r="J27" s="50">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="50">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="B28" s="50">
         <v>3</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D28" s="50">
         <v>1</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F28" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G28" s="50">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="H28" s="50">
         <v>300100000</v>
@@ -2808,214 +2817,214 @@
         <v>100</v>
       </c>
       <c r="J28" s="50">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="50">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="B29" s="50">
         <v>3</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="G29" s="50">
-        <v>300100101</v>
-      </c>
-      <c r="H29" s="50" t="s">
-        <v>96</v>
+        <v>300100004</v>
+      </c>
+      <c r="H29" s="50">
+        <v>300100000</v>
       </c>
       <c r="I29" s="50">
         <v>100</v>
       </c>
       <c r="J29" s="50">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="50">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="B30" s="50">
         <v>3</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D30" s="50">
         <v>1</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="G30" s="50">
-        <v>300100102</v>
-      </c>
-      <c r="H30" s="50">
         <v>300100101</v>
       </c>
+      <c r="H30" s="50" t="s">
+        <v>101</v>
+      </c>
       <c r="I30" s="50">
         <v>100</v>
       </c>
       <c r="J30" s="50">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="50">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="B31" s="50">
         <v>3</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G31" s="50">
-        <v>300100201</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>101</v>
+        <v>300100102</v>
+      </c>
+      <c r="H31" s="50">
+        <v>300100101</v>
       </c>
       <c r="I31" s="50">
         <v>100</v>
       </c>
       <c r="J31" s="50">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="B32" s="50">
         <v>3</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D32" s="50">
         <v>1</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>27</v>
       </c>
       <c r="G32" s="50">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="H32" s="50" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I32" s="50">
         <v>100</v>
       </c>
       <c r="J32" s="50">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="50">
-        <v>300200000</v>
+        <v>300100301</v>
       </c>
       <c r="B33" s="50">
         <v>3</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D33" s="50">
         <v>1</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="F33" s="50" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="G33" s="50">
-        <v>300200000</v>
-      </c>
-      <c r="I33" s="50" t="s">
-        <v>54</v>
+        <v>300100301</v>
+      </c>
+      <c r="H33" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="I33" s="50">
+        <v>100</v>
       </c>
       <c r="J33" s="50">
-        <v>300200000</v>
+        <v>300100301</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="50">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B34" s="50">
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D34" s="50">
         <v>1</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="F34" s="50" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="G34" s="50">
-        <v>300200001</v>
-      </c>
-      <c r="H34" s="50">
         <v>300200000</v>
       </c>
       <c r="I34" s="50" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="J34" s="50">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="K34" s="50" t="s">
         <v>111</v>
@@ -3023,13 +3032,13 @@
     </row>
     <row r="35">
       <c r="A35" s="50">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B35" s="50">
         <v>3</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D35" s="50">
         <v>1</v>
@@ -3038,80 +3047,80 @@
         <v>112</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="G35" s="50">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="H35" s="50">
         <v>300200000</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="J35" s="50">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="50">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B36" s="50">
         <v>3</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D36" s="50">
         <v>1</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F36" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G36" s="50">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="H36" s="50">
         <v>300200000</v>
       </c>
       <c r="I36" s="50" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J36" s="50">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="50">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B37" s="50">
         <v>3</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D37" s="50">
         <v>1</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F37" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G37" s="50">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="H37" s="50">
         <v>300200000</v>
@@ -3120,243 +3129,243 @@
         <v>28</v>
       </c>
       <c r="J37" s="50">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="50">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B38" s="50">
         <v>3</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D38" s="50">
         <v>1</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="G38" s="50">
-        <v>300200101</v>
-      </c>
-      <c r="H38" s="50" t="s">
-        <v>118</v>
+        <v>300200004</v>
+      </c>
+      <c r="H38" s="50">
+        <v>300200000</v>
       </c>
       <c r="I38" s="50" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="J38" s="50">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B39" s="50">
         <v>3</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D39" s="50">
         <v>1</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="G39" s="50">
-        <v>300200102</v>
-      </c>
-      <c r="H39" s="50">
         <v>300200101</v>
       </c>
-      <c r="I39" s="50">
-        <v>100</v>
+      <c r="H39" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="I39" s="50" t="s">
+        <v>123</v>
       </c>
       <c r="J39" s="50">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="50">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="B40" s="50">
         <v>3</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D40" s="50">
         <v>1</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="F40" s="50" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G40" s="50">
-        <v>300200201</v>
-      </c>
-      <c r="H40" s="50" t="s">
-        <v>122</v>
+        <v>300200102</v>
+      </c>
+      <c r="H40" s="50">
+        <v>300200101</v>
       </c>
       <c r="I40" s="50">
         <v>100</v>
       </c>
       <c r="J40" s="50">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="50">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="B41" s="50">
         <v>3</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D41" s="50">
         <v>1</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>27</v>
       </c>
       <c r="G41" s="50">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I41" s="50">
         <v>100</v>
       </c>
       <c r="J41" s="50">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="50">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="B42" s="50">
         <v>3</v>
       </c>
       <c r="C42" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="50">
+        <v>1</v>
+      </c>
+      <c r="E42" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G42" s="50">
+        <v>300200301</v>
+      </c>
+      <c r="H42" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="D42" s="50">
-        <v>1</v>
-      </c>
-      <c r="E42" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="F42" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="G42" s="50">
-        <v>300300000</v>
-      </c>
-      <c r="H42" s="50">
-        <v>300200000</v>
-      </c>
       <c r="I42" s="50">
         <v>100</v>
       </c>
       <c r="J42" s="50">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="50">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="B43" s="50">
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G43" s="50">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="H43" s="50">
+        <v>300200000</v>
+      </c>
+      <c r="I43" s="50">
+        <v>100</v>
+      </c>
+      <c r="J43" s="50">
         <v>300300000</v>
       </c>
-      <c r="I43" s="50">
-        <v>100</v>
-      </c>
-      <c r="J43" s="50">
-        <v>300300001</v>
-      </c>
       <c r="K43" s="50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="50">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="B44" s="50">
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F44" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G44" s="50">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="H44" s="50">
         <v>300300000</v>
@@ -3365,33 +3374,33 @@
         <v>100</v>
       </c>
       <c r="J44" s="50">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="50">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="B45" s="50">
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G45" s="50">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="H45" s="50">
         <v>300300000</v>
@@ -3400,33 +3409,33 @@
         <v>100</v>
       </c>
       <c r="J45" s="50">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="50">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="B46" s="50">
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F46" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G46" s="50">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="H46" s="50">
         <v>300300000</v>
@@ -3435,243 +3444,243 @@
         <v>100</v>
       </c>
       <c r="J46" s="50">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="50">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="B47" s="50">
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="F47" s="50" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="G47" s="50">
-        <v>300300101</v>
-      </c>
-      <c r="H47" s="50" t="s">
-        <v>139</v>
+        <v>300300004</v>
+      </c>
+      <c r="H47" s="50">
+        <v>300300000</v>
       </c>
       <c r="I47" s="50">
         <v>100</v>
       </c>
       <c r="J47" s="50">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="50">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="B48" s="50">
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="G48" s="50">
-        <v>300300102</v>
-      </c>
-      <c r="H48" s="50">
         <v>300300101</v>
       </c>
+      <c r="H48" s="50" t="s">
+        <v>143</v>
+      </c>
       <c r="I48" s="50">
         <v>100</v>
       </c>
       <c r="J48" s="50">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="50">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="B49" s="50">
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G49" s="50">
-        <v>300300201</v>
-      </c>
-      <c r="H49" s="50" t="s">
-        <v>142</v>
+        <v>300300102</v>
+      </c>
+      <c r="H49" s="50">
+        <v>300300101</v>
       </c>
       <c r="I49" s="50">
         <v>100</v>
       </c>
       <c r="J49" s="50">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="50">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="B50" s="50">
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>27</v>
       </c>
       <c r="G50" s="50">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I50" s="50">
         <v>100</v>
       </c>
       <c r="J50" s="50">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="50">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="B51" s="50">
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="50">
+        <v>1</v>
+      </c>
+      <c r="E51" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="F51" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51" s="50">
+        <v>300300301</v>
+      </c>
+      <c r="H51" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="D51" s="50">
-        <v>1</v>
-      </c>
-      <c r="E51" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="F51" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="G51" s="50">
-        <v>300400000</v>
-      </c>
-      <c r="H51" s="50">
-        <v>300600000</v>
-      </c>
       <c r="I51" s="50">
         <v>100</v>
       </c>
       <c r="J51" s="50">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="50">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="B52" s="50">
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F52" s="50" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G52" s="50">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="H52" s="50">
+        <v>300600000</v>
+      </c>
+      <c r="I52" s="50">
+        <v>100</v>
+      </c>
+      <c r="J52" s="50">
         <v>300400000</v>
       </c>
-      <c r="I52" s="50">
-        <v>100</v>
-      </c>
-      <c r="J52" s="50">
-        <v>300400001</v>
-      </c>
       <c r="K52" s="50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="50">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="B53" s="50">
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F53" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G53" s="50">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="H53" s="50">
         <v>300400000</v>
@@ -3680,33 +3689,33 @@
         <v>100</v>
       </c>
       <c r="J53" s="50">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="50">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="B54" s="50">
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F54" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G54" s="50">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="H54" s="50">
         <v>300400000</v>
@@ -3715,33 +3724,33 @@
         <v>100</v>
       </c>
       <c r="J54" s="50">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="50">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="B55" s="50">
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F55" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G55" s="50">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="H55" s="50">
         <v>300400000</v>
@@ -3750,33 +3759,33 @@
         <v>100</v>
       </c>
       <c r="J55" s="50">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="50">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="B56" s="50">
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G56" s="50">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="H56" s="50">
         <v>300400000</v>
@@ -3785,243 +3794,243 @@
         <v>100</v>
       </c>
       <c r="J56" s="50">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="50">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="B57" s="50">
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="G57" s="50">
-        <v>300400101</v>
-      </c>
-      <c r="H57" s="50" t="s">
-        <v>161</v>
+        <v>300400005</v>
+      </c>
+      <c r="H57" s="50">
+        <v>300400000</v>
       </c>
       <c r="I57" s="50">
         <v>100</v>
       </c>
       <c r="J57" s="50">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A58" s="50">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="B58" s="50">
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F58" s="50" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="G58" s="50">
-        <v>300400102</v>
-      </c>
-      <c r="H58" s="50">
         <v>300400101</v>
       </c>
+      <c r="H58" s="50" t="s">
+        <v>165</v>
+      </c>
       <c r="I58" s="50">
         <v>100</v>
       </c>
       <c r="J58" s="50">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A59" s="50">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="B59" s="50">
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G59" s="50">
-        <v>300400201</v>
-      </c>
-      <c r="H59" s="50" t="s">
-        <v>164</v>
+        <v>300400102</v>
+      </c>
+      <c r="H59" s="50">
+        <v>300400101</v>
       </c>
       <c r="I59" s="50">
         <v>100</v>
       </c>
       <c r="J59" s="50">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A60" s="50">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="B60" s="50">
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>27</v>
       </c>
       <c r="G60" s="50">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I60" s="50">
         <v>100</v>
       </c>
       <c r="J60" s="50">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A61" s="50">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="B61" s="50">
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="F61" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="50">
+        <v>300400301</v>
+      </c>
+      <c r="H61" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="F61" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="G61" s="50">
-        <v>300500000</v>
-      </c>
-      <c r="H61" s="50">
-        <v>300700000</v>
-      </c>
       <c r="I61" s="50">
         <v>100</v>
       </c>
       <c r="J61" s="50">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A62" s="50">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="B62" s="50">
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F62" s="50" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G62" s="50">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="H62" s="50">
+        <v>300700000</v>
+      </c>
+      <c r="I62" s="50">
+        <v>100</v>
+      </c>
+      <c r="J62" s="50">
         <v>300500000</v>
       </c>
-      <c r="I62" s="50">
-        <v>100</v>
-      </c>
-      <c r="J62" s="50">
-        <v>300500001</v>
-      </c>
       <c r="K62" s="50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A63" s="50">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="B63" s="50">
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G63" s="50">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="H63" s="50">
         <v>300500000</v>
@@ -4030,33 +4039,33 @@
         <v>100</v>
       </c>
       <c r="J63" s="50">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A64" s="50">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="B64" s="50">
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F64" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G64" s="50">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="H64" s="50">
         <v>300500000</v>
@@ -4065,33 +4074,33 @@
         <v>100</v>
       </c>
       <c r="J64" s="50">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="50">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="B65" s="50">
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G65" s="50">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="H65" s="50">
         <v>300500000</v>
@@ -4100,243 +4109,243 @@
         <v>100</v>
       </c>
       <c r="J65" s="50">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="50">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="B66" s="50">
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F66" s="50" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="G66" s="50">
-        <v>300500101</v>
-      </c>
-      <c r="H66" s="50" t="s">
-        <v>178</v>
+        <v>300500004</v>
+      </c>
+      <c r="H66" s="50">
+        <v>300500000</v>
       </c>
       <c r="I66" s="50">
         <v>100</v>
       </c>
       <c r="J66" s="50">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A67" s="50">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="B67" s="50">
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="G67" s="50">
-        <v>300500102</v>
-      </c>
-      <c r="H67" s="50">
         <v>300500101</v>
       </c>
+      <c r="H67" s="50" t="s">
+        <v>182</v>
+      </c>
       <c r="I67" s="50">
         <v>100</v>
       </c>
       <c r="J67" s="50">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A68" s="50">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="B68" s="50">
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F68" s="50" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G68" s="50">
-        <v>300500201</v>
-      </c>
-      <c r="H68" s="50" t="s">
-        <v>181</v>
+        <v>300500102</v>
+      </c>
+      <c r="H68" s="50">
+        <v>300500101</v>
       </c>
       <c r="I68" s="50">
         <v>100</v>
       </c>
       <c r="J68" s="50">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A69" s="50">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="B69" s="50">
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>27</v>
       </c>
       <c r="G69" s="50">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I69" s="50">
         <v>100</v>
       </c>
       <c r="J69" s="50">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A70" s="50">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="B70" s="50">
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="D70" s="50">
+        <v>1</v>
+      </c>
+      <c r="E70" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="F70" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G70" s="50">
+        <v>300500301</v>
+      </c>
+      <c r="H70" s="50" t="s">
         <v>185</v>
       </c>
-      <c r="D70" s="50">
-        <v>1</v>
-      </c>
-      <c r="E70" s="50" t="s">
-        <v>186</v>
-      </c>
-      <c r="F70" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="G70" s="50">
-        <v>300600000</v>
-      </c>
-      <c r="H70" s="50">
-        <v>300300000</v>
-      </c>
       <c r="I70" s="50">
         <v>100</v>
       </c>
       <c r="J70" s="50">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A71" s="50">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="B71" s="50">
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G71" s="50">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="H71" s="50">
+        <v>300300000</v>
+      </c>
+      <c r="I71" s="50">
+        <v>100</v>
+      </c>
+      <c r="J71" s="50">
         <v>300600000</v>
       </c>
-      <c r="I71" s="50">
-        <v>100</v>
-      </c>
-      <c r="J71" s="50">
-        <v>300600001</v>
-      </c>
       <c r="K71" s="50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A72" s="50">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="B72" s="50">
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G72" s="50">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="H72" s="50">
         <v>300600000</v>
@@ -4345,33 +4354,33 @@
         <v>100</v>
       </c>
       <c r="J72" s="50">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A73" s="50">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="B73" s="50">
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G73" s="50">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="H73" s="50">
         <v>300600000</v>
@@ -4380,33 +4389,33 @@
         <v>100</v>
       </c>
       <c r="J73" s="50">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A74" s="50">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="B74" s="50">
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G74" s="50">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="H74" s="50">
         <v>300600000</v>
@@ -4415,33 +4424,33 @@
         <v>100</v>
       </c>
       <c r="J74" s="50">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="50">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="B75" s="50">
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G75" s="50">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="H75" s="50">
         <v>300600000</v>
@@ -4450,243 +4459,243 @@
         <v>100</v>
       </c>
       <c r="J75" s="50">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="50">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="B76" s="50">
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="F76" s="50" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="G76" s="50">
-        <v>300600101</v>
-      </c>
-      <c r="H76" s="50" t="s">
-        <v>198</v>
+        <v>300600005</v>
+      </c>
+      <c r="H76" s="50">
+        <v>300600000</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
       </c>
       <c r="J76" s="50">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="50">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="B77" s="50">
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="G77" s="50">
-        <v>300600102</v>
-      </c>
-      <c r="H77" s="50">
         <v>300600101</v>
       </c>
+      <c r="H77" s="50" t="s">
+        <v>202</v>
+      </c>
       <c r="I77" s="50">
         <v>100</v>
       </c>
       <c r="J77" s="50">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A78" s="50">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="B78" s="50">
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G78" s="50">
-        <v>300600201</v>
-      </c>
-      <c r="H78" s="50" t="s">
-        <v>201</v>
+        <v>300600102</v>
+      </c>
+      <c r="H78" s="50">
+        <v>300600101</v>
       </c>
       <c r="I78" s="50">
         <v>100</v>
       </c>
       <c r="J78" s="50">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A79" s="50">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="B79" s="50">
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>27</v>
       </c>
       <c r="G79" s="50">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I79" s="50">
         <v>100</v>
       </c>
       <c r="J79" s="50">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A80" s="50">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="B80" s="50">
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>204</v>
+        <v>107</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="F80" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G80" s="50">
+        <v>300600301</v>
+      </c>
+      <c r="H80" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="F80" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="G80" s="50">
-        <v>300700000</v>
-      </c>
-      <c r="H80" s="50">
-        <v>300100000</v>
-      </c>
       <c r="I80" s="50">
         <v>100</v>
       </c>
       <c r="J80" s="50">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A81" s="50">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="B81" s="50">
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F81" s="50" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G81" s="50">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="H81" s="50">
+        <v>300100000</v>
+      </c>
+      <c r="I81" s="50">
+        <v>100</v>
+      </c>
+      <c r="J81" s="50">
         <v>300700000</v>
       </c>
-      <c r="I81" s="50">
-        <v>100</v>
-      </c>
-      <c r="J81" s="50">
-        <v>300700001</v>
-      </c>
       <c r="K81" s="50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A82" s="50">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="B82" s="50">
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G82" s="50">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="H82" s="50">
         <v>300700000</v>
@@ -4695,33 +4704,33 @@
         <v>100</v>
       </c>
       <c r="J82" s="50">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A83" s="50">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="B83" s="50">
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G83" s="50">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="H83" s="50">
         <v>300700000</v>
@@ -4730,33 +4739,33 @@
         <v>100</v>
       </c>
       <c r="J83" s="50">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="50">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="B84" s="50">
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>28</v>
       </c>
       <c r="G84" s="50">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="H84" s="50">
         <v>300700000</v>
@@ -4765,182 +4774,217 @@
         <v>100</v>
       </c>
       <c r="J84" s="50">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="50">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="B85" s="50">
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F85" s="50" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="G85" s="50">
-        <v>300700101</v>
-      </c>
-      <c r="H85" s="50" t="s">
-        <v>215</v>
+        <v>300700004</v>
+      </c>
+      <c r="H85" s="50">
+        <v>300700000</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
       </c>
       <c r="J85" s="50">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="50">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="B86" s="50">
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="G86" s="50">
-        <v>300700102</v>
-      </c>
-      <c r="H86" s="50">
         <v>300700101</v>
       </c>
+      <c r="H86" s="50" t="s">
+        <v>219</v>
+      </c>
       <c r="I86" s="50">
         <v>100</v>
       </c>
       <c r="J86" s="50">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="50">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="B87" s="50">
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G87" s="50">
-        <v>300700201</v>
-      </c>
-      <c r="H87" s="50" t="s">
-        <v>218</v>
+        <v>300700102</v>
+      </c>
+      <c r="H87" s="50">
+        <v>300700101</v>
       </c>
       <c r="I87" s="50">
         <v>100</v>
       </c>
       <c r="J87" s="50">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="50">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="B88" s="50">
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>103</v>
+        <v>208</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>27</v>
       </c>
       <c r="G88" s="50">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I88" s="50">
         <v>100</v>
       </c>
       <c r="J88" s="50">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="50">
+        <v>300700301</v>
+      </c>
+      <c r="B89" s="50">
+        <v>3</v>
+      </c>
+      <c r="C89" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="D89" s="50">
+        <v>1</v>
+      </c>
+      <c r="E89" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="F89" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G89" s="50">
+        <v>300700301</v>
+      </c>
+      <c r="H89" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="I89" s="50">
+        <v>100</v>
+      </c>
+      <c r="J89" s="50">
+        <v>300700301</v>
+      </c>
+      <c r="K89" s="50" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="50">
         <v>100500001</v>
       </c>
-      <c r="B89" s="50">
-        <v>1</v>
-      </c>
-      <c r="C89" s="50" t="s">
-        <v>222</v>
-      </c>
-      <c r="D89" s="50">
-        <v>1</v>
-      </c>
-      <c r="E89" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="F89" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="G89" s="50">
+      <c r="B90" s="50">
+        <v>1</v>
+      </c>
+      <c r="C90" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="D90" s="50">
+        <v>1</v>
+      </c>
+      <c r="E90" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F90" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G90" s="50">
         <v>100500001</v>
       </c>
-      <c r="I89" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="J89" s="50">
+      <c r="I90" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="J90" s="50">
         <v>100500001</v>
       </c>
-      <c r="K89" s="50" t="s">
-        <v>223</v>
+      <c r="K90" s="50" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="230">
   <si>
     <t>id</t>
   </si>
@@ -99,271 +99,277 @@
     <t>-200</t>
   </si>
   <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>开启进阶设施</t>
+  </si>
+  <si>
+    <t>ui_research_2</t>
+  </si>
+  <si>
+    <t>-350</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>100,200,300,400,500,</t>
+  </si>
+  <si>
+    <t>进阶设施+1</t>
+  </si>
+  <si>
+    <t>ui_research_3</t>
+  </si>
+  <si>
     <t>200</t>
   </si>
   <si>
-    <t>开启进阶设施</t>
-  </si>
-  <si>
-    <t>ui_research_2</t>
-  </si>
-  <si>
-    <t>-350</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>100,200,300,400,500,</t>
-  </si>
-  <si>
-    <t>进阶设施+1</t>
-  </si>
-  <si>
-    <t>ui_research_3</t>
+    <t>100</t>
+  </si>
+  <si>
+    <t>开启献祭设施</t>
+  </si>
+  <si>
+    <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
+  </si>
+  <si>
+    <t>献祭祭品数量+1</t>
+  </si>
+  <si>
+    <t>100100001</t>
+  </si>
+  <si>
+    <t>100,500,1000,5000,10000,20000,30000,40000,50000,100000</t>
+  </si>
+  <si>
+    <t>献祭失败保底概率提升</t>
+  </si>
+  <si>
+    <t>不同魔物献祭成功率提升</t>
+  </si>
+  <si>
+    <t>ui_research_7</t>
+  </si>
+  <si>
+    <t>开启终焉议会</t>
+  </si>
+  <si>
+    <t>ui_research_59</t>
+  </si>
+  <si>
+    <t>-400</t>
+  </si>
+  <si>
+    <t>终焉议会议案：魔物重命名</t>
+  </si>
+  <si>
+    <t>-600</t>
+  </si>
+  <si>
+    <t>终焉议会议案：魔王重命名</t>
+  </si>
+  <si>
+    <t>ui_research_9</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>ui_research_11</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>200,400,800,1600,3200,6400,12800,25600,51200,</t>
+  </si>
+  <si>
+    <t>剑与魔法：征服难度+1</t>
+  </si>
+  <si>
+    <t>ui_research_57</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>开启孕育功能</t>
+  </si>
+  <si>
+    <t>孕育可跳过</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：R</t>
+  </si>
+  <si>
+    <t>-396</t>
+  </si>
+  <si>
+    <t>-596</t>
+  </si>
+  <si>
+    <t>100*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：R 概率+1%</t>
+  </si>
+  <si>
+    <t>-800</t>
+  </si>
+  <si>
+    <t>100401000,100401001,</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：SR</t>
+  </si>
+  <si>
+    <t>1000*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：SR 概率+1%</t>
+  </si>
+  <si>
+    <t>-1000</t>
+  </si>
+  <si>
+    <t>100402000,100402001,</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：SSR</t>
+  </si>
+  <si>
+    <t>10000*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：SSR 概率+1%</t>
+  </si>
+  <si>
+    <t>ui_research_5</t>
+  </si>
+  <si>
+    <t>50,100,200,500,1000,2000,5000,10000,50000,100000,</t>
+  </si>
+  <si>
+    <t>阵容上限+1</t>
+  </si>
+  <si>
+    <t>ui_research_6</t>
+  </si>
+  <si>
+    <t>100,200,300,400,</t>
+  </si>
+  <si>
+    <t>解锁第二阵容</t>
+  </si>
+  <si>
+    <t>ui_research_36</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>解锁种族：人类</t>
+  </si>
+  <si>
+    <t>ui_research_43</t>
+  </si>
+  <si>
+    <t>575</t>
+  </si>
+  <si>
+    <t>解锁职业：人类战士</t>
+  </si>
+  <si>
+    <t>ui_research_42</t>
+  </si>
+  <si>
+    <t>725</t>
+  </si>
+  <si>
+    <t>解锁职业：人类弓箭手</t>
+  </si>
+  <si>
+    <t>ui_research_48</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>解锁职业：人类魔法师（火）</t>
+  </si>
+  <si>
+    <t>ui_research_47</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>解锁职业：人类魔法师（冰）</t>
+  </si>
+  <si>
+    <t>ui_research_33</t>
+  </si>
+  <si>
+    <t>300100001|300100002|300100003|300100004|</t>
+  </si>
+  <si>
+    <t>孕育人类x5</t>
+  </si>
+  <si>
+    <t>ui_research_34</t>
+  </si>
+  <si>
+    <t>孕育人类x10</t>
+  </si>
+  <si>
+    <t>100200001,300100000,</t>
+  </si>
+  <si>
+    <t>可转生为人类</t>
+  </si>
+  <si>
+    <t>ui_research_58</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>奖励-可获取人类装备</t>
+  </si>
+  <si>
+    <t>ui_research_35</t>
+  </si>
+  <si>
+    <t>解锁种族：骷髅</t>
+  </si>
+  <si>
+    <t>-223</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>解锁职业：骷髅战士</t>
+  </si>
+  <si>
+    <t>-75</t>
   </si>
   <si>
     <t>50</t>
-  </si>
-  <si>
-    <t>开启献祭设施</t>
-  </si>
-  <si>
-    <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
-  </si>
-  <si>
-    <t>献祭祭品数量+1</t>
-  </si>
-  <si>
-    <t>100100001</t>
-  </si>
-  <si>
-    <t>100,500,1000,5000,10000,20000,30000,40000,50000,100000</t>
-  </si>
-  <si>
-    <t>献祭失败保底概率提升</t>
-  </si>
-  <si>
-    <t>不同魔物献祭成功率提升</t>
-  </si>
-  <si>
-    <t>ui_research_7</t>
-  </si>
-  <si>
-    <t>开启终焉议会</t>
-  </si>
-  <si>
-    <t>ui_research_59</t>
-  </si>
-  <si>
-    <t>-400</t>
-  </si>
-  <si>
-    <t>终焉议会议案：魔物重命名</t>
-  </si>
-  <si>
-    <t>-600</t>
-  </si>
-  <si>
-    <t>终焉议会议案：魔王重命名</t>
-  </si>
-  <si>
-    <t>ui_research_9</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>ui_research_11</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>200,400,800,1600,3200,6400,12800,25600,51200,</t>
-  </si>
-  <si>
-    <t>剑与魔法：征服难度+1</t>
-  </si>
-  <si>
-    <t>ui_research_57</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>开启孕育功能</t>
-  </si>
-  <si>
-    <t>孕育可跳过</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：R</t>
-  </si>
-  <si>
-    <t>-396</t>
-  </si>
-  <si>
-    <t>-596</t>
-  </si>
-  <si>
-    <t>100*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：R 概率+1%</t>
-  </si>
-  <si>
-    <t>-800</t>
-  </si>
-  <si>
-    <t>100401000,100401001,</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：SR</t>
-  </si>
-  <si>
-    <t>1000*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：SR 概率+1%</t>
-  </si>
-  <si>
-    <t>-1000</t>
-  </si>
-  <si>
-    <t>100402000,100402001,</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：SSR</t>
-  </si>
-  <si>
-    <t>10000*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：SSR 概率+1%</t>
-  </si>
-  <si>
-    <t>ui_research_5</t>
-  </si>
-  <si>
-    <t>50,100,200,500,1000,2000,5000,10000,50000,100000,</t>
-  </si>
-  <si>
-    <t>阵容上限+1</t>
-  </si>
-  <si>
-    <t>ui_research_6</t>
-  </si>
-  <si>
-    <t>100,200,300,400,</t>
-  </si>
-  <si>
-    <t>解锁第二阵容</t>
-  </si>
-  <si>
-    <t>ui_research_36</t>
-  </si>
-  <si>
-    <t>800</t>
-  </si>
-  <si>
-    <t>解锁种族：人类</t>
-  </si>
-  <si>
-    <t>ui_research_43</t>
-  </si>
-  <si>
-    <t>575</t>
-  </si>
-  <si>
-    <t>解锁职业：人类战士</t>
-  </si>
-  <si>
-    <t>ui_research_42</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>解锁职业：人类弓箭手</t>
-  </si>
-  <si>
-    <t>ui_research_48</t>
-  </si>
-  <si>
-    <t>875</t>
-  </si>
-  <si>
-    <t>解锁职业：人类魔法师（火）</t>
-  </si>
-  <si>
-    <t>ui_research_47</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>解锁职业：人类魔法师（冰）</t>
-  </si>
-  <si>
-    <t>ui_research_33</t>
-  </si>
-  <si>
-    <t>300100001|300100002|300100003|300100004|</t>
-  </si>
-  <si>
-    <t>孕育人类x5</t>
-  </si>
-  <si>
-    <t>ui_research_34</t>
-  </si>
-  <si>
-    <t>孕育人类x10</t>
-  </si>
-  <si>
-    <t>100200001,300100000,</t>
-  </si>
-  <si>
-    <t>可转生为人类</t>
-  </si>
-  <si>
-    <t>ui_research_58</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>奖励-可获取人类装备</t>
-  </si>
-  <si>
-    <t>ui_research_35</t>
-  </si>
-  <si>
-    <t>解锁种族：骷髅</t>
-  </si>
-  <si>
-    <t>-223</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>解锁职业：骷髅战士</t>
-  </si>
-  <si>
-    <t>-75</t>
   </si>
   <si>
     <t>解锁职业：骷髅投手</t>
@@ -1994,14 +2000,14 @@
       <c r="G4" s="50">
         <v>100000000</v>
       </c>
-      <c r="I4" s="50">
-        <v>100</v>
+      <c r="I4" s="50" t="s">
+        <v>29</v>
       </c>
       <c r="J4" s="50">
         <v>100000000</v>
       </c>
       <c r="K4" s="50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -2012,16 +2018,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="50">
         <v>5</v>
       </c>
       <c r="E5" s="50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="50">
         <v>100000001</v>
@@ -2030,13 +2036,13 @@
         <v>100000000</v>
       </c>
       <c r="I5" s="50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J5" s="50">
         <v>100000001</v>
       </c>
       <c r="K5" s="50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -2047,28 +2053,28 @@
         <v>1</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="50">
         <v>1</v>
       </c>
       <c r="E6" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F6" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G6" s="50">
         <v>100100001</v>
       </c>
       <c r="I6" s="50" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J6" s="50">
         <v>100100001</v>
       </c>
       <c r="K6" s="50" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -2079,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="50">
         <v>10</v>
@@ -2097,13 +2103,13 @@
         <v>100100001</v>
       </c>
       <c r="I7" s="50" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J7" s="50">
         <v>100100002</v>
       </c>
       <c r="K7" s="50" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -2114,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="51">
         <v>10</v>
@@ -2123,22 +2129,22 @@
         <v>350</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G8" s="51">
         <v>100100003</v>
       </c>
       <c r="H8" s="51" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I8" s="51" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J8" s="51">
         <v>100100003</v>
       </c>
       <c r="K8" s="51" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -2149,31 +2155,31 @@
         <v>1</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="51">
         <v>10</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="51">
         <v>100100004</v>
       </c>
       <c r="H9" s="51" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I9" s="51" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J9" s="51">
         <v>100100004</v>
       </c>
       <c r="K9" s="51" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -2184,13 +2190,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" s="50">
         <v>1</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F10" s="50" t="s">
         <v>27</v>
@@ -2205,7 +2211,7 @@
         <v>100200001</v>
       </c>
       <c r="K10" s="50" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -2216,16 +2222,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" s="50">
         <v>1</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G11" s="50">
         <v>100200002</v>
@@ -2240,7 +2246,7 @@
         <v>100200002</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -2251,16 +2257,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="50">
         <v>1</v>
       </c>
       <c r="E12" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F12" s="50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G12" s="50">
         <v>100200003</v>
@@ -2275,7 +2281,7 @@
         <v>100200003</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -2286,28 +2292,28 @@
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G13" s="50">
         <v>100300001</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="J13" s="50">
         <v>100300001</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -2318,28 +2324,28 @@
         <v>1</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="51">
         <v>9</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G14" s="51">
         <v>100310112</v>
       </c>
       <c r="I14" s="51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J14" s="51">
         <v>100310112</v>
       </c>
       <c r="K14" s="51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2350,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" s="50">
         <v>1</v>
@@ -2365,13 +2371,13 @@
         <v>100400000</v>
       </c>
       <c r="I15" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J15" s="50">
         <v>100400000</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -2382,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -2391,7 +2397,7 @@
         <v>27</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G16" s="50">
         <v>100400001</v>
@@ -2406,7 +2412,7 @@
         <v>100400001</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -2417,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" s="50">
         <v>1</v>
@@ -2426,7 +2432,7 @@
         <v>27</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G17" s="50">
         <v>100401000</v>
@@ -2441,7 +2447,7 @@
         <v>100401000</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -2452,16 +2458,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="50">
         <v>50</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18" s="50">
         <v>100401001</v>
@@ -2470,13 +2476,13 @@
         <v>100401000</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J18" s="50">
         <v>100401001</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
@@ -2487,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" s="50">
         <v>1</v>
@@ -2496,13 +2502,13 @@
         <v>27</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="50">
         <v>100402000</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I19" s="50">
         <v>1000</v>
@@ -2511,7 +2517,7 @@
         <v>100402000</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -2522,16 +2528,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="50">
         <v>40</v>
       </c>
       <c r="E20" s="50" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="50">
         <v>100402001</v>
@@ -2540,13 +2546,13 @@
         <v>100402000</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J20" s="50">
         <v>100402001</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
@@ -2557,7 +2563,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D21" s="50">
         <v>1</v>
@@ -2566,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" s="50">
         <v>100403000</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I21" s="50">
         <v>10000</v>
@@ -2581,7 +2587,7 @@
         <v>100403000</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -2592,16 +2598,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D22" s="50">
         <v>30</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G22" s="50">
         <v>100403001</v>
@@ -2610,13 +2616,13 @@
         <v>100403000</v>
       </c>
       <c r="I22" s="50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J22" s="50">
         <v>100403001</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
@@ -2627,7 +2633,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" s="50">
         <v>30</v>
@@ -2642,13 +2648,13 @@
         <v>200000001</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J23" s="50">
         <v>200000001</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
@@ -2659,28 +2665,28 @@
         <v>2</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D24" s="50">
         <v>4</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G24" s="50">
         <v>200100001</v>
       </c>
       <c r="I24" s="50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J24" s="50">
         <v>200100001</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
@@ -2691,16 +2697,16 @@
         <v>3</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D25" s="50">
         <v>1</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G25" s="50">
         <v>300100000</v>
@@ -2715,7 +2721,7 @@
         <v>300100000</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">
@@ -2726,16 +2732,16 @@
         <v>3</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D26" s="50">
         <v>1</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G26" s="50">
         <v>300100001</v>
@@ -2750,7 +2756,7 @@
         <v>300100001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
@@ -2761,16 +2767,16 @@
         <v>3</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D27" s="50">
         <v>1</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G27" s="50">
         <v>300100002</v>
@@ -2785,7 +2791,7 @@
         <v>300100002</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
@@ -2796,16 +2802,16 @@
         <v>3</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D28" s="50">
         <v>1</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G28" s="50">
         <v>300100003</v>
@@ -2820,7 +2826,7 @@
         <v>300100003</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
@@ -2831,16 +2837,16 @@
         <v>3</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G29" s="50">
         <v>300100004</v>
@@ -2855,7 +2861,7 @@
         <v>300100004</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -2866,22 +2872,22 @@
         <v>3</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D30" s="50">
         <v>1</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G30" s="50">
         <v>300100101</v>
       </c>
       <c r="H30" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="50">
         <v>100</v>
@@ -2890,7 +2896,7 @@
         <v>300100101</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31">
@@ -2901,16 +2907,16 @@
         <v>3</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G31" s="50">
         <v>300100102</v>
@@ -2925,7 +2931,7 @@
         <v>300100102</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
@@ -2936,13 +2942,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" s="50">
         <v>1</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>27</v>
@@ -2951,7 +2957,7 @@
         <v>300100201</v>
       </c>
       <c r="H32" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I32" s="50">
         <v>100</v>
@@ -2960,7 +2966,7 @@
         <v>300100201</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33">
@@ -2971,13 +2977,13 @@
         <v>3</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D33" s="50">
         <v>1</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F33" s="50" t="s">
         <v>27</v>
@@ -2986,7 +2992,7 @@
         <v>300100301</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I33" s="50">
         <v>100</v>
@@ -2995,7 +3001,7 @@
         <v>300100301</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34">
@@ -3006,28 +3012,28 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D34" s="50">
         <v>1</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F34" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G34" s="50">
         <v>300200000</v>
       </c>
       <c r="I34" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J34" s="50">
         <v>300200000</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
@@ -3038,16 +3044,16 @@
         <v>3</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D35" s="50">
         <v>1</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G35" s="50">
         <v>300200001</v>
@@ -3056,13 +3062,13 @@
         <v>300200000</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J35" s="50">
         <v>300200001</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36">
@@ -3073,16 +3079,16 @@
         <v>3</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D36" s="50">
         <v>1</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F36" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G36" s="50">
         <v>300200002</v>
@@ -3091,13 +3097,13 @@
         <v>300200000</v>
       </c>
       <c r="I36" s="50" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="J36" s="50">
         <v>300200002</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
@@ -3108,16 +3114,16 @@
         <v>3</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D37" s="50">
         <v>1</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F37" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G37" s="50">
         <v>300200003</v>
@@ -3126,13 +3132,13 @@
         <v>300200000</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J37" s="50">
         <v>300200003</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38">
@@ -3143,16 +3149,16 @@
         <v>3</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D38" s="50">
         <v>1</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G38" s="50">
         <v>300200004</v>
@@ -3161,13 +3167,13 @@
         <v>300200000</v>
       </c>
       <c r="I38" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J38" s="50">
         <v>300200004</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39">
@@ -3178,31 +3184,31 @@
         <v>3</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D39" s="50">
         <v>1</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G39" s="50">
         <v>300200101</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J39" s="50">
         <v>300200101</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40">
@@ -3213,16 +3219,16 @@
         <v>3</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D40" s="50">
         <v>1</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F40" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G40" s="50">
         <v>300200102</v>
@@ -3237,7 +3243,7 @@
         <v>300200102</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41">
@@ -3248,13 +3254,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D41" s="50">
         <v>1</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>27</v>
@@ -3263,7 +3269,7 @@
         <v>300200201</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I41" s="50">
         <v>100</v>
@@ -3272,7 +3278,7 @@
         <v>300200201</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42">
@@ -3283,13 +3289,13 @@
         <v>3</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D42" s="50">
         <v>1</v>
       </c>
       <c r="E42" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F42" s="50" t="s">
         <v>27</v>
@@ -3298,7 +3304,7 @@
         <v>300200301</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I42" s="50">
         <v>100</v>
@@ -3307,7 +3313,7 @@
         <v>300200301</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43">
@@ -3318,16 +3324,16 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G43" s="50">
         <v>300300000</v>
@@ -3342,7 +3348,7 @@
         <v>300300000</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44">
@@ -3353,16 +3359,16 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F44" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G44" s="50">
         <v>300300001</v>
@@ -3377,7 +3383,7 @@
         <v>300300001</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45">
@@ -3388,16 +3394,16 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G45" s="50">
         <v>300300002</v>
@@ -3412,7 +3418,7 @@
         <v>300300002</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46">
@@ -3423,16 +3429,16 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F46" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G46" s="50">
         <v>300300003</v>
@@ -3447,7 +3453,7 @@
         <v>300300003</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47">
@@ -3458,16 +3464,16 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F47" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G47" s="50">
         <v>300300004</v>
@@ -3482,7 +3488,7 @@
         <v>300300004</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48">
@@ -3493,22 +3499,22 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G48" s="50">
         <v>300300101</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I48" s="50">
         <v>100</v>
@@ -3517,7 +3523,7 @@
         <v>300300101</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49">
@@ -3528,16 +3534,16 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G49" s="50">
         <v>300300102</v>
@@ -3552,7 +3558,7 @@
         <v>300300102</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50">
@@ -3563,13 +3569,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>27</v>
@@ -3578,7 +3584,7 @@
         <v>300300201</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I50" s="50">
         <v>100</v>
@@ -3587,7 +3593,7 @@
         <v>300300201</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51">
@@ -3598,13 +3604,13 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F51" s="50" t="s">
         <v>27</v>
@@ -3613,7 +3619,7 @@
         <v>300300301</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I51" s="50">
         <v>100</v>
@@ -3622,7 +3628,7 @@
         <v>300300301</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52">
@@ -3633,16 +3639,16 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F52" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G52" s="50">
         <v>300400000</v>
@@ -3657,7 +3663,7 @@
         <v>300400000</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53">
@@ -3668,16 +3674,16 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G53" s="50">
         <v>300400001</v>
@@ -3692,7 +3698,7 @@
         <v>300400001</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54">
@@ -3703,16 +3709,16 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F54" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G54" s="50">
         <v>300400002</v>
@@ -3727,7 +3733,7 @@
         <v>300400002</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55">
@@ -3738,16 +3744,16 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G55" s="50">
         <v>300400003</v>
@@ -3762,7 +3768,7 @@
         <v>300400003</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56">
@@ -3773,16 +3779,16 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F56" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G56" s="50">
         <v>300400004</v>
@@ -3797,7 +3803,7 @@
         <v>300400004</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57">
@@ -3808,16 +3814,16 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G57" s="50">
         <v>300400005</v>
@@ -3832,7 +3838,7 @@
         <v>300400005</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3843,22 +3849,22 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F58" s="50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G58" s="50">
         <v>300400101</v>
       </c>
       <c r="H58" s="50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I58" s="50">
         <v>100</v>
@@ -3867,7 +3873,7 @@
         <v>300400101</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3878,16 +3884,16 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G59" s="50">
         <v>300400102</v>
@@ -3902,7 +3908,7 @@
         <v>300400102</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3913,13 +3919,13 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>27</v>
@@ -3928,7 +3934,7 @@
         <v>300400201</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I60" s="50">
         <v>100</v>
@@ -3937,7 +3943,7 @@
         <v>300400201</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3948,13 +3954,13 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F61" s="50" t="s">
         <v>27</v>
@@ -3963,7 +3969,7 @@
         <v>300400301</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I61" s="50">
         <v>100</v>
@@ -3972,7 +3978,7 @@
         <v>300400301</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3983,16 +3989,16 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F62" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G62" s="50">
         <v>300500000</v>
@@ -4007,7 +4013,7 @@
         <v>300500000</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4018,16 +4024,16 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G63" s="50">
         <v>300500001</v>
@@ -4042,7 +4048,7 @@
         <v>300500001</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4053,16 +4059,16 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G64" s="50">
         <v>300500002</v>
@@ -4077,7 +4083,7 @@
         <v>300500002</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65">
@@ -4088,16 +4094,16 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G65" s="50">
         <v>300500003</v>
@@ -4112,7 +4118,7 @@
         <v>300500003</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66">
@@ -4123,16 +4129,16 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F66" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G66" s="50">
         <v>300500004</v>
@@ -4147,7 +4153,7 @@
         <v>300500004</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4158,22 +4164,22 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G67" s="50">
         <v>300500101</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I67" s="50">
         <v>100</v>
@@ -4182,7 +4188,7 @@
         <v>300500101</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4193,16 +4199,16 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F68" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G68" s="50">
         <v>300500102</v>
@@ -4217,7 +4223,7 @@
         <v>300500102</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4228,13 +4234,13 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>27</v>
@@ -4243,7 +4249,7 @@
         <v>300500201</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I69" s="50">
         <v>100</v>
@@ -4252,7 +4258,7 @@
         <v>300500201</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4263,13 +4269,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>27</v>
@@ -4278,7 +4284,7 @@
         <v>300500301</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I70" s="50">
         <v>100</v>
@@ -4287,7 +4293,7 @@
         <v>300500301</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4298,16 +4304,16 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G71" s="50">
         <v>300600000</v>
@@ -4322,7 +4328,7 @@
         <v>300600000</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4333,16 +4339,16 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F72" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G72" s="50">
         <v>300600001</v>
@@ -4357,7 +4363,7 @@
         <v>300600001</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4368,16 +4374,16 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G73" s="50">
         <v>300600002</v>
@@ -4392,7 +4398,7 @@
         <v>300600002</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4403,16 +4409,16 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F74" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G74" s="50">
         <v>300600003</v>
@@ -4427,7 +4433,7 @@
         <v>300600003</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75">
@@ -4438,16 +4444,16 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F75" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G75" s="50">
         <v>300600004</v>
@@ -4462,7 +4468,7 @@
         <v>300600004</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76">
@@ -4473,16 +4479,16 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F76" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G76" s="50">
         <v>300600005</v>
@@ -4497,7 +4503,7 @@
         <v>300600005</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77">
@@ -4508,22 +4514,22 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G77" s="50">
         <v>300600101</v>
       </c>
       <c r="H77" s="50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I77" s="50">
         <v>100</v>
@@ -4532,7 +4538,7 @@
         <v>300600101</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4543,16 +4549,16 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G78" s="50">
         <v>300600102</v>
@@ -4567,7 +4573,7 @@
         <v>300600102</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4578,13 +4584,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>27</v>
@@ -4593,7 +4599,7 @@
         <v>300600201</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I79" s="50">
         <v>100</v>
@@ -4602,7 +4608,7 @@
         <v>300600201</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4613,13 +4619,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>27</v>
@@ -4628,7 +4634,7 @@
         <v>300600301</v>
       </c>
       <c r="H80" s="50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I80" s="50">
         <v>100</v>
@@ -4637,7 +4643,7 @@
         <v>300600301</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4648,16 +4654,16 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F81" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G81" s="50">
         <v>300700000</v>
@@ -4672,7 +4678,7 @@
         <v>300700000</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4683,16 +4689,16 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F82" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G82" s="50">
         <v>300700001</v>
@@ -4707,7 +4713,7 @@
         <v>300700001</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4718,16 +4724,16 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F83" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G83" s="50">
         <v>300700002</v>
@@ -4742,7 +4748,7 @@
         <v>300700002</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84">
@@ -4753,16 +4759,16 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F84" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G84" s="50">
         <v>300700003</v>
@@ -4777,7 +4783,7 @@
         <v>300700003</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="85">
@@ -4788,16 +4794,16 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F85" s="50" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G85" s="50">
         <v>300700004</v>
@@ -4812,7 +4818,7 @@
         <v>300700004</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="86">
@@ -4823,22 +4829,22 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G86" s="50">
         <v>300700101</v>
       </c>
       <c r="H86" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I86" s="50">
         <v>100</v>
@@ -4847,7 +4853,7 @@
         <v>300700101</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="87">
@@ -4858,16 +4864,16 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G87" s="50">
         <v>300700102</v>
@@ -4882,7 +4888,7 @@
         <v>300700102</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88">
@@ -4893,13 +4899,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>27</v>
@@ -4908,7 +4914,7 @@
         <v>300700201</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I88" s="50">
         <v>100</v>
@@ -4917,7 +4923,7 @@
         <v>300700201</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="89">
@@ -4928,13 +4934,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>27</v>
@@ -4943,7 +4949,7 @@
         <v>300700301</v>
       </c>
       <c r="H89" s="50" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I89" s="50">
         <v>100</v>
@@ -4952,7 +4958,7 @@
         <v>300700301</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="90">
@@ -4963,28 +4969,28 @@
         <v>1</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F90" s="50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G90" s="50">
         <v>100500001</v>
       </c>
       <c r="I90" s="50" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J90" s="50">
         <v>100500001</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="238">
   <si>
     <t>id</t>
   </si>
@@ -273,178 +273,184 @@
     <t>解锁第二阵容</t>
   </si>
   <si>
+    <t>ui_research_60</t>
+  </si>
+  <si>
+    <t>100,500,1000,5000,10000,50000</t>
+  </si>
+  <si>
+    <t>魔晶掉落存在时长+5秒</t>
+  </si>
+  <si>
+    <t>ui_research_61</t>
+  </si>
+  <si>
+    <t>100,500,1000,5000,10000</t>
+  </si>
+  <si>
+    <t>魔王魔力上限+10</t>
+  </si>
+  <si>
+    <t>100,500,1000</t>
+  </si>
+  <si>
+    <t>魔王魔力恢复速度+1/s</t>
+  </si>
+  <si>
+    <t>ui_research_36</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>解锁种族：人类</t>
+  </si>
+  <si>
+    <t>ui_research_43</t>
+  </si>
+  <si>
+    <t>575</t>
+  </si>
+  <si>
+    <t>解锁职业：人类战士</t>
+  </si>
+  <si>
+    <t>ui_research_42</t>
+  </si>
+  <si>
+    <t>725</t>
+  </si>
+  <si>
+    <t>解锁职业：人类弓箭手</t>
+  </si>
+  <si>
+    <t>ui_research_48</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>解锁职业：人类魔法师（火）</t>
+  </si>
+  <si>
+    <t>ui_research_47</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>解锁职业：人类魔法师（冰）</t>
+  </si>
+  <si>
+    <t>ui_research_33</t>
+  </si>
+  <si>
+    <t>300100001|300100002|300100003|300100004|</t>
+  </si>
+  <si>
+    <t>孕育人类x5</t>
+  </si>
+  <si>
+    <t>ui_research_34</t>
+  </si>
+  <si>
+    <t>孕育人类x10</t>
+  </si>
+  <si>
+    <t>100200001,300100000,</t>
+  </si>
+  <si>
+    <t>可转生为人类</t>
+  </si>
+  <si>
+    <t>ui_research_58</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>奖励-可获取人类装备</t>
+  </si>
+  <si>
+    <t>ui_research_35</t>
+  </si>
+  <si>
+    <t>解锁种族：骷髅</t>
+  </si>
+  <si>
+    <t>-223</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>解锁职业：骷髅战士</t>
+  </si>
+  <si>
+    <t>-75</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>解锁职业：骷髅投手</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>解锁职业：骷髅魔法师（火）</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>解锁职业：骷髅魔法师（冰）</t>
+  </si>
+  <si>
+    <t>300200001|300200002|300200003|300200004|</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>孕育骷髅x5</t>
+  </si>
+  <si>
+    <t>孕育骷髅x10</t>
+  </si>
+  <si>
+    <t>100200001,300200000,</t>
+  </si>
+  <si>
+    <t>可转生为骷髅</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>奖励-可获取骷髅装备</t>
+  </si>
+  <si>
+    <t>ui_research_37</t>
+  </si>
+  <si>
+    <t>解锁种族：史莱姆</t>
+  </si>
+  <si>
+    <t>ui_research_51</t>
+  </si>
+  <si>
+    <t>-1025</t>
+  </si>
+  <si>
+    <t>解锁职业：守护史莱姆</t>
+  </si>
+  <si>
     <t>ui_research_54</t>
-  </si>
-  <si>
-    <t>100,500,1000,5000,10000,50000</t>
-  </si>
-  <si>
-    <t>魔晶掉落存在时长+5秒</t>
-  </si>
-  <si>
-    <t>100,500,1000,5000,10000</t>
-  </si>
-  <si>
-    <t>魔王魔力上限+10</t>
-  </si>
-  <si>
-    <t>100,500,1000</t>
-  </si>
-  <si>
-    <t>魔王魔力恢复速度+1/s</t>
-  </si>
-  <si>
-    <t>ui_research_36</t>
-  </si>
-  <si>
-    <t>800</t>
-  </si>
-  <si>
-    <t>解锁种族：人类</t>
-  </si>
-  <si>
-    <t>ui_research_43</t>
-  </si>
-  <si>
-    <t>575</t>
-  </si>
-  <si>
-    <t>解锁职业：人类战士</t>
-  </si>
-  <si>
-    <t>ui_research_42</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>解锁职业：人类弓箭手</t>
-  </si>
-  <si>
-    <t>ui_research_48</t>
-  </si>
-  <si>
-    <t>875</t>
-  </si>
-  <si>
-    <t>解锁职业：人类魔法师（火）</t>
-  </si>
-  <si>
-    <t>ui_research_47</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>解锁职业：人类魔法师（冰）</t>
-  </si>
-  <si>
-    <t>ui_research_33</t>
-  </si>
-  <si>
-    <t>300100001|300100002|300100003|300100004|</t>
-  </si>
-  <si>
-    <t>孕育人类x5</t>
-  </si>
-  <si>
-    <t>ui_research_34</t>
-  </si>
-  <si>
-    <t>孕育人类x10</t>
-  </si>
-  <si>
-    <t>100200001,300100000,</t>
-  </si>
-  <si>
-    <t>可转生为人类</t>
-  </si>
-  <si>
-    <t>ui_research_58</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>奖励-可获取人类装备</t>
-  </si>
-  <si>
-    <t>ui_research_35</t>
-  </si>
-  <si>
-    <t>解锁种族：骷髅</t>
-  </si>
-  <si>
-    <t>-223</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>解锁职业：骷髅战士</t>
-  </si>
-  <si>
-    <t>-75</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>解锁职业：骷髅投手</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>解锁职业：骷髅魔法师（火）</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>解锁职业：骷髅魔法师（冰）</t>
-  </si>
-  <si>
-    <t>300200001|300200002|300200003|300200004|</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>孕育骷髅x5</t>
-  </si>
-  <si>
-    <t>孕育骷髅x10</t>
-  </si>
-  <si>
-    <t>100200001,300200000,</t>
-  </si>
-  <si>
-    <t>可转生为骷髅</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>奖励-可获取骷髅装备</t>
-  </si>
-  <si>
-    <t>ui_research_37</t>
-  </si>
-  <si>
-    <t>解锁种族：史莱姆</t>
-  </si>
-  <si>
-    <t>ui_research_51</t>
-  </si>
-  <si>
-    <t>-1025</t>
-  </si>
-  <si>
-    <t>解锁职业：守护史莱姆</t>
   </si>
   <si>
     <t>-875</t>
@@ -2747,7 +2753,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D26" s="50">
         <v>5</v>
@@ -2762,13 +2768,13 @@
         <v>200300001</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J26" s="50">
         <v>200300001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
@@ -2779,7 +2785,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D27" s="51">
         <v>3</v>
@@ -2794,13 +2800,13 @@
         <v>200400001</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J27" s="51">
         <v>200400001</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28">
@@ -2811,13 +2817,13 @@
         <v>3</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D28" s="50">
         <v>1</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F28" s="50" t="s">
         <v>56</v>
@@ -2835,7 +2841,7 @@
         <v>300100000</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
@@ -2846,13 +2852,13 @@
         <v>3</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F29" s="50" t="s">
         <v>37</v>
@@ -2870,7 +2876,7 @@
         <v>300100001</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
@@ -2881,13 +2887,13 @@
         <v>3</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D30" s="50">
         <v>1</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F30" s="50" t="s">
         <v>37</v>
@@ -2905,7 +2911,7 @@
         <v>300100002</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
@@ -2916,13 +2922,13 @@
         <v>3</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F31" s="50" t="s">
         <v>37</v>
@@ -2940,7 +2946,7 @@
         <v>300100003</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
@@ -2951,13 +2957,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D32" s="50">
         <v>1</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>37</v>
@@ -2975,7 +2981,7 @@
         <v>300100004</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
@@ -2986,13 +2992,13 @@
         <v>3</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D33" s="50">
         <v>1</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F33" s="50" t="s">
         <v>55</v>
@@ -3001,7 +3007,7 @@
         <v>300100101</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I33" s="50">
         <v>100</v>
@@ -3010,7 +3016,7 @@
         <v>300100101</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34">
@@ -3021,13 +3027,13 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D34" s="50">
         <v>1</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F34" s="50" t="s">
         <v>58</v>
@@ -3045,7 +3051,7 @@
         <v>300100102</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35">
@@ -3056,13 +3062,13 @@
         <v>3</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D35" s="50">
         <v>1</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F35" s="50" t="s">
         <v>27</v>
@@ -3071,7 +3077,7 @@
         <v>300100201</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I35" s="50">
         <v>100</v>
@@ -3080,7 +3086,7 @@
         <v>300100201</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36">
@@ -3091,13 +3097,13 @@
         <v>3</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D36" s="50">
         <v>1</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F36" s="50" t="s">
         <v>27</v>
@@ -3106,7 +3112,7 @@
         <v>300100301</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I36" s="50">
         <v>100</v>
@@ -3115,7 +3121,7 @@
         <v>300100301</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37">
@@ -3126,7 +3132,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D37" s="50">
         <v>1</v>
@@ -3147,7 +3153,7 @@
         <v>300200000</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38">
@@ -3158,16 +3164,16 @@
         <v>3</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D38" s="50">
         <v>1</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G38" s="50">
         <v>300200001</v>
@@ -3176,13 +3182,13 @@
         <v>300200000</v>
       </c>
       <c r="I38" s="50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J38" s="50">
         <v>300200001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39">
@@ -3193,13 +3199,13 @@
         <v>3</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D39" s="50">
         <v>1</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F39" s="50" t="s">
         <v>37</v>
@@ -3211,13 +3217,13 @@
         <v>300200000</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J39" s="50">
         <v>300200002</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
@@ -3228,13 +3234,13 @@
         <v>3</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D40" s="50">
         <v>1</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F40" s="50" t="s">
         <v>37</v>
@@ -3252,7 +3258,7 @@
         <v>300200003</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41">
@@ -3263,13 +3269,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D41" s="50">
         <v>1</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>37</v>
@@ -3287,7 +3293,7 @@
         <v>300200004</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42">
@@ -3298,7 +3304,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D42" s="50">
         <v>1</v>
@@ -3313,16 +3319,16 @@
         <v>300200101</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I42" s="50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J42" s="50">
         <v>300200101</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43">
@@ -3333,7 +3339,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
@@ -3357,7 +3363,7 @@
         <v>300200102</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44">
@@ -3368,7 +3374,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
@@ -3383,7 +3389,7 @@
         <v>300200201</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I44" s="50">
         <v>100</v>
@@ -3392,7 +3398,7 @@
         <v>300200201</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45">
@@ -3403,13 +3409,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>27</v>
@@ -3418,7 +3424,7 @@
         <v>300200301</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I45" s="50">
         <v>100</v>
@@ -3427,7 +3433,7 @@
         <v>300200301</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46">
@@ -3438,7 +3444,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
@@ -3462,7 +3468,7 @@
         <v>300300000</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47">
@@ -3473,13 +3479,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>37</v>
@@ -3497,7 +3503,7 @@
         <v>300300001</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48">
@@ -3508,13 +3514,13 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F48" s="50" t="s">
         <v>37</v>
@@ -3532,7 +3538,7 @@
         <v>300300002</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49">
@@ -3543,13 +3549,13 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F49" s="50" t="s">
         <v>37</v>
@@ -3567,7 +3573,7 @@
         <v>300300003</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50">
@@ -3578,13 +3584,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>37</v>
@@ -3602,7 +3608,7 @@
         <v>300300004</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51">
@@ -3613,7 +3619,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
@@ -3628,7 +3634,7 @@
         <v>300300101</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I51" s="50">
         <v>100</v>
@@ -3637,7 +3643,7 @@
         <v>300300101</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52">
@@ -3648,7 +3654,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
@@ -3672,7 +3678,7 @@
         <v>300300102</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53">
@@ -3683,7 +3689,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
@@ -3698,7 +3704,7 @@
         <v>300300201</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I53" s="50">
         <v>100</v>
@@ -3707,7 +3713,7 @@
         <v>300300201</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54">
@@ -3718,13 +3724,13 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F54" s="50" t="s">
         <v>27</v>
@@ -3733,7 +3739,7 @@
         <v>300300301</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I54" s="50">
         <v>100</v>
@@ -3742,7 +3748,7 @@
         <v>300300301</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55">
@@ -3753,13 +3759,13 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F55" s="50" t="s">
         <v>56</v>
@@ -3777,7 +3783,7 @@
         <v>300400000</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56">
@@ -3788,13 +3794,13 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>37</v>
@@ -3812,7 +3818,7 @@
         <v>300400001</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57">
@@ -3823,13 +3829,13 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F57" s="50" t="s">
         <v>37</v>
@@ -3847,7 +3853,7 @@
         <v>300400002</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3858,13 +3864,13 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F58" s="50" t="s">
         <v>37</v>
@@ -3882,7 +3888,7 @@
         <v>300400003</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3893,13 +3899,13 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F59" s="50" t="s">
         <v>37</v>
@@ -3917,7 +3923,7 @@
         <v>300400004</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3928,13 +3934,13 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>37</v>
@@ -3952,7 +3958,7 @@
         <v>300400005</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3963,13 +3969,13 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F61" s="50" t="s">
         <v>55</v>
@@ -3978,7 +3984,7 @@
         <v>300400101</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I61" s="50">
         <v>100</v>
@@ -3987,7 +3993,7 @@
         <v>300400101</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3998,13 +4004,13 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>58</v>
@@ -4022,7 +4028,7 @@
         <v>300400102</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4033,13 +4039,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>27</v>
@@ -4048,7 +4054,7 @@
         <v>300400201</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I63" s="50">
         <v>100</v>
@@ -4057,7 +4063,7 @@
         <v>300400201</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4068,13 +4074,13 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F64" s="50" t="s">
         <v>27</v>
@@ -4083,7 +4089,7 @@
         <v>300400301</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I64" s="50">
         <v>100</v>
@@ -4092,7 +4098,7 @@
         <v>300400301</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65">
@@ -4103,13 +4109,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>56</v>
@@ -4127,7 +4133,7 @@
         <v>300500000</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66">
@@ -4138,13 +4144,13 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F66" s="50" t="s">
         <v>37</v>
@@ -4162,7 +4168,7 @@
         <v>300500001</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4173,13 +4179,13 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F67" s="50" t="s">
         <v>37</v>
@@ -4197,7 +4203,7 @@
         <v>300500002</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4208,13 +4214,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>37</v>
@@ -4232,7 +4238,7 @@
         <v>300500003</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4243,13 +4249,13 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>37</v>
@@ -4267,7 +4273,7 @@
         <v>300500004</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4278,13 +4284,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>55</v>
@@ -4293,7 +4299,7 @@
         <v>300500101</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I70" s="50">
         <v>100</v>
@@ -4302,7 +4308,7 @@
         <v>300500101</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4313,13 +4319,13 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>58</v>
@@ -4337,7 +4343,7 @@
         <v>300500102</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4348,13 +4354,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>27</v>
@@ -4363,7 +4369,7 @@
         <v>300500201</v>
       </c>
       <c r="H72" s="50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I72" s="50">
         <v>100</v>
@@ -4372,7 +4378,7 @@
         <v>300500201</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4383,13 +4389,13 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>27</v>
@@ -4398,7 +4404,7 @@
         <v>300500301</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I73" s="50">
         <v>100</v>
@@ -4407,7 +4413,7 @@
         <v>300500301</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4418,13 +4424,13 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>56</v>
@@ -4442,7 +4448,7 @@
         <v>300600000</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75">
@@ -4453,13 +4459,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>37</v>
@@ -4477,7 +4483,7 @@
         <v>300600001</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76">
@@ -4488,13 +4494,13 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>37</v>
@@ -4512,7 +4518,7 @@
         <v>300600002</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77">
@@ -4523,13 +4529,13 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F77" s="50" t="s">
         <v>37</v>
@@ -4547,7 +4553,7 @@
         <v>300600003</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4558,13 +4564,13 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>37</v>
@@ -4582,7 +4588,7 @@
         <v>300600004</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4593,13 +4599,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>37</v>
@@ -4617,7 +4623,7 @@
         <v>300600005</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4628,13 +4634,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>55</v>
@@ -4643,7 +4649,7 @@
         <v>300600101</v>
       </c>
       <c r="H80" s="50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I80" s="50">
         <v>100</v>
@@ -4652,7 +4658,7 @@
         <v>300600101</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4663,13 +4669,13 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>58</v>
@@ -4687,7 +4693,7 @@
         <v>300600102</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4698,13 +4704,13 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>27</v>
@@ -4713,7 +4719,7 @@
         <v>300600201</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I82" s="50">
         <v>100</v>
@@ -4722,7 +4728,7 @@
         <v>300600201</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4733,13 +4739,13 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>27</v>
@@ -4748,7 +4754,7 @@
         <v>300600301</v>
       </c>
       <c r="H83" s="50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I83" s="50">
         <v>100</v>
@@ -4757,7 +4763,7 @@
         <v>300600301</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84">
@@ -4768,13 +4774,13 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>56</v>
@@ -4792,7 +4798,7 @@
         <v>300700000</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="85">
@@ -4803,13 +4809,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>37</v>
@@ -4827,7 +4833,7 @@
         <v>300700001</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="86">
@@ -4838,13 +4844,13 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>37</v>
@@ -4862,7 +4868,7 @@
         <v>300700002</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87">
@@ -4873,13 +4879,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F87" s="50" t="s">
         <v>37</v>
@@ -4897,7 +4903,7 @@
         <v>300700003</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88">
@@ -4908,13 +4914,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>37</v>
@@ -4932,7 +4938,7 @@
         <v>300700004</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89">
@@ -4943,13 +4949,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>55</v>
@@ -4958,7 +4964,7 @@
         <v>300700101</v>
       </c>
       <c r="H89" s="50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I89" s="50">
         <v>100</v>
@@ -4967,7 +4973,7 @@
         <v>300700101</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="90">
@@ -4978,13 +4984,13 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>58</v>
@@ -5002,7 +5008,7 @@
         <v>300700102</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91">
@@ -5013,13 +5019,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>27</v>
@@ -5028,7 +5034,7 @@
         <v>300700201</v>
       </c>
       <c r="H91" s="50" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I91" s="50">
         <v>100</v>
@@ -5037,7 +5043,7 @@
         <v>300700201</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="92">
@@ -5048,13 +5054,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>27</v>
@@ -5063,7 +5069,7 @@
         <v>300700301</v>
       </c>
       <c r="H92" s="50" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I92" s="50">
         <v>100</v>
@@ -5072,7 +5078,7 @@
         <v>300700301</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="93">
@@ -5083,7 +5089,7 @@
         <v>1</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
@@ -5104,7 +5110,7 @@
         <v>100500001</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="240">
   <si>
     <t>id</t>
   </si>
@@ -207,16 +207,22 @@
     <t>开启孕育功能</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
     <t>孕育可跳过</t>
   </si>
   <si>
+    <t>-599</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
     <t>解锁孕育稀有度：R</t>
   </si>
   <si>
     <t>-396</t>
-  </si>
-  <si>
-    <t>-596</t>
   </si>
   <si>
     <t>100*1</t>
@@ -2429,14 +2435,14 @@
       <c r="H16" s="50">
         <v>100400000</v>
       </c>
-      <c r="I16" s="50">
-        <v>100</v>
+      <c r="I16" s="50" t="s">
+        <v>64</v>
       </c>
       <c r="J16" s="50">
         <v>100400001</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -2456,7 +2462,7 @@
         <v>27</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G17" s="50">
         <v>100401000</v>
@@ -2464,14 +2470,14 @@
       <c r="H17" s="50">
         <v>100400001</v>
       </c>
-      <c r="I17" s="50">
-        <v>100</v>
+      <c r="I17" s="50" t="s">
+        <v>67</v>
       </c>
       <c r="J17" s="50">
         <v>100401000</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -2488,10 +2494,10 @@
         <v>50</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="G18" s="50">
         <v>100401001</v>
@@ -2500,13 +2506,13 @@
         <v>100401000</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J18" s="50">
         <v>100401001</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
@@ -2526,13 +2532,13 @@
         <v>27</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G19" s="50">
         <v>100402000</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I19" s="50">
         <v>1000</v>
@@ -2541,7 +2547,7 @@
         <v>100402000</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -2561,7 +2567,7 @@
         <v>49</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G20" s="50">
         <v>100402001</v>
@@ -2570,13 +2576,13 @@
         <v>100402000</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J20" s="50">
         <v>100402001</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
@@ -2596,13 +2602,13 @@
         <v>27</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" s="50">
         <v>100403000</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I21" s="50">
         <v>10000</v>
@@ -2611,7 +2617,7 @@
         <v>100403000</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
@@ -2631,7 +2637,7 @@
         <v>49</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G22" s="50">
         <v>100403001</v>
@@ -2640,13 +2646,13 @@
         <v>100403000</v>
       </c>
       <c r="I22" s="50" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J22" s="50">
         <v>100403001</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
@@ -2657,7 +2663,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D23" s="50">
         <v>30</v>
@@ -2672,13 +2678,13 @@
         <v>200000001</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J23" s="50">
         <v>200000001</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24">
@@ -2689,7 +2695,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D24" s="50">
         <v>4</v>
@@ -2704,13 +2710,13 @@
         <v>200100001</v>
       </c>
       <c r="I24" s="50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J24" s="50">
         <v>200100001</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25">
@@ -2721,7 +2727,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D25" s="50">
         <v>6</v>
@@ -2736,13 +2742,13 @@
         <v>200200001</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J25" s="50">
         <v>200200001</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
@@ -2753,7 +2759,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D26" s="50">
         <v>5</v>
@@ -2768,13 +2774,13 @@
         <v>200300001</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J26" s="50">
         <v>200300001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27">
@@ -2785,7 +2791,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D27" s="51">
         <v>3</v>
@@ -2800,13 +2806,13 @@
         <v>200400001</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J27" s="51">
         <v>200400001</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28">
@@ -2817,13 +2823,13 @@
         <v>3</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D28" s="50">
         <v>1</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F28" s="50" t="s">
         <v>56</v>
@@ -2841,7 +2847,7 @@
         <v>300100000</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
@@ -2852,13 +2858,13 @@
         <v>3</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F29" s="50" t="s">
         <v>37</v>
@@ -2876,7 +2882,7 @@
         <v>300100001</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
@@ -2887,13 +2893,13 @@
         <v>3</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D30" s="50">
         <v>1</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F30" s="50" t="s">
         <v>37</v>
@@ -2911,7 +2917,7 @@
         <v>300100002</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31">
@@ -2922,13 +2928,13 @@
         <v>3</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F31" s="50" t="s">
         <v>37</v>
@@ -2946,7 +2952,7 @@
         <v>300100003</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32">
@@ -2957,13 +2963,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D32" s="50">
         <v>1</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>37</v>
@@ -2981,7 +2987,7 @@
         <v>300100004</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33">
@@ -2992,13 +2998,13 @@
         <v>3</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D33" s="50">
         <v>1</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F33" s="50" t="s">
         <v>55</v>
@@ -3007,7 +3013,7 @@
         <v>300100101</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I33" s="50">
         <v>100</v>
@@ -3016,7 +3022,7 @@
         <v>300100101</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
@@ -3027,13 +3033,13 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D34" s="50">
         <v>1</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F34" s="50" t="s">
         <v>58</v>
@@ -3051,7 +3057,7 @@
         <v>300100102</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35">
@@ -3062,13 +3068,13 @@
         <v>3</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D35" s="50">
         <v>1</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F35" s="50" t="s">
         <v>27</v>
@@ -3077,7 +3083,7 @@
         <v>300100201</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I35" s="50">
         <v>100</v>
@@ -3086,7 +3092,7 @@
         <v>300100201</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36">
@@ -3097,13 +3103,13 @@
         <v>3</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D36" s="50">
         <v>1</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F36" s="50" t="s">
         <v>27</v>
@@ -3112,7 +3118,7 @@
         <v>300100301</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I36" s="50">
         <v>100</v>
@@ -3121,7 +3127,7 @@
         <v>300100301</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37">
@@ -3132,7 +3138,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D37" s="50">
         <v>1</v>
@@ -3153,7 +3159,7 @@
         <v>300200000</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
@@ -3164,16 +3170,16 @@
         <v>3</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D38" s="50">
         <v>1</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G38" s="50">
         <v>300200001</v>
@@ -3182,13 +3188,13 @@
         <v>300200000</v>
       </c>
       <c r="I38" s="50" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J38" s="50">
         <v>300200001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39">
@@ -3199,13 +3205,13 @@
         <v>3</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D39" s="50">
         <v>1</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F39" s="50" t="s">
         <v>37</v>
@@ -3217,13 +3223,13 @@
         <v>300200000</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J39" s="50">
         <v>300200002</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40">
@@ -3234,13 +3240,13 @@
         <v>3</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D40" s="50">
         <v>1</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F40" s="50" t="s">
         <v>37</v>
@@ -3258,7 +3264,7 @@
         <v>300200003</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41">
@@ -3269,13 +3275,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D41" s="50">
         <v>1</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>37</v>
@@ -3293,7 +3299,7 @@
         <v>300200004</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42">
@@ -3304,7 +3310,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D42" s="50">
         <v>1</v>
@@ -3319,16 +3325,16 @@
         <v>300200101</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I42" s="50" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J42" s="50">
         <v>300200101</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43">
@@ -3339,7 +3345,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
@@ -3363,7 +3369,7 @@
         <v>300200102</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44">
@@ -3374,7 +3380,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
@@ -3389,7 +3395,7 @@
         <v>300200201</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I44" s="50">
         <v>100</v>
@@ -3398,7 +3404,7 @@
         <v>300200201</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45">
@@ -3409,13 +3415,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>27</v>
@@ -3424,7 +3430,7 @@
         <v>300200301</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I45" s="50">
         <v>100</v>
@@ -3433,7 +3439,7 @@
         <v>300200301</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46">
@@ -3444,13 +3450,13 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F46" s="50" t="s">
         <v>56</v>
@@ -3468,7 +3474,7 @@
         <v>300300000</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47">
@@ -3479,13 +3485,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>37</v>
@@ -3503,7 +3509,7 @@
         <v>300300001</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48">
@@ -3514,13 +3520,13 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F48" s="50" t="s">
         <v>37</v>
@@ -3538,7 +3544,7 @@
         <v>300300002</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49">
@@ -3549,13 +3555,13 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F49" s="50" t="s">
         <v>37</v>
@@ -3573,7 +3579,7 @@
         <v>300300003</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50">
@@ -3584,13 +3590,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>37</v>
@@ -3608,7 +3614,7 @@
         <v>300300004</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51">
@@ -3619,13 +3625,13 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F51" s="50" t="s">
         <v>55</v>
@@ -3634,7 +3640,7 @@
         <v>300300101</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I51" s="50">
         <v>100</v>
@@ -3643,7 +3649,7 @@
         <v>300300101</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52">
@@ -3654,13 +3660,13 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F52" s="50" t="s">
         <v>58</v>
@@ -3678,7 +3684,7 @@
         <v>300300102</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53">
@@ -3689,13 +3695,13 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F53" s="50" t="s">
         <v>27</v>
@@ -3704,7 +3710,7 @@
         <v>300300201</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I53" s="50">
         <v>100</v>
@@ -3713,7 +3719,7 @@
         <v>300300201</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54">
@@ -3724,13 +3730,13 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F54" s="50" t="s">
         <v>27</v>
@@ -3739,7 +3745,7 @@
         <v>300300301</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I54" s="50">
         <v>100</v>
@@ -3748,7 +3754,7 @@
         <v>300300301</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55">
@@ -3759,13 +3765,13 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F55" s="50" t="s">
         <v>56</v>
@@ -3783,7 +3789,7 @@
         <v>300400000</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56">
@@ -3794,13 +3800,13 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>37</v>
@@ -3818,7 +3824,7 @@
         <v>300400001</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57">
@@ -3829,13 +3835,13 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F57" s="50" t="s">
         <v>37</v>
@@ -3853,7 +3859,7 @@
         <v>300400002</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3864,13 +3870,13 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F58" s="50" t="s">
         <v>37</v>
@@ -3888,7 +3894,7 @@
         <v>300400003</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3899,13 +3905,13 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F59" s="50" t="s">
         <v>37</v>
@@ -3923,7 +3929,7 @@
         <v>300400004</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3934,13 +3940,13 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>37</v>
@@ -3958,7 +3964,7 @@
         <v>300400005</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3969,13 +3975,13 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F61" s="50" t="s">
         <v>55</v>
@@ -3984,7 +3990,7 @@
         <v>300400101</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I61" s="50">
         <v>100</v>
@@ -3993,7 +3999,7 @@
         <v>300400101</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4004,13 +4010,13 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>58</v>
@@ -4028,7 +4034,7 @@
         <v>300400102</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4039,13 +4045,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>27</v>
@@ -4054,7 +4060,7 @@
         <v>300400201</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I63" s="50">
         <v>100</v>
@@ -4063,7 +4069,7 @@
         <v>300400201</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4074,13 +4080,13 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F64" s="50" t="s">
         <v>27</v>
@@ -4089,7 +4095,7 @@
         <v>300400301</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I64" s="50">
         <v>100</v>
@@ -4098,7 +4104,7 @@
         <v>300400301</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65">
@@ -4109,13 +4115,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>56</v>
@@ -4133,7 +4139,7 @@
         <v>300500000</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66">
@@ -4144,13 +4150,13 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F66" s="50" t="s">
         <v>37</v>
@@ -4168,7 +4174,7 @@
         <v>300500001</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4179,13 +4185,13 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F67" s="50" t="s">
         <v>37</v>
@@ -4203,7 +4209,7 @@
         <v>300500002</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4214,13 +4220,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>37</v>
@@ -4238,7 +4244,7 @@
         <v>300500003</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4249,13 +4255,13 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>37</v>
@@ -4273,7 +4279,7 @@
         <v>300500004</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4284,13 +4290,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>55</v>
@@ -4299,7 +4305,7 @@
         <v>300500101</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I70" s="50">
         <v>100</v>
@@ -4308,7 +4314,7 @@
         <v>300500101</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4319,13 +4325,13 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>58</v>
@@ -4343,7 +4349,7 @@
         <v>300500102</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4354,13 +4360,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>27</v>
@@ -4369,7 +4375,7 @@
         <v>300500201</v>
       </c>
       <c r="H72" s="50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I72" s="50">
         <v>100</v>
@@ -4378,7 +4384,7 @@
         <v>300500201</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4389,13 +4395,13 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>27</v>
@@ -4404,7 +4410,7 @@
         <v>300500301</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I73" s="50">
         <v>100</v>
@@ -4413,7 +4419,7 @@
         <v>300500301</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4424,13 +4430,13 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>56</v>
@@ -4448,7 +4454,7 @@
         <v>300600000</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75">
@@ -4459,13 +4465,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>37</v>
@@ -4483,7 +4489,7 @@
         <v>300600001</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76">
@@ -4494,13 +4500,13 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>37</v>
@@ -4518,7 +4524,7 @@
         <v>300600002</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77">
@@ -4529,13 +4535,13 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F77" s="50" t="s">
         <v>37</v>
@@ -4553,7 +4559,7 @@
         <v>300600003</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4564,13 +4570,13 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>37</v>
@@ -4588,7 +4594,7 @@
         <v>300600004</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4599,13 +4605,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>37</v>
@@ -4623,7 +4629,7 @@
         <v>300600005</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4634,13 +4640,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>55</v>
@@ -4649,7 +4655,7 @@
         <v>300600101</v>
       </c>
       <c r="H80" s="50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I80" s="50">
         <v>100</v>
@@ -4658,7 +4664,7 @@
         <v>300600101</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4669,13 +4675,13 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>58</v>
@@ -4693,7 +4699,7 @@
         <v>300600102</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4704,13 +4710,13 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>27</v>
@@ -4719,7 +4725,7 @@
         <v>300600201</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I82" s="50">
         <v>100</v>
@@ -4728,7 +4734,7 @@
         <v>300600201</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4739,13 +4745,13 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>27</v>
@@ -4754,7 +4760,7 @@
         <v>300600301</v>
       </c>
       <c r="H83" s="50" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I83" s="50">
         <v>100</v>
@@ -4763,7 +4769,7 @@
         <v>300600301</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="84">
@@ -4774,13 +4780,13 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>56</v>
@@ -4798,7 +4804,7 @@
         <v>300700000</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85">
@@ -4809,13 +4815,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>37</v>
@@ -4833,7 +4839,7 @@
         <v>300700001</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86">
@@ -4844,13 +4850,13 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>37</v>
@@ -4868,7 +4874,7 @@
         <v>300700002</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="87">
@@ -4879,13 +4885,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F87" s="50" t="s">
         <v>37</v>
@@ -4903,7 +4909,7 @@
         <v>300700003</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88">
@@ -4914,13 +4920,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>37</v>
@@ -4938,7 +4944,7 @@
         <v>300700004</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="89">
@@ -4949,13 +4955,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>55</v>
@@ -4964,7 +4970,7 @@
         <v>300700101</v>
       </c>
       <c r="H89" s="50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I89" s="50">
         <v>100</v>
@@ -4973,7 +4979,7 @@
         <v>300700101</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90">
@@ -4984,13 +4990,13 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>58</v>
@@ -5008,7 +5014,7 @@
         <v>300700102</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="91">
@@ -5019,13 +5025,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>27</v>
@@ -5034,7 +5040,7 @@
         <v>300700201</v>
       </c>
       <c r="H91" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I91" s="50">
         <v>100</v>
@@ -5043,7 +5049,7 @@
         <v>300700201</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="92">
@@ -5054,13 +5060,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>27</v>
@@ -5069,7 +5075,7 @@
         <v>300700301</v>
       </c>
       <c r="H92" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I92" s="50">
         <v>100</v>
@@ -5078,7 +5084,7 @@
         <v>300700301</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="93">
@@ -5089,7 +5095,7 @@
         <v>1</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
@@ -5110,7 +5116,7 @@
         <v>100500001</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
   <si>
     <t>id</t>
   </si>
@@ -102,60 +102,63 @@
     <t>201</t>
   </si>
   <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>开启进阶设施</t>
+  </si>
+  <si>
+    <t>ui_research_2</t>
+  </si>
+  <si>
+    <t>-351</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>1000,2000,3000,4000,5000,</t>
+  </si>
+  <si>
+    <t>进阶设施+1</t>
+  </si>
+  <si>
+    <t>ui_research_3</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>开启献祭设施</t>
+  </si>
+  <si>
+    <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
+  </si>
+  <si>
+    <t>献祭祭品数量+1</t>
+  </si>
+  <si>
+    <t>100100001</t>
+  </si>
+  <si>
+    <t>100,500,1000,5000,10000,20000,30000,40000,50000,100000</t>
+  </si>
+  <si>
+    <t>献祭失败保底概率提升</t>
+  </si>
+  <si>
+    <t>不同魔物献祭成功率提升</t>
+  </si>
+  <si>
+    <t>ui_research_7</t>
+  </si>
+  <si>
     <t>1000</t>
   </si>
   <si>
-    <t>开启进阶设施</t>
-  </si>
-  <si>
-    <t>ui_research_2</t>
-  </si>
-  <si>
-    <t>-350</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>100,200,300,400,500,</t>
-  </si>
-  <si>
-    <t>进阶设施+1</t>
-  </si>
-  <si>
-    <t>ui_research_3</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>开启献祭设施</t>
-  </si>
-  <si>
-    <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
-  </si>
-  <si>
-    <t>献祭祭品数量+1</t>
-  </si>
-  <si>
-    <t>100100001</t>
-  </si>
-  <si>
-    <t>100,500,1000,5000,10000,20000,30000,40000,50000,100000</t>
-  </si>
-  <si>
-    <t>献祭失败保底概率提升</t>
-  </si>
-  <si>
-    <t>不同魔物献祭成功率提升</t>
-  </si>
-  <si>
-    <t>ui_research_7</t>
-  </si>
-  <si>
     <t>开启终焉议会</t>
   </si>
   <si>
@@ -186,12 +189,18 @@
     <t>0</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>ui_research_11</t>
   </si>
   <si>
     <t>600</t>
   </si>
   <si>
+    <t>100300001</t>
+  </si>
+  <si>
     <t>200,400,800,1600,3200,6400,12800,25600,51200,</t>
   </si>
   <si>
@@ -216,9 +225,6 @@
     <t>-599</t>
   </si>
   <si>
-    <t>500</t>
-  </si>
-  <si>
     <t>解锁孕育稀有度：R</t>
   </si>
   <si>
@@ -309,6 +315,9 @@
     <t>800</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>解锁种族：人类</t>
   </si>
   <si>
@@ -390,9 +399,6 @@
     <t>204</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>解锁职业：骷髅战士</t>
   </si>
   <si>
@@ -418,9 +424,6 @@
   </si>
   <si>
     <t>300200001|300200002|300200003|300200004|</t>
-  </si>
-  <si>
-    <t>250</t>
   </si>
   <si>
     <t>孕育骷髅x5</t>
@@ -2234,14 +2237,14 @@
       <c r="G10" s="50">
         <v>100200001</v>
       </c>
-      <c r="I10" s="50">
-        <v>100</v>
+      <c r="I10" s="50" t="s">
+        <v>47</v>
       </c>
       <c r="J10" s="50">
         <v>100200001</v>
       </c>
       <c r="K10" s="50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -2252,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="50">
         <v>1</v>
@@ -2261,7 +2264,7 @@
         <v>37</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" s="50">
         <v>100200002</v>
@@ -2276,7 +2279,7 @@
         <v>100200002</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -2287,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" s="50">
         <v>1</v>
@@ -2296,7 +2299,7 @@
         <v>37</v>
       </c>
       <c r="F12" s="50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="50">
         <v>100200003</v>
@@ -2311,7 +2314,7 @@
         <v>100200003</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -2322,28 +2325,28 @@
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" s="50">
         <v>100300001</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="J13" s="50">
         <v>100300001</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -2354,28 +2357,31 @@
         <v>1</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D14" s="50">
         <v>9</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F14" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" s="50">
         <v>100310112</v>
       </c>
+      <c r="H14" s="51" t="s">
+        <v>61</v>
+      </c>
       <c r="I14" s="50" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J14" s="50">
         <v>100310112</v>
       </c>
       <c r="K14" s="50" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2386,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D15" s="50">
         <v>1</v>
@@ -2401,13 +2407,13 @@
         <v>100400000</v>
       </c>
       <c r="I15" s="50" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J15" s="50">
         <v>100400000</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
@@ -2418,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -2427,7 +2433,7 @@
         <v>27</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" s="50">
         <v>100400001</v>
@@ -2436,13 +2442,13 @@
         <v>100400000</v>
       </c>
       <c r="I16" s="50" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J16" s="50">
         <v>100400001</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
@@ -2453,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D17" s="50">
         <v>1</v>
@@ -2462,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G17" s="50">
         <v>100401000</v>
@@ -2471,13 +2477,13 @@
         <v>100400001</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="J17" s="50">
         <v>100401000</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -2488,16 +2494,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D18" s="50">
         <v>50</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="50">
         <v>100401001</v>
@@ -2506,13 +2512,13 @@
         <v>100401000</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J18" s="50">
         <v>100401001</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -2523,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D19" s="50">
         <v>1</v>
@@ -2532,13 +2538,13 @@
         <v>27</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G19" s="50">
         <v>100402000</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I19" s="50">
         <v>1000</v>
@@ -2547,7 +2553,7 @@
         <v>100402000</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -2558,16 +2564,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D20" s="50">
         <v>40</v>
       </c>
       <c r="E20" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G20" s="50">
         <v>100402001</v>
@@ -2576,13 +2582,13 @@
         <v>100402000</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J20" s="50">
         <v>100402001</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21">
@@ -2593,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D21" s="50">
         <v>1</v>
@@ -2602,13 +2608,13 @@
         <v>27</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" s="50">
         <v>100403000</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I21" s="50">
         <v>10000</v>
@@ -2617,7 +2623,7 @@
         <v>100403000</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
@@ -2628,16 +2634,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D22" s="50">
         <v>30</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" s="50">
         <v>100403001</v>
@@ -2646,13 +2652,13 @@
         <v>100403000</v>
       </c>
       <c r="I22" s="50" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J22" s="50">
         <v>100403001</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23">
@@ -2663,7 +2669,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D23" s="50">
         <v>30</v>
@@ -2678,13 +2684,13 @@
         <v>200000001</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J23" s="50">
         <v>200000001</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
@@ -2695,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D24" s="50">
         <v>4</v>
@@ -2704,19 +2710,19 @@
         <v>37</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24" s="50">
         <v>200100001</v>
       </c>
       <c r="I24" s="50" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J24" s="50">
         <v>200100001</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25">
@@ -2727,7 +2733,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D25" s="50">
         <v>6</v>
@@ -2742,13 +2748,13 @@
         <v>200200001</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J25" s="50">
         <v>200200001</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26">
@@ -2759,7 +2765,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D26" s="50">
         <v>5</v>
@@ -2774,13 +2780,13 @@
         <v>200300001</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J26" s="50">
         <v>200300001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27">
@@ -2791,7 +2797,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D27" s="51">
         <v>3</v>
@@ -2806,13 +2812,13 @@
         <v>200400001</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J27" s="51">
         <v>200400001</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -2823,16 +2829,16 @@
         <v>3</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D28" s="50">
         <v>1</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G28" s="50">
         <v>300100000</v>
@@ -2840,14 +2846,14 @@
       <c r="H28" s="50">
         <v>300200000</v>
       </c>
-      <c r="I28" s="50">
+      <c r="I28" s="50" t="s">
         <v>100</v>
       </c>
       <c r="J28" s="50">
         <v>300100000</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
@@ -2858,13 +2864,13 @@
         <v>3</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F29" s="50" t="s">
         <v>37</v>
@@ -2882,7 +2888,7 @@
         <v>300100001</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30">
@@ -2893,13 +2899,13 @@
         <v>3</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D30" s="50">
         <v>1</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F30" s="50" t="s">
         <v>37</v>
@@ -2917,7 +2923,7 @@
         <v>300100002</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31">
@@ -2928,13 +2934,13 @@
         <v>3</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F31" s="50" t="s">
         <v>37</v>
@@ -2952,7 +2958,7 @@
         <v>300100003</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32">
@@ -2963,13 +2969,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D32" s="50">
         <v>1</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>37</v>
@@ -2987,7 +2993,7 @@
         <v>300100004</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33">
@@ -2998,22 +3004,22 @@
         <v>3</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D33" s="50">
         <v>1</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F33" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G33" s="50">
         <v>300100101</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I33" s="50">
         <v>100</v>
@@ -3022,7 +3028,7 @@
         <v>300100101</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34">
@@ -3033,16 +3039,16 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D34" s="50">
         <v>1</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F34" s="50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G34" s="50">
         <v>300100102</v>
@@ -3057,7 +3063,7 @@
         <v>300100102</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35">
@@ -3068,13 +3074,13 @@
         <v>3</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D35" s="50">
         <v>1</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F35" s="50" t="s">
         <v>27</v>
@@ -3083,7 +3089,7 @@
         <v>300100201</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I35" s="50">
         <v>100</v>
@@ -3092,7 +3098,7 @@
         <v>300100201</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36">
@@ -3103,13 +3109,13 @@
         <v>3</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D36" s="50">
         <v>1</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F36" s="50" t="s">
         <v>27</v>
@@ -3118,7 +3124,7 @@
         <v>300100301</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I36" s="50">
         <v>100</v>
@@ -3127,7 +3133,7 @@
         <v>300100301</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37">
@@ -3138,28 +3144,28 @@
         <v>3</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D37" s="50">
         <v>1</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F37" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G37" s="50">
         <v>300200000</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J37" s="50">
         <v>300200000</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
@@ -3170,16 +3176,16 @@
         <v>3</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D38" s="50">
         <v>1</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G38" s="50">
         <v>300200001</v>
@@ -3188,13 +3194,13 @@
         <v>300200000</v>
       </c>
       <c r="I38" s="50" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="J38" s="50">
         <v>300200001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39">
@@ -3205,13 +3211,13 @@
         <v>3</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D39" s="50">
         <v>1</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F39" s="50" t="s">
         <v>37</v>
@@ -3223,13 +3229,13 @@
         <v>300200000</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J39" s="50">
         <v>300200002</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
@@ -3240,13 +3246,13 @@
         <v>3</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D40" s="50">
         <v>1</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F40" s="50" t="s">
         <v>37</v>
@@ -3258,13 +3264,13 @@
         <v>300200000</v>
       </c>
       <c r="I40" s="50" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J40" s="50">
         <v>300200003</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41">
@@ -3275,13 +3281,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D41" s="50">
         <v>1</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>37</v>
@@ -3293,13 +3299,13 @@
         <v>300200000</v>
       </c>
       <c r="I41" s="50" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J41" s="50">
         <v>300200004</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42">
@@ -3310,31 +3316,31 @@
         <v>3</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D42" s="50">
         <v>1</v>
       </c>
       <c r="E42" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="50" t="s">
         <v>56</v>
-      </c>
-      <c r="F42" s="50" t="s">
-        <v>55</v>
       </c>
       <c r="G42" s="50">
         <v>300200101</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I42" s="50" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="J42" s="50">
         <v>300200101</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43">
@@ -3345,16 +3351,16 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G43" s="50">
         <v>300200102</v>
@@ -3369,7 +3375,7 @@
         <v>300200102</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44">
@@ -3380,13 +3386,13 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F44" s="50" t="s">
         <v>27</v>
@@ -3395,7 +3401,7 @@
         <v>300200201</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I44" s="50">
         <v>100</v>
@@ -3404,7 +3410,7 @@
         <v>300200201</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45">
@@ -3415,13 +3421,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>27</v>
@@ -3430,7 +3436,7 @@
         <v>300200301</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I45" s="50">
         <v>100</v>
@@ -3439,7 +3445,7 @@
         <v>300200301</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46">
@@ -3450,16 +3456,16 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F46" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G46" s="50">
         <v>300300000</v>
@@ -3467,14 +3473,14 @@
       <c r="H46" s="50">
         <v>300200000</v>
       </c>
-      <c r="I46" s="50">
+      <c r="I46" s="50" t="s">
         <v>100</v>
       </c>
       <c r="J46" s="50">
         <v>300300000</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47">
@@ -3485,13 +3491,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>37</v>
@@ -3509,7 +3515,7 @@
         <v>300300001</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48">
@@ -3520,13 +3526,13 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F48" s="50" t="s">
         <v>37</v>
@@ -3544,7 +3550,7 @@
         <v>300300002</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49">
@@ -3555,13 +3561,13 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F49" s="50" t="s">
         <v>37</v>
@@ -3579,7 +3585,7 @@
         <v>300300003</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50">
@@ -3590,13 +3596,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>37</v>
@@ -3614,7 +3620,7 @@
         <v>300300004</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51">
@@ -3625,22 +3631,22 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G51" s="50">
         <v>300300101</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I51" s="50">
         <v>100</v>
@@ -3649,7 +3655,7 @@
         <v>300300101</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52">
@@ -3660,16 +3666,16 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F52" s="50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G52" s="50">
         <v>300300102</v>
@@ -3684,7 +3690,7 @@
         <v>300300102</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53">
@@ -3695,13 +3701,13 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F53" s="50" t="s">
         <v>27</v>
@@ -3710,7 +3716,7 @@
         <v>300300201</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I53" s="50">
         <v>100</v>
@@ -3719,7 +3725,7 @@
         <v>300300201</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54">
@@ -3730,13 +3736,13 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F54" s="50" t="s">
         <v>27</v>
@@ -3745,7 +3751,7 @@
         <v>300300301</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I54" s="50">
         <v>100</v>
@@ -3754,7 +3760,7 @@
         <v>300300301</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55">
@@ -3765,16 +3771,16 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G55" s="50">
         <v>300400000</v>
@@ -3789,7 +3795,7 @@
         <v>300400000</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56">
@@ -3800,13 +3806,13 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>37</v>
@@ -3824,7 +3830,7 @@
         <v>300400001</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57">
@@ -3835,13 +3841,13 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F57" s="50" t="s">
         <v>37</v>
@@ -3859,7 +3865,7 @@
         <v>300400002</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3870,13 +3876,13 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F58" s="50" t="s">
         <v>37</v>
@@ -3894,7 +3900,7 @@
         <v>300400003</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3905,13 +3911,13 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F59" s="50" t="s">
         <v>37</v>
@@ -3929,7 +3935,7 @@
         <v>300400004</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3940,13 +3946,13 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>37</v>
@@ -3964,7 +3970,7 @@
         <v>300400005</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3975,22 +3981,22 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F61" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G61" s="50">
         <v>300400101</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I61" s="50">
         <v>100</v>
@@ -3999,7 +4005,7 @@
         <v>300400101</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4010,16 +4016,16 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F62" s="50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G62" s="50">
         <v>300400102</v>
@@ -4034,7 +4040,7 @@
         <v>300400102</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4045,13 +4051,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>27</v>
@@ -4060,7 +4066,7 @@
         <v>300400201</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I63" s="50">
         <v>100</v>
@@ -4069,7 +4075,7 @@
         <v>300400201</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4080,13 +4086,13 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F64" s="50" t="s">
         <v>27</v>
@@ -4095,7 +4101,7 @@
         <v>300400301</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I64" s="50">
         <v>100</v>
@@ -4104,7 +4110,7 @@
         <v>300400301</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65">
@@ -4115,16 +4121,16 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G65" s="50">
         <v>300500000</v>
@@ -4139,7 +4145,7 @@
         <v>300500000</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66">
@@ -4150,13 +4156,13 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F66" s="50" t="s">
         <v>37</v>
@@ -4174,7 +4180,7 @@
         <v>300500001</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4185,13 +4191,13 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F67" s="50" t="s">
         <v>37</v>
@@ -4209,7 +4215,7 @@
         <v>300500002</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4220,13 +4226,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>37</v>
@@ -4244,7 +4250,7 @@
         <v>300500003</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4255,13 +4261,13 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>37</v>
@@ -4279,7 +4285,7 @@
         <v>300500004</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4290,22 +4296,22 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F70" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G70" s="50">
         <v>300500101</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I70" s="50">
         <v>100</v>
@@ -4314,7 +4320,7 @@
         <v>300500101</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4325,16 +4331,16 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G71" s="50">
         <v>300500102</v>
@@ -4349,7 +4355,7 @@
         <v>300500102</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4360,13 +4366,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>27</v>
@@ -4375,7 +4381,7 @@
         <v>300500201</v>
       </c>
       <c r="H72" s="50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I72" s="50">
         <v>100</v>
@@ -4384,7 +4390,7 @@
         <v>300500201</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4395,13 +4401,13 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>27</v>
@@ -4410,7 +4416,7 @@
         <v>300500301</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I73" s="50">
         <v>100</v>
@@ -4419,7 +4425,7 @@
         <v>300500301</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4430,16 +4436,16 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F74" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G74" s="50">
         <v>300600000</v>
@@ -4454,7 +4460,7 @@
         <v>300600000</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75">
@@ -4465,13 +4471,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>37</v>
@@ -4489,7 +4495,7 @@
         <v>300600001</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76">
@@ -4500,13 +4506,13 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>37</v>
@@ -4524,7 +4530,7 @@
         <v>300600002</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77">
@@ -4535,13 +4541,13 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F77" s="50" t="s">
         <v>37</v>
@@ -4559,7 +4565,7 @@
         <v>300600003</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4570,13 +4576,13 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>37</v>
@@ -4594,7 +4600,7 @@
         <v>300600004</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4605,13 +4611,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>37</v>
@@ -4629,7 +4635,7 @@
         <v>300600005</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4640,22 +4646,22 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F80" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G80" s="50">
         <v>300600101</v>
       </c>
       <c r="H80" s="50" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I80" s="50">
         <v>100</v>
@@ -4664,7 +4670,7 @@
         <v>300600101</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4675,16 +4681,16 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F81" s="50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G81" s="50">
         <v>300600102</v>
@@ -4699,7 +4705,7 @@
         <v>300600102</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4710,13 +4716,13 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>27</v>
@@ -4725,7 +4731,7 @@
         <v>300600201</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I82" s="50">
         <v>100</v>
@@ -4734,7 +4740,7 @@
         <v>300600201</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4745,13 +4751,13 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>27</v>
@@ -4760,7 +4766,7 @@
         <v>300600301</v>
       </c>
       <c r="H83" s="50" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I83" s="50">
         <v>100</v>
@@ -4769,7 +4775,7 @@
         <v>300600301</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="84">
@@ -4780,16 +4786,16 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F84" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G84" s="50">
         <v>300700000</v>
@@ -4804,7 +4810,7 @@
         <v>300700000</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85">
@@ -4815,13 +4821,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>37</v>
@@ -4839,7 +4845,7 @@
         <v>300700001</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="86">
@@ -4850,13 +4856,13 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>37</v>
@@ -4874,7 +4880,7 @@
         <v>300700002</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87">
@@ -4885,13 +4891,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F87" s="50" t="s">
         <v>37</v>
@@ -4909,7 +4915,7 @@
         <v>300700003</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="88">
@@ -4920,13 +4926,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>37</v>
@@ -4944,7 +4950,7 @@
         <v>300700004</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="89">
@@ -4955,22 +4961,22 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F89" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G89" s="50">
         <v>300700101</v>
       </c>
       <c r="H89" s="50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I89" s="50">
         <v>100</v>
@@ -4979,7 +4985,7 @@
         <v>300700101</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="90">
@@ -4990,16 +4996,16 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F90" s="50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G90" s="50">
         <v>300700102</v>
@@ -5014,7 +5020,7 @@
         <v>300700102</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91">
@@ -5025,13 +5031,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>27</v>
@@ -5040,7 +5046,7 @@
         <v>300700201</v>
       </c>
       <c r="H91" s="50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I91" s="50">
         <v>100</v>
@@ -5049,7 +5055,7 @@
         <v>300700201</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="92">
@@ -5060,13 +5066,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>27</v>
@@ -5075,7 +5081,7 @@
         <v>300700301</v>
       </c>
       <c r="H92" s="50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I92" s="50">
         <v>100</v>
@@ -5084,7 +5090,7 @@
         <v>300700301</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="93">
@@ -5095,28 +5101,28 @@
         <v>1</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F93" s="50" t="s">
         <v>56</v>
-      </c>
-      <c r="F93" s="50" t="s">
-        <v>55</v>
       </c>
       <c r="G93" s="50">
         <v>100500001</v>
       </c>
       <c r="I93" s="50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J93" s="50">
         <v>100500001</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
   <si>
     <t>id</t>
   </si>
@@ -372,6 +372,9 @@
     <t>孕育人类x10</t>
   </si>
   <si>
+    <t>950</t>
+  </si>
+  <si>
     <t>100200001,300100000,</t>
   </si>
   <si>
@@ -381,7 +384,7 @@
     <t>ui_research_58</t>
   </si>
   <si>
-    <t>950</t>
+    <t>300100000,</t>
   </si>
   <si>
     <t>奖励-可获取人类装备</t>
@@ -432,13 +435,16 @@
     <t>孕育骷髅x10</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>100200001,300200000,</t>
   </si>
   <si>
     <t>可转生为骷髅</t>
   </si>
   <si>
-    <t>150</t>
+    <t>300200000,</t>
   </si>
   <si>
     <t>奖励-可获取骷髅装备</t>
@@ -492,13 +498,16 @@
     <t>孕育史莱姆x10</t>
   </si>
   <si>
+    <t>-650</t>
+  </si>
+  <si>
     <t>100200001,300300000,</t>
   </si>
   <si>
     <t>可转生为史莱姆</t>
   </si>
   <si>
-    <t>-650</t>
+    <t>300300000,</t>
   </si>
   <si>
     <t>奖励-可获取史莱姆装备</t>
@@ -564,6 +573,9 @@
     <t>可转生为魅魔</t>
   </si>
   <si>
+    <t>300400000,</t>
+  </si>
+  <si>
     <t>奖励-可获取魅魔装备</t>
   </si>
   <si>
@@ -609,13 +621,16 @@
     <t>孕育牛头人x10</t>
   </si>
   <si>
+    <t>2550</t>
+  </si>
+  <si>
     <t>100200001,300500000,</t>
   </si>
   <si>
     <t>可转生为牛头人</t>
   </si>
   <si>
-    <t>2550</t>
+    <t>300500000,</t>
   </si>
   <si>
     <t>奖励-可获取牛头人装备</t>
@@ -675,6 +690,9 @@
     <t>可转生为哥布林</t>
   </si>
   <si>
+    <t>300600000,</t>
+  </si>
+  <si>
     <t>奖励-可获取哥布林装备</t>
   </si>
   <si>
@@ -720,13 +738,16 @@
     <t>孕育兽人x10</t>
   </si>
   <si>
+    <t>1750</t>
+  </si>
+  <si>
     <t>100200001,300700000,</t>
   </si>
   <si>
     <t>可转生兽人</t>
   </si>
   <si>
-    <t>1750</t>
+    <t>300700000,</t>
   </si>
   <si>
     <t>奖励-可获取兽人装备</t>
@@ -3080,7 +3101,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="F35" s="50" t="s">
         <v>27</v>
@@ -3089,7 +3110,7 @@
         <v>300100201</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I35" s="50">
         <v>100</v>
@@ -3098,7 +3119,7 @@
         <v>300100201</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36">
@@ -3109,13 +3130,13 @@
         <v>3</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D36" s="50">
         <v>1</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="F36" s="50" t="s">
         <v>27</v>
@@ -3124,16 +3145,16 @@
         <v>300100301</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="I36" s="50">
+        <v>123</v>
+      </c>
+      <c r="I36" s="50" t="s">
         <v>100</v>
       </c>
       <c r="J36" s="50">
         <v>300100301</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37">
@@ -3144,7 +3165,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D37" s="50">
         <v>1</v>
@@ -3165,7 +3186,7 @@
         <v>300200000</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38">
@@ -3182,10 +3203,10 @@
         <v>1</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G38" s="50">
         <v>300200001</v>
@@ -3200,7 +3221,7 @@
         <v>300200001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39">
@@ -3217,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F39" s="50" t="s">
         <v>37</v>
@@ -3229,13 +3250,13 @@
         <v>300200000</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J39" s="50">
         <v>300200002</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40">
@@ -3252,7 +3273,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F40" s="50" t="s">
         <v>37</v>
@@ -3270,7 +3291,7 @@
         <v>300200003</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41">
@@ -3287,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>37</v>
@@ -3305,7 +3326,7 @@
         <v>300200004</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42">
@@ -3331,7 +3352,7 @@
         <v>300200101</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I42" s="50" t="s">
         <v>100</v>
@@ -3340,7 +3361,7 @@
         <v>300200101</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43">
@@ -3375,7 +3396,7 @@
         <v>300200102</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44">
@@ -3386,13 +3407,13 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="F44" s="50" t="s">
         <v>27</v>
@@ -3401,7 +3422,7 @@
         <v>300200201</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I44" s="50">
         <v>100</v>
@@ -3410,7 +3431,7 @@
         <v>300200201</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45">
@@ -3421,13 +3442,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>27</v>
@@ -3436,16 +3457,16 @@
         <v>300200301</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="I45" s="50">
-        <v>100</v>
+        <v>143</v>
+      </c>
+      <c r="I45" s="50" t="s">
+        <v>58</v>
       </c>
       <c r="J45" s="50">
         <v>300200301</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46">
@@ -3456,7 +3477,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
@@ -3480,7 +3501,7 @@
         <v>300300000</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47">
@@ -3491,13 +3512,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>37</v>
@@ -3515,7 +3536,7 @@
         <v>300300001</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48">
@@ -3526,13 +3547,13 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F48" s="50" t="s">
         <v>37</v>
@@ -3550,7 +3571,7 @@
         <v>300300002</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49">
@@ -3561,13 +3582,13 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F49" s="50" t="s">
         <v>37</v>
@@ -3585,7 +3606,7 @@
         <v>300300003</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50">
@@ -3596,13 +3617,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>37</v>
@@ -3620,7 +3641,7 @@
         <v>300300004</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51">
@@ -3646,7 +3667,7 @@
         <v>300300101</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I51" s="50">
         <v>100</v>
@@ -3655,7 +3676,7 @@
         <v>300300101</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52">
@@ -3690,7 +3711,7 @@
         <v>300300102</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53">
@@ -3701,13 +3722,13 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="F53" s="50" t="s">
         <v>27</v>
@@ -3716,7 +3737,7 @@
         <v>300300201</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I53" s="50">
         <v>100</v>
@@ -3725,7 +3746,7 @@
         <v>300300201</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54">
@@ -3736,13 +3757,13 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="F54" s="50" t="s">
         <v>27</v>
@@ -3751,16 +3772,16 @@
         <v>300300301</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="I54" s="50">
-        <v>100</v>
+        <v>164</v>
+      </c>
+      <c r="I54" s="50" t="s">
+        <v>29</v>
       </c>
       <c r="J54" s="50">
         <v>300300301</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55">
@@ -3771,13 +3792,13 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F55" s="50" t="s">
         <v>57</v>
@@ -3795,7 +3816,7 @@
         <v>300400000</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56">
@@ -3812,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>37</v>
@@ -3830,7 +3851,7 @@
         <v>300400001</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57">
@@ -3841,13 +3862,13 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F57" s="50" t="s">
         <v>37</v>
@@ -3865,7 +3886,7 @@
         <v>300400002</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3876,13 +3897,13 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F58" s="50" t="s">
         <v>37</v>
@@ -3900,7 +3921,7 @@
         <v>300400003</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3911,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F59" s="50" t="s">
         <v>37</v>
@@ -3935,7 +3956,7 @@
         <v>300400004</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3946,13 +3967,13 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>37</v>
@@ -3970,7 +3991,7 @@
         <v>300400005</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3987,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F61" s="50" t="s">
         <v>56</v>
@@ -3996,7 +4017,7 @@
         <v>300400101</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I61" s="50">
         <v>100</v>
@@ -4005,7 +4026,7 @@
         <v>300400101</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4022,7 +4043,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>60</v>
@@ -4040,7 +4061,7 @@
         <v>300400102</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4051,13 +4072,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>27</v>
@@ -4066,7 +4087,7 @@
         <v>300400201</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I63" s="50">
         <v>100</v>
@@ -4075,7 +4096,7 @@
         <v>300400201</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4086,13 +4107,13 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F64" s="50" t="s">
         <v>27</v>
@@ -4101,7 +4122,7 @@
         <v>300400301</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I64" s="50">
         <v>100</v>
@@ -4110,7 +4131,7 @@
         <v>300400301</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65">
@@ -4121,13 +4142,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>57</v>
@@ -4145,7 +4166,7 @@
         <v>300500000</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66">
@@ -4162,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F66" s="50" t="s">
         <v>37</v>
@@ -4180,7 +4201,7 @@
         <v>300500001</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4197,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F67" s="50" t="s">
         <v>37</v>
@@ -4215,7 +4236,7 @@
         <v>300500002</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4232,7 +4253,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>37</v>
@@ -4250,7 +4271,7 @@
         <v>300500003</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4267,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>37</v>
@@ -4285,7 +4306,7 @@
         <v>300500004</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4302,7 +4323,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>56</v>
@@ -4311,7 +4332,7 @@
         <v>300500101</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I70" s="50">
         <v>100</v>
@@ -4320,7 +4341,7 @@
         <v>300500101</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4337,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>60</v>
@@ -4355,7 +4376,7 @@
         <v>300500102</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4366,13 +4387,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>27</v>
@@ -4381,7 +4402,7 @@
         <v>300500201</v>
       </c>
       <c r="H72" s="50" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I72" s="50">
         <v>100</v>
@@ -4390,7 +4411,7 @@
         <v>300500201</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4401,13 +4422,13 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>27</v>
@@ -4416,7 +4437,7 @@
         <v>300500301</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="I73" s="50">
         <v>100</v>
@@ -4425,7 +4446,7 @@
         <v>300500301</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4436,13 +4457,13 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>57</v>
@@ -4460,7 +4481,7 @@
         <v>300600000</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75">
@@ -4471,13 +4492,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>37</v>
@@ -4495,7 +4516,7 @@
         <v>300600001</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76">
@@ -4512,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>37</v>
@@ -4530,7 +4551,7 @@
         <v>300600002</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="77">
@@ -4547,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F77" s="50" t="s">
         <v>37</v>
@@ -4565,7 +4586,7 @@
         <v>300600003</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4582,7 +4603,7 @@
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>37</v>
@@ -4600,7 +4621,7 @@
         <v>300600004</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4617,7 +4638,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>37</v>
@@ -4635,7 +4656,7 @@
         <v>300600005</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4652,7 +4673,7 @@
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>56</v>
@@ -4661,7 +4682,7 @@
         <v>300600101</v>
       </c>
       <c r="H80" s="50" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I80" s="50">
         <v>100</v>
@@ -4670,7 +4691,7 @@
         <v>300600101</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4687,7 +4708,7 @@
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>60</v>
@@ -4705,7 +4726,7 @@
         <v>300600102</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4716,13 +4737,13 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>27</v>
@@ -4731,7 +4752,7 @@
         <v>300600201</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I82" s="50">
         <v>100</v>
@@ -4740,7 +4761,7 @@
         <v>300600201</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4751,13 +4772,13 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>27</v>
@@ -4766,7 +4787,7 @@
         <v>300600301</v>
       </c>
       <c r="H83" s="50" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="I83" s="50">
         <v>100</v>
@@ -4775,7 +4796,7 @@
         <v>300600301</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84">
@@ -4786,13 +4807,13 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>57</v>
@@ -4810,7 +4831,7 @@
         <v>300700000</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85">
@@ -4827,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>37</v>
@@ -4845,7 +4866,7 @@
         <v>300700001</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="86">
@@ -4862,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>37</v>
@@ -4880,7 +4901,7 @@
         <v>300700002</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="87">
@@ -4897,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F87" s="50" t="s">
         <v>37</v>
@@ -4915,7 +4936,7 @@
         <v>300700003</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="88">
@@ -4932,7 +4953,7 @@
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>37</v>
@@ -4950,7 +4971,7 @@
         <v>300700004</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89">
@@ -4967,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>56</v>
@@ -4976,7 +4997,7 @@
         <v>300700101</v>
       </c>
       <c r="H89" s="50" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="I89" s="50">
         <v>100</v>
@@ -4985,7 +5006,7 @@
         <v>300700101</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90">
@@ -5002,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>60</v>
@@ -5020,7 +5041,7 @@
         <v>300700102</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91">
@@ -5031,13 +5052,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>27</v>
@@ -5046,7 +5067,7 @@
         <v>300700201</v>
       </c>
       <c r="H91" s="50" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="I91" s="50">
         <v>100</v>
@@ -5055,7 +5076,7 @@
         <v>300700201</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92">
@@ -5066,13 +5087,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>27</v>
@@ -5081,7 +5102,7 @@
         <v>300700301</v>
       </c>
       <c r="H92" s="50" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I92" s="50">
         <v>100</v>
@@ -5090,7 +5111,7 @@
         <v>300700301</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="93">
@@ -5101,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
@@ -5122,7 +5143,7 @@
         <v>100500001</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -1367,16 +1367,21 @@
       </c>
       <c r="E4" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>-300</t>
         </is>
       </c>
       <c r="F4" s="50" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G4" s="50" t="n">
         <v>100000000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
       </c>
       <c r="I4" s="50" t="inlineStr">
         <is>
@@ -1409,12 +1414,12 @@
       </c>
       <c r="E5" s="50" t="inlineStr">
         <is>
-          <t>-351</t>
+          <t>-500</t>
         </is>
       </c>
       <c r="F5" s="50" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G5" s="50" t="n">
@@ -1454,16 +1459,21 @@
       </c>
       <c r="E6" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F6" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G6" s="50" t="n">
         <v>100100001</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
       </c>
       <c r="I6" s="50" t="inlineStr">
         <is>
@@ -1494,11 +1504,15 @@
       <c r="D7" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="50" t="n">
-        <v>350</v>
-      </c>
-      <c r="F7" s="50" t="n">
-        <v>350</v>
+      <c r="E7" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F7" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="G7" s="50" t="n">
         <v>100100002</v>
@@ -1535,12 +1549,14 @@
       <c r="D8" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="50" t="n">
-        <v>350</v>
+      <c r="E8" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="F8" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G8" s="50" t="n">
@@ -1582,12 +1598,12 @@
       </c>
       <c r="E9" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F9" s="50" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G9" s="50" t="n">
@@ -1629,16 +1645,21 @@
       </c>
       <c r="E10" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-300</t>
         </is>
       </c>
       <c r="F10" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>-300</t>
         </is>
       </c>
       <c r="G10" s="50" t="n">
         <v>100200001</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
       </c>
       <c r="I10" s="50" t="inlineStr">
         <is>
@@ -1671,12 +1692,12 @@
       </c>
       <c r="E11" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-500</t>
         </is>
       </c>
       <c r="F11" s="50" t="inlineStr">
         <is>
-          <t>-400</t>
+          <t>-300</t>
         </is>
       </c>
       <c r="G11" s="50" t="n">
@@ -1714,19 +1735,21 @@
       </c>
       <c r="E12" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-700</t>
         </is>
       </c>
       <c r="F12" s="50" t="inlineStr">
         <is>
-          <t>-600</t>
+          <t>-300</t>
         </is>
       </c>
       <c r="G12" s="50" t="n">
         <v>100200003</v>
       </c>
-      <c r="H12" s="50" t="n">
-        <v>100200001</v>
+      <c r="H12" s="50" t="inlineStr">
+        <is>
+          <t>100200002</t>
+        </is>
       </c>
       <c r="I12" s="50" t="n">
         <v>100</v>
@@ -1759,17 +1782,22 @@
       </c>
       <c r="E13" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="G13" s="50" t="n">
         <v>100300001</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
+      </c>
       <c r="I13" s="50" t="inlineStr">
         <is>
           <t>10</t>
@@ -1785,277 +1813,298 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="n">
-        <v>100310112</v>
-      </c>
-      <c r="B14" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_11</t>
-        </is>
-      </c>
-      <c r="D14" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" s="50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="F14" s="50" t="inlineStr">
+      <c r="A14" t="n">
+        <v>100300002</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-150</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-800</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>100300002</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>100300003</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>100300002</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>传送门详情-线路数量预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100300003</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="50" t="n">
-        <v>100310112</v>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-600</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>100300003</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>100300001</t>
         </is>
       </c>
-      <c r="I14" s="50" t="inlineStr">
-        <is>
-          <t>200,400,800,1600,3200,6400,12800,25600,51200,</t>
-        </is>
-      </c>
-      <c r="J14" s="50" t="n">
-        <v>100310112</v>
-      </c>
-      <c r="K14" s="50" t="inlineStr">
-        <is>
-          <t>剑与魔法：征服难度+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="B15" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_57</t>
-        </is>
-      </c>
-      <c r="D15" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
-      </c>
-      <c r="F15" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
-      </c>
-      <c r="G15" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="I15" s="50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="K15" s="50" t="inlineStr">
-        <is>
-          <t>开启孕育功能</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>100300003</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>传送门详情-关卡数量预览</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="B16" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_57</t>
-        </is>
-      </c>
-      <c r="D16" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
-      </c>
-      <c r="F16" s="50" t="inlineStr">
+      <c r="A16" t="n">
+        <v>100300004</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-800</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>100300004</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>100300003</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>100300004</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>传送门详情-路径长度预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100300005</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-800</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>100300005</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>100300003</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>100300005</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>传送门详情-奖励预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100300006</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>-400</t>
         </is>
       </c>
-      <c r="G16" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="H16" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="I16" s="50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="K16" s="50" t="inlineStr">
-        <is>
-          <t>孕育可跳过</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="B17" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_57</t>
-        </is>
-      </c>
-      <c r="D17" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
-      </c>
-      <c r="F17" s="50" t="inlineStr">
-        <is>
-          <t>-599</t>
-        </is>
-      </c>
-      <c r="G17" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="H17" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="I17" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J17" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="K17" s="50" t="inlineStr">
-        <is>
-          <t>解锁孕育稀有度：R</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="50" t="n">
-        <v>100401001</v>
-      </c>
-      <c r="B18" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_57</t>
-        </is>
-      </c>
-      <c r="D18" s="50" t="n">
-        <v>50</v>
-      </c>
-      <c r="E18" s="50" t="inlineStr">
-        <is>
-          <t>-396</t>
-        </is>
-      </c>
-      <c r="F18" s="50" t="inlineStr">
-        <is>
-          <t>-600</t>
-        </is>
-      </c>
-      <c r="G18" s="50" t="n">
-        <v>100401001</v>
-      </c>
-      <c r="H18" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="I18" s="50" t="inlineStr">
-        <is>
-          <t>100*1</t>
-        </is>
-      </c>
-      <c r="J18" s="50" t="n">
-        <v>100401001</v>
-      </c>
-      <c r="K18" s="50" t="inlineStr">
-        <is>
-          <t>孕育稀有度：R 概率+1%</t>
+      <c r="G18" t="n">
+        <v>100300006</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>100300001</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>300*2</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>100300006</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>传送门刷新解锁</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="50" t="n">
-        <v>100402000</v>
+        <v>100310112</v>
       </c>
       <c r="B19" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="50" t="inlineStr">
         <is>
-          <t>ui_research_57</t>
+          <t>ui_research_11</t>
         </is>
       </c>
       <c r="D19" s="50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E19" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F19" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-600</t>
         </is>
       </c>
       <c r="G19" s="50" t="n">
-        <v>100402000</v>
+        <v>100310112</v>
       </c>
       <c r="H19" s="50" t="inlineStr">
         <is>
-          <t>100401000,100401001,</t>
-        </is>
-      </c>
-      <c r="I19" s="50" t="n">
-        <v>1000</v>
+          <t>100300001</t>
+        </is>
+      </c>
+      <c r="I19" s="50" t="inlineStr">
+        <is>
+          <t>200,400,800,1600,3200,6400,12800,25600,51200,</t>
+        </is>
       </c>
       <c r="J19" s="50" t="n">
-        <v>100402000</v>
+        <v>100310112</v>
       </c>
       <c r="K19" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>剑与魔法：征服难度+1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="n">
-        <v>100402001</v>
+        <v>100400000</v>
       </c>
       <c r="B20" s="50" t="n">
         <v>1</v>
@@ -2066,41 +2115,43 @@
         </is>
       </c>
       <c r="D20" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E20" s="50" t="inlineStr">
         <is>
-          <t>-400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G20" s="50" t="n">
-        <v>100402001</v>
-      </c>
-      <c r="H20" s="50" t="n">
-        <v>100402000</v>
+        <v>100400000</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
       </c>
       <c r="I20" s="50" t="inlineStr">
         <is>
-          <t>1000*1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" s="50" t="n">
-        <v>100402001</v>
+        <v>100400000</v>
       </c>
       <c r="K20" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="50" t="n">
-        <v>100403000</v>
+        <v>100400001</v>
       </c>
       <c r="B21" s="50" t="n">
         <v>1</v>
@@ -2115,37 +2166,37 @@
       </c>
       <c r="E21" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" s="50" t="inlineStr">
         <is>
-          <t>-1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G21" s="50" t="n">
-        <v>100403000</v>
-      </c>
-      <c r="H21" s="50" t="inlineStr">
-        <is>
-          <t>100402000,100402001,</t>
-        </is>
-      </c>
-      <c r="I21" s="50" t="n">
-        <v>10000</v>
+        <v>100400001</v>
+      </c>
+      <c r="H21" s="50" t="n">
+        <v>100400000</v>
+      </c>
+      <c r="I21" s="50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="J21" s="50" t="n">
-        <v>100403000</v>
+        <v>100400001</v>
       </c>
       <c r="K21" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="50" t="n">
-        <v>100403001</v>
+        <v>100401000</v>
       </c>
       <c r="B22" s="50" t="n">
         <v>1</v>
@@ -2156,459 +2207,467 @@
         </is>
       </c>
       <c r="D22" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E22" s="50" t="inlineStr">
         <is>
-          <t>-400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="50" t="inlineStr">
         <is>
-          <t>-1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="G22" s="50" t="n">
-        <v>100403001</v>
+        <v>100401000</v>
       </c>
       <c r="H22" s="50" t="n">
-        <v>100403000</v>
+        <v>100400001</v>
       </c>
       <c r="I22" s="50" t="inlineStr">
         <is>
-          <t>10000*1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J22" s="50" t="n">
-        <v>100403001</v>
+        <v>100401000</v>
       </c>
       <c r="K22" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="50" t="n">
-        <v>200000001</v>
+        <v>100401001</v>
       </c>
       <c r="B23" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>ui_research_5</t>
+          <t>ui_research_57</t>
         </is>
       </c>
       <c r="D23" s="50" t="n">
-        <v>30</v>
-      </c>
-      <c r="E23" s="50" t="n">
-        <v>-200</v>
-      </c>
-      <c r="F23" s="50" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="E23" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F23" s="50" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="G23" s="50" t="n">
-        <v>200000001</v>
+        <v>100401001</v>
+      </c>
+      <c r="H23" s="50" t="n">
+        <v>100401000</v>
       </c>
       <c r="I23" s="50" t="inlineStr">
         <is>
-          <t>50,100,200,500,1000,2000,5000,10000,50000,100000,</t>
+          <t>100*1</t>
         </is>
       </c>
       <c r="J23" s="50" t="n">
-        <v>200000001</v>
+        <v>100401001</v>
       </c>
       <c r="K23" s="50" t="inlineStr">
         <is>
-          <t>阵容上限+1</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50" t="n">
-        <v>200100001</v>
+        <v>100402000</v>
       </c>
       <c r="B24" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="50" t="inlineStr">
         <is>
-          <t>ui_research_6</t>
+          <t>ui_research_57</t>
         </is>
       </c>
       <c r="D24" s="50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E24" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="G24" s="50" t="n">
-        <v>200100001</v>
-      </c>
-      <c r="I24" s="50" t="inlineStr">
-        <is>
-          <t>100,200,300,400,</t>
-        </is>
+        <v>100402000</v>
+      </c>
+      <c r="H24" s="50" t="inlineStr">
+        <is>
+          <t>100401000,100401001,</t>
+        </is>
+      </c>
+      <c r="I24" s="50" t="n">
+        <v>1000</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>200100001</v>
+        <v>100402000</v>
       </c>
       <c r="K24" s="50" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50" t="n">
-        <v>200200001</v>
+        <v>100402001</v>
       </c>
       <c r="B25" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="50" t="inlineStr">
         <is>
-          <t>ui_research_60</t>
+          <t>ui_research_57</t>
         </is>
       </c>
       <c r="D25" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="50" t="n">
-        <v>-200</v>
-      </c>
-      <c r="F25" s="50" t="n">
-        <v>-200</v>
+        <v>50</v>
+      </c>
+      <c r="E25" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F25" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="G25" s="50" t="n">
-        <v>200200001</v>
+        <v>100402001</v>
+      </c>
+      <c r="H25" s="50" t="n">
+        <v>100402000</v>
       </c>
       <c r="I25" s="50" t="inlineStr">
         <is>
-          <t>100,500,1000,5000,10000,50000</t>
+          <t>1000*1</t>
         </is>
       </c>
       <c r="J25" s="50" t="n">
-        <v>200200001</v>
+        <v>100402001</v>
       </c>
       <c r="K25" s="50" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="50" t="n">
-        <v>200300001</v>
+        <v>100403000</v>
       </c>
       <c r="B26" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="50" t="inlineStr">
         <is>
-          <t>ui_research_61</t>
+          <t>ui_research_57</t>
         </is>
       </c>
       <c r="D26" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="50" t="n">
-        <v>-200</v>
+        <v>1</v>
+      </c>
+      <c r="E26" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="50" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="G26" s="50" t="n">
-        <v>200300001</v>
-      </c>
-      <c r="I26" s="50" t="inlineStr">
-        <is>
-          <t>100,500,1000,5000,10000</t>
-        </is>
+        <v>100403000</v>
+      </c>
+      <c r="H26" s="50" t="inlineStr">
+        <is>
+          <t>100402000,100402001,</t>
+        </is>
+      </c>
+      <c r="I26" s="50" t="n">
+        <v>10000</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>200300001</v>
+        <v>100403000</v>
       </c>
       <c r="K26" s="50" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>200400001</v>
-      </c>
-      <c r="B27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ui_research_61</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>200</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-200</v>
-      </c>
-      <c r="G27" t="n">
-        <v>200400001</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100,500,1000</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>200400001</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>魔王魔力恢复速度+1/s</t>
+      <c r="A27" s="50" t="n">
+        <v>100403001</v>
+      </c>
+      <c r="B27" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_57</t>
+        </is>
+      </c>
+      <c r="D27" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F27" s="50" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G27" s="50" t="n">
+        <v>100403001</v>
+      </c>
+      <c r="H27" s="50" t="n">
+        <v>100403000</v>
+      </c>
+      <c r="I27" s="50" t="inlineStr">
+        <is>
+          <t>10000*1</t>
+        </is>
+      </c>
+      <c r="J27" s="50" t="n">
+        <v>100403001</v>
+      </c>
+      <c r="K27" s="50" t="inlineStr">
+        <is>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="50" t="n">
-        <v>300100000</v>
+        <v>200000001</v>
       </c>
       <c r="B28" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_5</t>
         </is>
       </c>
       <c r="D28" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="50" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="F28" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="E28" s="50" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F28" s="50" t="n">
+        <v>0</v>
       </c>
       <c r="G28" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="H28" s="50" t="n">
-        <v>300200000</v>
+        <v>200000001</v>
       </c>
       <c r="I28" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>50,100,200,500,1000,2000,5000,10000,50000,100000,</t>
         </is>
       </c>
       <c r="J28" s="50" t="n">
-        <v>300100000</v>
+        <v>200000001</v>
       </c>
       <c r="K28" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>阵容上限+1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="50" t="n">
-        <v>300100001</v>
+        <v>200100001</v>
       </c>
       <c r="B29" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_6</t>
         </is>
       </c>
       <c r="D29" s="50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" s="50" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F29" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G29" s="50" t="n">
-        <v>300100001</v>
-      </c>
-      <c r="H29" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="I29" s="50" t="n">
-        <v>100</v>
+        <v>200100001</v>
+      </c>
+      <c r="I29" s="50" t="inlineStr">
+        <is>
+          <t>100,200,300,400,</t>
+        </is>
       </c>
       <c r="J29" s="50" t="n">
-        <v>300100001</v>
+        <v>200100001</v>
       </c>
       <c r="K29" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="50" t="n">
-        <v>300100002</v>
+        <v>200200001</v>
       </c>
       <c r="B30" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_60</t>
         </is>
       </c>
       <c r="D30" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="50" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="F30" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="E30" s="50" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F30" s="50" t="n">
+        <v>-200</v>
       </c>
       <c r="G30" s="50" t="n">
-        <v>300100002</v>
-      </c>
-      <c r="H30" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="I30" s="50" t="n">
-        <v>100</v>
+        <v>200200001</v>
+      </c>
+      <c r="I30" s="50" t="inlineStr">
+        <is>
+          <t>100,500,1000,5000,10000,50000</t>
+        </is>
       </c>
       <c r="J30" s="50" t="n">
-        <v>300100002</v>
+        <v>200200001</v>
       </c>
       <c r="K30" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="50" t="n">
-        <v>300100003</v>
+        <v>200300001</v>
       </c>
       <c r="B31" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_61</t>
         </is>
       </c>
       <c r="D31" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="50" t="inlineStr">
-        <is>
-          <t>875</t>
-        </is>
-      </c>
-      <c r="F31" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E31" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="50" t="n">
+        <v>-200</v>
       </c>
       <c r="G31" s="50" t="n">
-        <v>300100003</v>
-      </c>
-      <c r="H31" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="I31" s="50" t="n">
-        <v>100</v>
+        <v>200300001</v>
+      </c>
+      <c r="I31" s="50" t="inlineStr">
+        <is>
+          <t>100,500,1000,5000,10000</t>
+        </is>
       </c>
       <c r="J31" s="50" t="n">
-        <v>300100003</v>
+        <v>200300001</v>
       </c>
       <c r="K31" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50" t="n">
-        <v>300100004</v>
+        <v>200400001</v>
       </c>
       <c r="B32" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_61</t>
         </is>
       </c>
       <c r="D32" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="50" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="F32" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E32" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="F32" s="50" t="n">
+        <v>-200</v>
       </c>
       <c r="G32" s="50" t="n">
-        <v>300100004</v>
-      </c>
-      <c r="H32" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="I32" s="50" t="n">
-        <v>100</v>
+        <v>200400001</v>
+      </c>
+      <c r="I32" s="50" t="inlineStr">
+        <is>
+          <t>100,500,1000</t>
+        </is>
       </c>
       <c r="J32" s="50" t="n">
-        <v>300100004</v>
+        <v>200400001</v>
       </c>
       <c r="K32" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="50" t="n">
-        <v>300100101</v>
+        <v>300100000</v>
       </c>
       <c r="B33" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D33" s="50" t="n">
@@ -2621,39 +2680,39 @@
       </c>
       <c r="F33" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G33" s="50" t="n">
-        <v>300100101</v>
-      </c>
-      <c r="H33" s="50" t="inlineStr">
-        <is>
-          <t>300100001|300100002|300100003|300100004|</t>
-        </is>
-      </c>
-      <c r="I33" s="50" t="n">
-        <v>100</v>
+        <v>300100000</v>
+      </c>
+      <c r="H33" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="I33" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="J33" s="50" t="n">
-        <v>300100101</v>
+        <v>300100000</v>
       </c>
       <c r="K33" s="50" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="50" t="n">
-        <v>300100102</v>
+        <v>300100001</v>
       </c>
       <c r="B34" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D34" s="50" t="n">
@@ -2661,42 +2720,42 @@
       </c>
       <c r="E34" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F34" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G34" s="50" t="n">
-        <v>300100102</v>
+        <v>300100001</v>
       </c>
       <c r="H34" s="50" t="n">
-        <v>300100101</v>
+        <v>300100000</v>
       </c>
       <c r="I34" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>300100102</v>
+        <v>300100001</v>
       </c>
       <c r="K34" s="50" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="50" t="n">
-        <v>300100201</v>
+        <v>300100002</v>
       </c>
       <c r="B35" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C35" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D35" s="50" t="n">
@@ -2704,44 +2763,42 @@
       </c>
       <c r="E35" s="50" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F35" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G35" s="50" t="n">
-        <v>300100201</v>
-      </c>
-      <c r="H35" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300100000,</t>
-        </is>
+        <v>300100002</v>
+      </c>
+      <c r="H35" s="50" t="n">
+        <v>300100000</v>
       </c>
       <c r="I35" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J35" s="50" t="n">
-        <v>300100201</v>
+        <v>300100002</v>
       </c>
       <c r="K35" s="50" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="50" t="n">
-        <v>300100301</v>
+        <v>300100003</v>
       </c>
       <c r="B36" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D36" s="50" t="n">
@@ -2749,46 +2806,42 @@
       </c>
       <c r="E36" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F36" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G36" s="50" t="n">
-        <v>300100301</v>
-      </c>
-      <c r="H36" s="50" t="inlineStr">
-        <is>
-          <t>300100000,</t>
-        </is>
-      </c>
-      <c r="I36" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+        <v>300100003</v>
+      </c>
+      <c r="H36" s="50" t="n">
+        <v>300100000</v>
+      </c>
+      <c r="I36" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J36" s="50" t="n">
-        <v>300100301</v>
+        <v>300100003</v>
       </c>
       <c r="K36" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="50" t="n">
-        <v>300200000</v>
+        <v>300100004</v>
       </c>
       <c r="B37" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D37" s="50" t="n">
@@ -2796,41 +2849,42 @@
       </c>
       <c r="E37" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F37" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G37" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I37" s="50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+        <v>300100004</v>
+      </c>
+      <c r="H37" s="50" t="n">
+        <v>300100000</v>
+      </c>
+      <c r="I37" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J37" s="50" t="n">
-        <v>300200000</v>
+        <v>300100004</v>
       </c>
       <c r="K37" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="50" t="n">
-        <v>300200001</v>
+        <v>300100101</v>
       </c>
       <c r="B38" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D38" s="50" t="n">
@@ -2838,44 +2892,44 @@
       </c>
       <c r="E38" s="50" t="inlineStr">
         <is>
-          <t>-223</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F38" s="50" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G38" s="50" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="H38" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I38" s="50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>300100101</v>
+      </c>
+      <c r="H38" s="50" t="inlineStr">
+        <is>
+          <t>300100001|300100002|300100003|300100004|</t>
+        </is>
+      </c>
+      <c r="I38" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J38" s="50" t="n">
-        <v>300200001</v>
+        <v>300100101</v>
       </c>
       <c r="K38" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50" t="n">
-        <v>300200002</v>
+        <v>300100102</v>
       </c>
       <c r="B39" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D39" s="50" t="n">
@@ -2883,44 +2937,42 @@
       </c>
       <c r="E39" s="50" t="inlineStr">
         <is>
-          <t>-75</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F39" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G39" s="50" t="n">
-        <v>300200002</v>
+        <v>300100102</v>
       </c>
       <c r="H39" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I39" s="50" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+        <v>300100101</v>
+      </c>
+      <c r="I39" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J39" s="50" t="n">
-        <v>300200002</v>
+        <v>300100102</v>
       </c>
       <c r="K39" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="50" t="n">
-        <v>300200003</v>
+        <v>300100201</v>
       </c>
       <c r="B40" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C40" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D40" s="50" t="n">
@@ -2928,44 +2980,44 @@
       </c>
       <c r="E40" s="50" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F40" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G40" s="50" t="n">
-        <v>300200003</v>
-      </c>
-      <c r="H40" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I40" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>300100201</v>
+      </c>
+      <c r="H40" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300100000,</t>
+        </is>
+      </c>
+      <c r="I40" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J40" s="50" t="n">
-        <v>300200003</v>
+        <v>300100201</v>
       </c>
       <c r="K40" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="50" t="n">
-        <v>300200004</v>
+        <v>300100301</v>
       </c>
       <c r="B41" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C41" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D41" s="50" t="n">
@@ -2973,44 +3025,46 @@
       </c>
       <c r="E41" s="50" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F41" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G41" s="50" t="n">
-        <v>300200004</v>
-      </c>
-      <c r="H41" s="50" t="n">
-        <v>300200000</v>
+        <v>300100301</v>
+      </c>
+      <c r="H41" s="50" t="inlineStr">
+        <is>
+          <t>300100000,</t>
+        </is>
       </c>
       <c r="I41" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J41" s="50" t="n">
-        <v>300200004</v>
+        <v>300100301</v>
       </c>
       <c r="K41" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="50" t="n">
-        <v>300200101</v>
+        <v>300200000</v>
       </c>
       <c r="B42" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D42" s="50" t="n">
@@ -3023,41 +3077,36 @@
       </c>
       <c r="F42" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G42" s="50" t="n">
-        <v>300200101</v>
-      </c>
-      <c r="H42" s="50" t="inlineStr">
-        <is>
-          <t>300200001|300200002|300200003|300200004|</t>
-        </is>
+        <v>300200000</v>
       </c>
       <c r="I42" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" s="50" t="n">
-        <v>300200101</v>
+        <v>300200000</v>
       </c>
       <c r="K42" s="50" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="50" t="n">
-        <v>300200102</v>
+        <v>300200001</v>
       </c>
       <c r="B43" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C43" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D43" s="50" t="n">
@@ -3065,42 +3114,44 @@
       </c>
       <c r="E43" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-223</t>
         </is>
       </c>
       <c r="F43" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G43" s="50" t="n">
-        <v>300200102</v>
+        <v>300200001</v>
       </c>
       <c r="H43" s="50" t="n">
-        <v>300200101</v>
-      </c>
-      <c r="I43" s="50" t="n">
-        <v>100</v>
+        <v>300200000</v>
+      </c>
+      <c r="I43" s="50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J43" s="50" t="n">
-        <v>300200102</v>
+        <v>300200001</v>
       </c>
       <c r="K43" s="50" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="50" t="n">
-        <v>300200201</v>
+        <v>300200002</v>
       </c>
       <c r="B44" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D44" s="50" t="n">
@@ -3108,44 +3159,44 @@
       </c>
       <c r="E44" s="50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>-75</t>
         </is>
       </c>
       <c r="F44" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G44" s="50" t="n">
-        <v>300200201</v>
-      </c>
-      <c r="H44" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300200000,</t>
-        </is>
-      </c>
-      <c r="I44" s="50" t="n">
-        <v>100</v>
+        <v>300200002</v>
+      </c>
+      <c r="H44" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="I44" s="50" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="J44" s="50" t="n">
-        <v>300200201</v>
+        <v>300200002</v>
       </c>
       <c r="K44" s="50" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="50" t="n">
-        <v>300200301</v>
+        <v>300200003</v>
       </c>
       <c r="B45" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C45" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D45" s="50" t="n">
@@ -3153,46 +3204,44 @@
       </c>
       <c r="E45" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F45" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G45" s="50" t="n">
-        <v>300200301</v>
-      </c>
-      <c r="H45" s="50" t="inlineStr">
-        <is>
-          <t>300200000,</t>
-        </is>
+        <v>300200003</v>
+      </c>
+      <c r="H45" s="50" t="n">
+        <v>300200000</v>
       </c>
       <c r="I45" s="50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J45" s="50" t="n">
-        <v>300200301</v>
+        <v>300200003</v>
       </c>
       <c r="K45" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="50" t="n">
-        <v>300300000</v>
+        <v>300200004</v>
       </c>
       <c r="B46" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C46" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D46" s="50" t="n">
@@ -3200,44 +3249,44 @@
       </c>
       <c r="E46" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F46" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G46" s="50" t="n">
-        <v>300300000</v>
+        <v>300200004</v>
       </c>
       <c r="H46" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I46" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J46" s="50" t="n">
-        <v>300300000</v>
+        <v>300200004</v>
       </c>
       <c r="K46" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="50" t="n">
-        <v>300300001</v>
+        <v>300200101</v>
       </c>
       <c r="B47" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C47" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D47" s="50" t="n">
@@ -3245,42 +3294,46 @@
       </c>
       <c r="E47" s="50" t="inlineStr">
         <is>
-          <t>-1025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F47" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G47" s="50" t="n">
-        <v>300300001</v>
-      </c>
-      <c r="H47" s="50" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="I47" s="50" t="n">
-        <v>100</v>
+        <v>300200101</v>
+      </c>
+      <c r="H47" s="50" t="inlineStr">
+        <is>
+          <t>300200001|300200002|300200003|300200004|</t>
+        </is>
+      </c>
+      <c r="I47" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="J47" s="50" t="n">
-        <v>300300001</v>
+        <v>300200101</v>
       </c>
       <c r="K47" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="50" t="n">
-        <v>300300002</v>
+        <v>300200102</v>
       </c>
       <c r="B48" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="50" t="inlineStr">
         <is>
-          <t>ui_research_54</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D48" s="50" t="n">
@@ -3288,42 +3341,42 @@
       </c>
       <c r="E48" s="50" t="inlineStr">
         <is>
-          <t>-875</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G48" s="50" t="n">
-        <v>300300002</v>
+        <v>300200102</v>
       </c>
       <c r="H48" s="50" t="n">
-        <v>300300000</v>
+        <v>300200101</v>
       </c>
       <c r="I48" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J48" s="50" t="n">
-        <v>300300002</v>
+        <v>300200102</v>
       </c>
       <c r="K48" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="50" t="n">
-        <v>300300003</v>
+        <v>300200201</v>
       </c>
       <c r="B49" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="50" t="inlineStr">
         <is>
-          <t>ui_research_54</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D49" s="50" t="n">
@@ -3331,42 +3384,44 @@
       </c>
       <c r="E49" s="50" t="inlineStr">
         <is>
-          <t>-725</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F49" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G49" s="50" t="n">
-        <v>300300003</v>
-      </c>
-      <c r="H49" s="50" t="n">
-        <v>300300000</v>
+        <v>300200201</v>
+      </c>
+      <c r="H49" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300200000,</t>
+        </is>
       </c>
       <c r="I49" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J49" s="50" t="n">
-        <v>300300003</v>
+        <v>300200201</v>
       </c>
       <c r="K49" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="50" t="n">
-        <v>300300004</v>
+        <v>300200301</v>
       </c>
       <c r="B50" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C50" s="50" t="inlineStr">
         <is>
-          <t>ui_research_53</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D50" s="50" t="n">
@@ -3374,42 +3429,46 @@
       </c>
       <c r="E50" s="50" t="inlineStr">
         <is>
-          <t>-575</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F50" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G50" s="50" t="n">
-        <v>300300004</v>
-      </c>
-      <c r="H50" s="50" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="I50" s="50" t="n">
-        <v>100</v>
+        <v>300200301</v>
+      </c>
+      <c r="H50" s="50" t="inlineStr">
+        <is>
+          <t>300200000,</t>
+        </is>
+      </c>
+      <c r="I50" s="50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J50" s="50" t="n">
-        <v>300300004</v>
+        <v>300200301</v>
       </c>
       <c r="K50" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="50" t="n">
-        <v>300300101</v>
+        <v>300300000</v>
       </c>
       <c r="B51" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C51" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D51" s="50" t="n">
@@ -3422,39 +3481,39 @@
       </c>
       <c r="F51" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G51" s="50" t="n">
-        <v>300300101</v>
-      </c>
-      <c r="H51" s="50" t="inlineStr">
-        <is>
-          <t>300300001|300300002|300300003|300300004|</t>
-        </is>
-      </c>
-      <c r="I51" s="50" t="n">
-        <v>100</v>
+        <v>300300000</v>
+      </c>
+      <c r="H51" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="I51" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="J51" s="50" t="n">
-        <v>300300101</v>
+        <v>300300000</v>
       </c>
       <c r="K51" s="50" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="50" t="n">
-        <v>300300102</v>
+        <v>300300001</v>
       </c>
       <c r="B52" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C52" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D52" s="50" t="n">
@@ -3462,42 +3521,42 @@
       </c>
       <c r="E52" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-1025</t>
         </is>
       </c>
       <c r="F52" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G52" s="50" t="n">
-        <v>300300102</v>
+        <v>300300001</v>
       </c>
       <c r="H52" s="50" t="n">
-        <v>300300101</v>
+        <v>300300000</v>
       </c>
       <c r="I52" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J52" s="50" t="n">
-        <v>300300102</v>
+        <v>300300001</v>
       </c>
       <c r="K52" s="50" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="50" t="n">
-        <v>300300201</v>
+        <v>300300002</v>
       </c>
       <c r="B53" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C53" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_54</t>
         </is>
       </c>
       <c r="D53" s="50" t="n">
@@ -3505,44 +3564,42 @@
       </c>
       <c r="E53" s="50" t="inlineStr">
         <is>
-          <t>-650</t>
+          <t>-875</t>
         </is>
       </c>
       <c r="F53" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G53" s="50" t="n">
-        <v>300300201</v>
-      </c>
-      <c r="H53" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300300000,</t>
-        </is>
+        <v>300300002</v>
+      </c>
+      <c r="H53" s="50" t="n">
+        <v>300300000</v>
       </c>
       <c r="I53" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J53" s="50" t="n">
-        <v>300300201</v>
+        <v>300300002</v>
       </c>
       <c r="K53" s="50" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="50" t="n">
-        <v>300300301</v>
+        <v>300300003</v>
       </c>
       <c r="B54" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_54</t>
         </is>
       </c>
       <c r="D54" s="50" t="n">
@@ -3550,46 +3607,42 @@
       </c>
       <c r="E54" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-725</t>
         </is>
       </c>
       <c r="F54" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G54" s="50" t="n">
-        <v>300300301</v>
-      </c>
-      <c r="H54" s="50" t="inlineStr">
-        <is>
-          <t>300300000,</t>
-        </is>
-      </c>
-      <c r="I54" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>300300003</v>
+      </c>
+      <c r="H54" s="50" t="n">
+        <v>300300000</v>
+      </c>
+      <c r="I54" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J54" s="50" t="n">
-        <v>300300301</v>
+        <v>300300003</v>
       </c>
       <c r="K54" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="50" t="n">
-        <v>300400000</v>
+        <v>300300004</v>
       </c>
       <c r="B55" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C55" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_53</t>
         </is>
       </c>
       <c r="D55" s="50" t="n">
@@ -3597,42 +3650,42 @@
       </c>
       <c r="E55" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-575</t>
         </is>
       </c>
       <c r="F55" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G55" s="50" t="n">
-        <v>300400000</v>
+        <v>300300004</v>
       </c>
       <c r="H55" s="50" t="n">
-        <v>300600000</v>
+        <v>300300000</v>
       </c>
       <c r="I55" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J55" s="50" t="n">
-        <v>300400000</v>
+        <v>300300004</v>
       </c>
       <c r="K55" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="50" t="n">
-        <v>300400001</v>
+        <v>300300101</v>
       </c>
       <c r="B56" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C56" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D56" s="50" t="n">
@@ -3640,42 +3693,44 @@
       </c>
       <c r="E56" s="50" t="inlineStr">
         <is>
-          <t>-2700</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F56" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G56" s="50" t="n">
-        <v>300400001</v>
-      </c>
-      <c r="H56" s="50" t="n">
-        <v>300400000</v>
+        <v>300300101</v>
+      </c>
+      <c r="H56" s="50" t="inlineStr">
+        <is>
+          <t>300300001|300300002|300300003|300300004|</t>
+        </is>
       </c>
       <c r="I56" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J56" s="50" t="n">
-        <v>300400001</v>
+        <v>300300101</v>
       </c>
       <c r="K56" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="50" t="n">
-        <v>300400002</v>
+        <v>300300102</v>
       </c>
       <c r="B57" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C57" s="50" t="inlineStr">
         <is>
-          <t>ui_research_45</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D57" s="50" t="n">
@@ -3683,42 +3738,42 @@
       </c>
       <c r="E57" s="50" t="inlineStr">
         <is>
-          <t>-2550</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F57" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G57" s="50" t="n">
-        <v>300400002</v>
+        <v>300300102</v>
       </c>
       <c r="H57" s="50" t="n">
-        <v>300400000</v>
+        <v>300300101</v>
       </c>
       <c r="I57" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J57" s="50" t="n">
-        <v>300400002</v>
+        <v>300300102</v>
       </c>
       <c r="K57" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51">
       <c r="A58" s="50" t="n">
-        <v>300400003</v>
+        <v>300300201</v>
       </c>
       <c r="B58" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C58" s="50" t="inlineStr">
         <is>
-          <t>ui_research_52</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D58" s="50" t="n">
@@ -3726,42 +3781,44 @@
       </c>
       <c r="E58" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-650</t>
         </is>
       </c>
       <c r="F58" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G58" s="50" t="n">
-        <v>300400003</v>
-      </c>
-      <c r="H58" s="50" t="n">
-        <v>300400000</v>
+        <v>300300201</v>
+      </c>
+      <c r="H58" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300300000,</t>
+        </is>
       </c>
       <c r="I58" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J58" s="50" t="n">
-        <v>300400003</v>
+        <v>300300201</v>
       </c>
       <c r="K58" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51">
       <c r="A59" s="50" t="n">
-        <v>300400004</v>
+        <v>300300301</v>
       </c>
       <c r="B59" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C59" s="50" t="inlineStr">
         <is>
-          <t>ui_research_49</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D59" s="50" t="n">
@@ -3769,42 +3826,46 @@
       </c>
       <c r="E59" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F59" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G59" s="50" t="n">
-        <v>300400004</v>
-      </c>
-      <c r="H59" s="50" t="n">
-        <v>300400000</v>
-      </c>
-      <c r="I59" s="50" t="n">
-        <v>100</v>
+        <v>300300301</v>
+      </c>
+      <c r="H59" s="50" t="inlineStr">
+        <is>
+          <t>300300000,</t>
+        </is>
+      </c>
+      <c r="I59" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="J59" s="50" t="n">
-        <v>300400004</v>
+        <v>300300301</v>
       </c>
       <c r="K59" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51">
       <c r="A60" s="50" t="n">
-        <v>300400005</v>
+        <v>300400000</v>
       </c>
       <c r="B60" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D60" s="50" t="n">
@@ -3812,42 +3873,42 @@
       </c>
       <c r="E60" s="50" t="inlineStr">
         <is>
-          <t>-2100</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F60" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G60" s="50" t="n">
-        <v>300400005</v>
+        <v>300400000</v>
       </c>
       <c r="H60" s="50" t="n">
-        <v>300400000</v>
+        <v>300600000</v>
       </c>
       <c r="I60" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J60" s="50" t="n">
-        <v>300400005</v>
+        <v>300400000</v>
       </c>
       <c r="K60" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51">
       <c r="A61" s="50" t="n">
-        <v>300400101</v>
+        <v>300400001</v>
       </c>
       <c r="B61" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C61" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D61" s="50" t="n">
@@ -3855,44 +3916,42 @@
       </c>
       <c r="E61" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2700</t>
         </is>
       </c>
       <c r="F61" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G61" s="50" t="n">
-        <v>300400101</v>
-      </c>
-      <c r="H61" s="50" t="inlineStr">
-        <is>
-          <t>300400001|300400002|300400003|300400004|300400005|</t>
-        </is>
+        <v>300400001</v>
+      </c>
+      <c r="H61" s="50" t="n">
+        <v>300400000</v>
       </c>
       <c r="I61" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J61" s="50" t="n">
-        <v>300400101</v>
+        <v>300400001</v>
       </c>
       <c r="K61" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51">
       <c r="A62" s="50" t="n">
-        <v>300400102</v>
+        <v>300400002</v>
       </c>
       <c r="B62" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_45</t>
         </is>
       </c>
       <c r="D62" s="50" t="n">
@@ -3900,42 +3959,42 @@
       </c>
       <c r="E62" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2550</t>
         </is>
       </c>
       <c r="F62" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G62" s="50" t="n">
-        <v>300400102</v>
+        <v>300400002</v>
       </c>
       <c r="H62" s="50" t="n">
-        <v>300400101</v>
+        <v>300400000</v>
       </c>
       <c r="I62" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J62" s="50" t="n">
-        <v>300400102</v>
+        <v>300400002</v>
       </c>
       <c r="K62" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51">
       <c r="A63" s="50" t="n">
-        <v>300400201</v>
+        <v>300400003</v>
       </c>
       <c r="B63" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C63" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_52</t>
         </is>
       </c>
       <c r="D63" s="50" t="n">
@@ -3943,44 +4002,42 @@
       </c>
       <c r="E63" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F63" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G63" s="50" t="n">
-        <v>300400201</v>
-      </c>
-      <c r="H63" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300400000,</t>
-        </is>
+        <v>300400003</v>
+      </c>
+      <c r="H63" s="50" t="n">
+        <v>300400000</v>
       </c>
       <c r="I63" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J63" s="50" t="n">
-        <v>300400201</v>
+        <v>300400003</v>
       </c>
       <c r="K63" s="50" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51">
       <c r="A64" s="50" t="n">
-        <v>300400301</v>
+        <v>300400004</v>
       </c>
       <c r="B64" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C64" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_49</t>
         </is>
       </c>
       <c r="D64" s="50" t="n">
@@ -3988,44 +4045,42 @@
       </c>
       <c r="E64" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F64" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G64" s="50" t="n">
-        <v>300400301</v>
-      </c>
-      <c r="H64" s="50" t="inlineStr">
-        <is>
-          <t>300400000,</t>
-        </is>
+        <v>300400004</v>
+      </c>
+      <c r="H64" s="50" t="n">
+        <v>300400000</v>
       </c>
       <c r="I64" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J64" s="50" t="n">
-        <v>300400301</v>
+        <v>300400004</v>
       </c>
       <c r="K64" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="50" t="n">
-        <v>300500000</v>
+        <v>300400005</v>
       </c>
       <c r="B65" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C65" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D65" s="50" t="n">
@@ -4033,42 +4088,42 @@
       </c>
       <c r="E65" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>-2100</t>
         </is>
       </c>
       <c r="F65" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G65" s="50" t="n">
-        <v>300500000</v>
+        <v>300400005</v>
       </c>
       <c r="H65" s="50" t="n">
-        <v>300700000</v>
+        <v>300400000</v>
       </c>
       <c r="I65" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J65" s="50" t="n">
-        <v>300500000</v>
+        <v>300400005</v>
       </c>
       <c r="K65" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="50" t="n">
-        <v>300500001</v>
+        <v>300400101</v>
       </c>
       <c r="B66" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C66" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D66" s="50" t="n">
@@ -4076,42 +4131,44 @@
       </c>
       <c r="E66" s="50" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F66" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G66" s="50" t="n">
-        <v>300500001</v>
-      </c>
-      <c r="H66" s="50" t="n">
-        <v>300500000</v>
+        <v>300400101</v>
+      </c>
+      <c r="H66" s="50" t="inlineStr">
+        <is>
+          <t>300400001|300400002|300400003|300400004|300400005|</t>
+        </is>
       </c>
       <c r="I66" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J66" s="50" t="n">
-        <v>300500001</v>
+        <v>300400101</v>
       </c>
       <c r="K66" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51">
       <c r="A67" s="50" t="n">
-        <v>300500002</v>
+        <v>300400102</v>
       </c>
       <c r="B67" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D67" s="50" t="n">
@@ -4119,42 +4176,42 @@
       </c>
       <c r="E67" s="50" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F67" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G67" s="50" t="n">
-        <v>300500002</v>
+        <v>300400102</v>
       </c>
       <c r="H67" s="50" t="n">
-        <v>300500000</v>
+        <v>300400101</v>
       </c>
       <c r="I67" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J67" s="50" t="n">
-        <v>300500002</v>
+        <v>300400102</v>
       </c>
       <c r="K67" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51">
       <c r="A68" s="50" t="n">
-        <v>300500003</v>
+        <v>300400201</v>
       </c>
       <c r="B68" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C68" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D68" s="50" t="n">
@@ -4162,42 +4219,44 @@
       </c>
       <c r="E68" s="50" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F68" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G68" s="50" t="n">
-        <v>300500003</v>
-      </c>
-      <c r="H68" s="50" t="n">
-        <v>300500000</v>
+        <v>300400201</v>
+      </c>
+      <c r="H68" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300400000,</t>
+        </is>
       </c>
       <c r="I68" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J68" s="50" t="n">
-        <v>300500003</v>
+        <v>300400201</v>
       </c>
       <c r="K68" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51">
       <c r="A69" s="50" t="n">
-        <v>300500004</v>
+        <v>300400301</v>
       </c>
       <c r="B69" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D69" s="50" t="n">
@@ -4205,42 +4264,44 @@
       </c>
       <c r="E69" s="50" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F69" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G69" s="50" t="n">
-        <v>300500004</v>
-      </c>
-      <c r="H69" s="50" t="n">
-        <v>300500000</v>
+        <v>300400301</v>
+      </c>
+      <c r="H69" s="50" t="inlineStr">
+        <is>
+          <t>300400000,</t>
+        </is>
       </c>
       <c r="I69" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J69" s="50" t="n">
-        <v>300500004</v>
+        <v>300400301</v>
       </c>
       <c r="K69" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51">
       <c r="A70" s="50" t="n">
-        <v>300500101</v>
+        <v>300500000</v>
       </c>
       <c r="B70" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D70" s="50" t="n">
@@ -4253,39 +4314,37 @@
       </c>
       <c r="F70" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G70" s="50" t="n">
-        <v>300500101</v>
-      </c>
-      <c r="H70" s="50" t="inlineStr">
-        <is>
-          <t>300500001|300500002|300500003|300500004|</t>
-        </is>
+        <v>300500000</v>
+      </c>
+      <c r="H70" s="50" t="n">
+        <v>300700000</v>
       </c>
       <c r="I70" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J70" s="50" t="n">
-        <v>300500101</v>
+        <v>300500000</v>
       </c>
       <c r="K70" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51">
       <c r="A71" s="50" t="n">
-        <v>300500102</v>
+        <v>300500001</v>
       </c>
       <c r="B71" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C71" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D71" s="50" t="n">
@@ -4293,42 +4352,42 @@
       </c>
       <c r="E71" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F71" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G71" s="50" t="n">
-        <v>300500102</v>
+        <v>300500001</v>
       </c>
       <c r="H71" s="50" t="n">
-        <v>300500101</v>
+        <v>300500000</v>
       </c>
       <c r="I71" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J71" s="50" t="n">
-        <v>300500102</v>
+        <v>300500001</v>
       </c>
       <c r="K71" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51">
       <c r="A72" s="50" t="n">
-        <v>300500201</v>
+        <v>300500002</v>
       </c>
       <c r="B72" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C72" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D72" s="50" t="n">
@@ -4336,44 +4395,42 @@
       </c>
       <c r="E72" s="50" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F72" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G72" s="50" t="n">
-        <v>300500201</v>
-      </c>
-      <c r="H72" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300500000,</t>
-        </is>
+        <v>300500002</v>
+      </c>
+      <c r="H72" s="50" t="n">
+        <v>300500000</v>
       </c>
       <c r="I72" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J72" s="50" t="n">
-        <v>300500201</v>
+        <v>300500002</v>
       </c>
       <c r="K72" s="50" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51">
       <c r="A73" s="50" t="n">
-        <v>300500301</v>
+        <v>300500003</v>
       </c>
       <c r="B73" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C73" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D73" s="50" t="n">
@@ -4381,44 +4438,42 @@
       </c>
       <c r="E73" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F73" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G73" s="50" t="n">
-        <v>300500301</v>
-      </c>
-      <c r="H73" s="50" t="inlineStr">
-        <is>
-          <t>300500000,</t>
-        </is>
+        <v>300500003</v>
+      </c>
+      <c r="H73" s="50" t="n">
+        <v>300500000</v>
       </c>
       <c r="I73" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J73" s="50" t="n">
-        <v>300500301</v>
+        <v>300500003</v>
       </c>
       <c r="K73" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51">
       <c r="A74" s="50" t="n">
-        <v>300600000</v>
+        <v>300500004</v>
       </c>
       <c r="B74" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C74" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D74" s="50" t="n">
@@ -4426,42 +4481,42 @@
       </c>
       <c r="E74" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="F74" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G74" s="50" t="n">
-        <v>300600000</v>
+        <v>300500004</v>
       </c>
       <c r="H74" s="50" t="n">
-        <v>300300000</v>
+        <v>300500000</v>
       </c>
       <c r="I74" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J74" s="50" t="n">
-        <v>300600000</v>
+        <v>300500004</v>
       </c>
       <c r="K74" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="50" t="n">
-        <v>300600001</v>
+        <v>300500101</v>
       </c>
       <c r="B75" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C75" s="50" t="inlineStr">
         <is>
-          <t>ui_research_44</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D75" s="50" t="n">
@@ -4469,42 +4524,44 @@
       </c>
       <c r="E75" s="50" t="inlineStr">
         <is>
-          <t>-1900</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F75" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G75" s="50" t="n">
-        <v>300600001</v>
-      </c>
-      <c r="H75" s="50" t="n">
-        <v>300600000</v>
+        <v>300500101</v>
+      </c>
+      <c r="H75" s="50" t="inlineStr">
+        <is>
+          <t>300500001|300500002|300500003|300500004|</t>
+        </is>
       </c>
       <c r="I75" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J75" s="50" t="n">
-        <v>300600001</v>
+        <v>300500101</v>
       </c>
       <c r="K75" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="50" t="n">
-        <v>300600002</v>
+        <v>300500102</v>
       </c>
       <c r="B76" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C76" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D76" s="50" t="n">
@@ -4512,42 +4569,42 @@
       </c>
       <c r="E76" s="50" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F76" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G76" s="50" t="n">
-        <v>300600002</v>
+        <v>300500102</v>
       </c>
       <c r="H76" s="50" t="n">
-        <v>300600000</v>
+        <v>300500101</v>
       </c>
       <c r="I76" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J76" s="50" t="n">
-        <v>300600002</v>
+        <v>300500102</v>
       </c>
       <c r="K76" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="50" t="n">
-        <v>300600003</v>
+        <v>300500201</v>
       </c>
       <c r="B77" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C77" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D77" s="50" t="n">
@@ -4555,42 +4612,44 @@
       </c>
       <c r="E77" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="F77" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G77" s="50" t="n">
-        <v>300600003</v>
-      </c>
-      <c r="H77" s="50" t="n">
-        <v>300600000</v>
+        <v>300500201</v>
+      </c>
+      <c r="H77" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300500000,</t>
+        </is>
       </c>
       <c r="I77" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J77" s="50" t="n">
-        <v>300600003</v>
+        <v>300500201</v>
       </c>
       <c r="K77" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51">
       <c r="A78" s="50" t="n">
-        <v>300600004</v>
+        <v>300500301</v>
       </c>
       <c r="B78" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C78" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D78" s="50" t="n">
@@ -4598,42 +4657,44 @@
       </c>
       <c r="E78" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F78" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G78" s="50" t="n">
-        <v>300600004</v>
-      </c>
-      <c r="H78" s="50" t="n">
-        <v>300600000</v>
+        <v>300500301</v>
+      </c>
+      <c r="H78" s="50" t="inlineStr">
+        <is>
+          <t>300500000,</t>
+        </is>
       </c>
       <c r="I78" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J78" s="50" t="n">
-        <v>300600004</v>
+        <v>300500301</v>
       </c>
       <c r="K78" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51">
       <c r="A79" s="50" t="n">
-        <v>300600005</v>
+        <v>300600000</v>
       </c>
       <c r="B79" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C79" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D79" s="50" t="n">
@@ -4641,42 +4702,42 @@
       </c>
       <c r="E79" s="50" t="inlineStr">
         <is>
-          <t>-1300</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F79" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G79" s="50" t="n">
-        <v>300600005</v>
+        <v>300600000</v>
       </c>
       <c r="H79" s="50" t="n">
-        <v>300600000</v>
+        <v>300300000</v>
       </c>
       <c r="I79" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J79" s="50" t="n">
-        <v>300600005</v>
+        <v>300600000</v>
       </c>
       <c r="K79" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51">
       <c r="A80" s="50" t="n">
-        <v>300600101</v>
+        <v>300600001</v>
       </c>
       <c r="B80" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C80" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_44</t>
         </is>
       </c>
       <c r="D80" s="50" t="n">
@@ -4684,44 +4745,42 @@
       </c>
       <c r="E80" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1900</t>
         </is>
       </c>
       <c r="F80" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G80" s="50" t="n">
-        <v>300600101</v>
-      </c>
-      <c r="H80" s="50" t="inlineStr">
-        <is>
-          <t>300600001|300600002|300600003|300600004|</t>
-        </is>
+        <v>300600001</v>
+      </c>
+      <c r="H80" s="50" t="n">
+        <v>300600000</v>
       </c>
       <c r="I80" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J80" s="50" t="n">
-        <v>300600101</v>
+        <v>300600001</v>
       </c>
       <c r="K80" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51">
       <c r="A81" s="50" t="n">
-        <v>300600102</v>
+        <v>300600002</v>
       </c>
       <c r="B81" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C81" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D81" s="50" t="n">
@@ -4729,42 +4788,42 @@
       </c>
       <c r="E81" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="F81" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G81" s="50" t="n">
-        <v>300600102</v>
+        <v>300600002</v>
       </c>
       <c r="H81" s="50" t="n">
-        <v>300600101</v>
+        <v>300600000</v>
       </c>
       <c r="I81" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J81" s="50" t="n">
-        <v>300600102</v>
+        <v>300600002</v>
       </c>
       <c r="K81" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51">
       <c r="A82" s="50" t="n">
-        <v>300600201</v>
+        <v>300600003</v>
       </c>
       <c r="B82" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C82" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D82" s="50" t="n">
@@ -4772,44 +4831,42 @@
       </c>
       <c r="E82" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F82" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G82" s="50" t="n">
-        <v>300600201</v>
-      </c>
-      <c r="H82" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300600000,</t>
-        </is>
+        <v>300600003</v>
+      </c>
+      <c r="H82" s="50" t="n">
+        <v>300600000</v>
       </c>
       <c r="I82" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J82" s="50" t="n">
-        <v>300600201</v>
+        <v>300600003</v>
       </c>
       <c r="K82" s="50" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51">
       <c r="A83" s="50" t="n">
-        <v>300600301</v>
+        <v>300600004</v>
       </c>
       <c r="B83" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C83" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D83" s="50" t="n">
@@ -4817,44 +4874,42 @@
       </c>
       <c r="E83" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F83" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G83" s="50" t="n">
-        <v>300600301</v>
-      </c>
-      <c r="H83" s="50" t="inlineStr">
-        <is>
-          <t>300600000,</t>
-        </is>
+        <v>300600004</v>
+      </c>
+      <c r="H83" s="50" t="n">
+        <v>300600000</v>
       </c>
       <c r="I83" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J83" s="50" t="n">
-        <v>300600301</v>
+        <v>300600004</v>
       </c>
       <c r="K83" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="50" t="n">
-        <v>300700000</v>
+        <v>300600005</v>
       </c>
       <c r="B84" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C84" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D84" s="50" t="n">
@@ -4862,42 +4917,42 @@
       </c>
       <c r="E84" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>-1300</t>
         </is>
       </c>
       <c r="F84" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G84" s="50" t="n">
-        <v>300700000</v>
+        <v>300600005</v>
       </c>
       <c r="H84" s="50" t="n">
-        <v>300100000</v>
+        <v>300600000</v>
       </c>
       <c r="I84" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J84" s="50" t="n">
-        <v>300700000</v>
+        <v>300600005</v>
       </c>
       <c r="K84" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="50" t="n">
-        <v>300700001</v>
+        <v>300600101</v>
       </c>
       <c r="B85" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C85" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D85" s="50" t="n">
@@ -4905,42 +4960,44 @@
       </c>
       <c r="E85" s="50" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F85" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G85" s="50" t="n">
-        <v>300700001</v>
-      </c>
-      <c r="H85" s="50" t="n">
-        <v>300700000</v>
+        <v>300600101</v>
+      </c>
+      <c r="H85" s="50" t="inlineStr">
+        <is>
+          <t>300600001|300600002|300600003|300600004|</t>
+        </is>
       </c>
       <c r="I85" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J85" s="50" t="n">
-        <v>300700001</v>
+        <v>300600101</v>
       </c>
       <c r="K85" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="50" t="n">
-        <v>300700002</v>
+        <v>300600102</v>
       </c>
       <c r="B86" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C86" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D86" s="50" t="n">
@@ -4948,42 +5005,42 @@
       </c>
       <c r="E86" s="50" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F86" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G86" s="50" t="n">
-        <v>300700002</v>
+        <v>300600102</v>
       </c>
       <c r="H86" s="50" t="n">
-        <v>300700000</v>
+        <v>300600101</v>
       </c>
       <c r="I86" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J86" s="50" t="n">
-        <v>300700002</v>
+        <v>300600102</v>
       </c>
       <c r="K86" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="50" t="n">
-        <v>300700003</v>
+        <v>300600201</v>
       </c>
       <c r="B87" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C87" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D87" s="50" t="n">
@@ -4991,42 +5048,44 @@
       </c>
       <c r="E87" s="50" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F87" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G87" s="50" t="n">
-        <v>300700003</v>
-      </c>
-      <c r="H87" s="50" t="n">
-        <v>300700000</v>
+        <v>300600201</v>
+      </c>
+      <c r="H87" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300600000,</t>
+        </is>
       </c>
       <c r="I87" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J87" s="50" t="n">
-        <v>300700003</v>
+        <v>300600201</v>
       </c>
       <c r="K87" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="50" t="n">
-        <v>300700004</v>
+        <v>300600301</v>
       </c>
       <c r="B88" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C88" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D88" s="50" t="n">
@@ -5034,42 +5093,44 @@
       </c>
       <c r="E88" s="50" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F88" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G88" s="50" t="n">
-        <v>300700004</v>
-      </c>
-      <c r="H88" s="50" t="n">
-        <v>300700000</v>
+        <v>300600301</v>
+      </c>
+      <c r="H88" s="50" t="inlineStr">
+        <is>
+          <t>300600000,</t>
+        </is>
       </c>
       <c r="I88" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J88" s="50" t="n">
-        <v>300700004</v>
+        <v>300600301</v>
       </c>
       <c r="K88" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="50" t="n">
-        <v>300700101</v>
+        <v>300700000</v>
       </c>
       <c r="B89" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C89" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_38</t>
         </is>
       </c>
       <c r="D89" s="50" t="n">
@@ -5082,39 +5143,37 @@
       </c>
       <c r="F89" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G89" s="50" t="n">
-        <v>300700101</v>
-      </c>
-      <c r="H89" s="50" t="inlineStr">
-        <is>
-          <t>300700001|300700002|300700003|300700004|</t>
-        </is>
+        <v>300700000</v>
+      </c>
+      <c r="H89" s="50" t="n">
+        <v>300100000</v>
       </c>
       <c r="I89" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J89" s="50" t="n">
-        <v>300700101</v>
+        <v>300700000</v>
       </c>
       <c r="K89" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="50" t="n">
-        <v>300700102</v>
+        <v>300700001</v>
       </c>
       <c r="B90" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C90" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D90" s="50" t="n">
@@ -5122,42 +5181,42 @@
       </c>
       <c r="E90" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="F90" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G90" s="50" t="n">
-        <v>300700102</v>
+        <v>300700001</v>
       </c>
       <c r="H90" s="50" t="n">
-        <v>300700101</v>
+        <v>300700000</v>
       </c>
       <c r="I90" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J90" s="50" t="n">
-        <v>300700102</v>
+        <v>300700001</v>
       </c>
       <c r="K90" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="50" t="n">
-        <v>300700201</v>
+        <v>300700002</v>
       </c>
       <c r="B91" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D91" s="50" t="n">
@@ -5165,44 +5224,42 @@
       </c>
       <c r="E91" s="50" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F91" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G91" s="50" t="n">
-        <v>300700201</v>
-      </c>
-      <c r="H91" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300700000,</t>
-        </is>
+        <v>300700002</v>
+      </c>
+      <c r="H91" s="50" t="n">
+        <v>300700000</v>
       </c>
       <c r="I91" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J91" s="50" t="n">
-        <v>300700201</v>
+        <v>300700002</v>
       </c>
       <c r="K91" s="50" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="50" t="n">
-        <v>300700301</v>
+        <v>300700003</v>
       </c>
       <c r="B92" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D92" s="50" t="n">
@@ -5210,71 +5267,290 @@
       </c>
       <c r="E92" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="F92" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G92" s="50" t="n">
-        <v>300700301</v>
-      </c>
-      <c r="H92" s="50" t="inlineStr">
-        <is>
-          <t>300700000,</t>
-        </is>
+        <v>300700003</v>
+      </c>
+      <c r="H92" s="50" t="n">
+        <v>300700000</v>
       </c>
       <c r="I92" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J92" s="50" t="n">
-        <v>300700301</v>
+        <v>300700003</v>
       </c>
       <c r="K92" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="50" t="n">
+        <v>300700004</v>
+      </c>
+      <c r="B93" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_47</t>
+        </is>
+      </c>
+      <c r="D93" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="50" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="F93" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G93" s="50" t="n">
+        <v>300700004</v>
+      </c>
+      <c r="H93" s="50" t="n">
+        <v>300700000</v>
+      </c>
+      <c r="I93" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J93" s="50" t="n">
+        <v>300700004</v>
+      </c>
+      <c r="K93" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人魔法师（冰）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="50" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="B94" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_33</t>
+        </is>
+      </c>
+      <c r="D94" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="50" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="F94" s="50" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="G94" s="50" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="H94" s="50" t="inlineStr">
+        <is>
+          <t>300700001|300700002|300700003|300700004|</t>
+        </is>
+      </c>
+      <c r="I94" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J94" s="50" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="K94" s="50" t="inlineStr">
+        <is>
+          <t>孕育兽人x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="50" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="B95" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C95" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_34</t>
+        </is>
+      </c>
+      <c r="D95" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="50" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="F95" s="50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="G95" s="50" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="H95" s="50" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="I95" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J95" s="50" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="K95" s="50" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B96" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C96" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_38</t>
+        </is>
+      </c>
+      <c r="D96" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="50" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="F96" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="G96" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="H96" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300700000,</t>
+        </is>
+      </c>
+      <c r="I96" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J96" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="K96" s="50" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B97" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C97" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_58</t>
+        </is>
+      </c>
+      <c r="D97" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="50" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="F97" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="G97" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="H97" s="50" t="inlineStr">
+        <is>
+          <t>300700000,</t>
+        </is>
+      </c>
+      <c r="I97" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J97" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="K97" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="B93" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" s="50" t="inlineStr">
+      <c r="B98" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" s="50" t="inlineStr">
         <is>
           <t>ui_research_18</t>
         </is>
       </c>
-      <c r="D93" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="50" t="inlineStr">
+      <c r="D98" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F93" s="50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="G93" s="50" t="n">
+      <c r="F98" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G98" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="I93" s="50" t="inlineStr">
+      <c r="I98" s="50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J93" s="50" t="n">
+      <c r="J98" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="K93" s="50" t="inlineStr">
+      <c r="K98" s="50" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -1378,7 +1378,7 @@
       <c r="G4" s="50" t="n">
         <v>100000000</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="50" t="inlineStr">
         <is>
           <t>100500001</t>
         </is>
@@ -1443,55 +1443,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="n">
-        <v>100100001</v>
-      </c>
-      <c r="B6" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_3</t>
-        </is>
-      </c>
-      <c r="D6" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="50" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="F6" s="50" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G6" s="50" t="n">
-        <v>100100001</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>100500001</t>
-        </is>
-      </c>
-      <c r="I6" s="50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" s="50" t="n">
-        <v>100100001</v>
-      </c>
-      <c r="K6" s="50" t="inlineStr">
-        <is>
-          <t>开启献祭设施</t>
+      <c r="A6" t="n">
+        <v>100000003</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ui_research_1</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100000006</v>
+      </c>
+      <c r="H6" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>500</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100000006</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>进阶增益范围预览</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="50" t="n">
-        <v>100100002</v>
+        <v>100100001</v>
       </c>
       <c r="B7" s="50" t="n">
         <v>1</v>
@@ -1502,41 +1494,43 @@
         </is>
       </c>
       <c r="D7" s="50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E7" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F7" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G7" s="50" t="n">
-        <v>100100002</v>
-      </c>
-      <c r="H7" s="50" t="n">
         <v>100100001</v>
       </c>
+      <c r="H7" s="50" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
+      </c>
       <c r="I7" s="50" t="inlineStr">
         <is>
-          <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" s="50" t="n">
-        <v>100100002</v>
+        <v>100100001</v>
       </c>
       <c r="K7" s="50" t="inlineStr">
         <is>
-          <t>献祭祭品数量+1</t>
+          <t>开启献祭设施</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="50" t="n">
-        <v>100100003</v>
+        <v>100100002</v>
       </c>
       <c r="B8" s="50" t="n">
         <v>1</v>
@@ -1556,34 +1550,32 @@
       </c>
       <c r="F8" s="50" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G8" s="50" t="n">
-        <v>100100003</v>
-      </c>
-      <c r="H8" s="50" t="inlineStr">
-        <is>
-          <t>100100001</t>
-        </is>
+        <v>100100002</v>
+      </c>
+      <c r="H8" s="50" t="n">
+        <v>100100001</v>
       </c>
       <c r="I8" s="50" t="inlineStr">
         <is>
-          <t>100,500,1000,5000,10000,20000,30000,40000,50000,100000</t>
+          <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
         </is>
       </c>
       <c r="J8" s="50" t="n">
-        <v>100100003</v>
+        <v>100100002</v>
       </c>
       <c r="K8" s="50" t="inlineStr">
         <is>
-          <t>献祭失败保底概率提升</t>
+          <t>献祭祭品数量+1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="50" t="n">
-        <v>100100004</v>
+        <v>100100003</v>
       </c>
       <c r="B9" s="50" t="n">
         <v>1</v>
@@ -1598,16 +1590,16 @@
       </c>
       <c r="E9" s="50" t="inlineStr">
         <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F9" s="50" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="F9" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
       <c r="G9" s="50" t="n">
-        <v>100100004</v>
+        <v>100100003</v>
       </c>
       <c r="H9" s="50" t="inlineStr">
         <is>
@@ -1620,71 +1612,71 @@
         </is>
       </c>
       <c r="J9" s="50" t="n">
-        <v>100100004</v>
+        <v>100100003</v>
       </c>
       <c r="K9" s="50" t="inlineStr">
         <is>
-          <t>不同魔物献祭成功率提升</t>
+          <t>献祭失败保底概率提升</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="50" t="n">
-        <v>100200001</v>
+        <v>100100004</v>
       </c>
       <c r="B10" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="50" t="inlineStr">
         <is>
-          <t>ui_research_7</t>
+          <t>ui_research_3</t>
         </is>
       </c>
       <c r="D10" s="50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E10" s="50" t="inlineStr">
         <is>
-          <t>-300</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F10" s="50" t="inlineStr">
         <is>
-          <t>-300</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G10" s="50" t="n">
-        <v>100200001</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>100500001</t>
+        <v>100100004</v>
+      </c>
+      <c r="H10" s="50" t="inlineStr">
+        <is>
+          <t>100100001</t>
         </is>
       </c>
       <c r="I10" s="50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100,500,1000,5000,10000,20000,30000,40000,50000,100000</t>
         </is>
       </c>
       <c r="J10" s="50" t="n">
-        <v>100200001</v>
+        <v>100100004</v>
       </c>
       <c r="K10" s="50" t="inlineStr">
         <is>
-          <t>开启终焉议会</t>
+          <t>不同魔物献祭成功率提升</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="50" t="n">
-        <v>100200002</v>
+        <v>100200001</v>
       </c>
       <c r="B11" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="50" t="inlineStr">
         <is>
-          <t>ui_research_59</t>
+          <t>ui_research_7</t>
         </is>
       </c>
       <c r="D11" s="50" t="n">
@@ -1692,7 +1684,7 @@
       </c>
       <c r="E11" s="50" t="inlineStr">
         <is>
-          <t>-500</t>
+          <t>-300</t>
         </is>
       </c>
       <c r="F11" s="50" t="inlineStr">
@@ -1701,26 +1693,30 @@
         </is>
       </c>
       <c r="G11" s="50" t="n">
-        <v>100200002</v>
-      </c>
-      <c r="H11" s="50" t="n">
         <v>100200001</v>
       </c>
-      <c r="I11" s="50" t="n">
-        <v>100</v>
+      <c r="H11" s="50" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
+      </c>
+      <c r="I11" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="J11" s="50" t="n">
-        <v>100200002</v>
+        <v>100200001</v>
       </c>
       <c r="K11" s="50" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="50" t="n">
-        <v>100200003</v>
+        <v>100200002</v>
       </c>
       <c r="B12" s="50" t="n">
         <v>1</v>
@@ -1735,7 +1731,7 @@
       </c>
       <c r="E12" s="50" t="inlineStr">
         <is>
-          <t>-700</t>
+          <t>-500</t>
         </is>
       </c>
       <c r="F12" s="50" t="inlineStr">
@@ -1744,331 +1740,327 @@
         </is>
       </c>
       <c r="G12" s="50" t="n">
-        <v>100200003</v>
-      </c>
-      <c r="H12" s="50" t="inlineStr">
-        <is>
-          <t>100200002</t>
-        </is>
+        <v>100200002</v>
+      </c>
+      <c r="H12" s="50" t="n">
+        <v>100200001</v>
       </c>
       <c r="I12" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>100200003</v>
+        <v>100200002</v>
       </c>
       <c r="K12" s="50" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="50" t="n">
+        <v>100200003</v>
+      </c>
+      <c r="B13" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_59</t>
+        </is>
+      </c>
+      <c r="D13" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="50" t="inlineStr">
+        <is>
+          <t>-700</t>
+        </is>
+      </c>
+      <c r="F13" s="50" t="inlineStr">
+        <is>
+          <t>-300</t>
+        </is>
+      </c>
+      <c r="G13" s="50" t="n">
+        <v>100200003</v>
+      </c>
+      <c r="H13" s="50" t="inlineStr">
+        <is>
+          <t>100200002</t>
+        </is>
+      </c>
+      <c r="I13" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" s="50" t="n">
+        <v>100200003</v>
+      </c>
+      <c r="K13" s="50" t="inlineStr">
+        <is>
+          <t>终焉议会议案：魔王重命名</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="n">
         <v>100300001</v>
       </c>
-      <c r="B13" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="50" t="inlineStr">
+      <c r="B14" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>ui_research_9</t>
         </is>
       </c>
-      <c r="D13" s="50" t="inlineStr">
+      <c r="D14" s="50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="50" t="inlineStr">
+      <c r="E14" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="50" t="inlineStr">
+      <c r="F14" s="50" t="inlineStr">
         <is>
           <t>-400</t>
         </is>
       </c>
-      <c r="G13" s="50" t="n">
+      <c r="G14" s="50" t="n">
         <v>100300001</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" s="50" t="inlineStr">
         <is>
           <t>100500001</t>
         </is>
       </c>
-      <c r="I13" s="50" t="inlineStr">
+      <c r="I14" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="J14" s="50" t="n">
         <v>100300001</v>
       </c>
-      <c r="K13" s="50" t="inlineStr">
+      <c r="K14" s="50" t="inlineStr">
         <is>
           <t>开启终焉议会</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="15">
+      <c r="A15" s="50" t="n">
         <v>100300002</v>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>ui_research_9</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" s="50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" s="50" t="inlineStr">
         <is>
           <t>-150</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>-800</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="G15" s="50" t="n">
         <v>100300002</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" s="50" t="inlineStr">
         <is>
           <t>100300003</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" s="50" t="n">
         <v>100300002</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" s="50" t="inlineStr">
         <is>
           <t>传送门详情-线路数量预览</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="16">
+      <c r="A16" s="50" t="n">
         <v>100300003</v>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B16" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>ui_research_9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" s="50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" s="50" t="inlineStr">
         <is>
           <t>-600</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" s="50" t="n">
         <v>100300003</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" s="50" t="inlineStr">
         <is>
           <t>100300001</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" s="50" t="n">
         <v>100300003</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" s="50" t="inlineStr">
         <is>
           <t>传送门详情-关卡数量预览</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="17">
+      <c r="A17" s="50" t="n">
         <v>100300004</v>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>ui_research_9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" s="50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" s="50" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" s="50" t="inlineStr">
         <is>
           <t>-800</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="G17" s="50" t="n">
         <v>100300004</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" s="50" t="inlineStr">
         <is>
           <t>100300003</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" s="50" t="n">
         <v>100300004</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" s="50" t="inlineStr">
         <is>
           <t>传送门详情-路径长度预览</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="18">
+      <c r="A18" s="50" t="n">
         <v>100300005</v>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t>ui_research_9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" s="50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" s="50" t="inlineStr">
         <is>
           <t>-800</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" s="50" t="n">
         <v>100300005</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" s="50" t="inlineStr">
         <is>
           <t>100300003</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" s="50" t="n">
         <v>100300005</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" s="50" t="inlineStr">
         <is>
           <t>传送门详情-奖励预览</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>100300006</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ui_research_9</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-400</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>100300006</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>100300001</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>300*2</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>100300006</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>传送门刷新解锁</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="50" t="n">
-        <v>100310112</v>
+        <v>100300006</v>
       </c>
       <c r="B19" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_9</t>
         </is>
       </c>
       <c r="D19" s="50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" s="50" t="inlineStr">
         <is>
@@ -2077,11 +2069,11 @@
       </c>
       <c r="F19" s="50" t="inlineStr">
         <is>
-          <t>-600</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="G19" s="50" t="n">
-        <v>100310112</v>
+        <v>100300006</v>
       </c>
       <c r="H19" s="50" t="inlineStr">
         <is>
@@ -2090,68 +2082,68 @@
       </c>
       <c r="I19" s="50" t="inlineStr">
         <is>
-          <t>200,400,800,1600,3200,6400,12800,25600,51200,</t>
+          <t>300*2</t>
         </is>
       </c>
       <c r="J19" s="50" t="n">
-        <v>100310112</v>
+        <v>100300006</v>
       </c>
       <c r="K19" s="50" t="inlineStr">
         <is>
-          <t>剑与魔法：征服难度+1</t>
+          <t>传送门刷新解锁</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="n">
-        <v>100400000</v>
+        <v>100310112</v>
       </c>
       <c r="B20" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="50" t="inlineStr">
         <is>
-          <t>ui_research_57</t>
+          <t>ui_research_11</t>
         </is>
       </c>
       <c r="D20" s="50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E20" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F20" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-600</t>
         </is>
       </c>
       <c r="G20" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>100500001</t>
+        <v>100310112</v>
+      </c>
+      <c r="H20" s="50" t="inlineStr">
+        <is>
+          <t>100300001</t>
         </is>
       </c>
       <c r="I20" s="50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200,400,800,1600,3200,6400,12800,25600,51200,</t>
         </is>
       </c>
       <c r="J20" s="50" t="n">
-        <v>100400000</v>
+        <v>100310112</v>
       </c>
       <c r="K20" s="50" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>剑与魔法：征服难度+1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="50" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B21" s="50" t="n">
         <v>1</v>
@@ -2171,32 +2163,34 @@
       </c>
       <c r="F21" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G21" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="H21" s="50" t="n">
         <v>100400000</v>
       </c>
+      <c r="H21" s="50" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
+      </c>
       <c r="I21" s="50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" s="50" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="K21" s="50" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="50" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B22" s="50" t="n">
         <v>1</v>
@@ -2216,32 +2210,32 @@
       </c>
       <c r="F22" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G22" s="50" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="H22" s="50" t="n">
+        <v>100400000</v>
+      </c>
+      <c r="I22" s="50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" s="50" t="n">
         <v>100400001</v>
       </c>
-      <c r="I22" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J22" s="50" t="n">
-        <v>100401000</v>
-      </c>
       <c r="K22" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="50" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B23" s="50" t="n">
         <v>1</v>
@@ -2252,11 +2246,11 @@
         </is>
       </c>
       <c r="D23" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E23" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="50" t="inlineStr">
@@ -2265,28 +2259,28 @@
         </is>
       </c>
       <c r="G23" s="50" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="H23" s="50" t="n">
+        <v>100400001</v>
+      </c>
+      <c r="I23" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J23" s="50" t="n">
         <v>100401000</v>
       </c>
-      <c r="I23" s="50" t="inlineStr">
-        <is>
-          <t>100*1</t>
-        </is>
-      </c>
-      <c r="J23" s="50" t="n">
-        <v>100401001</v>
-      </c>
       <c r="K23" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B24" s="50" t="n">
         <v>1</v>
@@ -2297,41 +2291,41 @@
         </is>
       </c>
       <c r="D24" s="50" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E24" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="F24" s="50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="G24" s="50" t="n">
-        <v>100402000</v>
-      </c>
-      <c r="H24" s="50" t="inlineStr">
-        <is>
-          <t>100401000,100401001,</t>
-        </is>
-      </c>
-      <c r="I24" s="50" t="n">
-        <v>1000</v>
+        <v>100401001</v>
+      </c>
+      <c r="H24" s="50" t="n">
+        <v>100401000</v>
+      </c>
+      <c r="I24" s="50" t="inlineStr">
+        <is>
+          <t>100*1</t>
+        </is>
       </c>
       <c r="J24" s="50" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="K24" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B25" s="50" t="n">
         <v>1</v>
@@ -2342,11 +2336,11 @@
         </is>
       </c>
       <c r="D25" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E25" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="50" t="inlineStr">
@@ -2355,28 +2349,28 @@
         </is>
       </c>
       <c r="G25" s="50" t="n">
-        <v>100402001</v>
-      </c>
-      <c r="H25" s="50" t="n">
         <v>100402000</v>
       </c>
-      <c r="I25" s="50" t="inlineStr">
-        <is>
-          <t>1000*1</t>
-        </is>
+      <c r="H25" s="50" t="inlineStr">
+        <is>
+          <t>100401000,100401001,</t>
+        </is>
+      </c>
+      <c r="I25" s="50" t="n">
+        <v>1000</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="K25" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="50" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B26" s="50" t="n">
         <v>1</v>
@@ -2387,41 +2381,41 @@
         </is>
       </c>
       <c r="D26" s="50" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E26" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="F26" s="50" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="G26" s="50" t="n">
-        <v>100403000</v>
-      </c>
-      <c r="H26" s="50" t="inlineStr">
-        <is>
-          <t>100402000,100402001,</t>
-        </is>
-      </c>
-      <c r="I26" s="50" t="n">
-        <v>10000</v>
+        <v>100402001</v>
+      </c>
+      <c r="H26" s="50" t="n">
+        <v>100402000</v>
+      </c>
+      <c r="I26" s="50" t="inlineStr">
+        <is>
+          <t>1000*1</t>
+        </is>
       </c>
       <c r="J26" s="50" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="K26" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="50" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B27" s="50" t="n">
         <v>1</v>
@@ -2432,11 +2426,11 @@
         </is>
       </c>
       <c r="D27" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E27" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F27" s="50" t="inlineStr">
@@ -2445,184 +2439,191 @@
         </is>
       </c>
       <c r="G27" s="50" t="n">
-        <v>100403001</v>
-      </c>
-      <c r="H27" s="50" t="n">
         <v>100403000</v>
       </c>
-      <c r="I27" s="50" t="inlineStr">
-        <is>
-          <t>10000*1</t>
-        </is>
+      <c r="H27" s="50" t="inlineStr">
+        <is>
+          <t>100402000,100402001,</t>
+        </is>
+      </c>
+      <c r="I27" s="50" t="n">
+        <v>10000</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="K27" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="50" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B28" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="50" t="inlineStr">
         <is>
-          <t>ui_research_5</t>
+          <t>ui_research_57</t>
         </is>
       </c>
       <c r="D28" s="50" t="n">
-        <v>30</v>
-      </c>
-      <c r="E28" s="50" t="n">
-        <v>-200</v>
-      </c>
-      <c r="F28" s="50" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="E28" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F28" s="50" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="G28" s="50" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
+      </c>
+      <c r="H28" s="50" t="n">
+        <v>100403000</v>
       </c>
       <c r="I28" s="50" t="inlineStr">
         <is>
-          <t>50,100,200,500,1000,2000,5000,10000,50000,100000,</t>
+          <t>10000*1</t>
         </is>
       </c>
       <c r="J28" s="50" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="K28" s="50" t="inlineStr">
         <is>
-          <t>阵容上限+1</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="50" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="B29" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C29" s="50" t="inlineStr">
         <is>
-          <t>ui_research_6</t>
+          <t>ui_research_5</t>
         </is>
       </c>
       <c r="D29" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F29" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="E29" s="50" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F29" s="50" t="n">
+        <v>0</v>
       </c>
       <c r="G29" s="50" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="I29" s="50" t="inlineStr">
         <is>
-          <t>100,200,300,400,</t>
+          <t>50,100,200,500,1000,2000,5000,10000,50000,100000,</t>
         </is>
       </c>
       <c r="J29" s="50" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="K29" s="50" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容上限+1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="50" t="n">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="B30" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C30" s="50" t="inlineStr">
         <is>
-          <t>ui_research_60</t>
+          <t>ui_research_6</t>
         </is>
       </c>
       <c r="D30" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="50" t="n">
-        <v>-200</v>
-      </c>
-      <c r="F30" s="50" t="n">
-        <v>-200</v>
+        <v>4</v>
+      </c>
+      <c r="E30" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F30" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G30" s="50" t="n">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="I30" s="50" t="inlineStr">
         <is>
-          <t>100,500,1000,5000,10000,50000</t>
+          <t>100,200,300,400,</t>
         </is>
       </c>
       <c r="J30" s="50" t="n">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="K30" s="50" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="50" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B31" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>ui_research_61</t>
+          <t>ui_research_60</t>
         </is>
       </c>
       <c r="D31" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="50" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F31" s="50" t="n">
         <v>-200</v>
       </c>
       <c r="G31" s="50" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="I31" s="50" t="inlineStr">
         <is>
-          <t>100,500,1000,5000,10000</t>
+          <t>100,500,1000,5000,10000,50000</t>
         </is>
       </c>
       <c r="J31" s="50" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="K31" s="50" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B32" s="50" t="n">
         <v>2</v>
@@ -2633,129 +2634,121 @@
         </is>
       </c>
       <c r="D32" s="50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E32" s="50" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F32" s="50" t="n">
         <v>-200</v>
       </c>
       <c r="G32" s="50" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="I32" s="50" t="inlineStr">
         <is>
-          <t>100,500,1000</t>
+          <t>100,500,1000,5000,10000</t>
         </is>
       </c>
       <c r="J32" s="50" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="K32" s="50" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="50" t="n">
-        <v>300100000</v>
+        <v>200400001</v>
       </c>
       <c r="B33" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_61</t>
         </is>
       </c>
       <c r="D33" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="50" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="F33" s="50" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E33" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="F33" s="50" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G33" s="50" t="n">
+        <v>200400001</v>
+      </c>
+      <c r="I33" s="50" t="inlineStr">
+        <is>
+          <t>100,500,1000</t>
+        </is>
+      </c>
+      <c r="J33" s="50" t="n">
+        <v>200400001</v>
+      </c>
+      <c r="K33" s="50" t="inlineStr">
+        <is>
+          <t>魔王魔力恢复速度+1/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>200500001</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ui_research_62</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G33" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="H33" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I33" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J33" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="K33" s="50" t="inlineStr">
-        <is>
-          <t>解锁种族：人类</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="50" t="n">
-        <v>300100001</v>
-      </c>
-      <c r="B34" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_43</t>
-        </is>
-      </c>
-      <c r="D34" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="50" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="F34" s="50" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="G34" s="50" t="n">
-        <v>300100001</v>
-      </c>
-      <c r="H34" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="I34" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J34" s="50" t="n">
-        <v>300100001</v>
-      </c>
-      <c r="K34" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：人类战士</t>
+      <c r="G34" t="n">
+        <v>200500001</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100,500,1000,5000,10000</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>200500001</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>深渊馈赠刷新次数+1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="50" t="n">
-        <v>300100002</v>
+        <v>300100000</v>
       </c>
       <c r="B35" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C35" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D35" s="50" t="n">
@@ -2763,42 +2756,44 @@
       </c>
       <c r="E35" s="50" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F35" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G35" s="50" t="n">
-        <v>300100002</v>
+        <v>300100000</v>
       </c>
       <c r="H35" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="I35" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J35" s="50" t="n">
         <v>300100000</v>
       </c>
-      <c r="I35" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J35" s="50" t="n">
-        <v>300100002</v>
-      </c>
       <c r="K35" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="50" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="B36" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D36" s="50" t="n">
@@ -2806,7 +2801,7 @@
       </c>
       <c r="E36" s="50" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F36" s="50" t="inlineStr">
@@ -2815,7 +2810,7 @@
         </is>
       </c>
       <c r="G36" s="50" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="H36" s="50" t="n">
         <v>300100000</v>
@@ -2824,24 +2819,24 @@
         <v>100</v>
       </c>
       <c r="J36" s="50" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="K36" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="50" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="B37" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D37" s="50" t="n">
@@ -2849,7 +2844,7 @@
       </c>
       <c r="E37" s="50" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F37" s="50" t="inlineStr">
@@ -2858,7 +2853,7 @@
         </is>
       </c>
       <c r="G37" s="50" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="H37" s="50" t="n">
         <v>300100000</v>
@@ -2867,24 +2862,24 @@
         <v>100</v>
       </c>
       <c r="J37" s="50" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="K37" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="50" t="n">
-        <v>300100101</v>
+        <v>300100003</v>
       </c>
       <c r="B38" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D38" s="50" t="n">
@@ -2892,44 +2887,42 @@
       </c>
       <c r="E38" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F38" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G38" s="50" t="n">
-        <v>300100101</v>
-      </c>
-      <c r="H38" s="50" t="inlineStr">
-        <is>
-          <t>300100001|300100002|300100003|300100004|</t>
-        </is>
+        <v>300100003</v>
+      </c>
+      <c r="H38" s="50" t="n">
+        <v>300100000</v>
       </c>
       <c r="I38" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J38" s="50" t="n">
-        <v>300100101</v>
+        <v>300100003</v>
       </c>
       <c r="K38" s="50" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="B39" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D39" s="50" t="n">
@@ -2937,42 +2930,42 @@
       </c>
       <c r="E39" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F39" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G39" s="50" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="H39" s="50" t="n">
-        <v>300100101</v>
+        <v>300100000</v>
       </c>
       <c r="I39" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J39" s="50" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="K39" s="50" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="50" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="B40" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C40" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D40" s="50" t="n">
@@ -2980,44 +2973,44 @@
       </c>
       <c r="E40" s="50" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F40" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G40" s="50" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="H40" s="50" t="inlineStr">
         <is>
-          <t>100200001,300100000,</t>
+          <t>300100001|300100002|300100003|300100004|</t>
         </is>
       </c>
       <c r="I40" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J40" s="50" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="K40" s="50" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="50" t="n">
-        <v>300100301</v>
+        <v>300100102</v>
       </c>
       <c r="B41" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C41" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D41" s="50" t="n">
@@ -3030,41 +3023,37 @@
       </c>
       <c r="F41" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G41" s="50" t="n">
-        <v>300100301</v>
-      </c>
-      <c r="H41" s="50" t="inlineStr">
-        <is>
-          <t>300100000,</t>
-        </is>
-      </c>
-      <c r="I41" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+        <v>300100102</v>
+      </c>
+      <c r="H41" s="50" t="n">
+        <v>300100101</v>
+      </c>
+      <c r="I41" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J41" s="50" t="n">
-        <v>300100301</v>
+        <v>300100102</v>
       </c>
       <c r="K41" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="50" t="n">
-        <v>300200000</v>
+        <v>300100201</v>
       </c>
       <c r="B42" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D42" s="50" t="n">
@@ -3072,41 +3061,44 @@
       </c>
       <c r="E42" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F42" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G42" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I42" s="50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+        <v>300100201</v>
+      </c>
+      <c r="H42" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300100000,</t>
+        </is>
+      </c>
+      <c r="I42" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J42" s="50" t="n">
-        <v>300200000</v>
+        <v>300100201</v>
       </c>
       <c r="K42" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="50" t="n">
-        <v>300200001</v>
+        <v>300100301</v>
       </c>
       <c r="B43" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C43" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D43" s="50" t="n">
@@ -3114,44 +3106,46 @@
       </c>
       <c r="E43" s="50" t="inlineStr">
         <is>
-          <t>-223</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F43" s="50" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G43" s="50" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="H43" s="50" t="n">
-        <v>300200000</v>
+        <v>300100301</v>
+      </c>
+      <c r="H43" s="50" t="inlineStr">
+        <is>
+          <t>300100000,</t>
+        </is>
       </c>
       <c r="I43" s="50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J43" s="50" t="n">
-        <v>300200001</v>
+        <v>300100301</v>
       </c>
       <c r="K43" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="50" t="n">
-        <v>300200002</v>
+        <v>300200000</v>
       </c>
       <c r="B44" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D44" s="50" t="n">
@@ -3159,44 +3153,41 @@
       </c>
       <c r="E44" s="50" t="inlineStr">
         <is>
-          <t>-75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G44" s="50" t="n">
-        <v>300200002</v>
-      </c>
-      <c r="H44" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I44" s="50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" s="50" t="n">
-        <v>300200002</v>
+        <v>300200000</v>
       </c>
       <c r="K44" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="50" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="B45" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C45" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D45" s="50" t="n">
@@ -3204,44 +3195,44 @@
       </c>
       <c r="E45" s="50" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-223</t>
         </is>
       </c>
       <c r="F45" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G45" s="50" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="H45" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I45" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" s="50" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="K45" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="50" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="B46" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C46" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D46" s="50" t="n">
@@ -3249,7 +3240,7 @@
       </c>
       <c r="E46" s="50" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-75</t>
         </is>
       </c>
       <c r="F46" s="50" t="inlineStr">
@@ -3258,35 +3249,35 @@
         </is>
       </c>
       <c r="G46" s="50" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="H46" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I46" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J46" s="50" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="K46" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="50" t="n">
-        <v>300200101</v>
+        <v>300200003</v>
       </c>
       <c r="B47" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C47" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D47" s="50" t="n">
@@ -3294,46 +3285,44 @@
       </c>
       <c r="E47" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F47" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G47" s="50" t="n">
-        <v>300200101</v>
-      </c>
-      <c r="H47" s="50" t="inlineStr">
-        <is>
-          <t>300200001|300200002|300200003|300200004|</t>
-        </is>
+        <v>300200003</v>
+      </c>
+      <c r="H47" s="50" t="n">
+        <v>300200000</v>
       </c>
       <c r="I47" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J47" s="50" t="n">
-        <v>300200101</v>
+        <v>300200003</v>
       </c>
       <c r="K47" s="50" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="50" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="B48" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D48" s="50" t="n">
@@ -3341,42 +3330,44 @@
       </c>
       <c r="E48" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G48" s="50" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="H48" s="50" t="n">
-        <v>300200101</v>
-      </c>
-      <c r="I48" s="50" t="n">
-        <v>100</v>
+        <v>300200000</v>
+      </c>
+      <c r="I48" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="J48" s="50" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="K48" s="50" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="50" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="B49" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D49" s="50" t="n">
@@ -3384,44 +3375,46 @@
       </c>
       <c r="E49" s="50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G49" s="50" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="H49" s="50" t="inlineStr">
         <is>
-          <t>100200001,300200000,</t>
-        </is>
-      </c>
-      <c r="I49" s="50" t="n">
-        <v>100</v>
+          <t>300200001|300200002|300200003|300200004|</t>
+        </is>
+      </c>
+      <c r="I49" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="J49" s="50" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="K49" s="50" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="50" t="n">
-        <v>300200301</v>
+        <v>300200102</v>
       </c>
       <c r="B50" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C50" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D50" s="50" t="n">
@@ -3434,41 +3427,37 @@
       </c>
       <c r="F50" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G50" s="50" t="n">
-        <v>300200301</v>
-      </c>
-      <c r="H50" s="50" t="inlineStr">
-        <is>
-          <t>300200000,</t>
-        </is>
-      </c>
-      <c r="I50" s="50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>300200102</v>
+      </c>
+      <c r="H50" s="50" t="n">
+        <v>300200101</v>
+      </c>
+      <c r="I50" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J50" s="50" t="n">
-        <v>300200301</v>
+        <v>300200102</v>
       </c>
       <c r="K50" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="50" t="n">
-        <v>300300000</v>
+        <v>300200201</v>
       </c>
       <c r="B51" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C51" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D51" s="50" t="n">
@@ -3476,44 +3465,44 @@
       </c>
       <c r="E51" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F51" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G51" s="50" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="H51" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I51" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+        <v>300200201</v>
+      </c>
+      <c r="H51" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300200000,</t>
+        </is>
+      </c>
+      <c r="I51" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J51" s="50" t="n">
-        <v>300300000</v>
+        <v>300200201</v>
       </c>
       <c r="K51" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="50" t="n">
-        <v>300300001</v>
+        <v>300200301</v>
       </c>
       <c r="B52" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C52" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D52" s="50" t="n">
@@ -3521,42 +3510,46 @@
       </c>
       <c r="E52" s="50" t="inlineStr">
         <is>
-          <t>-1025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F52" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G52" s="50" t="n">
-        <v>300300001</v>
-      </c>
-      <c r="H52" s="50" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="I52" s="50" t="n">
-        <v>100</v>
+        <v>300200301</v>
+      </c>
+      <c r="H52" s="50" t="inlineStr">
+        <is>
+          <t>300200000,</t>
+        </is>
+      </c>
+      <c r="I52" s="50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J52" s="50" t="n">
-        <v>300300001</v>
+        <v>300200301</v>
       </c>
       <c r="K52" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="50" t="n">
-        <v>300300002</v>
+        <v>300300000</v>
       </c>
       <c r="B53" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C53" s="50" t="inlineStr">
         <is>
-          <t>ui_research_54</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D53" s="50" t="n">
@@ -3564,42 +3557,44 @@
       </c>
       <c r="E53" s="50" t="inlineStr">
         <is>
-          <t>-875</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F53" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G53" s="50" t="n">
-        <v>300300002</v>
+        <v>300300000</v>
       </c>
       <c r="H53" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="I53" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J53" s="50" t="n">
         <v>300300000</v>
       </c>
-      <c r="I53" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J53" s="50" t="n">
-        <v>300300002</v>
-      </c>
       <c r="K53" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="50" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="B54" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="50" t="inlineStr">
         <is>
-          <t>ui_research_54</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D54" s="50" t="n">
@@ -3607,7 +3602,7 @@
       </c>
       <c r="E54" s="50" t="inlineStr">
         <is>
-          <t>-725</t>
+          <t>-1025</t>
         </is>
       </c>
       <c r="F54" s="50" t="inlineStr">
@@ -3616,7 +3611,7 @@
         </is>
       </c>
       <c r="G54" s="50" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="H54" s="50" t="n">
         <v>300300000</v>
@@ -3625,24 +3620,24 @@
         <v>100</v>
       </c>
       <c r="J54" s="50" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="K54" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="50" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="B55" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C55" s="50" t="inlineStr">
         <is>
-          <t>ui_research_53</t>
+          <t>ui_research_54</t>
         </is>
       </c>
       <c r="D55" s="50" t="n">
@@ -3650,7 +3645,7 @@
       </c>
       <c r="E55" s="50" t="inlineStr">
         <is>
-          <t>-575</t>
+          <t>-875</t>
         </is>
       </c>
       <c r="F55" s="50" t="inlineStr">
@@ -3659,7 +3654,7 @@
         </is>
       </c>
       <c r="G55" s="50" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="H55" s="50" t="n">
         <v>300300000</v>
@@ -3668,24 +3663,24 @@
         <v>100</v>
       </c>
       <c r="J55" s="50" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="K55" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="50" t="n">
-        <v>300300101</v>
+        <v>300300003</v>
       </c>
       <c r="B56" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C56" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_54</t>
         </is>
       </c>
       <c r="D56" s="50" t="n">
@@ -3693,44 +3688,42 @@
       </c>
       <c r="E56" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-725</t>
         </is>
       </c>
       <c r="F56" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G56" s="50" t="n">
-        <v>300300101</v>
-      </c>
-      <c r="H56" s="50" t="inlineStr">
-        <is>
-          <t>300300001|300300002|300300003|300300004|</t>
-        </is>
+        <v>300300003</v>
+      </c>
+      <c r="H56" s="50" t="n">
+        <v>300300000</v>
       </c>
       <c r="I56" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J56" s="50" t="n">
-        <v>300300101</v>
+        <v>300300003</v>
       </c>
       <c r="K56" s="50" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="50" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="B57" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C57" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_53</t>
         </is>
       </c>
       <c r="D57" s="50" t="n">
@@ -3738,42 +3731,42 @@
       </c>
       <c r="E57" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-575</t>
         </is>
       </c>
       <c r="F57" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G57" s="50" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="H57" s="50" t="n">
-        <v>300300101</v>
+        <v>300300000</v>
       </c>
       <c r="I57" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J57" s="50" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="K57" s="50" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51">
       <c r="A58" s="50" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="B58" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C58" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D58" s="50" t="n">
@@ -3781,44 +3774,44 @@
       </c>
       <c r="E58" s="50" t="inlineStr">
         <is>
-          <t>-650</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F58" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G58" s="50" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="H58" s="50" t="inlineStr">
         <is>
-          <t>100200001,300300000,</t>
+          <t>300300001|300300002|300300003|300300004|</t>
         </is>
       </c>
       <c r="I58" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J58" s="50" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="K58" s="50" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51">
       <c r="A59" s="50" t="n">
-        <v>300300301</v>
+        <v>300300102</v>
       </c>
       <c r="B59" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C59" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D59" s="50" t="n">
@@ -3831,41 +3824,37 @@
       </c>
       <c r="F59" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G59" s="50" t="n">
-        <v>300300301</v>
-      </c>
-      <c r="H59" s="50" t="inlineStr">
-        <is>
-          <t>300300000,</t>
-        </is>
-      </c>
-      <c r="I59" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>300300102</v>
+      </c>
+      <c r="H59" s="50" t="n">
+        <v>300300101</v>
+      </c>
+      <c r="I59" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J59" s="50" t="n">
-        <v>300300301</v>
+        <v>300300102</v>
       </c>
       <c r="K59" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51">
       <c r="A60" s="50" t="n">
-        <v>300400000</v>
+        <v>300300201</v>
       </c>
       <c r="B60" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D60" s="50" t="n">
@@ -3873,42 +3862,44 @@
       </c>
       <c r="E60" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-650</t>
         </is>
       </c>
       <c r="F60" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G60" s="50" t="n">
-        <v>300400000</v>
-      </c>
-      <c r="H60" s="50" t="n">
-        <v>300600000</v>
+        <v>300300201</v>
+      </c>
+      <c r="H60" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300300000,</t>
+        </is>
       </c>
       <c r="I60" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J60" s="50" t="n">
-        <v>300400000</v>
+        <v>300300201</v>
       </c>
       <c r="K60" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51">
       <c r="A61" s="50" t="n">
-        <v>300400001</v>
+        <v>300300301</v>
       </c>
       <c r="B61" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C61" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D61" s="50" t="n">
@@ -3916,42 +3907,46 @@
       </c>
       <c r="E61" s="50" t="inlineStr">
         <is>
-          <t>-2700</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F61" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G61" s="50" t="n">
-        <v>300400001</v>
-      </c>
-      <c r="H61" s="50" t="n">
-        <v>300400000</v>
-      </c>
-      <c r="I61" s="50" t="n">
-        <v>100</v>
+        <v>300300301</v>
+      </c>
+      <c r="H61" s="50" t="inlineStr">
+        <is>
+          <t>300300000,</t>
+        </is>
+      </c>
+      <c r="I61" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="J61" s="50" t="n">
-        <v>300400001</v>
+        <v>300300301</v>
       </c>
       <c r="K61" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51">
       <c r="A62" s="50" t="n">
-        <v>300400002</v>
+        <v>300400000</v>
       </c>
       <c r="B62" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="50" t="inlineStr">
         <is>
-          <t>ui_research_45</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D62" s="50" t="n">
@@ -3959,42 +3954,42 @@
       </c>
       <c r="E62" s="50" t="inlineStr">
         <is>
-          <t>-2550</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F62" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G62" s="50" t="n">
-        <v>300400002</v>
+        <v>300400000</v>
       </c>
       <c r="H62" s="50" t="n">
-        <v>300400000</v>
+        <v>300600000</v>
       </c>
       <c r="I62" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J62" s="50" t="n">
-        <v>300400002</v>
+        <v>300400000</v>
       </c>
       <c r="K62" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51">
       <c r="A63" s="50" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="B63" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C63" s="50" t="inlineStr">
         <is>
-          <t>ui_research_52</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D63" s="50" t="n">
@@ -4002,7 +3997,7 @@
       </c>
       <c r="E63" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2700</t>
         </is>
       </c>
       <c r="F63" s="50" t="inlineStr">
@@ -4011,7 +4006,7 @@
         </is>
       </c>
       <c r="G63" s="50" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="H63" s="50" t="n">
         <v>300400000</v>
@@ -4020,24 +4015,24 @@
         <v>100</v>
       </c>
       <c r="J63" s="50" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="K63" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51">
       <c r="A64" s="50" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="B64" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C64" s="50" t="inlineStr">
         <is>
-          <t>ui_research_49</t>
+          <t>ui_research_45</t>
         </is>
       </c>
       <c r="D64" s="50" t="n">
@@ -4045,7 +4040,7 @@
       </c>
       <c r="E64" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2550</t>
         </is>
       </c>
       <c r="F64" s="50" t="inlineStr">
@@ -4054,7 +4049,7 @@
         </is>
       </c>
       <c r="G64" s="50" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="H64" s="50" t="n">
         <v>300400000</v>
@@ -4063,24 +4058,24 @@
         <v>100</v>
       </c>
       <c r="J64" s="50" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="K64" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="50" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="B65" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C65" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_52</t>
         </is>
       </c>
       <c r="D65" s="50" t="n">
@@ -4088,7 +4083,7 @@
       </c>
       <c r="E65" s="50" t="inlineStr">
         <is>
-          <t>-2100</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F65" s="50" t="inlineStr">
@@ -4097,7 +4092,7 @@
         </is>
       </c>
       <c r="G65" s="50" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="H65" s="50" t="n">
         <v>300400000</v>
@@ -4106,24 +4101,24 @@
         <v>100</v>
       </c>
       <c r="J65" s="50" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="K65" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="50" t="n">
-        <v>300400101</v>
+        <v>300400004</v>
       </c>
       <c r="B66" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C66" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_49</t>
         </is>
       </c>
       <c r="D66" s="50" t="n">
@@ -4131,44 +4126,42 @@
       </c>
       <c r="E66" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F66" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G66" s="50" t="n">
-        <v>300400101</v>
-      </c>
-      <c r="H66" s="50" t="inlineStr">
-        <is>
-          <t>300400001|300400002|300400003|300400004|300400005|</t>
-        </is>
+        <v>300400004</v>
+      </c>
+      <c r="H66" s="50" t="n">
+        <v>300400000</v>
       </c>
       <c r="I66" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J66" s="50" t="n">
-        <v>300400101</v>
+        <v>300400004</v>
       </c>
       <c r="K66" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51">
       <c r="A67" s="50" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="B67" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D67" s="50" t="n">
@@ -4176,42 +4169,42 @@
       </c>
       <c r="E67" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2100</t>
         </is>
       </c>
       <c r="F67" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G67" s="50" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="H67" s="50" t="n">
-        <v>300400101</v>
+        <v>300400000</v>
       </c>
       <c r="I67" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J67" s="50" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="K67" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51">
       <c r="A68" s="50" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="B68" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C68" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D68" s="50" t="n">
@@ -4219,44 +4212,44 @@
       </c>
       <c r="E68" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F68" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G68" s="50" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="H68" s="50" t="inlineStr">
         <is>
-          <t>100200001,300400000,</t>
+          <t>300400001|300400002|300400003|300400004|300400005|</t>
         </is>
       </c>
       <c r="I68" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J68" s="50" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="K68" s="50" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51">
       <c r="A69" s="50" t="n">
-        <v>300400301</v>
+        <v>300400102</v>
       </c>
       <c r="B69" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D69" s="50" t="n">
@@ -4269,39 +4262,37 @@
       </c>
       <c r="F69" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G69" s="50" t="n">
-        <v>300400301</v>
-      </c>
-      <c r="H69" s="50" t="inlineStr">
-        <is>
-          <t>300400000,</t>
-        </is>
+        <v>300400102</v>
+      </c>
+      <c r="H69" s="50" t="n">
+        <v>300400101</v>
       </c>
       <c r="I69" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J69" s="50" t="n">
-        <v>300400301</v>
+        <v>300400102</v>
       </c>
       <c r="K69" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51">
       <c r="A70" s="50" t="n">
-        <v>300500000</v>
+        <v>300400201</v>
       </c>
       <c r="B70" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D70" s="50" t="n">
@@ -4309,42 +4300,44 @@
       </c>
       <c r="E70" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F70" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G70" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="H70" s="50" t="n">
-        <v>300700000</v>
+        <v>300400201</v>
+      </c>
+      <c r="H70" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300400000,</t>
+        </is>
       </c>
       <c r="I70" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J70" s="50" t="n">
-        <v>300500000</v>
+        <v>300400201</v>
       </c>
       <c r="K70" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51">
       <c r="A71" s="50" t="n">
-        <v>300500001</v>
+        <v>300400301</v>
       </c>
       <c r="B71" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C71" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D71" s="50" t="n">
@@ -4352,42 +4345,44 @@
       </c>
       <c r="E71" s="50" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F71" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G71" s="50" t="n">
-        <v>300500001</v>
-      </c>
-      <c r="H71" s="50" t="n">
-        <v>300500000</v>
+        <v>300400301</v>
+      </c>
+      <c r="H71" s="50" t="inlineStr">
+        <is>
+          <t>300400000,</t>
+        </is>
       </c>
       <c r="I71" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J71" s="50" t="n">
-        <v>300500001</v>
+        <v>300400301</v>
       </c>
       <c r="K71" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51">
       <c r="A72" s="50" t="n">
-        <v>300500002</v>
+        <v>300500000</v>
       </c>
       <c r="B72" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C72" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D72" s="50" t="n">
@@ -4395,42 +4390,42 @@
       </c>
       <c r="E72" s="50" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F72" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G72" s="50" t="n">
-        <v>300500002</v>
+        <v>300500000</v>
       </c>
       <c r="H72" s="50" t="n">
-        <v>300500000</v>
+        <v>300700000</v>
       </c>
       <c r="I72" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J72" s="50" t="n">
-        <v>300500002</v>
+        <v>300500000</v>
       </c>
       <c r="K72" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51">
       <c r="A73" s="50" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="B73" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C73" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D73" s="50" t="n">
@@ -4438,7 +4433,7 @@
       </c>
       <c r="E73" s="50" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F73" s="50" t="inlineStr">
@@ -4447,7 +4442,7 @@
         </is>
       </c>
       <c r="G73" s="50" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="H73" s="50" t="n">
         <v>300500000</v>
@@ -4456,24 +4451,24 @@
         <v>100</v>
       </c>
       <c r="J73" s="50" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="K73" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51">
       <c r="A74" s="50" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="B74" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C74" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D74" s="50" t="n">
@@ -4481,7 +4476,7 @@
       </c>
       <c r="E74" s="50" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F74" s="50" t="inlineStr">
@@ -4490,7 +4485,7 @@
         </is>
       </c>
       <c r="G74" s="50" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="H74" s="50" t="n">
         <v>300500000</v>
@@ -4499,24 +4494,24 @@
         <v>100</v>
       </c>
       <c r="J74" s="50" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="K74" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="50" t="n">
-        <v>300500101</v>
+        <v>300500003</v>
       </c>
       <c r="B75" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C75" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D75" s="50" t="n">
@@ -4524,44 +4519,42 @@
       </c>
       <c r="E75" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F75" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G75" s="50" t="n">
-        <v>300500101</v>
-      </c>
-      <c r="H75" s="50" t="inlineStr">
-        <is>
-          <t>300500001|300500002|300500003|300500004|</t>
-        </is>
+        <v>300500003</v>
+      </c>
+      <c r="H75" s="50" t="n">
+        <v>300500000</v>
       </c>
       <c r="I75" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J75" s="50" t="n">
-        <v>300500101</v>
+        <v>300500003</v>
       </c>
       <c r="K75" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="50" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="B76" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C76" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D76" s="50" t="n">
@@ -4569,42 +4562,42 @@
       </c>
       <c r="E76" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="F76" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G76" s="50" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="H76" s="50" t="n">
-        <v>300500101</v>
+        <v>300500000</v>
       </c>
       <c r="I76" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J76" s="50" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="K76" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="50" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="B77" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C77" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D77" s="50" t="n">
@@ -4612,44 +4605,44 @@
       </c>
       <c r="E77" s="50" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F77" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G77" s="50" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="H77" s="50" t="inlineStr">
         <is>
-          <t>100200001,300500000,</t>
+          <t>300500001|300500002|300500003|300500004|</t>
         </is>
       </c>
       <c r="I77" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J77" s="50" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="K77" s="50" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51">
       <c r="A78" s="50" t="n">
-        <v>300500301</v>
+        <v>300500102</v>
       </c>
       <c r="B78" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C78" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D78" s="50" t="n">
@@ -4662,39 +4655,37 @@
       </c>
       <c r="F78" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G78" s="50" t="n">
-        <v>300500301</v>
-      </c>
-      <c r="H78" s="50" t="inlineStr">
-        <is>
-          <t>300500000,</t>
-        </is>
+        <v>300500102</v>
+      </c>
+      <c r="H78" s="50" t="n">
+        <v>300500101</v>
       </c>
       <c r="I78" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J78" s="50" t="n">
-        <v>300500301</v>
+        <v>300500102</v>
       </c>
       <c r="K78" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51">
       <c r="A79" s="50" t="n">
-        <v>300600000</v>
+        <v>300500201</v>
       </c>
       <c r="B79" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C79" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D79" s="50" t="n">
@@ -4702,42 +4693,44 @@
       </c>
       <c r="E79" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="F79" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G79" s="50" t="n">
-        <v>300600000</v>
-      </c>
-      <c r="H79" s="50" t="n">
-        <v>300300000</v>
+        <v>300500201</v>
+      </c>
+      <c r="H79" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300500000,</t>
+        </is>
       </c>
       <c r="I79" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J79" s="50" t="n">
-        <v>300600000</v>
+        <v>300500201</v>
       </c>
       <c r="K79" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51">
       <c r="A80" s="50" t="n">
-        <v>300600001</v>
+        <v>300500301</v>
       </c>
       <c r="B80" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C80" s="50" t="inlineStr">
         <is>
-          <t>ui_research_44</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D80" s="50" t="n">
@@ -4745,42 +4738,44 @@
       </c>
       <c r="E80" s="50" t="inlineStr">
         <is>
-          <t>-1900</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F80" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G80" s="50" t="n">
-        <v>300600001</v>
-      </c>
-      <c r="H80" s="50" t="n">
-        <v>300600000</v>
+        <v>300500301</v>
+      </c>
+      <c r="H80" s="50" t="inlineStr">
+        <is>
+          <t>300500000,</t>
+        </is>
       </c>
       <c r="I80" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J80" s="50" t="n">
-        <v>300600001</v>
+        <v>300500301</v>
       </c>
       <c r="K80" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51">
       <c r="A81" s="50" t="n">
-        <v>300600002</v>
+        <v>300600000</v>
       </c>
       <c r="B81" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C81" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D81" s="50" t="n">
@@ -4788,42 +4783,42 @@
       </c>
       <c r="E81" s="50" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F81" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G81" s="50" t="n">
-        <v>300600002</v>
+        <v>300600000</v>
       </c>
       <c r="H81" s="50" t="n">
-        <v>300600000</v>
+        <v>300300000</v>
       </c>
       <c r="I81" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J81" s="50" t="n">
-        <v>300600002</v>
+        <v>300600000</v>
       </c>
       <c r="K81" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51">
       <c r="A82" s="50" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="B82" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C82" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_44</t>
         </is>
       </c>
       <c r="D82" s="50" t="n">
@@ -4831,7 +4826,7 @@
       </c>
       <c r="E82" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1900</t>
         </is>
       </c>
       <c r="F82" s="50" t="inlineStr">
@@ -4840,7 +4835,7 @@
         </is>
       </c>
       <c r="G82" s="50" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="H82" s="50" t="n">
         <v>300600000</v>
@@ -4849,24 +4844,24 @@
         <v>100</v>
       </c>
       <c r="J82" s="50" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="K82" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51">
       <c r="A83" s="50" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="B83" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C83" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D83" s="50" t="n">
@@ -4874,7 +4869,7 @@
       </c>
       <c r="E83" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="F83" s="50" t="inlineStr">
@@ -4883,7 +4878,7 @@
         </is>
       </c>
       <c r="G83" s="50" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="H83" s="50" t="n">
         <v>300600000</v>
@@ -4892,24 +4887,24 @@
         <v>100</v>
       </c>
       <c r="J83" s="50" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="K83" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="50" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="B84" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C84" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D84" s="50" t="n">
@@ -4917,7 +4912,7 @@
       </c>
       <c r="E84" s="50" t="inlineStr">
         <is>
-          <t>-1300</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F84" s="50" t="inlineStr">
@@ -4926,7 +4921,7 @@
         </is>
       </c>
       <c r="G84" s="50" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="H84" s="50" t="n">
         <v>300600000</v>
@@ -4935,24 +4930,24 @@
         <v>100</v>
       </c>
       <c r="J84" s="50" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="K84" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="50" t="n">
-        <v>300600101</v>
+        <v>300600004</v>
       </c>
       <c r="B85" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C85" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D85" s="50" t="n">
@@ -4960,44 +4955,42 @@
       </c>
       <c r="E85" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F85" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G85" s="50" t="n">
-        <v>300600101</v>
-      </c>
-      <c r="H85" s="50" t="inlineStr">
-        <is>
-          <t>300600001|300600002|300600003|300600004|</t>
-        </is>
+        <v>300600004</v>
+      </c>
+      <c r="H85" s="50" t="n">
+        <v>300600000</v>
       </c>
       <c r="I85" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J85" s="50" t="n">
-        <v>300600101</v>
+        <v>300600004</v>
       </c>
       <c r="K85" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="50" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="B86" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C86" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D86" s="50" t="n">
@@ -5005,42 +4998,42 @@
       </c>
       <c r="E86" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1300</t>
         </is>
       </c>
       <c r="F86" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G86" s="50" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="H86" s="50" t="n">
-        <v>300600101</v>
+        <v>300600000</v>
       </c>
       <c r="I86" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J86" s="50" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="K86" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="50" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="B87" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C87" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D87" s="50" t="n">
@@ -5048,44 +5041,44 @@
       </c>
       <c r="E87" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F87" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G87" s="50" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="H87" s="50" t="inlineStr">
         <is>
-          <t>100200001,300600000,</t>
+          <t>300600001|300600002|300600003|300600004|</t>
         </is>
       </c>
       <c r="I87" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J87" s="50" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="K87" s="50" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="50" t="n">
-        <v>300600301</v>
+        <v>300600102</v>
       </c>
       <c r="B88" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C88" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D88" s="50" t="n">
@@ -5098,39 +5091,37 @@
       </c>
       <c r="F88" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G88" s="50" t="n">
-        <v>300600301</v>
-      </c>
-      <c r="H88" s="50" t="inlineStr">
-        <is>
-          <t>300600000,</t>
-        </is>
+        <v>300600102</v>
+      </c>
+      <c r="H88" s="50" t="n">
+        <v>300600101</v>
       </c>
       <c r="I88" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J88" s="50" t="n">
-        <v>300600301</v>
+        <v>300600102</v>
       </c>
       <c r="K88" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="50" t="n">
-        <v>300700000</v>
+        <v>300600201</v>
       </c>
       <c r="B89" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C89" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D89" s="50" t="n">
@@ -5138,42 +5129,44 @@
       </c>
       <c r="E89" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F89" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G89" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="H89" s="50" t="n">
-        <v>300100000</v>
+        <v>300600201</v>
+      </c>
+      <c r="H89" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300600000,</t>
+        </is>
       </c>
       <c r="I89" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J89" s="50" t="n">
-        <v>300700000</v>
+        <v>300600201</v>
       </c>
       <c r="K89" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="50" t="n">
-        <v>300700001</v>
+        <v>300600301</v>
       </c>
       <c r="B90" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C90" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D90" s="50" t="n">
@@ -5181,42 +5174,44 @@
       </c>
       <c r="E90" s="50" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F90" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G90" s="50" t="n">
-        <v>300700001</v>
-      </c>
-      <c r="H90" s="50" t="n">
-        <v>300700000</v>
+        <v>300600301</v>
+      </c>
+      <c r="H90" s="50" t="inlineStr">
+        <is>
+          <t>300600000,</t>
+        </is>
       </c>
       <c r="I90" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J90" s="50" t="n">
-        <v>300700001</v>
+        <v>300600301</v>
       </c>
       <c r="K90" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="50" t="n">
-        <v>300700002</v>
+        <v>300700000</v>
       </c>
       <c r="B91" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_38</t>
         </is>
       </c>
       <c r="D91" s="50" t="n">
@@ -5224,42 +5219,42 @@
       </c>
       <c r="E91" s="50" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F91" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G91" s="50" t="n">
-        <v>300700002</v>
+        <v>300700000</v>
       </c>
       <c r="H91" s="50" t="n">
-        <v>300700000</v>
+        <v>300100000</v>
       </c>
       <c r="I91" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J91" s="50" t="n">
-        <v>300700002</v>
+        <v>300700000</v>
       </c>
       <c r="K91" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="50" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="B92" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D92" s="50" t="n">
@@ -5267,7 +5262,7 @@
       </c>
       <c r="E92" s="50" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="F92" s="50" t="inlineStr">
@@ -5276,7 +5271,7 @@
         </is>
       </c>
       <c r="G92" s="50" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="H92" s="50" t="n">
         <v>300700000</v>
@@ -5285,24 +5280,24 @@
         <v>100</v>
       </c>
       <c r="J92" s="50" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="K92" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="50" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="B93" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D93" s="50" t="n">
@@ -5310,7 +5305,7 @@
       </c>
       <c r="E93" s="50" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F93" s="50" t="inlineStr">
@@ -5319,7 +5314,7 @@
         </is>
       </c>
       <c r="G93" s="50" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="H93" s="50" t="n">
         <v>300700000</v>
@@ -5328,24 +5323,24 @@
         <v>100</v>
       </c>
       <c r="J93" s="50" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="K93" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="50" t="n">
-        <v>300700101</v>
+        <v>300700003</v>
       </c>
       <c r="B94" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C94" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D94" s="50" t="n">
@@ -5353,44 +5348,42 @@
       </c>
       <c r="E94" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="F94" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G94" s="50" t="n">
-        <v>300700101</v>
-      </c>
-      <c r="H94" s="50" t="inlineStr">
-        <is>
-          <t>300700001|300700002|300700003|300700004|</t>
-        </is>
+        <v>300700003</v>
+      </c>
+      <c r="H94" s="50" t="n">
+        <v>300700000</v>
       </c>
       <c r="I94" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J94" s="50" t="n">
-        <v>300700101</v>
+        <v>300700003</v>
       </c>
       <c r="K94" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="50" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="B95" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C95" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D95" s="50" t="n">
@@ -5398,42 +5391,42 @@
       </c>
       <c r="E95" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F95" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G95" s="50" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="H95" s="50" t="n">
-        <v>300700101</v>
+        <v>300700000</v>
       </c>
       <c r="I95" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J95" s="50" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="K95" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="50" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="B96" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C96" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D96" s="50" t="n">
@@ -5441,44 +5434,44 @@
       </c>
       <c r="E96" s="50" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F96" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G96" s="50" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="H96" s="50" t="inlineStr">
         <is>
-          <t>100200001,300700000,</t>
+          <t>300700001|300700002|300700003|300700004|</t>
         </is>
       </c>
       <c r="I96" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J96" s="50" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="K96" s="50" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="50" t="n">
-        <v>300700301</v>
+        <v>300700102</v>
       </c>
       <c r="B97" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C97" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D97" s="50" t="n">
@@ -5491,66 +5484,154 @@
       </c>
       <c r="F97" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G97" s="50" t="n">
-        <v>300700301</v>
-      </c>
-      <c r="H97" s="50" t="inlineStr">
-        <is>
-          <t>300700000,</t>
-        </is>
+        <v>300700102</v>
+      </c>
+      <c r="H97" s="50" t="n">
+        <v>300700101</v>
       </c>
       <c r="I97" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J97" s="50" t="n">
-        <v>300700301</v>
+        <v>300700102</v>
       </c>
       <c r="K97" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B98" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C98" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_38</t>
+        </is>
+      </c>
+      <c r="D98" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="50" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="F98" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="G98" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="H98" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300700000,</t>
+        </is>
+      </c>
+      <c r="I98" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J98" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="K98" s="50" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B99" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C99" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_58</t>
+        </is>
+      </c>
+      <c r="D99" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="50" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="F99" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="G99" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="H99" s="50" t="inlineStr">
+        <is>
+          <t>300700000,</t>
+        </is>
+      </c>
+      <c r="I99" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J99" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="K99" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="B98" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" s="50" t="inlineStr">
+      <c r="B100" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="50" t="inlineStr">
         <is>
           <t>ui_research_18</t>
         </is>
       </c>
-      <c r="D98" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="50" t="inlineStr">
+      <c r="D100" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F98" s="50" t="inlineStr">
+      <c r="F100" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G98" s="50" t="n">
+      <c r="G100" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="I98" s="50" t="inlineStr">
+      <c r="I100" s="50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J98" s="50" t="n">
+      <c r="J100" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="K98" s="50" t="inlineStr">
+      <c r="K100" s="50" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -1535,47 +1535,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="50" t="n">
         <v>100000005</v>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>ui_research_5</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="50" t="inlineStr">
         <is>
           <t>-500</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="50" t="n">
         <v>100000008</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="50" t="inlineStr">
         <is>
           <t>100000000</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="50" t="inlineStr">
         <is>
           <t>1000,2000,3000,4000,5000,</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="50" t="n">
         <v>100000008</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="50" t="inlineStr">
         <is>
           <t>进阶素材可选数量+1</t>
         </is>
@@ -1903,57 +1903,55 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="n">
-        <v>100300001</v>
-      </c>
-      <c r="B16" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_9</t>
-        </is>
-      </c>
-      <c r="D16" s="50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="50" t="inlineStr">
-        <is>
-          <t>-400</t>
-        </is>
-      </c>
-      <c r="G16" s="50" t="n">
-        <v>100300001</v>
-      </c>
-      <c r="H16" s="50" t="inlineStr">
-        <is>
-          <t>100500001</t>
-        </is>
-      </c>
-      <c r="I16" s="50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" s="50" t="n">
-        <v>100300001</v>
-      </c>
-      <c r="K16" s="50" t="inlineStr">
-        <is>
-          <t>开启终焉议会</t>
+      <c r="A16" t="n">
+        <v>100200004</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ui_research_59</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-300</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-500</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>100200004</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>100200001</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>100200004</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>征服通关获得声望</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="50" t="n">
-        <v>100300002</v>
+        <v>100300001</v>
       </c>
       <c r="B17" s="50" t="n">
         <v>1</v>
@@ -1970,20 +1968,20 @@
       </c>
       <c r="E17" s="50" t="inlineStr">
         <is>
-          <t>-150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="G17" s="50" t="n">
-        <v>100300002</v>
+        <v>100300001</v>
       </c>
       <c r="H17" s="50" t="inlineStr">
         <is>
-          <t>100300003</t>
+          <t>100500001</t>
         </is>
       </c>
       <c r="I17" s="50" t="inlineStr">
@@ -1992,17 +1990,17 @@
         </is>
       </c>
       <c r="J17" s="50" t="n">
-        <v>100300002</v>
+        <v>100300001</v>
       </c>
       <c r="K17" s="50" t="inlineStr">
         <is>
-          <t>传送门详情-线路数量预览</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="50" t="n">
-        <v>100300003</v>
+        <v>100300002</v>
       </c>
       <c r="B18" s="50" t="n">
         <v>1</v>
@@ -2019,20 +2017,20 @@
       </c>
       <c r="E18" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-150</t>
         </is>
       </c>
       <c r="F18" s="50" t="inlineStr">
         <is>
-          <t>-600</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="G18" s="50" t="n">
-        <v>100300003</v>
+        <v>100300002</v>
       </c>
       <c r="H18" s="50" t="inlineStr">
         <is>
-          <t>100300001</t>
+          <t>100300003</t>
         </is>
       </c>
       <c r="I18" s="50" t="inlineStr">
@@ -2041,17 +2039,17 @@
         </is>
       </c>
       <c r="J18" s="50" t="n">
-        <v>100300003</v>
+        <v>100300002</v>
       </c>
       <c r="K18" s="50" t="inlineStr">
         <is>
-          <t>传送门详情-关卡数量预览</t>
+          <t>传送门详情-线路数量预览</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="50" t="n">
-        <v>100300004</v>
+        <v>100300003</v>
       </c>
       <c r="B19" s="50" t="n">
         <v>1</v>
@@ -2068,20 +2066,20 @@
       </c>
       <c r="E19" s="50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-600</t>
         </is>
       </c>
       <c r="G19" s="50" t="n">
-        <v>100300004</v>
+        <v>100300003</v>
       </c>
       <c r="H19" s="50" t="inlineStr">
         <is>
-          <t>100300003</t>
+          <t>100300001</t>
         </is>
       </c>
       <c r="I19" s="50" t="inlineStr">
@@ -2090,17 +2088,17 @@
         </is>
       </c>
       <c r="J19" s="50" t="n">
-        <v>100300004</v>
+        <v>100300003</v>
       </c>
       <c r="K19" s="50" t="inlineStr">
         <is>
-          <t>传送门详情-路径长度预览</t>
+          <t>传送门详情-关卡数量预览</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="n">
-        <v>100300005</v>
+        <v>100300004</v>
       </c>
       <c r="B20" s="50" t="n">
         <v>1</v>
@@ -2117,7 +2115,7 @@
       </c>
       <c r="E20" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F20" s="50" t="inlineStr">
@@ -2126,7 +2124,7 @@
         </is>
       </c>
       <c r="G20" s="50" t="n">
-        <v>100300005</v>
+        <v>100300004</v>
       </c>
       <c r="H20" s="50" t="inlineStr">
         <is>
@@ -2139,17 +2137,17 @@
         </is>
       </c>
       <c r="J20" s="50" t="n">
-        <v>100300005</v>
+        <v>100300004</v>
       </c>
       <c r="K20" s="50" t="inlineStr">
         <is>
-          <t>传送门详情-奖励预览</t>
+          <t>传送门详情-路径长度预览</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="50" t="n">
-        <v>100300006</v>
+        <v>100300005</v>
       </c>
       <c r="B21" s="50" t="n">
         <v>1</v>
@@ -2159,55 +2157,57 @@
           <t>ui_research_9</t>
         </is>
       </c>
-      <c r="D21" s="50" t="n">
-        <v>10</v>
+      <c r="D21" s="50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="E21" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" s="50" t="inlineStr">
         <is>
-          <t>-400</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="G21" s="50" t="n">
-        <v>100300006</v>
+        <v>100300005</v>
       </c>
       <c r="H21" s="50" t="inlineStr">
         <is>
-          <t>100300001</t>
+          <t>100300003</t>
         </is>
       </c>
       <c r="I21" s="50" t="inlineStr">
         <is>
-          <t>300*2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" s="50" t="n">
-        <v>100300006</v>
+        <v>100300005</v>
       </c>
       <c r="K21" s="50" t="inlineStr">
         <is>
-          <t>传送门刷新解锁</t>
+          <t>传送门详情-奖励预览</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="50" t="n">
-        <v>100310112</v>
+        <v>100300006</v>
       </c>
       <c r="B22" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_9</t>
         </is>
       </c>
       <c r="D22" s="50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" s="50" t="inlineStr">
         <is>
@@ -2216,11 +2216,11 @@
       </c>
       <c r="F22" s="50" t="inlineStr">
         <is>
-          <t>-600</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="G22" s="50" t="n">
-        <v>100310112</v>
+        <v>100300006</v>
       </c>
       <c r="H22" s="50" t="inlineStr">
         <is>
@@ -2229,68 +2229,68 @@
       </c>
       <c r="I22" s="50" t="inlineStr">
         <is>
-          <t>100,400,800,1600,3200,6400,12800,25600,51200,</t>
+          <t>300*2</t>
         </is>
       </c>
       <c r="J22" s="50" t="n">
-        <v>100310112</v>
+        <v>100300006</v>
       </c>
       <c r="K22" s="50" t="inlineStr">
         <is>
-          <t>剑与魔法：征服难度+1</t>
+          <t>传送门刷新解锁</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="50" t="n">
-        <v>100400000</v>
+        <v>100310112</v>
       </c>
       <c r="B23" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>ui_research_57</t>
+          <t>ui_research_11</t>
         </is>
       </c>
       <c r="D23" s="50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E23" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F23" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-600</t>
         </is>
       </c>
       <c r="G23" s="50" t="n">
-        <v>100400000</v>
+        <v>100310112</v>
       </c>
       <c r="H23" s="50" t="inlineStr">
         <is>
-          <t>100500001</t>
+          <t>100300001</t>
         </is>
       </c>
       <c r="I23" s="50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100,400,800,1600,3200,6400,12800,25600,51200,</t>
         </is>
       </c>
       <c r="J23" s="50" t="n">
-        <v>100400000</v>
+        <v>100310112</v>
       </c>
       <c r="K23" s="50" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>剑与魔法：征服难度+1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B24" s="50" t="n">
         <v>1</v>
@@ -2305,37 +2305,39 @@
       </c>
       <c r="E24" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G24" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="H24" s="50" t="n">
         <v>100400000</v>
       </c>
+      <c r="H24" s="50" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
+      </c>
       <c r="I24" s="50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" s="50" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="K24" s="50" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B25" s="50" t="n">
         <v>1</v>
@@ -2350,7 +2352,7 @@
       </c>
       <c r="E25" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F25" s="50" t="inlineStr">
@@ -2359,30 +2361,28 @@
         </is>
       </c>
       <c r="G25" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="H25" s="50" t="inlineStr">
-        <is>
-          <t>100400000</t>
-        </is>
+        <v>100400001</v>
+      </c>
+      <c r="H25" s="50" t="n">
+        <v>100400000</v>
       </c>
       <c r="I25" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" s="50" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="K25" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="50" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B26" s="50" t="n">
         <v>1</v>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="D26" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E26" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="50" t="inlineStr">
@@ -2406,28 +2406,30 @@
         </is>
       </c>
       <c r="G26" s="50" t="n">
-        <v>100401001</v>
-      </c>
-      <c r="H26" s="50" t="n">
         <v>100401000</v>
       </c>
+      <c r="H26" s="50" t="inlineStr">
+        <is>
+          <t>100400000</t>
+        </is>
+      </c>
       <c r="I26" s="50" t="inlineStr">
         <is>
-          <t>100*1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J26" s="50" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="K26" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="50" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B27" s="50" t="n">
         <v>1</v>
@@ -2438,41 +2440,41 @@
         </is>
       </c>
       <c r="D27" s="50" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E27" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="F27" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G27" s="50" t="n">
-        <v>100402000</v>
-      </c>
-      <c r="H27" s="50" t="inlineStr">
-        <is>
-          <t>100401000,100401001,</t>
-        </is>
-      </c>
-      <c r="I27" s="50" t="n">
-        <v>1000</v>
+        <v>100401001</v>
+      </c>
+      <c r="H27" s="50" t="n">
+        <v>100401000</v>
+      </c>
+      <c r="I27" s="50" t="inlineStr">
+        <is>
+          <t>100*1</t>
+        </is>
       </c>
       <c r="J27" s="50" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="K27" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="50" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B28" s="50" t="n">
         <v>1</v>
@@ -2483,11 +2485,11 @@
         </is>
       </c>
       <c r="D28" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E28" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F28" s="50" t="inlineStr">
@@ -2496,28 +2498,28 @@
         </is>
       </c>
       <c r="G28" s="50" t="n">
-        <v>100402001</v>
-      </c>
-      <c r="H28" s="50" t="n">
         <v>100402000</v>
       </c>
-      <c r="I28" s="50" t="inlineStr">
-        <is>
-          <t>1000*1</t>
-        </is>
+      <c r="H28" s="50" t="inlineStr">
+        <is>
+          <t>100401000,100401001,</t>
+        </is>
+      </c>
+      <c r="I28" s="50" t="n">
+        <v>1000</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="K28" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="50" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B29" s="50" t="n">
         <v>1</v>
@@ -2528,41 +2530,41 @@
         </is>
       </c>
       <c r="D29" s="50" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E29" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="F29" s="50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="G29" s="50" t="n">
-        <v>100403000</v>
-      </c>
-      <c r="H29" s="50" t="inlineStr">
-        <is>
-          <t>100402000,100402001,</t>
-        </is>
-      </c>
-      <c r="I29" s="50" t="n">
-        <v>10000</v>
+        <v>100402001</v>
+      </c>
+      <c r="H29" s="50" t="n">
+        <v>100402000</v>
+      </c>
+      <c r="I29" s="50" t="inlineStr">
+        <is>
+          <t>1000*1</t>
+        </is>
       </c>
       <c r="J29" s="50" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="K29" s="50" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="50" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B30" s="50" t="n">
         <v>1</v>
@@ -2573,11 +2575,11 @@
         </is>
       </c>
       <c r="D30" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E30" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="50" t="inlineStr">
@@ -2586,184 +2588,191 @@
         </is>
       </c>
       <c r="G30" s="50" t="n">
-        <v>100403001</v>
-      </c>
-      <c r="H30" s="50" t="n">
         <v>100403000</v>
       </c>
-      <c r="I30" s="50" t="inlineStr">
-        <is>
-          <t>10000*1</t>
-        </is>
+      <c r="H30" s="50" t="inlineStr">
+        <is>
+          <t>100402000,100402001,</t>
+        </is>
+      </c>
+      <c r="I30" s="50" t="n">
+        <v>10000</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="K30" s="50" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="50" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B31" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>ui_research_5</t>
+          <t>ui_research_57</t>
         </is>
       </c>
       <c r="D31" s="50" t="n">
-        <v>30</v>
-      </c>
-      <c r="E31" s="50" t="n">
-        <v>-200</v>
-      </c>
-      <c r="F31" s="50" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="E31" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F31" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="G31" s="50" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
+      </c>
+      <c r="H31" s="50" t="n">
+        <v>100403000</v>
       </c>
       <c r="I31" s="50" t="inlineStr">
         <is>
-          <t>50,100,150,200,250,300,350,400,450,500,</t>
+          <t>10000*1</t>
         </is>
       </c>
       <c r="J31" s="50" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="K31" s="50" t="inlineStr">
         <is>
-          <t>阵容上限+1</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="B32" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
-          <t>ui_research_6</t>
+          <t>ui_research_5</t>
         </is>
       </c>
       <c r="D32" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F32" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="E32" s="50" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="50" t="n">
+        <v>0</v>
       </c>
       <c r="G32" s="50" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="I32" s="50" t="inlineStr">
         <is>
-          <t>100,200,300,400,</t>
+          <t>50,100,150,200,250,300,350,400,450,500,</t>
         </is>
       </c>
       <c r="J32" s="50" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="K32" s="50" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容上限+1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="50" t="n">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="B33" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
-          <t>ui_research_60</t>
+          <t>ui_research_6</t>
         </is>
       </c>
       <c r="D33" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="E33" s="50" t="n">
-        <v>-200</v>
-      </c>
-      <c r="F33" s="50" t="n">
-        <v>-200</v>
+        <v>4</v>
+      </c>
+      <c r="E33" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F33" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G33" s="50" t="n">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="I33" s="50" t="inlineStr">
         <is>
-          <t>100,500,1000,5000,10000,50000</t>
+          <t>100,200,300,400,</t>
         </is>
       </c>
       <c r="J33" s="50" t="n">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="K33" s="50" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="50" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B34" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="50" t="inlineStr">
         <is>
-          <t>ui_research_61</t>
+          <t>ui_research_60</t>
         </is>
       </c>
       <c r="D34" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" s="50" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F34" s="50" t="n">
         <v>-200</v>
       </c>
       <c r="G34" s="50" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="I34" s="50" t="inlineStr">
         <is>
-          <t>100,500,1000,5000,10000</t>
+          <t>100,500,1000,5000,10000,50000</t>
         </is>
       </c>
       <c r="J34" s="50" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="K34" s="50" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="50" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B35" s="50" t="n">
         <v>2</v>
@@ -2774,218 +2783,211 @@
         </is>
       </c>
       <c r="D35" s="50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35" s="50" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F35" s="50" t="n">
         <v>-200</v>
       </c>
       <c r="G35" s="50" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="I35" s="50" t="inlineStr">
         <is>
-          <t>100,500,1000</t>
+          <t>100,500,1000,5000,10000</t>
         </is>
       </c>
       <c r="J35" s="50" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="K35" s="50" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="50" t="n">
-        <v>200500001</v>
+        <v>200400001</v>
       </c>
       <c r="B36" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C36" s="50" t="inlineStr">
         <is>
+          <t>ui_research_61</t>
+        </is>
+      </c>
+      <c r="D36" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="F36" s="50" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G36" s="50" t="n">
+        <v>200400001</v>
+      </c>
+      <c r="I36" s="50" t="inlineStr">
+        <is>
+          <t>100,500,1000</t>
+        </is>
+      </c>
+      <c r="J36" s="50" t="n">
+        <v>200400001</v>
+      </c>
+      <c r="K36" s="50" t="inlineStr">
+        <is>
+          <t>魔王魔力恢复速度+1/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="50" t="n">
+        <v>200500001</v>
+      </c>
+      <c r="B37" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="50" t="inlineStr">
+        <is>
           <t>ui_research_62</t>
         </is>
       </c>
-      <c r="D36" s="50" t="n">
+      <c r="D37" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="E36" s="50" t="inlineStr">
+      <c r="E37" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="50" t="inlineStr">
+      <c r="F37" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="G36" s="50" t="n">
+      <c r="G37" s="50" t="n">
         <v>200500001</v>
       </c>
-      <c r="I36" s="50" t="inlineStr">
+      <c r="I37" s="50" t="inlineStr">
         <is>
           <t>100,500,1000,5000,10000</t>
         </is>
       </c>
-      <c r="J36" s="50" t="n">
+      <c r="J37" s="50" t="n">
         <v>200500001</v>
       </c>
-      <c r="K36" s="50" t="inlineStr">
+      <c r="K37" s="50" t="inlineStr">
         <is>
           <t>深渊馈赠刷新次数+1</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="38">
+      <c r="A38" s="50" t="n">
         <v>200600001</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B38" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" s="50" t="inlineStr">
         <is>
           <t>ui_research_6</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="D38" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="50" t="inlineStr">
         <is>
           <t>-200</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="G38" s="50" t="n">
         <v>200600001</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="H38" s="50" t="inlineStr"/>
+      <c r="I38" s="50" t="inlineStr">
         <is>
           <t>1000,5000,20000</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J38" s="50" t="n">
         <v>200600001</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K38" s="50" t="inlineStr">
         <is>
           <t>空格突进</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>200700001</v>
-      </c>
-      <c r="B38" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ui_research_60</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-400</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>200700001</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>200600001</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1000,3000,8000,20000</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>200700001</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50" t="n">
-        <v>300100000</v>
+        <v>200700001</v>
       </c>
       <c r="B39" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_60</t>
         </is>
       </c>
       <c r="D39" s="50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="F39" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G39" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="H39" s="50" t="n">
-        <v>300200000</v>
+        <v>200700001</v>
+      </c>
+      <c r="H39" s="50" t="inlineStr">
+        <is>
+          <t>200600001</t>
+        </is>
       </c>
       <c r="I39" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>1000,3000,8000,20000</t>
         </is>
       </c>
       <c r="J39" s="50" t="n">
-        <v>300100000</v>
+        <v>200700001</v>
       </c>
       <c r="K39" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="50" t="n">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="B40" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C40" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D40" s="50" t="n">
@@ -2993,42 +2995,44 @@
       </c>
       <c r="E40" s="50" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F40" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G40" s="50" t="n">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="H40" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="I40" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J40" s="50" t="n">
         <v>300100000</v>
       </c>
-      <c r="I40" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J40" s="50" t="n">
-        <v>300100001</v>
-      </c>
       <c r="K40" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="50" t="n">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="B41" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C41" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D41" s="50" t="n">
@@ -3036,7 +3040,7 @@
       </c>
       <c r="E41" s="50" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F41" s="50" t="inlineStr">
@@ -3045,7 +3049,7 @@
         </is>
       </c>
       <c r="G41" s="50" t="n">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="H41" s="50" t="n">
         <v>300100000</v>
@@ -3054,24 +3058,24 @@
         <v>100</v>
       </c>
       <c r="J41" s="50" t="n">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="K41" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="50" t="n">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="B42" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D42" s="50" t="n">
@@ -3079,7 +3083,7 @@
       </c>
       <c r="E42" s="50" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F42" s="50" t="inlineStr">
@@ -3088,7 +3092,7 @@
         </is>
       </c>
       <c r="G42" s="50" t="n">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="H42" s="50" t="n">
         <v>300100000</v>
@@ -3097,24 +3101,24 @@
         <v>100</v>
       </c>
       <c r="J42" s="50" t="n">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="K42" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="50" t="n">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="B43" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C43" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D43" s="50" t="n">
@@ -3122,7 +3126,7 @@
       </c>
       <c r="E43" s="50" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F43" s="50" t="inlineStr">
@@ -3131,7 +3135,7 @@
         </is>
       </c>
       <c r="G43" s="50" t="n">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="H43" s="50" t="n">
         <v>300100000</v>
@@ -3140,24 +3144,24 @@
         <v>100</v>
       </c>
       <c r="J43" s="50" t="n">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="K43" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="50" t="n">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="B44" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D44" s="50" t="n">
@@ -3165,44 +3169,42 @@
       </c>
       <c r="E44" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F44" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G44" s="50" t="n">
-        <v>300100101</v>
-      </c>
-      <c r="H44" s="50" t="inlineStr">
-        <is>
-          <t>300100001|300100002|300100003|300100004|</t>
-        </is>
+        <v>300100004</v>
+      </c>
+      <c r="H44" s="50" t="n">
+        <v>300100000</v>
       </c>
       <c r="I44" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J44" s="50" t="n">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="K44" s="50" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="50" t="n">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="B45" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C45" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D45" s="50" t="n">
@@ -3215,37 +3217,39 @@
       </c>
       <c r="F45" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G45" s="50" t="n">
-        <v>300100102</v>
-      </c>
-      <c r="H45" s="50" t="n">
         <v>300100101</v>
+      </c>
+      <c r="H45" s="50" t="inlineStr">
+        <is>
+          <t>300100001|300100002|300100003|300100004|</t>
+        </is>
       </c>
       <c r="I45" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J45" s="50" t="n">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="K45" s="50" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="50" t="n">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="B46" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C46" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D46" s="50" t="n">
@@ -3253,44 +3257,42 @@
       </c>
       <c r="E46" s="50" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F46" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G46" s="50" t="n">
-        <v>300100201</v>
-      </c>
-      <c r="H46" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300100000,</t>
-        </is>
+        <v>300100102</v>
+      </c>
+      <c r="H46" s="50" t="n">
+        <v>300100101</v>
       </c>
       <c r="I46" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J46" s="50" t="n">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="K46" s="50" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="50" t="n">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="B47" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C47" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D47" s="50" t="n">
@@ -3298,7 +3300,7 @@
       </c>
       <c r="E47" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F47" s="50" t="inlineStr">
@@ -3307,37 +3309,35 @@
         </is>
       </c>
       <c r="G47" s="50" t="n">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="H47" s="50" t="inlineStr">
         <is>
-          <t>300100000,</t>
-        </is>
-      </c>
-      <c r="I47" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+          <t>100200001,300100000,</t>
+        </is>
+      </c>
+      <c r="I47" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J47" s="50" t="n">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="K47" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="50" t="n">
-        <v>300200000</v>
+        <v>300100301</v>
       </c>
       <c r="B48" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D48" s="50" t="n">
@@ -3345,41 +3345,46 @@
       </c>
       <c r="E48" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G48" s="50" t="n">
-        <v>300200000</v>
+        <v>300100301</v>
+      </c>
+      <c r="H48" s="50" t="inlineStr">
+        <is>
+          <t>300100000,</t>
+        </is>
       </c>
       <c r="I48" s="50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J48" s="50" t="n">
-        <v>300200000</v>
+        <v>300100301</v>
       </c>
       <c r="K48" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="50" t="n">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B49" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D49" s="50" t="n">
@@ -3387,44 +3392,41 @@
       </c>
       <c r="E49" s="50" t="inlineStr">
         <is>
-          <t>-223</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" s="50" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G49" s="50" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="H49" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I49" s="50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" s="50" t="n">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="K49" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="50" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B50" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C50" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D50" s="50" t="n">
@@ -3432,44 +3434,44 @@
       </c>
       <c r="E50" s="50" t="inlineStr">
         <is>
-          <t>-75</t>
+          <t>-223</t>
         </is>
       </c>
       <c r="F50" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G50" s="50" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="H50" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I50" s="50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" s="50" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="K50" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="50" t="n">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B51" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C51" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D51" s="50" t="n">
@@ -3477,7 +3479,7 @@
       </c>
       <c r="E51" s="50" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-75</t>
         </is>
       </c>
       <c r="F51" s="50" t="inlineStr">
@@ -3486,35 +3488,35 @@
         </is>
       </c>
       <c r="G51" s="50" t="n">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="H51" s="50" t="n">
         <v>300200000</v>
       </c>
       <c r="I51" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J51" s="50" t="n">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="K51" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="50" t="n">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B52" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C52" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D52" s="50" t="n">
@@ -3522,7 +3524,7 @@
       </c>
       <c r="E52" s="50" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F52" s="50" t="inlineStr">
@@ -3531,7 +3533,7 @@
         </is>
       </c>
       <c r="G52" s="50" t="n">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="H52" s="50" t="n">
         <v>300200000</v>
@@ -3542,24 +3544,24 @@
         </is>
       </c>
       <c r="J52" s="50" t="n">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="K52" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="50" t="n">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B53" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C53" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D53" s="50" t="n">
@@ -3567,46 +3569,44 @@
       </c>
       <c r="E53" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F53" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G53" s="50" t="n">
-        <v>300200101</v>
-      </c>
-      <c r="H53" s="50" t="inlineStr">
-        <is>
-          <t>300200001|300200002|300200003|300200004|</t>
-        </is>
+        <v>300200004</v>
+      </c>
+      <c r="H53" s="50" t="n">
+        <v>300200000</v>
       </c>
       <c r="I53" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J53" s="50" t="n">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="K53" s="50" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="50" t="n">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B54" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D54" s="50" t="n">
@@ -3619,37 +3619,41 @@
       </c>
       <c r="F54" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G54" s="50" t="n">
-        <v>300200102</v>
-      </c>
-      <c r="H54" s="50" t="n">
         <v>300200101</v>
       </c>
-      <c r="I54" s="50" t="n">
-        <v>100</v>
+      <c r="H54" s="50" t="inlineStr">
+        <is>
+          <t>300200001|300200002|300200003|300200004|</t>
+        </is>
+      </c>
+      <c r="I54" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="J54" s="50" t="n">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="K54" s="50" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="50" t="n">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="B55" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C55" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D55" s="50" t="n">
@@ -3657,44 +3661,42 @@
       </c>
       <c r="E55" s="50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F55" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G55" s="50" t="n">
-        <v>300200201</v>
-      </c>
-      <c r="H55" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300200000,</t>
-        </is>
+        <v>300200102</v>
+      </c>
+      <c r="H55" s="50" t="n">
+        <v>300200101</v>
       </c>
       <c r="I55" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J55" s="50" t="n">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="K55" s="50" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="50" t="n">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="B56" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C56" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D56" s="50" t="n">
@@ -3702,7 +3704,7 @@
       </c>
       <c r="E56" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F56" s="50" t="inlineStr">
@@ -3711,37 +3713,35 @@
         </is>
       </c>
       <c r="G56" s="50" t="n">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="H56" s="50" t="inlineStr">
         <is>
-          <t>300200000,</t>
-        </is>
-      </c>
-      <c r="I56" s="50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>100200001,300200000,</t>
+        </is>
+      </c>
+      <c r="I56" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J56" s="50" t="n">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="K56" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="50" t="n">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="B57" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C57" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D57" s="50" t="n">
@@ -3749,44 +3749,46 @@
       </c>
       <c r="E57" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F57" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G57" s="50" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="H57" s="50" t="n">
-        <v>300200000</v>
+        <v>300200301</v>
+      </c>
+      <c r="H57" s="50" t="inlineStr">
+        <is>
+          <t>300200000,</t>
+        </is>
       </c>
       <c r="I57" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" s="50" t="n">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="K57" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51">
       <c r="A58" s="50" t="n">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="B58" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C58" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D58" s="50" t="n">
@@ -3794,42 +3796,44 @@
       </c>
       <c r="E58" s="50" t="inlineStr">
         <is>
-          <t>-1025</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F58" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G58" s="50" t="n">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="H58" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="I58" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J58" s="50" t="n">
         <v>300300000</v>
       </c>
-      <c r="I58" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J58" s="50" t="n">
-        <v>300300001</v>
-      </c>
       <c r="K58" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51">
       <c r="A59" s="50" t="n">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="B59" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C59" s="50" t="inlineStr">
         <is>
-          <t>ui_research_54</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D59" s="50" t="n">
@@ -3837,7 +3841,7 @@
       </c>
       <c r="E59" s="50" t="inlineStr">
         <is>
-          <t>-875</t>
+          <t>-1025</t>
         </is>
       </c>
       <c r="F59" s="50" t="inlineStr">
@@ -3846,7 +3850,7 @@
         </is>
       </c>
       <c r="G59" s="50" t="n">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="H59" s="50" t="n">
         <v>300300000</v>
@@ -3855,17 +3859,17 @@
         <v>100</v>
       </c>
       <c r="J59" s="50" t="n">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="K59" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51">
       <c r="A60" s="50" t="n">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="B60" s="50" t="n">
         <v>3</v>
@@ -3880,7 +3884,7 @@
       </c>
       <c r="E60" s="50" t="inlineStr">
         <is>
-          <t>-725</t>
+          <t>-875</t>
         </is>
       </c>
       <c r="F60" s="50" t="inlineStr">
@@ -3889,7 +3893,7 @@
         </is>
       </c>
       <c r="G60" s="50" t="n">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="H60" s="50" t="n">
         <v>300300000</v>
@@ -3898,24 +3902,24 @@
         <v>100</v>
       </c>
       <c r="J60" s="50" t="n">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="K60" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51">
       <c r="A61" s="50" t="n">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="B61" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C61" s="50" t="inlineStr">
         <is>
-          <t>ui_research_53</t>
+          <t>ui_research_54</t>
         </is>
       </c>
       <c r="D61" s="50" t="n">
@@ -3923,7 +3927,7 @@
       </c>
       <c r="E61" s="50" t="inlineStr">
         <is>
-          <t>-575</t>
+          <t>-725</t>
         </is>
       </c>
       <c r="F61" s="50" t="inlineStr">
@@ -3932,7 +3936,7 @@
         </is>
       </c>
       <c r="G61" s="50" t="n">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="H61" s="50" t="n">
         <v>300300000</v>
@@ -3941,24 +3945,24 @@
         <v>100</v>
       </c>
       <c r="J61" s="50" t="n">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="K61" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51">
       <c r="A62" s="50" t="n">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="B62" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_53</t>
         </is>
       </c>
       <c r="D62" s="50" t="n">
@@ -3966,44 +3970,42 @@
       </c>
       <c r="E62" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-575</t>
         </is>
       </c>
       <c r="F62" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G62" s="50" t="n">
-        <v>300300101</v>
-      </c>
-      <c r="H62" s="50" t="inlineStr">
-        <is>
-          <t>300300001|300300002|300300003|300300004|</t>
-        </is>
+        <v>300300004</v>
+      </c>
+      <c r="H62" s="50" t="n">
+        <v>300300000</v>
       </c>
       <c r="I62" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J62" s="50" t="n">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="K62" s="50" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51">
       <c r="A63" s="50" t="n">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="B63" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C63" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D63" s="50" t="n">
@@ -4016,37 +4018,39 @@
       </c>
       <c r="F63" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G63" s="50" t="n">
-        <v>300300102</v>
-      </c>
-      <c r="H63" s="50" t="n">
         <v>300300101</v>
+      </c>
+      <c r="H63" s="50" t="inlineStr">
+        <is>
+          <t>300300001|300300002|300300003|300300004|</t>
+        </is>
       </c>
       <c r="I63" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J63" s="50" t="n">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="K63" s="50" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51">
       <c r="A64" s="50" t="n">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="B64" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C64" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D64" s="50" t="n">
@@ -4054,44 +4058,42 @@
       </c>
       <c r="E64" s="50" t="inlineStr">
         <is>
-          <t>-650</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F64" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G64" s="50" t="n">
-        <v>300300201</v>
-      </c>
-      <c r="H64" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300300000,</t>
-        </is>
+        <v>300300102</v>
+      </c>
+      <c r="H64" s="50" t="n">
+        <v>300300101</v>
       </c>
       <c r="I64" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J64" s="50" t="n">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="K64" s="50" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="50" t="n">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="B65" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C65" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D65" s="50" t="n">
@@ -4099,7 +4101,7 @@
       </c>
       <c r="E65" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-650</t>
         </is>
       </c>
       <c r="F65" s="50" t="inlineStr">
@@ -4108,37 +4110,35 @@
         </is>
       </c>
       <c r="G65" s="50" t="n">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="H65" s="50" t="inlineStr">
         <is>
-          <t>300300000,</t>
-        </is>
-      </c>
-      <c r="I65" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+          <t>100200001,300300000,</t>
+        </is>
+      </c>
+      <c r="I65" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="J65" s="50" t="n">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="K65" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="50" t="n">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="B66" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C66" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D66" s="50" t="n">
@@ -4146,42 +4146,46 @@
       </c>
       <c r="E66" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F66" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G66" s="50" t="n">
-        <v>300400000</v>
-      </c>
-      <c r="H66" s="50" t="n">
-        <v>300600000</v>
-      </c>
-      <c r="I66" s="50" t="n">
-        <v>100</v>
+        <v>300300301</v>
+      </c>
+      <c r="H66" s="50" t="inlineStr">
+        <is>
+          <t>300300000,</t>
+        </is>
+      </c>
+      <c r="I66" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="J66" s="50" t="n">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="K66" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51">
       <c r="A67" s="50" t="n">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="B67" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D67" s="50" t="n">
@@ -4189,42 +4193,42 @@
       </c>
       <c r="E67" s="50" t="inlineStr">
         <is>
-          <t>-2700</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F67" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G67" s="50" t="n">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="H67" s="50" t="n">
-        <v>300400000</v>
+        <v>300600000</v>
       </c>
       <c r="I67" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J67" s="50" t="n">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="K67" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51">
       <c r="A68" s="50" t="n">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="B68" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C68" s="50" t="inlineStr">
         <is>
-          <t>ui_research_45</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D68" s="50" t="n">
@@ -4232,7 +4236,7 @@
       </c>
       <c r="E68" s="50" t="inlineStr">
         <is>
-          <t>-2550</t>
+          <t>-2700</t>
         </is>
       </c>
       <c r="F68" s="50" t="inlineStr">
@@ -4241,7 +4245,7 @@
         </is>
       </c>
       <c r="G68" s="50" t="n">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="H68" s="50" t="n">
         <v>300400000</v>
@@ -4250,24 +4254,24 @@
         <v>100</v>
       </c>
       <c r="J68" s="50" t="n">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="K68" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51">
       <c r="A69" s="50" t="n">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="B69" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="50" t="inlineStr">
         <is>
-          <t>ui_research_52</t>
+          <t>ui_research_45</t>
         </is>
       </c>
       <c r="D69" s="50" t="n">
@@ -4275,7 +4279,7 @@
       </c>
       <c r="E69" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2550</t>
         </is>
       </c>
       <c r="F69" s="50" t="inlineStr">
@@ -4284,7 +4288,7 @@
         </is>
       </c>
       <c r="G69" s="50" t="n">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="H69" s="50" t="n">
         <v>300400000</v>
@@ -4293,24 +4297,24 @@
         <v>100</v>
       </c>
       <c r="J69" s="50" t="n">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="K69" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51">
       <c r="A70" s="50" t="n">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="B70" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="50" t="inlineStr">
         <is>
-          <t>ui_research_49</t>
+          <t>ui_research_52</t>
         </is>
       </c>
       <c r="D70" s="50" t="n">
@@ -4318,7 +4322,7 @@
       </c>
       <c r="E70" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F70" s="50" t="inlineStr">
@@ -4327,7 +4331,7 @@
         </is>
       </c>
       <c r="G70" s="50" t="n">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="H70" s="50" t="n">
         <v>300400000</v>
@@ -4336,24 +4340,24 @@
         <v>100</v>
       </c>
       <c r="J70" s="50" t="n">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="K70" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51">
       <c r="A71" s="50" t="n">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="B71" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C71" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_49</t>
         </is>
       </c>
       <c r="D71" s="50" t="n">
@@ -4361,7 +4365,7 @@
       </c>
       <c r="E71" s="50" t="inlineStr">
         <is>
-          <t>-2100</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F71" s="50" t="inlineStr">
@@ -4370,7 +4374,7 @@
         </is>
       </c>
       <c r="G71" s="50" t="n">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="H71" s="50" t="n">
         <v>300400000</v>
@@ -4379,24 +4383,24 @@
         <v>100</v>
       </c>
       <c r="J71" s="50" t="n">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="K71" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51">
       <c r="A72" s="50" t="n">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="B72" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C72" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D72" s="50" t="n">
@@ -4404,44 +4408,42 @@
       </c>
       <c r="E72" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2100</t>
         </is>
       </c>
       <c r="F72" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G72" s="50" t="n">
-        <v>300400101</v>
-      </c>
-      <c r="H72" s="50" t="inlineStr">
-        <is>
-          <t>300400001|300400002|300400003|300400004|300400005|</t>
-        </is>
+        <v>300400005</v>
+      </c>
+      <c r="H72" s="50" t="n">
+        <v>300400000</v>
       </c>
       <c r="I72" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J72" s="50" t="n">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="K72" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51">
       <c r="A73" s="50" t="n">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="B73" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C73" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D73" s="50" t="n">
@@ -4454,37 +4456,39 @@
       </c>
       <c r="F73" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G73" s="50" t="n">
-        <v>300400102</v>
-      </c>
-      <c r="H73" s="50" t="n">
         <v>300400101</v>
+      </c>
+      <c r="H73" s="50" t="inlineStr">
+        <is>
+          <t>300400001|300400002|300400003|300400004|300400005|</t>
+        </is>
       </c>
       <c r="I73" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J73" s="50" t="n">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="K73" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51">
       <c r="A74" s="50" t="n">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="B74" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C74" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D74" s="50" t="n">
@@ -4492,44 +4496,42 @@
       </c>
       <c r="E74" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F74" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G74" s="50" t="n">
-        <v>300400201</v>
-      </c>
-      <c r="H74" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300400000,</t>
-        </is>
+        <v>300400102</v>
+      </c>
+      <c r="H74" s="50" t="n">
+        <v>300400101</v>
       </c>
       <c r="I74" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J74" s="50" t="n">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="K74" s="50" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="50" t="n">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="B75" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C75" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D75" s="50" t="n">
@@ -4537,7 +4539,7 @@
       </c>
       <c r="E75" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F75" s="50" t="inlineStr">
@@ -4546,35 +4548,35 @@
         </is>
       </c>
       <c r="G75" s="50" t="n">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="H75" s="50" t="inlineStr">
         <is>
-          <t>300400000,</t>
+          <t>100200001,300400000,</t>
         </is>
       </c>
       <c r="I75" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J75" s="50" t="n">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="K75" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="50" t="n">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="B76" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C76" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D76" s="50" t="n">
@@ -4582,42 +4584,44 @@
       </c>
       <c r="E76" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F76" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G76" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="H76" s="50" t="n">
-        <v>300700000</v>
+        <v>300400301</v>
+      </c>
+      <c r="H76" s="50" t="inlineStr">
+        <is>
+          <t>300400000,</t>
+        </is>
       </c>
       <c r="I76" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J76" s="50" t="n">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="K76" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="50" t="n">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="B77" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C77" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D77" s="50" t="n">
@@ -4625,42 +4629,42 @@
       </c>
       <c r="E77" s="50" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F77" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G77" s="50" t="n">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="H77" s="50" t="n">
-        <v>300500000</v>
+        <v>300700000</v>
       </c>
       <c r="I77" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J77" s="50" t="n">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="K77" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51">
       <c r="A78" s="50" t="n">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="B78" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C78" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D78" s="50" t="n">
@@ -4668,7 +4672,7 @@
       </c>
       <c r="E78" s="50" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F78" s="50" t="inlineStr">
@@ -4677,7 +4681,7 @@
         </is>
       </c>
       <c r="G78" s="50" t="n">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="H78" s="50" t="n">
         <v>300500000</v>
@@ -4686,24 +4690,24 @@
         <v>100</v>
       </c>
       <c r="J78" s="50" t="n">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="K78" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51">
       <c r="A79" s="50" t="n">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="B79" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C79" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D79" s="50" t="n">
@@ -4711,7 +4715,7 @@
       </c>
       <c r="E79" s="50" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F79" s="50" t="inlineStr">
@@ -4720,7 +4724,7 @@
         </is>
       </c>
       <c r="G79" s="50" t="n">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="H79" s="50" t="n">
         <v>300500000</v>
@@ -4729,24 +4733,24 @@
         <v>100</v>
       </c>
       <c r="J79" s="50" t="n">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="K79" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51">
       <c r="A80" s="50" t="n">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="B80" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C80" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D80" s="50" t="n">
@@ -4754,7 +4758,7 @@
       </c>
       <c r="E80" s="50" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F80" s="50" t="inlineStr">
@@ -4763,7 +4767,7 @@
         </is>
       </c>
       <c r="G80" s="50" t="n">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="H80" s="50" t="n">
         <v>300500000</v>
@@ -4772,24 +4776,24 @@
         <v>100</v>
       </c>
       <c r="J80" s="50" t="n">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="K80" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51">
       <c r="A81" s="50" t="n">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="B81" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C81" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D81" s="50" t="n">
@@ -4797,44 +4801,42 @@
       </c>
       <c r="E81" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="F81" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G81" s="50" t="n">
-        <v>300500101</v>
-      </c>
-      <c r="H81" s="50" t="inlineStr">
-        <is>
-          <t>300500001|300500002|300500003|300500004|</t>
-        </is>
+        <v>300500004</v>
+      </c>
+      <c r="H81" s="50" t="n">
+        <v>300500000</v>
       </c>
       <c r="I81" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J81" s="50" t="n">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="K81" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51">
       <c r="A82" s="50" t="n">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="B82" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C82" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D82" s="50" t="n">
@@ -4847,37 +4849,39 @@
       </c>
       <c r="F82" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G82" s="50" t="n">
-        <v>300500102</v>
-      </c>
-      <c r="H82" s="50" t="n">
         <v>300500101</v>
+      </c>
+      <c r="H82" s="50" t="inlineStr">
+        <is>
+          <t>300500001|300500002|300500003|300500004|</t>
+        </is>
       </c>
       <c r="I82" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J82" s="50" t="n">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="K82" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51">
       <c r="A83" s="50" t="n">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="B83" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C83" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D83" s="50" t="n">
@@ -4885,44 +4889,42 @@
       </c>
       <c r="E83" s="50" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F83" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G83" s="50" t="n">
-        <v>300500201</v>
-      </c>
-      <c r="H83" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300500000,</t>
-        </is>
+        <v>300500102</v>
+      </c>
+      <c r="H83" s="50" t="n">
+        <v>300500101</v>
       </c>
       <c r="I83" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J83" s="50" t="n">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="K83" s="50" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="50" t="n">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="B84" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C84" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D84" s="50" t="n">
@@ -4930,7 +4932,7 @@
       </c>
       <c r="E84" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="F84" s="50" t="inlineStr">
@@ -4939,35 +4941,35 @@
         </is>
       </c>
       <c r="G84" s="50" t="n">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="H84" s="50" t="inlineStr">
         <is>
-          <t>300500000,</t>
+          <t>100200001,300500000,</t>
         </is>
       </c>
       <c r="I84" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J84" s="50" t="n">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="K84" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="50" t="n">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="B85" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C85" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D85" s="50" t="n">
@@ -4975,42 +4977,44 @@
       </c>
       <c r="E85" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F85" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G85" s="50" t="n">
-        <v>300600000</v>
-      </c>
-      <c r="H85" s="50" t="n">
-        <v>300300000</v>
+        <v>300500301</v>
+      </c>
+      <c r="H85" s="50" t="inlineStr">
+        <is>
+          <t>300500000,</t>
+        </is>
       </c>
       <c r="I85" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J85" s="50" t="n">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="K85" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="50" t="n">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="B86" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C86" s="50" t="inlineStr">
         <is>
-          <t>ui_research_44</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D86" s="50" t="n">
@@ -5018,42 +5022,42 @@
       </c>
       <c r="E86" s="50" t="inlineStr">
         <is>
-          <t>-1900</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F86" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G86" s="50" t="n">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="H86" s="50" t="n">
-        <v>300600000</v>
+        <v>300300000</v>
       </c>
       <c r="I86" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J86" s="50" t="n">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="K86" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="50" t="n">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="B87" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C87" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_44</t>
         </is>
       </c>
       <c r="D87" s="50" t="n">
@@ -5061,7 +5065,7 @@
       </c>
       <c r="E87" s="50" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-1900</t>
         </is>
       </c>
       <c r="F87" s="50" t="inlineStr">
@@ -5070,7 +5074,7 @@
         </is>
       </c>
       <c r="G87" s="50" t="n">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="H87" s="50" t="n">
         <v>300600000</v>
@@ -5079,24 +5083,24 @@
         <v>100</v>
       </c>
       <c r="J87" s="50" t="n">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="K87" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="50" t="n">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="B88" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C88" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D88" s="50" t="n">
@@ -5104,7 +5108,7 @@
       </c>
       <c r="E88" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="F88" s="50" t="inlineStr">
@@ -5113,7 +5117,7 @@
         </is>
       </c>
       <c r="G88" s="50" t="n">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="H88" s="50" t="n">
         <v>300600000</v>
@@ -5122,24 +5126,24 @@
         <v>100</v>
       </c>
       <c r="J88" s="50" t="n">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="K88" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="50" t="n">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="B89" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C89" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D89" s="50" t="n">
@@ -5147,7 +5151,7 @@
       </c>
       <c r="E89" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F89" s="50" t="inlineStr">
@@ -5156,7 +5160,7 @@
         </is>
       </c>
       <c r="G89" s="50" t="n">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="H89" s="50" t="n">
         <v>300600000</v>
@@ -5165,24 +5169,24 @@
         <v>100</v>
       </c>
       <c r="J89" s="50" t="n">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="K89" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="50" t="n">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="B90" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C90" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D90" s="50" t="n">
@@ -5190,7 +5194,7 @@
       </c>
       <c r="E90" s="50" t="inlineStr">
         <is>
-          <t>-1300</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F90" s="50" t="inlineStr">
@@ -5199,7 +5203,7 @@
         </is>
       </c>
       <c r="G90" s="50" t="n">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="H90" s="50" t="n">
         <v>300600000</v>
@@ -5208,24 +5212,24 @@
         <v>100</v>
       </c>
       <c r="J90" s="50" t="n">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="K90" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="50" t="n">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="B91" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D91" s="50" t="n">
@@ -5233,44 +5237,42 @@
       </c>
       <c r="E91" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1300</t>
         </is>
       </c>
       <c r="F91" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G91" s="50" t="n">
-        <v>300600101</v>
-      </c>
-      <c r="H91" s="50" t="inlineStr">
-        <is>
-          <t>300600001|300600002|300600003|300600004|</t>
-        </is>
+        <v>300600005</v>
+      </c>
+      <c r="H91" s="50" t="n">
+        <v>300600000</v>
       </c>
       <c r="I91" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J91" s="50" t="n">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="K91" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="50" t="n">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="B92" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D92" s="50" t="n">
@@ -5283,37 +5285,39 @@
       </c>
       <c r="F92" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G92" s="50" t="n">
-        <v>300600102</v>
-      </c>
-      <c r="H92" s="50" t="n">
         <v>300600101</v>
+      </c>
+      <c r="H92" s="50" t="inlineStr">
+        <is>
+          <t>300600001|300600002|300600003|300600004|</t>
+        </is>
       </c>
       <c r="I92" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J92" s="50" t="n">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="K92" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="50" t="n">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="B93" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D93" s="50" t="n">
@@ -5321,44 +5325,42 @@
       </c>
       <c r="E93" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F93" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G93" s="50" t="n">
-        <v>300600201</v>
-      </c>
-      <c r="H93" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300600000,</t>
-        </is>
+        <v>300600102</v>
+      </c>
+      <c r="H93" s="50" t="n">
+        <v>300600101</v>
       </c>
       <c r="I93" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J93" s="50" t="n">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="K93" s="50" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="50" t="n">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="B94" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C94" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D94" s="50" t="n">
@@ -5366,7 +5368,7 @@
       </c>
       <c r="E94" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F94" s="50" t="inlineStr">
@@ -5375,35 +5377,35 @@
         </is>
       </c>
       <c r="G94" s="50" t="n">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="H94" s="50" t="inlineStr">
         <is>
-          <t>300600000,</t>
+          <t>100200001,300600000,</t>
         </is>
       </c>
       <c r="I94" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J94" s="50" t="n">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="K94" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="50" t="n">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="B95" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C95" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D95" s="50" t="n">
@@ -5411,42 +5413,44 @@
       </c>
       <c r="E95" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F95" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G95" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="H95" s="50" t="n">
-        <v>300100000</v>
+        <v>300600301</v>
+      </c>
+      <c r="H95" s="50" t="inlineStr">
+        <is>
+          <t>300600000,</t>
+        </is>
       </c>
       <c r="I95" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J95" s="50" t="n">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="K95" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="50" t="n">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="B96" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C96" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_38</t>
         </is>
       </c>
       <c r="D96" s="50" t="n">
@@ -5454,42 +5458,42 @@
       </c>
       <c r="E96" s="50" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F96" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G96" s="50" t="n">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="H96" s="50" t="n">
-        <v>300700000</v>
+        <v>300100000</v>
       </c>
       <c r="I96" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J96" s="50" t="n">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="K96" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="50" t="n">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="B97" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C97" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D97" s="50" t="n">
@@ -5497,7 +5501,7 @@
       </c>
       <c r="E97" s="50" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="F97" s="50" t="inlineStr">
@@ -5506,7 +5510,7 @@
         </is>
       </c>
       <c r="G97" s="50" t="n">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="H97" s="50" t="n">
         <v>300700000</v>
@@ -5515,24 +5519,24 @@
         <v>100</v>
       </c>
       <c r="J97" s="50" t="n">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="K97" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="50" t="n">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="B98" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C98" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D98" s="50" t="n">
@@ -5540,7 +5544,7 @@
       </c>
       <c r="E98" s="50" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F98" s="50" t="inlineStr">
@@ -5549,7 +5553,7 @@
         </is>
       </c>
       <c r="G98" s="50" t="n">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="H98" s="50" t="n">
         <v>300700000</v>
@@ -5558,24 +5562,24 @@
         <v>100</v>
       </c>
       <c r="J98" s="50" t="n">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="K98" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="50" t="n">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="B99" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C99" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D99" s="50" t="n">
@@ -5583,7 +5587,7 @@
       </c>
       <c r="E99" s="50" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="F99" s="50" t="inlineStr">
@@ -5592,7 +5596,7 @@
         </is>
       </c>
       <c r="G99" s="50" t="n">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="H99" s="50" t="n">
         <v>300700000</v>
@@ -5601,24 +5605,24 @@
         <v>100</v>
       </c>
       <c r="J99" s="50" t="n">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="K99" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="50" t="n">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="B100" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C100" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D100" s="50" t="n">
@@ -5626,44 +5630,42 @@
       </c>
       <c r="E100" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F100" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G100" s="50" t="n">
-        <v>300700101</v>
-      </c>
-      <c r="H100" s="50" t="inlineStr">
-        <is>
-          <t>300700001|300700002|300700003|300700004|</t>
-        </is>
+        <v>300700004</v>
+      </c>
+      <c r="H100" s="50" t="n">
+        <v>300700000</v>
       </c>
       <c r="I100" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J100" s="50" t="n">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="K100" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="50" t="n">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="B101" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C101" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D101" s="50" t="n">
@@ -5676,37 +5678,39 @@
       </c>
       <c r="F101" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G101" s="50" t="n">
-        <v>300700102</v>
-      </c>
-      <c r="H101" s="50" t="n">
         <v>300700101</v>
+      </c>
+      <c r="H101" s="50" t="inlineStr">
+        <is>
+          <t>300700001|300700002|300700003|300700004|</t>
+        </is>
       </c>
       <c r="I101" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J101" s="50" t="n">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="K101" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="50" t="n">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="B102" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C102" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D102" s="50" t="n">
@@ -5714,44 +5718,42 @@
       </c>
       <c r="E102" s="50" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F102" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G102" s="50" t="n">
-        <v>300700201</v>
-      </c>
-      <c r="H102" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300700000,</t>
-        </is>
+        <v>300700102</v>
+      </c>
+      <c r="H102" s="50" t="n">
+        <v>300700101</v>
       </c>
       <c r="I102" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J102" s="50" t="n">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="K102" s="50" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="50" t="n">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="B103" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C103" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_38</t>
         </is>
       </c>
       <c r="D103" s="50" t="n">
@@ -5759,7 +5761,7 @@
       </c>
       <c r="E103" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="F103" s="50" t="inlineStr">
@@ -5768,62 +5770,107 @@
         </is>
       </c>
       <c r="G103" s="50" t="n">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="H103" s="50" t="inlineStr">
         <is>
-          <t>300700000,</t>
+          <t>100200001,300700000,</t>
         </is>
       </c>
       <c r="I103" s="50" t="n">
         <v>100</v>
       </c>
       <c r="J103" s="50" t="n">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="K103" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B104" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_58</t>
+        </is>
+      </c>
+      <c r="D104" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="50" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="F104" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="G104" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="H104" s="50" t="inlineStr">
+        <is>
+          <t>300700000,</t>
+        </is>
+      </c>
+      <c r="I104" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="J104" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="K104" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="B104" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C104" s="50" t="inlineStr">
+      <c r="B105" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="50" t="inlineStr">
         <is>
           <t>ui_research_18</t>
         </is>
       </c>
-      <c r="D104" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="50" t="inlineStr">
+      <c r="D105" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F104" s="50" t="inlineStr">
+      <c r="F105" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G104" s="50" t="n">
+      <c r="G105" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="I104" s="50" t="inlineStr">
+      <c r="I105" s="50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J104" s="50" t="n">
+      <c r="J105" s="50" t="n">
         <v>100500001</v>
       </c>
-      <c r="K104" s="50" t="inlineStr">
+      <c r="K105" s="50" t="inlineStr">
         <is>
           <t>开启成就系统</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
   <si>
     <t>id</t>
   </si>
@@ -342,6 +342,9 @@
     <t>ui_research_6</t>
   </si>
   <si>
+    <t>200000001</t>
+  </si>
+  <si>
     <t>100,200,300,400,</t>
   </si>
   <si>
@@ -358,6 +361,9 @@
   </si>
   <si>
     <t>ui_research_61</t>
+  </si>
+  <si>
+    <t>200400001</t>
   </si>
   <si>
     <t>100,500,1000,5000,10000</t>
@@ -3133,7 +3139,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F33" s="50" t="s">
         <v>65</v>
@@ -3141,14 +3147,17 @@
       <c r="G33" s="50">
         <v>200100001</v>
       </c>
+      <c r="H33" s="51" t="s">
+        <v>109</v>
+      </c>
       <c r="I33" s="50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J33" s="50">
         <v>200100001</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34">
@@ -3159,7 +3168,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D34" s="50">
         <v>6</v>
@@ -3174,13 +3183,13 @@
         <v>200200001</v>
       </c>
       <c r="I34" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J34" s="50">
         <v>200200001</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35">
@@ -3191,7 +3200,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D35" s="50">
         <v>5</v>
@@ -3199,20 +3208,23 @@
       <c r="E35" s="50">
         <v>0</v>
       </c>
-      <c r="F35" s="50">
-        <v>-200</v>
+      <c r="F35" s="50" t="s">
+        <v>66</v>
       </c>
       <c r="G35" s="50">
         <v>200300001</v>
       </c>
+      <c r="H35" s="51" t="s">
+        <v>116</v>
+      </c>
       <c r="I35" s="50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J35" s="50">
         <v>200300001</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36">
@@ -3223,13 +3235,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D36" s="50">
         <v>3</v>
       </c>
-      <c r="E36" s="50">
-        <v>200</v>
+      <c r="E36" s="50" t="s">
+        <v>65</v>
       </c>
       <c r="F36" s="50">
         <v>-200</v>
@@ -3238,13 +3250,13 @@
         <v>200400001</v>
       </c>
       <c r="I36" s="50" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J36" s="50">
         <v>200400001</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37">
@@ -3255,7 +3267,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D37" s="50">
         <v>5</v>
@@ -3270,13 +3282,13 @@
         <v>200500001</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J37" s="50">
         <v>200500001</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
@@ -3303,13 +3315,13 @@
       </c>
       <c r="H38" s="50"/>
       <c r="I38" s="50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J38" s="50">
         <v>200600001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39">
@@ -3320,7 +3332,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D39" s="50">
         <v>4</v>
@@ -3329,22 +3341,22 @@
         <v>66</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G39" s="50">
         <v>200700001</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J39" s="50">
         <v>200700001</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
@@ -3355,7 +3367,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D40" s="50">
         <v>1</v>
@@ -3373,13 +3385,13 @@
         <v>300200000</v>
       </c>
       <c r="I40" s="50" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="J40" s="50">
         <v>300100000</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41">
@@ -3390,13 +3402,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D41" s="50">
         <v>1</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>78</v>
@@ -3414,7 +3426,7 @@
         <v>300100001</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42">
@@ -3425,13 +3437,13 @@
         <v>3</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D42" s="50">
         <v>1</v>
       </c>
       <c r="E42" s="50" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F42" s="50" t="s">
         <v>78</v>
@@ -3449,7 +3461,7 @@
         <v>300100002</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43">
@@ -3460,13 +3472,13 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F43" s="50" t="s">
         <v>78</v>
@@ -3484,7 +3496,7 @@
         <v>300100003</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44">
@@ -3495,13 +3507,13 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F44" s="50" t="s">
         <v>78</v>
@@ -3519,7 +3531,7 @@
         <v>300100004</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45">
@@ -3530,7 +3542,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
@@ -3545,7 +3557,7 @@
         <v>300100101</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I45" s="50">
         <v>100</v>
@@ -3554,7 +3566,7 @@
         <v>300100101</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46">
@@ -3565,7 +3577,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
@@ -3589,7 +3601,7 @@
         <v>300100102</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47">
@@ -3600,13 +3612,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>94</v>
@@ -3615,7 +3627,7 @@
         <v>300100201</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I47" s="50">
         <v>100</v>
@@ -3624,7 +3636,7 @@
         <v>300100201</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48">
@@ -3635,7 +3647,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
@@ -3650,7 +3662,7 @@
         <v>300100301</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I48" s="50" t="s">
         <v>92</v>
@@ -3659,7 +3671,7 @@
         <v>300100301</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49">
@@ -3670,7 +3682,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
@@ -3685,13 +3697,13 @@
         <v>300200000</v>
       </c>
       <c r="I49" s="50" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="J49" s="50">
         <v>300200000</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50">
@@ -3702,16 +3714,16 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F50" s="50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G50" s="50">
         <v>300200001</v>
@@ -3726,7 +3738,7 @@
         <v>300200001</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51">
@@ -3737,13 +3749,13 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F51" s="50" t="s">
         <v>78</v>
@@ -3755,13 +3767,13 @@
         <v>300200000</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J51" s="50">
         <v>300200002</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52">
@@ -3772,13 +3784,13 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F52" s="50" t="s">
         <v>78</v>
@@ -3796,7 +3808,7 @@
         <v>300200003</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53">
@@ -3807,13 +3819,13 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F53" s="50" t="s">
         <v>78</v>
@@ -3831,7 +3843,7 @@
         <v>300200004</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54">
@@ -3842,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
@@ -3857,16 +3869,16 @@
         <v>300200101</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I54" s="50" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J54" s="50">
         <v>300200101</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55">
@@ -3877,7 +3889,7 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
@@ -3901,7 +3913,7 @@
         <v>300200102</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56">
@@ -3912,7 +3924,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
@@ -3927,7 +3939,7 @@
         <v>300200201</v>
       </c>
       <c r="H56" s="50" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I56" s="50">
         <v>100</v>
@@ -3936,7 +3948,7 @@
         <v>300200201</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57">
@@ -3947,7 +3959,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
@@ -3962,7 +3974,7 @@
         <v>300200301</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I57" s="50" t="s">
         <v>67</v>
@@ -3971,7 +3983,7 @@
         <v>300200301</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -3982,7 +3994,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
@@ -4006,7 +4018,7 @@
         <v>300300000</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4017,13 +4029,13 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F59" s="50" t="s">
         <v>78</v>
@@ -4041,7 +4053,7 @@
         <v>300300001</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4052,13 +4064,13 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>78</v>
@@ -4076,7 +4088,7 @@
         <v>300300002</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4087,13 +4099,13 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F61" s="50" t="s">
         <v>78</v>
@@ -4111,7 +4123,7 @@
         <v>300300003</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4122,13 +4134,13 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>78</v>
@@ -4146,7 +4158,7 @@
         <v>300300004</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4157,7 +4169,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
@@ -4172,7 +4184,7 @@
         <v>300300101</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I63" s="50">
         <v>100</v>
@@ -4181,7 +4193,7 @@
         <v>300300101</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4192,7 +4204,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
@@ -4216,7 +4228,7 @@
         <v>300300102</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65">
@@ -4227,13 +4239,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>94</v>
@@ -4242,7 +4254,7 @@
         <v>300300201</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I65" s="50">
         <v>100</v>
@@ -4251,7 +4263,7 @@
         <v>300300201</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66">
@@ -4262,7 +4274,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
@@ -4277,7 +4289,7 @@
         <v>300300301</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I66" s="50" t="s">
         <v>33</v>
@@ -4286,7 +4298,7 @@
         <v>300300301</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4297,13 +4309,13 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F67" s="50" t="s">
         <v>65</v>
@@ -4321,7 +4333,7 @@
         <v>300400000</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4332,13 +4344,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>78</v>
@@ -4356,7 +4368,7 @@
         <v>300400001</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4367,13 +4379,13 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F69" s="50" t="s">
         <v>78</v>
@@ -4391,7 +4403,7 @@
         <v>300400002</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4402,13 +4414,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>78</v>
@@ -4426,7 +4438,7 @@
         <v>300400003</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4437,13 +4449,13 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>78</v>
@@ -4461,7 +4473,7 @@
         <v>300400004</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4472,13 +4484,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>78</v>
@@ -4496,7 +4508,7 @@
         <v>300400005</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4507,13 +4519,13 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>85</v>
@@ -4522,7 +4534,7 @@
         <v>300400101</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I73" s="50">
         <v>100</v>
@@ -4531,7 +4543,7 @@
         <v>300400101</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4542,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>88</v>
@@ -4566,7 +4578,7 @@
         <v>300400102</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75">
@@ -4577,13 +4589,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>94</v>
@@ -4592,7 +4604,7 @@
         <v>300400201</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I75" s="50">
         <v>100</v>
@@ -4601,7 +4613,7 @@
         <v>300400201</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76">
@@ -4612,13 +4624,13 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>94</v>
@@ -4627,7 +4639,7 @@
         <v>300400301</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
@@ -4636,7 +4648,7 @@
         <v>300400301</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="77">
@@ -4647,13 +4659,13 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F77" s="50" t="s">
         <v>65</v>
@@ -4671,7 +4683,7 @@
         <v>300500000</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4682,13 +4694,13 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>78</v>
@@ -4706,7 +4718,7 @@
         <v>300500001</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4717,13 +4729,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>78</v>
@@ -4741,7 +4753,7 @@
         <v>300500002</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4752,13 +4764,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>78</v>
@@ -4776,7 +4788,7 @@
         <v>300500003</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4787,13 +4799,13 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>78</v>
@@ -4811,7 +4823,7 @@
         <v>300500004</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4822,13 +4834,13 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>85</v>
@@ -4837,7 +4849,7 @@
         <v>300500101</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I82" s="50">
         <v>100</v>
@@ -4846,7 +4858,7 @@
         <v>300500101</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4857,13 +4869,13 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>88</v>
@@ -4881,7 +4893,7 @@
         <v>300500102</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84">
@@ -4892,13 +4904,13 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>94</v>
@@ -4907,7 +4919,7 @@
         <v>300500201</v>
       </c>
       <c r="H84" s="50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I84" s="50">
         <v>100</v>
@@ -4916,7 +4928,7 @@
         <v>300500201</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85">
@@ -4927,13 +4939,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>94</v>
@@ -4942,7 +4954,7 @@
         <v>300500301</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
@@ -4951,7 +4963,7 @@
         <v>300500301</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86">
@@ -4962,13 +4974,13 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>65</v>
@@ -4986,7 +4998,7 @@
         <v>300600000</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="87">
@@ -4997,13 +5009,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F87" s="50" t="s">
         <v>78</v>
@@ -5021,7 +5033,7 @@
         <v>300600001</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88">
@@ -5032,13 +5044,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>78</v>
@@ -5056,7 +5068,7 @@
         <v>300600002</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="89">
@@ -5067,13 +5079,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>78</v>
@@ -5091,7 +5103,7 @@
         <v>300600003</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="90">
@@ -5102,13 +5114,13 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>78</v>
@@ -5126,7 +5138,7 @@
         <v>300600004</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91">
@@ -5137,13 +5149,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>78</v>
@@ -5161,7 +5173,7 @@
         <v>300600005</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="92">
@@ -5172,13 +5184,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>85</v>
@@ -5187,7 +5199,7 @@
         <v>300600101</v>
       </c>
       <c r="H92" s="50" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I92" s="50">
         <v>100</v>
@@ -5196,7 +5208,7 @@
         <v>300600101</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93">
@@ -5207,13 +5219,13 @@
         <v>3</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F93" s="50" t="s">
         <v>88</v>
@@ -5231,7 +5243,7 @@
         <v>300600102</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94">
@@ -5242,13 +5254,13 @@
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D94" s="50">
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F94" s="50" t="s">
         <v>94</v>
@@ -5257,7 +5269,7 @@
         <v>300600201</v>
       </c>
       <c r="H94" s="50" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I94" s="50">
         <v>100</v>
@@ -5266,7 +5278,7 @@
         <v>300600201</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="95">
@@ -5277,13 +5289,13 @@
         <v>3</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D95" s="50">
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F95" s="50" t="s">
         <v>94</v>
@@ -5292,7 +5304,7 @@
         <v>300600301</v>
       </c>
       <c r="H95" s="50" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I95" s="50">
         <v>100</v>
@@ -5301,7 +5313,7 @@
         <v>300600301</v>
       </c>
       <c r="K95" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="96">
@@ -5312,13 +5324,13 @@
         <v>3</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D96" s="50">
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F96" s="50" t="s">
         <v>65</v>
@@ -5336,7 +5348,7 @@
         <v>300700000</v>
       </c>
       <c r="K96" s="50" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97">
@@ -5347,13 +5359,13 @@
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D97" s="50">
         <v>1</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F97" s="50" t="s">
         <v>78</v>
@@ -5371,7 +5383,7 @@
         <v>300700001</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="98">
@@ -5382,13 +5394,13 @@
         <v>3</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D98" s="50">
         <v>1</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F98" s="50" t="s">
         <v>78</v>
@@ -5406,7 +5418,7 @@
         <v>300700002</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="99">
@@ -5417,13 +5429,13 @@
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D99" s="50">
         <v>1</v>
       </c>
       <c r="E99" s="50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F99" s="50" t="s">
         <v>78</v>
@@ -5441,7 +5453,7 @@
         <v>300700003</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="100">
@@ -5452,13 +5464,13 @@
         <v>3</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D100" s="50">
         <v>1</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F100" s="50" t="s">
         <v>78</v>
@@ -5476,7 +5488,7 @@
         <v>300700004</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101">
@@ -5487,13 +5499,13 @@
         <v>3</v>
       </c>
       <c r="C101" s="50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D101" s="50">
         <v>1</v>
       </c>
       <c r="E101" s="50" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F101" s="50" t="s">
         <v>85</v>
@@ -5502,7 +5514,7 @@
         <v>300700101</v>
       </c>
       <c r="H101" s="50" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I101" s="50">
         <v>100</v>
@@ -5511,7 +5523,7 @@
         <v>300700101</v>
       </c>
       <c r="K101" s="50" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="102">
@@ -5522,13 +5534,13 @@
         <v>3</v>
       </c>
       <c r="C102" s="50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D102" s="50">
         <v>1</v>
       </c>
       <c r="E102" s="50" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F102" s="50" t="s">
         <v>88</v>
@@ -5546,7 +5558,7 @@
         <v>300700102</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="103">
@@ -5557,13 +5569,13 @@
         <v>3</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D103" s="50">
         <v>1</v>
       </c>
       <c r="E103" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F103" s="50" t="s">
         <v>94</v>
@@ -5572,7 +5584,7 @@
         <v>300700201</v>
       </c>
       <c r="H103" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I103" s="50">
         <v>100</v>
@@ -5581,7 +5593,7 @@
         <v>300700201</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104">
@@ -5592,13 +5604,13 @@
         <v>3</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D104" s="50">
         <v>1</v>
       </c>
       <c r="E104" s="50" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F104" s="50" t="s">
         <v>94</v>
@@ -5607,7 +5619,7 @@
         <v>300700301</v>
       </c>
       <c r="H104" s="50" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I104" s="50">
         <v>100</v>
@@ -5616,7 +5628,7 @@
         <v>300700301</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105">
@@ -5627,7 +5639,7 @@
         <v>1</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D105" s="50">
         <v>1</v>
@@ -5648,7 +5660,7 @@
         <v>100500001</v>
       </c>
       <c r="K105" s="50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="284">
   <si>
     <t>id</t>
   </si>
@@ -261,12 +261,27 @@
     <t>ui_research_11</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>100,400,800,1600,3200,6400,12800,25600,51200,</t>
   </si>
   <si>
     <t>剑与魔法：征服难度+1</t>
   </si>
   <si>
+    <t>ui_research_30</t>
+  </si>
+  <si>
+    <t>100310112</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>剑与魔法-加快进攻节奏</t>
+  </si>
+  <si>
     <t>ui_research_57</t>
   </si>
   <si>
@@ -397,6 +412,18 @@
   </si>
   <si>
     <t>突进冷却</t>
+  </si>
+  <si>
+    <t>魔王自动拾取魔晶</t>
+  </si>
+  <si>
+    <t>200800001</t>
+  </si>
+  <si>
+    <t>2000*1</t>
+  </si>
+  <si>
+    <t>每次拾取魔晶+1</t>
   </si>
   <si>
     <t>ui_research_36</t>
@@ -1991,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1" style="51"/>
@@ -2534,37 +2561,37 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51">
+      <c r="A16" s="50">
         <v>100200004</v>
       </c>
-      <c r="B16" s="51">
-        <v>1</v>
-      </c>
-      <c r="C16" s="51" t="s">
+      <c r="B16" s="50">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="51">
-        <v>1</v>
-      </c>
-      <c r="E16" s="51" t="s">
+      <c r="D16" s="50">
+        <v>1</v>
+      </c>
+      <c r="E16" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="51" t="s">
+      <c r="F16" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="51">
+      <c r="G16" s="50">
         <v>100200004</v>
       </c>
-      <c r="H16" s="51" t="s">
+      <c r="H16" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="51" t="s">
+      <c r="I16" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="51">
+      <c r="J16" s="50">
         <v>100200004</v>
       </c>
-      <c r="K16" s="51" t="s">
+      <c r="K16" s="50" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2783,7 +2810,7 @@
         <v>100310112</v>
       </c>
       <c r="B23" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23" s="50" t="s">
         <v>81</v>
@@ -2792,36 +2819,36 @@
         <v>9</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G23" s="50">
         <v>100310112</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J23" s="50">
         <v>100310112</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50">
-        <v>100400000</v>
+        <v>100310130</v>
       </c>
       <c r="B24" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D24" s="50">
         <v>1</v>
@@ -2830,670 +2857,681 @@
         <v>65</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G24" s="50">
-        <v>100400000</v>
+        <v>100310130</v>
       </c>
       <c r="H24" s="50" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="I24" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J24" s="50">
-        <v>100400000</v>
+        <v>100310130</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B25" s="50">
         <v>1</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D25" s="50">
         <v>1</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G25" s="50">
-        <v>100400001</v>
-      </c>
-      <c r="H25" s="50">
         <v>100400000</v>
       </c>
+      <c r="H25" s="50" t="s">
+        <v>29</v>
+      </c>
       <c r="I25" s="50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J25" s="50">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="50">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B26" s="50">
         <v>1</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D26" s="50">
         <v>1</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G26" s="50">
-        <v>100401000</v>
-      </c>
-      <c r="H26" s="50" t="s">
-        <v>91</v>
+        <v>100400001</v>
+      </c>
+      <c r="H26" s="50">
+        <v>100400000</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J26" s="50">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="50">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B27" s="50">
         <v>1</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D27" s="50">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G27" s="50">
-        <v>100401001</v>
-      </c>
-      <c r="H27" s="50">
         <v>100401000</v>
       </c>
+      <c r="H27" s="50" t="s">
+        <v>96</v>
+      </c>
       <c r="I27" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J27" s="50">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="50">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B28" s="50">
         <v>1</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D28" s="50">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G28" s="50">
-        <v>100402000</v>
-      </c>
-      <c r="H28" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="I28" s="50">
-        <v>1000</v>
+        <v>100401001</v>
+      </c>
+      <c r="H28" s="50">
+        <v>100401000</v>
+      </c>
+      <c r="I28" s="50" t="s">
+        <v>100</v>
       </c>
       <c r="J28" s="50">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="50">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B29" s="50">
         <v>1</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D29" s="50">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G29" s="50">
-        <v>100402001</v>
-      </c>
-      <c r="H29" s="50">
         <v>100402000</v>
       </c>
-      <c r="I29" s="50" t="s">
-        <v>100</v>
+      <c r="H29" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="I29" s="50">
+        <v>1000</v>
       </c>
       <c r="J29" s="50">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="50">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B30" s="50">
         <v>1</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D30" s="50">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="G30" s="50">
-        <v>100403000</v>
-      </c>
-      <c r="H30" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="I30" s="50">
-        <v>10000</v>
+        <v>100402001</v>
+      </c>
+      <c r="H30" s="50">
+        <v>100402000</v>
+      </c>
+      <c r="I30" s="50" t="s">
+        <v>105</v>
       </c>
       <c r="J30" s="50">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="50">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B31" s="50">
         <v>1</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D31" s="50">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="F31" s="50" t="s">
         <v>55</v>
       </c>
       <c r="G31" s="50">
-        <v>100403001</v>
-      </c>
-      <c r="H31" s="50">
         <v>100403000</v>
       </c>
-      <c r="I31" s="50" t="s">
-        <v>104</v>
+      <c r="H31" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" s="50">
+        <v>10000</v>
       </c>
       <c r="J31" s="50">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B32" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D32" s="50">
-        <v>30</v>
-      </c>
-      <c r="E32" s="50">
-        <v>-200</v>
-      </c>
-      <c r="F32" s="50">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="50" t="s">
+        <v>55</v>
       </c>
       <c r="G32" s="50">
-        <v>200000001</v>
+        <v>100403001</v>
+      </c>
+      <c r="H32" s="50">
+        <v>100403000</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J32" s="50">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="50">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="B33" s="50">
         <v>2</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="D33" s="50">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="F33" s="50" t="s">
         <v>65</v>
       </c>
+      <c r="F33" s="50">
+        <v>0</v>
+      </c>
       <c r="G33" s="50">
-        <v>200100001</v>
-      </c>
-      <c r="H33" s="51" t="s">
-        <v>109</v>
+        <v>200000001</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J33" s="50">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="50">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="B34" s="50">
         <v>2</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D34" s="50">
-        <v>6</v>
-      </c>
-      <c r="E34" s="50">
-        <v>-200</v>
-      </c>
-      <c r="F34" s="50">
-        <v>-200</v>
+        <v>4</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="50" t="s">
+        <v>65</v>
       </c>
       <c r="G34" s="50">
-        <v>200200001</v>
+        <v>200100001</v>
+      </c>
+      <c r="H34" s="50" t="s">
+        <v>114</v>
       </c>
       <c r="I34" s="50" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J34" s="50">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="50">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B35" s="50">
         <v>2</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D35" s="50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="50">
-        <v>0</v>
-      </c>
-      <c r="F35" s="50" t="s">
-        <v>66</v>
+        <v>-200</v>
+      </c>
+      <c r="F35" s="50">
+        <v>-200</v>
       </c>
       <c r="G35" s="50">
-        <v>200300001</v>
-      </c>
-      <c r="H35" s="51" t="s">
-        <v>116</v>
+        <v>200200001</v>
+      </c>
+      <c r="H35" s="50" t="s">
+        <v>114</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J35" s="50">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="50">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B36" s="50">
         <v>2</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D36" s="50">
-        <v>3</v>
-      </c>
-      <c r="E36" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="F36" s="50">
-        <v>-200</v>
+        <v>5</v>
+      </c>
+      <c r="E36" s="50">
+        <v>0</v>
+      </c>
+      <c r="F36" s="50" t="s">
+        <v>66</v>
       </c>
       <c r="G36" s="50">
-        <v>200400001</v>
+        <v>200300001</v>
+      </c>
+      <c r="H36" s="50" t="s">
+        <v>121</v>
       </c>
       <c r="I36" s="50" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J36" s="50">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="50">
-        <v>200500001</v>
+        <v>200400001</v>
       </c>
       <c r="B37" s="50">
         <v>2</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D37" s="50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E37" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F37" s="50" t="s">
-        <v>78</v>
+      <c r="F37" s="50">
+        <v>-200</v>
       </c>
       <c r="G37" s="50">
-        <v>200500001</v>
+        <v>200400001</v>
+      </c>
+      <c r="H37" s="50" t="s">
+        <v>114</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="J37" s="50">
-        <v>200500001</v>
+        <v>200400001</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="50">
-        <v>200600001</v>
+        <v>200500001</v>
       </c>
       <c r="B38" s="50">
         <v>2</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D38" s="50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G38" s="50">
-        <v>200600001</v>
-      </c>
-      <c r="H38" s="50"/>
+        <v>200500001</v>
+      </c>
+      <c r="H38" s="50" t="s">
+        <v>114</v>
+      </c>
       <c r="I38" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J38" s="50">
-        <v>200600001</v>
+        <v>200500001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="B39" s="50">
         <v>2</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D39" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G39" s="50">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J39" s="50">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="50">
-        <v>300100000</v>
+        <v>200700001</v>
       </c>
       <c r="B40" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D40" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F40" s="50" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G40" s="50">
-        <v>300100000</v>
-      </c>
-      <c r="H40" s="50">
-        <v>300200000</v>
+        <v>200700001</v>
+      </c>
+      <c r="H40" s="50" t="s">
+        <v>130</v>
       </c>
       <c r="I40" s="50" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="J40" s="50">
-        <v>300100000</v>
+        <v>200700001</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="50">
-        <v>300100001</v>
+        <v>200800001</v>
       </c>
       <c r="B41" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D41" s="50">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>78</v>
       </c>
       <c r="G41" s="50">
-        <v>300100001</v>
-      </c>
-      <c r="H41" s="50">
-        <v>300100000</v>
-      </c>
-      <c r="I41" s="50">
-        <v>100</v>
+        <v>200800001</v>
+      </c>
+      <c r="H41" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="I41" s="50" t="s">
+        <v>105</v>
       </c>
       <c r="J41" s="50">
-        <v>300100001</v>
+        <v>200800001</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="50">
-        <v>300100002</v>
+        <v>200900001</v>
       </c>
       <c r="B42" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D42" s="50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E42" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="F42" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G42" s="50">
+        <v>200900001</v>
+      </c>
+      <c r="H42" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="F42" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="G42" s="50">
-        <v>300100002</v>
-      </c>
-      <c r="H42" s="50">
-        <v>300100000</v>
-      </c>
-      <c r="I42" s="50">
-        <v>100</v>
+      <c r="I42" s="50" t="s">
+        <v>135</v>
       </c>
       <c r="J42" s="50">
-        <v>300100002</v>
+        <v>200900001</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="50">
-        <v>300100003</v>
+        <v>300100000</v>
       </c>
       <c r="B43" s="50">
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G43" s="50">
-        <v>300100003</v>
+        <v>300100000</v>
       </c>
       <c r="H43" s="50">
+        <v>300200000</v>
+      </c>
+      <c r="I43" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="J43" s="50">
         <v>300100000</v>
-      </c>
-      <c r="I43" s="50">
-        <v>100</v>
-      </c>
-      <c r="J43" s="50">
-        <v>300100003</v>
       </c>
       <c r="K43" s="50" t="s">
         <v>138</v>
@@ -3501,7 +3539,7 @@
     </row>
     <row r="44">
       <c r="A44" s="50">
-        <v>300100004</v>
+        <v>300100001</v>
       </c>
       <c r="B44" s="50">
         <v>3</v>
@@ -3519,7 +3557,7 @@
         <v>78</v>
       </c>
       <c r="G44" s="50">
-        <v>300100004</v>
+        <v>300100001</v>
       </c>
       <c r="H44" s="50">
         <v>300100000</v>
@@ -3528,7 +3566,7 @@
         <v>100</v>
       </c>
       <c r="J44" s="50">
-        <v>300100004</v>
+        <v>300100001</v>
       </c>
       <c r="K44" s="50" t="s">
         <v>141</v>
@@ -3536,7 +3574,7 @@
     </row>
     <row r="45">
       <c r="A45" s="50">
-        <v>300100101</v>
+        <v>300100002</v>
       </c>
       <c r="B45" s="50">
         <v>3</v>
@@ -3548,22 +3586,22 @@
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G45" s="50">
-        <v>300100101</v>
-      </c>
-      <c r="H45" s="50" t="s">
-        <v>143</v>
+        <v>300100002</v>
+      </c>
+      <c r="H45" s="50">
+        <v>300100000</v>
       </c>
       <c r="I45" s="50">
         <v>100</v>
       </c>
       <c r="J45" s="50">
-        <v>300100101</v>
+        <v>300100002</v>
       </c>
       <c r="K45" s="50" t="s">
         <v>144</v>
@@ -3571,7 +3609,7 @@
     </row>
     <row r="46">
       <c r="A46" s="50">
-        <v>300100102</v>
+        <v>300100003</v>
       </c>
       <c r="B46" s="50">
         <v>3</v>
@@ -3583,237 +3621,237 @@
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="F46" s="50" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G46" s="50">
-        <v>300100102</v>
+        <v>300100003</v>
       </c>
       <c r="H46" s="50">
-        <v>300100101</v>
+        <v>300100000</v>
       </c>
       <c r="I46" s="50">
         <v>100</v>
       </c>
       <c r="J46" s="50">
-        <v>300100102</v>
+        <v>300100003</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="50">
-        <v>300100201</v>
+        <v>300100004</v>
       </c>
       <c r="B47" s="50">
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F47" s="50" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G47" s="50">
-        <v>300100201</v>
-      </c>
-      <c r="H47" s="50" t="s">
-        <v>148</v>
+        <v>300100004</v>
+      </c>
+      <c r="H47" s="50">
+        <v>300100000</v>
       </c>
       <c r="I47" s="50">
         <v>100</v>
       </c>
       <c r="J47" s="50">
-        <v>300100201</v>
+        <v>300100004</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="50">
-        <v>300100301</v>
+        <v>300100101</v>
       </c>
       <c r="B48" s="50">
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G48" s="50">
-        <v>300100301</v>
+        <v>300100101</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="I48" s="50" t="s">
-        <v>92</v>
+        <v>152</v>
+      </c>
+      <c r="I48" s="50">
+        <v>100</v>
       </c>
       <c r="J48" s="50">
-        <v>300100301</v>
+        <v>300100101</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="50">
-        <v>300200000</v>
+        <v>300100102</v>
       </c>
       <c r="B49" s="50">
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="G49" s="50">
-        <v>300200000</v>
-      </c>
-      <c r="I49" s="50" t="s">
-        <v>64</v>
+        <v>300100102</v>
+      </c>
+      <c r="H49" s="50">
+        <v>300100101</v>
+      </c>
+      <c r="I49" s="50">
+        <v>100</v>
       </c>
       <c r="J49" s="50">
-        <v>300200000</v>
+        <v>300100102</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="50">
-        <v>300200001</v>
+        <v>300100201</v>
       </c>
       <c r="B50" s="50">
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F50" s="50" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="G50" s="50">
-        <v>300200001</v>
-      </c>
-      <c r="H50" s="50">
-        <v>300200000</v>
-      </c>
-      <c r="I50" s="50" t="s">
-        <v>67</v>
+        <v>300100201</v>
+      </c>
+      <c r="H50" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="I50" s="50">
+        <v>100</v>
       </c>
       <c r="J50" s="50">
-        <v>300200001</v>
+        <v>300100201</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="50">
-        <v>300200002</v>
+        <v>300100301</v>
       </c>
       <c r="B51" s="50">
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G51" s="50">
-        <v>300200002</v>
-      </c>
-      <c r="H51" s="50">
-        <v>300200000</v>
+        <v>300100301</v>
+      </c>
+      <c r="H51" s="50" t="s">
+        <v>160</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="J51" s="50">
-        <v>300200002</v>
+        <v>300100301</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="50">
-        <v>300200003</v>
+        <v>300200000</v>
       </c>
       <c r="B52" s="50">
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="F52" s="50" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G52" s="50">
-        <v>300200003</v>
-      </c>
-      <c r="H52" s="50">
         <v>300200000</v>
       </c>
       <c r="I52" s="50" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J52" s="50">
-        <v>300200003</v>
+        <v>300200000</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="50">
-        <v>300200004</v>
+        <v>300200001</v>
       </c>
       <c r="B53" s="50">
         <v>3</v>
@@ -3825,30 +3863,30 @@
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="G53" s="50">
-        <v>300200004</v>
+        <v>300200001</v>
       </c>
       <c r="H53" s="50">
         <v>300200000</v>
       </c>
       <c r="I53" s="50" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="J53" s="50">
-        <v>300200004</v>
+        <v>300200001</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="50">
-        <v>300200101</v>
+        <v>300200002</v>
       </c>
       <c r="B54" s="50">
         <v>3</v>
@@ -3860,30 +3898,30 @@
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>65</v>
+        <v>167</v>
       </c>
       <c r="F54" s="50" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G54" s="50">
-        <v>300200101</v>
-      </c>
-      <c r="H54" s="50" t="s">
-        <v>165</v>
+        <v>300200002</v>
+      </c>
+      <c r="H54" s="50">
+        <v>300200000</v>
       </c>
       <c r="I54" s="50" t="s">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c r="J54" s="50">
-        <v>300200101</v>
+        <v>300200002</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="50">
-        <v>300200102</v>
+        <v>300200003</v>
       </c>
       <c r="B55" s="50">
         <v>3</v>
@@ -3895,71 +3933,71 @@
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G55" s="50">
-        <v>300200102</v>
+        <v>300200003</v>
       </c>
       <c r="H55" s="50">
-        <v>300200101</v>
-      </c>
-      <c r="I55" s="50">
-        <v>100</v>
+        <v>300200000</v>
+      </c>
+      <c r="I55" s="50" t="s">
+        <v>33</v>
       </c>
       <c r="J55" s="50">
-        <v>300200102</v>
+        <v>300200003</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="50">
-        <v>300200201</v>
+        <v>300200004</v>
       </c>
       <c r="B56" s="50">
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="F56" s="50" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G56" s="50">
-        <v>300200201</v>
-      </c>
-      <c r="H56" s="50" t="s">
-        <v>168</v>
-      </c>
-      <c r="I56" s="50">
-        <v>100</v>
+        <v>300200004</v>
+      </c>
+      <c r="H56" s="50">
+        <v>300200000</v>
+      </c>
+      <c r="I56" s="50" t="s">
+        <v>33</v>
       </c>
       <c r="J56" s="50">
-        <v>300200201</v>
+        <v>300200004</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="50">
-        <v>300200301</v>
+        <v>300200101</v>
       </c>
       <c r="B57" s="50">
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
@@ -3968,185 +4006,185 @@
         <v>65</v>
       </c>
       <c r="F57" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G57" s="50">
+        <v>300200101</v>
+      </c>
+      <c r="H57" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="I57" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="G57" s="50">
-        <v>300200301</v>
-      </c>
-      <c r="H57" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="I57" s="50" t="s">
-        <v>67</v>
-      </c>
       <c r="J57" s="50">
-        <v>300200301</v>
+        <v>300200101</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A58" s="50">
-        <v>300300000</v>
+        <v>300200102</v>
       </c>
       <c r="B58" s="50">
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F58" s="50" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="G58" s="50">
-        <v>300300000</v>
+        <v>300200102</v>
       </c>
       <c r="H58" s="50">
-        <v>300200000</v>
-      </c>
-      <c r="I58" s="50" t="s">
-        <v>92</v>
+        <v>300200101</v>
+      </c>
+      <c r="I58" s="50">
+        <v>100</v>
       </c>
       <c r="J58" s="50">
-        <v>300300000</v>
+        <v>300200102</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A59" s="50">
-        <v>300300001</v>
+        <v>300200201</v>
       </c>
       <c r="B59" s="50">
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G59" s="50">
-        <v>300300001</v>
-      </c>
-      <c r="H59" s="50">
-        <v>300300000</v>
+        <v>300200201</v>
+      </c>
+      <c r="H59" s="50" t="s">
+        <v>177</v>
       </c>
       <c r="I59" s="50">
         <v>100</v>
       </c>
       <c r="J59" s="50">
-        <v>300300001</v>
+        <v>300200201</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A60" s="50">
-        <v>300300002</v>
+        <v>300200301</v>
       </c>
       <c r="B60" s="50">
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F60" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G60" s="50">
-        <v>300300002</v>
-      </c>
-      <c r="H60" s="50">
-        <v>300300000</v>
-      </c>
-      <c r="I60" s="50">
-        <v>100</v>
+        <v>300200301</v>
+      </c>
+      <c r="H60" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="I60" s="50" t="s">
+        <v>67</v>
       </c>
       <c r="J60" s="50">
-        <v>300300002</v>
+        <v>300200301</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A61" s="50">
-        <v>300300003</v>
+        <v>300300000</v>
       </c>
       <c r="B61" s="50">
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="F61" s="50" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G61" s="50">
-        <v>300300003</v>
+        <v>300300000</v>
       </c>
       <c r="H61" s="50">
+        <v>300200000</v>
+      </c>
+      <c r="I61" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="J61" s="50">
         <v>300300000</v>
       </c>
-      <c r="I61" s="50">
-        <v>100</v>
-      </c>
-      <c r="J61" s="50">
-        <v>300300003</v>
-      </c>
       <c r="K61" s="50" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A62" s="50">
-        <v>300300004</v>
+        <v>300300001</v>
       </c>
       <c r="B62" s="50">
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>78</v>
       </c>
       <c r="G62" s="50">
-        <v>300300004</v>
+        <v>300300001</v>
       </c>
       <c r="H62" s="50">
         <v>300300000</v>
@@ -4155,126 +4193,126 @@
         <v>100</v>
       </c>
       <c r="J62" s="50">
-        <v>300300004</v>
+        <v>300300001</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A63" s="50">
-        <v>300300101</v>
+        <v>300300002</v>
       </c>
       <c r="B63" s="50">
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G63" s="50">
-        <v>300300101</v>
-      </c>
-      <c r="H63" s="50" t="s">
-        <v>185</v>
+        <v>300300002</v>
+      </c>
+      <c r="H63" s="50">
+        <v>300300000</v>
       </c>
       <c r="I63" s="50">
         <v>100</v>
       </c>
       <c r="J63" s="50">
-        <v>300300101</v>
+        <v>300300002</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A64" s="50">
-        <v>300300102</v>
+        <v>300300003</v>
       </c>
       <c r="B64" s="50">
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G64" s="50">
-        <v>300300102</v>
+        <v>300300003</v>
       </c>
       <c r="H64" s="50">
-        <v>300300101</v>
+        <v>300300000</v>
       </c>
       <c r="I64" s="50">
         <v>100</v>
       </c>
       <c r="J64" s="50">
-        <v>300300102</v>
+        <v>300300003</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="50">
-        <v>300300201</v>
+        <v>300300004</v>
       </c>
       <c r="B65" s="50">
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G65" s="50">
-        <v>300300201</v>
-      </c>
-      <c r="H65" s="50" t="s">
-        <v>189</v>
+        <v>300300004</v>
+      </c>
+      <c r="H65" s="50">
+        <v>300300000</v>
       </c>
       <c r="I65" s="50">
         <v>100</v>
       </c>
       <c r="J65" s="50">
-        <v>300300201</v>
+        <v>300300004</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="50">
-        <v>300300301</v>
+        <v>300300101</v>
       </c>
       <c r="B66" s="50">
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
@@ -4283,185 +4321,185 @@
         <v>69</v>
       </c>
       <c r="F66" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G66" s="50">
-        <v>300300301</v>
+        <v>300300101</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>191</v>
-      </c>
-      <c r="I66" s="50" t="s">
-        <v>33</v>
+        <v>194</v>
+      </c>
+      <c r="I66" s="50">
+        <v>100</v>
       </c>
       <c r="J66" s="50">
-        <v>300300301</v>
+        <v>300300101</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A67" s="50">
-        <v>300400000</v>
+        <v>300300102</v>
       </c>
       <c r="B67" s="50">
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="G67" s="50">
-        <v>300400000</v>
+        <v>300300102</v>
       </c>
       <c r="H67" s="50">
-        <v>300600000</v>
+        <v>300300101</v>
       </c>
       <c r="I67" s="50">
         <v>100</v>
       </c>
       <c r="J67" s="50">
-        <v>300400000</v>
+        <v>300300102</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A68" s="50">
-        <v>300400001</v>
+        <v>300300201</v>
       </c>
       <c r="B68" s="50">
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F68" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G68" s="50">
-        <v>300400001</v>
-      </c>
-      <c r="H68" s="50">
-        <v>300400000</v>
+        <v>300300201</v>
+      </c>
+      <c r="H68" s="50" t="s">
+        <v>198</v>
       </c>
       <c r="I68" s="50">
         <v>100</v>
       </c>
       <c r="J68" s="50">
-        <v>300400001</v>
+        <v>300300201</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A69" s="50">
-        <v>300400002</v>
+        <v>300300301</v>
       </c>
       <c r="B69" s="50">
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G69" s="50">
-        <v>300400002</v>
-      </c>
-      <c r="H69" s="50">
-        <v>300400000</v>
-      </c>
-      <c r="I69" s="50">
-        <v>100</v>
+        <v>300300301</v>
+      </c>
+      <c r="H69" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="I69" s="50" t="s">
+        <v>33</v>
       </c>
       <c r="J69" s="50">
-        <v>300400002</v>
+        <v>300300301</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A70" s="50">
-        <v>300400003</v>
+        <v>300400000</v>
       </c>
       <c r="B70" s="50">
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F70" s="50" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G70" s="50">
-        <v>300400003</v>
+        <v>300400000</v>
       </c>
       <c r="H70" s="50">
-        <v>300400000</v>
+        <v>300600000</v>
       </c>
       <c r="I70" s="50">
         <v>100</v>
       </c>
       <c r="J70" s="50">
-        <v>300400003</v>
+        <v>300400000</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A71" s="50">
-        <v>300400004</v>
+        <v>300400001</v>
       </c>
       <c r="B71" s="50">
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>78</v>
       </c>
       <c r="G71" s="50">
-        <v>300400004</v>
+        <v>300400001</v>
       </c>
       <c r="H71" s="50">
         <v>300400000</v>
@@ -4470,33 +4508,33 @@
         <v>100</v>
       </c>
       <c r="J71" s="50">
-        <v>300400004</v>
+        <v>300400001</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A72" s="50">
-        <v>300400005</v>
+        <v>300400002</v>
       </c>
       <c r="B72" s="50">
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>78</v>
       </c>
       <c r="G72" s="50">
-        <v>300400005</v>
+        <v>300400002</v>
       </c>
       <c r="H72" s="50">
         <v>300400000</v>
@@ -4505,295 +4543,295 @@
         <v>100</v>
       </c>
       <c r="J72" s="50">
-        <v>300400005</v>
+        <v>300400002</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A73" s="50">
-        <v>300400101</v>
+        <v>300400003</v>
       </c>
       <c r="B73" s="50">
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G73" s="50">
-        <v>300400101</v>
-      </c>
-      <c r="H73" s="50" t="s">
-        <v>208</v>
+        <v>300400003</v>
+      </c>
+      <c r="H73" s="50">
+        <v>300400000</v>
       </c>
       <c r="I73" s="50">
         <v>100</v>
       </c>
       <c r="J73" s="50">
-        <v>300400101</v>
+        <v>300400003</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A74" s="50">
-        <v>300400102</v>
+        <v>300400004</v>
       </c>
       <c r="B74" s="50">
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>145</v>
+        <v>212</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="F74" s="50" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G74" s="50">
-        <v>300400102</v>
+        <v>300400004</v>
       </c>
       <c r="H74" s="50">
-        <v>300400101</v>
+        <v>300400000</v>
       </c>
       <c r="I74" s="50">
         <v>100</v>
       </c>
       <c r="J74" s="50">
-        <v>300400102</v>
+        <v>300400004</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="50">
-        <v>300400201</v>
+        <v>300400005</v>
       </c>
       <c r="B75" s="50">
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F75" s="50" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G75" s="50">
-        <v>300400201</v>
-      </c>
-      <c r="H75" s="50" t="s">
-        <v>211</v>
+        <v>300400005</v>
+      </c>
+      <c r="H75" s="50">
+        <v>300400000</v>
       </c>
       <c r="I75" s="50">
         <v>100</v>
       </c>
       <c r="J75" s="50">
-        <v>300400201</v>
+        <v>300400005</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="50">
-        <v>300400301</v>
+        <v>300400101</v>
       </c>
       <c r="B76" s="50">
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F76" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G76" s="50">
-        <v>300400301</v>
+        <v>300400101</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
       </c>
       <c r="J76" s="50">
-        <v>300400301</v>
+        <v>300400101</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="50">
-        <v>300500000</v>
+        <v>300400102</v>
       </c>
       <c r="B77" s="50">
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>215</v>
+        <v>154</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="G77" s="50">
-        <v>300500000</v>
+        <v>300400102</v>
       </c>
       <c r="H77" s="50">
-        <v>300700000</v>
+        <v>300400101</v>
       </c>
       <c r="I77" s="50">
         <v>100</v>
       </c>
       <c r="J77" s="50">
-        <v>300500000</v>
+        <v>300400102</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A78" s="50">
-        <v>300500001</v>
+        <v>300400201</v>
       </c>
       <c r="B78" s="50">
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G78" s="50">
-        <v>300500001</v>
-      </c>
-      <c r="H78" s="50">
-        <v>300500000</v>
+        <v>300400201</v>
+      </c>
+      <c r="H78" s="50" t="s">
+        <v>220</v>
       </c>
       <c r="I78" s="50">
         <v>100</v>
       </c>
       <c r="J78" s="50">
-        <v>300500001</v>
+        <v>300400201</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A79" s="50">
-        <v>300500002</v>
+        <v>300400301</v>
       </c>
       <c r="B79" s="50">
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="F79" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G79" s="50">
-        <v>300500002</v>
-      </c>
-      <c r="H79" s="50">
-        <v>300500000</v>
+        <v>300400301</v>
+      </c>
+      <c r="H79" s="50" t="s">
+        <v>222</v>
       </c>
       <c r="I79" s="50">
         <v>100</v>
       </c>
       <c r="J79" s="50">
-        <v>300500002</v>
+        <v>300400301</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A80" s="50">
-        <v>300500003</v>
+        <v>300500000</v>
       </c>
       <c r="B80" s="50">
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F80" s="50" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G80" s="50">
-        <v>300500003</v>
+        <v>300500000</v>
       </c>
       <c r="H80" s="50">
-        <v>300500000</v>
+        <v>300700000</v>
       </c>
       <c r="I80" s="50">
         <v>100</v>
       </c>
       <c r="J80" s="50">
-        <v>300500003</v>
+        <v>300500000</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A81" s="50">
-        <v>300500004</v>
+        <v>300500001</v>
       </c>
       <c r="B81" s="50">
         <v>3</v>
@@ -4805,13 +4843,13 @@
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>78</v>
       </c>
       <c r="G81" s="50">
-        <v>300500004</v>
+        <v>300500001</v>
       </c>
       <c r="H81" s="50">
         <v>300500000</v>
@@ -4820,15 +4858,15 @@
         <v>100</v>
       </c>
       <c r="J81" s="50">
-        <v>300500004</v>
+        <v>300500001</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A82" s="50">
-        <v>300500101</v>
+        <v>300500002</v>
       </c>
       <c r="B82" s="50">
         <v>3</v>
@@ -4840,30 +4878,30 @@
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="F82" s="50" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G82" s="50">
-        <v>300500101</v>
-      </c>
-      <c r="H82" s="50" t="s">
-        <v>226</v>
+        <v>300500002</v>
+      </c>
+      <c r="H82" s="50">
+        <v>300500000</v>
       </c>
       <c r="I82" s="50">
         <v>100</v>
       </c>
       <c r="J82" s="50">
-        <v>300500101</v>
+        <v>300500002</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A83" s="50">
-        <v>300500102</v>
+        <v>300500003</v>
       </c>
       <c r="B83" s="50">
         <v>3</v>
@@ -4875,141 +4913,141 @@
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="F83" s="50" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G83" s="50">
-        <v>300500102</v>
+        <v>300500003</v>
       </c>
       <c r="H83" s="50">
-        <v>300500101</v>
+        <v>300500000</v>
       </c>
       <c r="I83" s="50">
         <v>100</v>
       </c>
       <c r="J83" s="50">
-        <v>300500102</v>
+        <v>300500003</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="50">
-        <v>300500201</v>
+        <v>300500004</v>
       </c>
       <c r="B84" s="50">
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>215</v>
+        <v>148</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F84" s="50" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G84" s="50">
-        <v>300500201</v>
-      </c>
-      <c r="H84" s="50" t="s">
-        <v>230</v>
+        <v>300500004</v>
+      </c>
+      <c r="H84" s="50">
+        <v>300500000</v>
       </c>
       <c r="I84" s="50">
         <v>100</v>
       </c>
       <c r="J84" s="50">
-        <v>300500201</v>
+        <v>300500004</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="50">
-        <v>300500301</v>
+        <v>300500101</v>
       </c>
       <c r="B85" s="50">
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F85" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G85" s="50">
-        <v>300500301</v>
+        <v>300500101</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
       </c>
       <c r="J85" s="50">
-        <v>300500301</v>
+        <v>300500101</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="50">
-        <v>300600000</v>
+        <v>300500102</v>
       </c>
       <c r="B86" s="50">
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="G86" s="50">
-        <v>300600000</v>
+        <v>300500102</v>
       </c>
       <c r="H86" s="50">
-        <v>300300000</v>
+        <v>300500101</v>
       </c>
       <c r="I86" s="50">
         <v>100</v>
       </c>
       <c r="J86" s="50">
-        <v>300600000</v>
+        <v>300500102</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="50">
-        <v>300600001</v>
+        <v>300500201</v>
       </c>
       <c r="B87" s="50">
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
@@ -5018,115 +5056,115 @@
         <v>238</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G87" s="50">
-        <v>300600001</v>
-      </c>
-      <c r="H87" s="50">
-        <v>300600000</v>
+        <v>300500201</v>
+      </c>
+      <c r="H87" s="50" t="s">
+        <v>239</v>
       </c>
       <c r="I87" s="50">
         <v>100</v>
       </c>
       <c r="J87" s="50">
-        <v>300600001</v>
+        <v>300500201</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="50">
-        <v>300600002</v>
+        <v>300500301</v>
       </c>
       <c r="B88" s="50">
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="F88" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G88" s="50">
-        <v>300600002</v>
-      </c>
-      <c r="H88" s="50">
-        <v>300600000</v>
+        <v>300500301</v>
+      </c>
+      <c r="H88" s="50" t="s">
+        <v>241</v>
       </c>
       <c r="I88" s="50">
         <v>100</v>
       </c>
       <c r="J88" s="50">
-        <v>300600002</v>
+        <v>300500301</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="50">
-        <v>300600003</v>
+        <v>300600000</v>
       </c>
       <c r="B89" s="50">
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>133</v>
+        <v>243</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="F89" s="50" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G89" s="50">
-        <v>300600003</v>
+        <v>300600000</v>
       </c>
       <c r="H89" s="50">
-        <v>300600000</v>
+        <v>300300000</v>
       </c>
       <c r="I89" s="50">
         <v>100</v>
       </c>
       <c r="J89" s="50">
-        <v>300600003</v>
+        <v>300600000</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="50">
-        <v>300600004</v>
+        <v>300600001</v>
       </c>
       <c r="B90" s="50">
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>136</v>
+        <v>246</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>78</v>
       </c>
       <c r="G90" s="50">
-        <v>300600004</v>
+        <v>300600001</v>
       </c>
       <c r="H90" s="50">
         <v>300600000</v>
@@ -5135,15 +5173,15 @@
         <v>100</v>
       </c>
       <c r="J90" s="50">
-        <v>300600004</v>
+        <v>300600001</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="50">
-        <v>300600005</v>
+        <v>300600002</v>
       </c>
       <c r="B91" s="50">
         <v>3</v>
@@ -5155,13 +5193,13 @@
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>78</v>
       </c>
       <c r="G91" s="50">
-        <v>300600005</v>
+        <v>300600002</v>
       </c>
       <c r="H91" s="50">
         <v>300600000</v>
@@ -5170,15 +5208,15 @@
         <v>100</v>
       </c>
       <c r="J91" s="50">
-        <v>300600005</v>
+        <v>300600002</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="50">
-        <v>300600101</v>
+        <v>300600003</v>
       </c>
       <c r="B92" s="50">
         <v>3</v>
@@ -5190,30 +5228,30 @@
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="F92" s="50" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G92" s="50">
-        <v>300600101</v>
-      </c>
-      <c r="H92" s="50" t="s">
-        <v>247</v>
+        <v>300600003</v>
+      </c>
+      <c r="H92" s="50">
+        <v>300600000</v>
       </c>
       <c r="I92" s="50">
         <v>100</v>
       </c>
       <c r="J92" s="50">
-        <v>300600101</v>
+        <v>300600003</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="50">
-        <v>300600102</v>
+        <v>300600004</v>
       </c>
       <c r="B93" s="50">
         <v>3</v>
@@ -5225,240 +5263,240 @@
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="F93" s="50" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G93" s="50">
-        <v>300600102</v>
+        <v>300600004</v>
       </c>
       <c r="H93" s="50">
-        <v>300600101</v>
+        <v>300600000</v>
       </c>
       <c r="I93" s="50">
         <v>100</v>
       </c>
       <c r="J93" s="50">
-        <v>300600102</v>
+        <v>300600004</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="50">
-        <v>300600201</v>
+        <v>300600005</v>
       </c>
       <c r="B94" s="50">
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="D94" s="50">
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F94" s="50" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G94" s="50">
-        <v>300600201</v>
-      </c>
-      <c r="H94" s="50" t="s">
-        <v>250</v>
+        <v>300600005</v>
+      </c>
+      <c r="H94" s="50">
+        <v>300600000</v>
       </c>
       <c r="I94" s="50">
         <v>100</v>
       </c>
       <c r="J94" s="50">
-        <v>300600201</v>
+        <v>300600005</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="50">
-        <v>300600301</v>
+        <v>300600101</v>
       </c>
       <c r="B95" s="50">
         <v>3</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D95" s="50">
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="F95" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G95" s="50">
-        <v>300600301</v>
+        <v>300600101</v>
       </c>
       <c r="H95" s="50" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I95" s="50">
         <v>100</v>
       </c>
       <c r="J95" s="50">
-        <v>300600301</v>
+        <v>300600101</v>
       </c>
       <c r="K95" s="50" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="50">
-        <v>300700000</v>
+        <v>300600102</v>
       </c>
       <c r="B96" s="50">
         <v>3</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="D96" s="50">
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="G96" s="50">
-        <v>300700000</v>
+        <v>300600102</v>
       </c>
       <c r="H96" s="50">
-        <v>300100000</v>
+        <v>300600101</v>
       </c>
       <c r="I96" s="50">
         <v>100</v>
       </c>
       <c r="J96" s="50">
-        <v>300700000</v>
+        <v>300600102</v>
       </c>
       <c r="K96" s="50" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="50">
-        <v>300700001</v>
+        <v>300600201</v>
       </c>
       <c r="B97" s="50">
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>130</v>
+        <v>243</v>
       </c>
       <c r="D97" s="50">
         <v>1</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F97" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G97" s="50">
-        <v>300700001</v>
-      </c>
-      <c r="H97" s="50">
-        <v>300700000</v>
+        <v>300600201</v>
+      </c>
+      <c r="H97" s="50" t="s">
+        <v>259</v>
       </c>
       <c r="I97" s="50">
         <v>100</v>
       </c>
       <c r="J97" s="50">
-        <v>300700001</v>
+        <v>300600201</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="50">
-        <v>300700002</v>
+        <v>300600301</v>
       </c>
       <c r="B98" s="50">
         <v>3</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="D98" s="50">
         <v>1</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="F98" s="50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G98" s="50">
-        <v>300700002</v>
-      </c>
-      <c r="H98" s="50">
-        <v>300700000</v>
+        <v>300600301</v>
+      </c>
+      <c r="H98" s="50" t="s">
+        <v>261</v>
       </c>
       <c r="I98" s="50">
         <v>100</v>
       </c>
       <c r="J98" s="50">
-        <v>300700002</v>
+        <v>300600301</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="50">
-        <v>300700003</v>
+        <v>300700000</v>
       </c>
       <c r="B99" s="50">
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>136</v>
+        <v>263</v>
       </c>
       <c r="D99" s="50">
         <v>1</v>
       </c>
       <c r="E99" s="50" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F99" s="50" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G99" s="50">
-        <v>300700003</v>
+        <v>300700000</v>
       </c>
       <c r="H99" s="50">
-        <v>300700000</v>
+        <v>300100000</v>
       </c>
       <c r="I99" s="50">
         <v>100</v>
       </c>
       <c r="J99" s="50">
-        <v>300700003</v>
+        <v>300700000</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="50">
-        <v>300700004</v>
+        <v>300700001</v>
       </c>
       <c r="B100" s="50">
         <v>3</v>
@@ -5470,13 +5508,13 @@
         <v>1</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F100" s="50" t="s">
         <v>78</v>
       </c>
       <c r="G100" s="50">
-        <v>300700004</v>
+        <v>300700001</v>
       </c>
       <c r="H100" s="50">
         <v>300700000</v>
@@ -5485,15 +5523,15 @@
         <v>100</v>
       </c>
       <c r="J100" s="50">
-        <v>300700004</v>
+        <v>300700001</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="50">
-        <v>300700101</v>
+        <v>300700002</v>
       </c>
       <c r="B101" s="50">
         <v>3</v>
@@ -5505,30 +5543,30 @@
         <v>1</v>
       </c>
       <c r="E101" s="50" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="F101" s="50" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G101" s="50">
-        <v>300700101</v>
-      </c>
-      <c r="H101" s="50" t="s">
-        <v>265</v>
+        <v>300700002</v>
+      </c>
+      <c r="H101" s="50">
+        <v>300700000</v>
       </c>
       <c r="I101" s="50">
         <v>100</v>
       </c>
       <c r="J101" s="50">
-        <v>300700101</v>
+        <v>300700002</v>
       </c>
       <c r="K101" s="50" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="50">
-        <v>300700102</v>
+        <v>300700003</v>
       </c>
       <c r="B102" s="50">
         <v>3</v>
@@ -5540,127 +5578,232 @@
         <v>1</v>
       </c>
       <c r="E102" s="50" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="F102" s="50" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G102" s="50">
-        <v>300700102</v>
+        <v>300700003</v>
       </c>
       <c r="H102" s="50">
-        <v>300700101</v>
+        <v>300700000</v>
       </c>
       <c r="I102" s="50">
         <v>100</v>
       </c>
       <c r="J102" s="50">
-        <v>300700102</v>
+        <v>300700003</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="50">
-        <v>300700201</v>
+        <v>300700004</v>
       </c>
       <c r="B103" s="50">
         <v>3</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>254</v>
+        <v>148</v>
       </c>
       <c r="D103" s="50">
         <v>1</v>
       </c>
       <c r="E103" s="50" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F103" s="50" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G103" s="50">
-        <v>300700201</v>
-      </c>
-      <c r="H103" s="50" t="s">
-        <v>269</v>
+        <v>300700004</v>
+      </c>
+      <c r="H103" s="50">
+        <v>300700000</v>
       </c>
       <c r="I103" s="50">
         <v>100</v>
       </c>
       <c r="J103" s="50">
-        <v>300700201</v>
+        <v>300700004</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="50">
-        <v>300700301</v>
+        <v>300700101</v>
       </c>
       <c r="B104" s="50">
         <v>3</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D104" s="50">
         <v>1</v>
       </c>
       <c r="E104" s="50" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="F104" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G104" s="50">
-        <v>300700301</v>
+        <v>300700101</v>
       </c>
       <c r="H104" s="50" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I104" s="50">
         <v>100</v>
       </c>
       <c r="J104" s="50">
-        <v>300700301</v>
+        <v>300700101</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="50">
+        <v>300700102</v>
+      </c>
+      <c r="B105" s="50">
+        <v>3</v>
+      </c>
+      <c r="C105" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="D105" s="50">
+        <v>1</v>
+      </c>
+      <c r="E105" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="F105" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="G105" s="50">
+        <v>300700102</v>
+      </c>
+      <c r="H105" s="50">
+        <v>300700101</v>
+      </c>
+      <c r="I105" s="50">
+        <v>100</v>
+      </c>
+      <c r="J105" s="50">
+        <v>300700102</v>
+      </c>
+      <c r="K105" s="50" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="50">
+        <v>300700201</v>
+      </c>
+      <c r="B106" s="50">
+        <v>3</v>
+      </c>
+      <c r="C106" s="50" t="s">
+        <v>263</v>
+      </c>
+      <c r="D106" s="50">
+        <v>1</v>
+      </c>
+      <c r="E106" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="F106" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="G106" s="50">
+        <v>300700201</v>
+      </c>
+      <c r="H106" s="50" t="s">
+        <v>278</v>
+      </c>
+      <c r="I106" s="50">
+        <v>100</v>
+      </c>
+      <c r="J106" s="50">
+        <v>300700201</v>
+      </c>
+      <c r="K106" s="50" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="50">
+        <v>300700301</v>
+      </c>
+      <c r="B107" s="50">
+        <v>3</v>
+      </c>
+      <c r="C107" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="D107" s="50">
+        <v>1</v>
+      </c>
+      <c r="E107" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="F107" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="G107" s="50">
+        <v>300700301</v>
+      </c>
+      <c r="H107" s="50" t="s">
+        <v>280</v>
+      </c>
+      <c r="I107" s="50">
+        <v>100</v>
+      </c>
+      <c r="J107" s="50">
+        <v>300700301</v>
+      </c>
+      <c r="K107" s="50" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="50">
         <v>100500001</v>
       </c>
-      <c r="B105" s="50">
-        <v>1</v>
-      </c>
-      <c r="C105" s="50" t="s">
-        <v>273</v>
-      </c>
-      <c r="D105" s="50">
-        <v>1</v>
-      </c>
-      <c r="E105" s="50" t="s">
+      <c r="B108" s="50">
+        <v>1</v>
+      </c>
+      <c r="C108" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="D108" s="50">
+        <v>1</v>
+      </c>
+      <c r="E108" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F105" s="50" t="s">
+      <c r="F108" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G105" s="50">
+      <c r="G108" s="50">
         <v>100500001</v>
       </c>
-      <c r="I105" s="50" t="s">
+      <c r="I108" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="J105" s="50">
+      <c r="J108" s="50">
         <v>100500001</v>
       </c>
-      <c r="K105" s="50" t="s">
-        <v>274</v>
+      <c r="K108" s="50" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -276,9 +276,6 @@
     <t>100310112</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
     <t>剑与魔法-加快进攻节奏</t>
   </si>
   <si>
@@ -412,6 +409,9 @@
   </si>
   <si>
     <t>突进冷却</t>
+  </si>
+  <si>
+    <t>500*1</t>
   </si>
   <si>
     <t>魔王自动拾取魔晶</t>
@@ -2866,13 +2866,13 @@
         <v>86</v>
       </c>
       <c r="I24" s="50" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J24" s="50">
         <v>100310130</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25">
@@ -2883,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D25" s="50">
         <v>1</v>
@@ -2892,7 +2892,7 @@
         <v>65</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G25" s="50">
         <v>100400000</v>
@@ -2901,13 +2901,13 @@
         <v>29</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J25" s="50">
         <v>100400000</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26">
@@ -2918,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D26" s="50">
         <v>1</v>
@@ -2927,7 +2927,7 @@
         <v>78</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="50">
         <v>100400001</v>
@@ -2936,13 +2936,13 @@
         <v>100400000</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J26" s="50">
         <v>100400001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27">
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D27" s="50">
         <v>1</v>
@@ -2962,22 +2962,22 @@
         <v>65</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G27" s="50">
         <v>100401000</v>
       </c>
       <c r="H27" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27" s="50" t="s">
         <v>96</v>
-      </c>
-      <c r="I27" s="50" t="s">
-        <v>97</v>
       </c>
       <c r="J27" s="50">
         <v>100401000</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -2988,16 +2988,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" s="50">
         <v>50</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G28" s="50">
         <v>100401001</v>
@@ -3006,13 +3006,13 @@
         <v>100401000</v>
       </c>
       <c r="I28" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J28" s="50">
         <v>100401001</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
@@ -3032,13 +3032,13 @@
         <v>65</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G29" s="50">
         <v>100402000</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I29" s="50">
         <v>1000</v>
@@ -3047,7 +3047,7 @@
         <v>100402000</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30">
@@ -3058,16 +3058,16 @@
         <v>1</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D30" s="50">
         <v>50</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G30" s="50">
         <v>100402001</v>
@@ -3076,13 +3076,13 @@
         <v>100402000</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J30" s="50">
         <v>100402001</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31">
@@ -3093,7 +3093,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
@@ -3108,7 +3108,7 @@
         <v>100403000</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I31" s="50">
         <v>10000</v>
@@ -3117,7 +3117,7 @@
         <v>100403000</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32">
@@ -3128,13 +3128,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D32" s="50">
         <v>50</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>55</v>
@@ -3146,13 +3146,13 @@
         <v>100403000</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J32" s="50">
         <v>100403001</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33">
@@ -3178,13 +3178,13 @@
         <v>200000001</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J33" s="50">
         <v>200000001</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34">
@@ -3195,13 +3195,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D34" s="50">
         <v>4</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F34" s="50" t="s">
         <v>65</v>
@@ -3210,16 +3210,16 @@
         <v>200100001</v>
       </c>
       <c r="H34" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="I34" s="50" t="s">
         <v>114</v>
-      </c>
-      <c r="I34" s="50" t="s">
-        <v>115</v>
       </c>
       <c r="J34" s="50">
         <v>200100001</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35">
@@ -3230,7 +3230,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D35" s="50">
         <v>6</v>
@@ -3245,16 +3245,16 @@
         <v>200200001</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J35" s="50">
         <v>200200001</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36">
@@ -3265,7 +3265,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D36" s="50">
         <v>5</v>
@@ -3280,16 +3280,16 @@
         <v>200300001</v>
       </c>
       <c r="H36" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="I36" s="50" t="s">
         <v>121</v>
-      </c>
-      <c r="I36" s="50" t="s">
-        <v>122</v>
       </c>
       <c r="J36" s="50">
         <v>200300001</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
@@ -3300,7 +3300,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D37" s="50">
         <v>3</v>
@@ -3315,16 +3315,16 @@
         <v>200400001</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J37" s="50">
         <v>200400001</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38">
@@ -3335,7 +3335,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D38" s="50">
         <v>5</v>
@@ -3350,16 +3350,16 @@
         <v>200500001</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I38" s="50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J38" s="50">
         <v>200500001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39">
@@ -3370,13 +3370,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D39" s="50">
         <v>3</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F39" s="50" t="s">
         <v>78</v>
@@ -3385,16 +3385,16 @@
         <v>200600001</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J39" s="50">
         <v>200600001</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40">
@@ -3405,7 +3405,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D40" s="50">
         <v>4</v>
@@ -3414,22 +3414,22 @@
         <v>66</v>
       </c>
       <c r="F40" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G40" s="50">
         <v>200700001</v>
       </c>
       <c r="H40" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="I40" s="50" t="s">
         <v>130</v>
-      </c>
-      <c r="I40" s="50" t="s">
-        <v>131</v>
       </c>
       <c r="J40" s="50">
         <v>200700001</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41">
@@ -3440,7 +3440,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D41" s="50">
         <v>10</v>
@@ -3455,10 +3455,10 @@
         <v>200800001</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I41" s="50" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="J41" s="50">
         <v>200800001</v>
@@ -3475,7 +3475,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D42" s="50">
         <v>5</v>
@@ -3484,7 +3484,7 @@
         <v>65</v>
       </c>
       <c r="F42" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G42" s="50">
         <v>200900001</v>
@@ -3516,7 +3516,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F43" s="50" t="s">
         <v>65</v>
@@ -3691,10 +3691,10 @@
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G48" s="50">
         <v>300100101</v>
@@ -3726,10 +3726,10 @@
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G49" s="50">
         <v>300100102</v>
@@ -3764,7 +3764,7 @@
         <v>156</v>
       </c>
       <c r="F50" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G50" s="50">
         <v>300100201</v>
@@ -3796,10 +3796,10 @@
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G51" s="50">
         <v>300100301</v>
@@ -3808,7 +3808,7 @@
         <v>160</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J51" s="50">
         <v>300100301</v>
@@ -4006,7 +4006,7 @@
         <v>65</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G57" s="50">
         <v>300200101</v>
@@ -4015,7 +4015,7 @@
         <v>174</v>
       </c>
       <c r="I57" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J57" s="50">
         <v>300200101</v>
@@ -4041,7 +4041,7 @@
         <v>65</v>
       </c>
       <c r="F58" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G58" s="50">
         <v>300200102</v>
@@ -4076,7 +4076,7 @@
         <v>75</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G59" s="50">
         <v>300200201</v>
@@ -4111,7 +4111,7 @@
         <v>65</v>
       </c>
       <c r="F60" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G60" s="50">
         <v>300200301</v>
@@ -4155,7 +4155,7 @@
         <v>300200000</v>
       </c>
       <c r="I61" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J61" s="50">
         <v>300300000</v>
@@ -4321,7 +4321,7 @@
         <v>69</v>
       </c>
       <c r="F66" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G66" s="50">
         <v>300300101</v>
@@ -4356,7 +4356,7 @@
         <v>69</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G67" s="50">
         <v>300300102</v>
@@ -4391,7 +4391,7 @@
         <v>197</v>
       </c>
       <c r="F68" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G68" s="50">
         <v>300300201</v>
@@ -4426,7 +4426,7 @@
         <v>69</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G69" s="50">
         <v>300300301</v>
@@ -4671,7 +4671,7 @@
         <v>203</v>
       </c>
       <c r="F76" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G76" s="50">
         <v>300400101</v>
@@ -4706,7 +4706,7 @@
         <v>203</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G77" s="50">
         <v>300400102</v>
@@ -4741,7 +4741,7 @@
         <v>213</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G78" s="50">
         <v>300400201</v>
@@ -4776,7 +4776,7 @@
         <v>203</v>
       </c>
       <c r="F79" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G79" s="50">
         <v>300400301</v>
@@ -4986,7 +4986,7 @@
         <v>225</v>
       </c>
       <c r="F85" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G85" s="50">
         <v>300500101</v>
@@ -5021,7 +5021,7 @@
         <v>225</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G86" s="50">
         <v>300500102</v>
@@ -5056,7 +5056,7 @@
         <v>238</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G87" s="50">
         <v>300500201</v>
@@ -5091,7 +5091,7 @@
         <v>225</v>
       </c>
       <c r="F88" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G88" s="50">
         <v>300500301</v>
@@ -5336,7 +5336,7 @@
         <v>244</v>
       </c>
       <c r="F95" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G95" s="50">
         <v>300600101</v>
@@ -5371,7 +5371,7 @@
         <v>244</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G96" s="50">
         <v>300600102</v>
@@ -5406,7 +5406,7 @@
         <v>252</v>
       </c>
       <c r="F97" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G97" s="50">
         <v>300600201</v>
@@ -5441,7 +5441,7 @@
         <v>244</v>
       </c>
       <c r="F98" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G98" s="50">
         <v>300600301</v>
@@ -5651,7 +5651,7 @@
         <v>264</v>
       </c>
       <c r="F104" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G104" s="50">
         <v>300700101</v>
@@ -5686,7 +5686,7 @@
         <v>264</v>
       </c>
       <c r="F105" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G105" s="50">
         <v>300700102</v>
@@ -5721,7 +5721,7 @@
         <v>277</v>
       </c>
       <c r="F106" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G106" s="50">
         <v>300700201</v>
@@ -5756,7 +5756,7 @@
         <v>264</v>
       </c>
       <c r="F107" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G107" s="50">
         <v>300700301</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="285">
   <si>
     <t>id</t>
   </si>
@@ -102,57 +102,60 @@
     <t>300</t>
   </si>
   <si>
+    <t>100500001,100401000</t>
+  </si>
+  <si>
+    <t>开启进阶设施</t>
+  </si>
+  <si>
+    <t>ui_research_2</t>
+  </si>
+  <si>
+    <t>-500</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>1000,2000,3000,4000,5000,</t>
+  </si>
+  <si>
+    <t>进阶设施+1</t>
+  </si>
+  <si>
+    <t>-700</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>100000001</t>
+  </si>
+  <si>
+    <t>进阶增益范围预览</t>
+  </si>
+  <si>
+    <t>ui_research_4</t>
+  </si>
+  <si>
+    <t>100000000</t>
+  </si>
+  <si>
+    <t>进阶魔晶加速倍率+1</t>
+  </si>
+  <si>
+    <t>ui_research_5</t>
+  </si>
+  <si>
+    <t>进阶素材可选数量+1</t>
+  </si>
+  <si>
+    <t>ui_research_3</t>
+  </si>
+  <si>
     <t>100500001</t>
   </si>
   <si>
-    <t>开启进阶设施</t>
-  </si>
-  <si>
-    <t>ui_research_2</t>
-  </si>
-  <si>
-    <t>-500</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>1000,2000,3000,4000,5000,</t>
-  </si>
-  <si>
-    <t>进阶设施+1</t>
-  </si>
-  <si>
-    <t>-700</t>
-  </si>
-  <si>
-    <t>700</t>
-  </si>
-  <si>
-    <t>100000001</t>
-  </si>
-  <si>
-    <t>进阶增益范围预览</t>
-  </si>
-  <si>
-    <t>ui_research_4</t>
-  </si>
-  <si>
-    <t>100000000</t>
-  </si>
-  <si>
-    <t>进阶魔晶加速倍率+1</t>
-  </si>
-  <si>
-    <t>ui_research_5</t>
-  </si>
-  <si>
-    <t>进阶素材可选数量+1</t>
-  </si>
-  <si>
-    <t>ui_research_3</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -270,7 +273,7 @@
     <t>剑与魔法：征服难度+1</t>
   </si>
   <si>
-    <t>ui_research_30</t>
+    <t>ui_research_66</t>
   </si>
   <si>
     <t>100310112</t>
@@ -396,7 +399,7 @@
     <t>深渊馈赠刷新次数+1</t>
   </si>
   <si>
-    <t>1000,5000,20000</t>
+    <t>100,1000,10000</t>
   </si>
   <si>
     <t>空格突进</t>
@@ -405,7 +408,7 @@
     <t>200600001</t>
   </si>
   <si>
-    <t>1000,3000,8000,20000</t>
+    <t>200,2000,20000,200000</t>
   </si>
   <si>
     <t>突进冷却</t>
@@ -2338,16 +2341,16 @@
         <v>100100001</v>
       </c>
       <c r="H9" s="50" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I9" s="50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" s="50">
         <v>100100001</v>
       </c>
       <c r="K9" s="50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -2376,13 +2379,13 @@
         <v>100100001</v>
       </c>
       <c r="I10" s="50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J10" s="50">
         <v>100100002</v>
       </c>
       <c r="K10" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -2408,16 +2411,16 @@
         <v>100100003</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J11" s="50">
         <v>100100003</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -2443,16 +2446,16 @@
         <v>100100004</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I12" s="50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J12" s="50">
         <v>100100004</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -2463,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="50">
         <v>1</v>
@@ -2478,16 +2481,16 @@
         <v>100200001</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J13" s="50">
         <v>100200001</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -2498,7 +2501,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="50">
         <v>1</v>
@@ -2522,7 +2525,7 @@
         <v>100200002</v>
       </c>
       <c r="K14" s="50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2533,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="50">
         <v>1</v>
@@ -2548,7 +2551,7 @@
         <v>100200003</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I15" s="50">
         <v>100</v>
@@ -2557,7 +2560,7 @@
         <v>100200003</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -2568,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -2583,16 +2586,16 @@
         <v>100200004</v>
       </c>
       <c r="H16" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I16" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J16" s="50">
         <v>100200004</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -2603,31 +2606,31 @@
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="50">
         <v>100300001</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J17" s="50">
         <v>100300001</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -2638,31 +2641,31 @@
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="50">
         <v>100300002</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J18" s="50">
         <v>100300002</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -2673,31 +2676,31 @@
         <v>1</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G19" s="50">
         <v>100300003</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J19" s="50">
         <v>100300003</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -2708,31 +2711,31 @@
         <v>1</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D20" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="50">
         <v>100300004</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J20" s="50">
         <v>100300004</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -2743,31 +2746,31 @@
         <v>1</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="50">
         <v>100300005</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J21" s="50">
         <v>100300005</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22">
@@ -2778,31 +2781,31 @@
         <v>1</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" s="50">
         <v>10</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" s="50">
         <v>100300006</v>
       </c>
       <c r="H22" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I22" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J22" s="50">
         <v>100300006</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
@@ -2813,31 +2816,31 @@
         <v>4</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" s="50">
         <v>9</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23" s="50">
         <v>100310112</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J23" s="50">
         <v>100310112</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
@@ -2848,31 +2851,31 @@
         <v>4</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D24" s="50">
         <v>1</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" s="50">
         <v>100310130</v>
       </c>
       <c r="H24" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I24" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J24" s="50">
         <v>100310130</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
@@ -2883,31 +2886,31 @@
         <v>1</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D25" s="50">
         <v>1</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G25" s="50">
         <v>100400000</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J25" s="50">
         <v>100400000</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26">
@@ -2918,16 +2921,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D26" s="50">
         <v>1</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G26" s="50">
         <v>100400001</v>
@@ -2936,13 +2939,13 @@
         <v>100400000</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J26" s="50">
         <v>100400001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27">
@@ -2953,31 +2956,31 @@
         <v>1</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D27" s="50">
         <v>1</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G27" s="50">
         <v>100401000</v>
       </c>
       <c r="H27" s="50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J27" s="50">
         <v>100401000</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
@@ -2988,16 +2991,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D28" s="50">
         <v>50</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" s="50">
         <v>100401001</v>
@@ -3006,13 +3009,13 @@
         <v>100401000</v>
       </c>
       <c r="I28" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" s="50">
         <v>100401001</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
@@ -3023,22 +3026,22 @@
         <v>1</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G29" s="50">
         <v>100402000</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I29" s="50">
         <v>1000</v>
@@ -3047,7 +3050,7 @@
         <v>100402000</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30">
@@ -3058,16 +3061,16 @@
         <v>1</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" s="50">
         <v>50</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G30" s="50">
         <v>100402001</v>
@@ -3076,13 +3079,13 @@
         <v>100402000</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J30" s="50">
         <v>100402001</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
@@ -3093,22 +3096,22 @@
         <v>1</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G31" s="50">
         <v>100403000</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I31" s="50">
         <v>10000</v>
@@ -3117,7 +3120,7 @@
         <v>100403000</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
@@ -3128,16 +3131,16 @@
         <v>1</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D32" s="50">
         <v>50</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F32" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G32" s="50">
         <v>100403001</v>
@@ -3146,13 +3149,13 @@
         <v>100403000</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J32" s="50">
         <v>100403001</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33">
@@ -3169,7 +3172,7 @@
         <v>30</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F33" s="50">
         <v>0</v>
@@ -3178,13 +3181,13 @@
         <v>200000001</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J33" s="50">
         <v>200000001</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34">
@@ -3195,31 +3198,31 @@
         <v>2</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D34" s="50">
         <v>4</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F34" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G34" s="50">
         <v>200100001</v>
       </c>
       <c r="H34" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I34" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J34" s="50">
         <v>200100001</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35">
@@ -3230,7 +3233,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D35" s="50">
         <v>6</v>
@@ -3245,16 +3248,16 @@
         <v>200200001</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J35" s="50">
         <v>200200001</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
@@ -3265,7 +3268,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D36" s="50">
         <v>5</v>
@@ -3274,22 +3277,22 @@
         <v>0</v>
       </c>
       <c r="F36" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G36" s="50">
         <v>200300001</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I36" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J36" s="50">
         <v>200300001</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37">
@@ -3300,13 +3303,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D37" s="50">
         <v>3</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F37" s="50">
         <v>-200</v>
@@ -3315,16 +3318,16 @@
         <v>200400001</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J37" s="50">
         <v>200400001</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
@@ -3335,31 +3338,31 @@
         <v>2</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D38" s="50">
         <v>5</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G38" s="50">
         <v>200500001</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I38" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J38" s="50">
         <v>200500001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39">
@@ -3370,31 +3373,31 @@
         <v>2</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D39" s="50">
         <v>3</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G39" s="50">
         <v>200600001</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J39" s="50">
         <v>200600001</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40">
@@ -3405,31 +3408,31 @@
         <v>2</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D40" s="50">
         <v>4</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F40" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G40" s="50">
         <v>200700001</v>
       </c>
       <c r="H40" s="50" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I40" s="50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J40" s="50">
         <v>200700001</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41">
@@ -3440,31 +3443,31 @@
         <v>2</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D41" s="50">
         <v>10</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F41" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G41" s="50">
         <v>200800001</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I41" s="50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J41" s="50">
         <v>200800001</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42">
@@ -3475,31 +3478,31 @@
         <v>2</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D42" s="50">
         <v>5</v>
       </c>
       <c r="E42" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F42" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G42" s="50">
         <v>200900001</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I42" s="50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J42" s="50">
         <v>200900001</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43">
@@ -3510,16 +3513,16 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G43" s="50">
         <v>300100000</v>
@@ -3534,7 +3537,7 @@
         <v>300100000</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44">
@@ -3545,16 +3548,16 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F44" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G44" s="50">
         <v>300100001</v>
@@ -3569,7 +3572,7 @@
         <v>300100001</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45">
@@ -3580,16 +3583,16 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G45" s="50">
         <v>300100002</v>
@@ -3604,7 +3607,7 @@
         <v>300100002</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46">
@@ -3615,16 +3618,16 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F46" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G46" s="50">
         <v>300100003</v>
@@ -3639,7 +3642,7 @@
         <v>300100003</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47">
@@ -3650,16 +3653,16 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F47" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G47" s="50">
         <v>300100004</v>
@@ -3674,7 +3677,7 @@
         <v>300100004</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48">
@@ -3685,22 +3688,22 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G48" s="50">
         <v>300100101</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I48" s="50">
         <v>100</v>
@@ -3709,7 +3712,7 @@
         <v>300100101</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49">
@@ -3720,16 +3723,16 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G49" s="50">
         <v>300100102</v>
@@ -3744,7 +3747,7 @@
         <v>300100102</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50">
@@ -3755,22 +3758,22 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F50" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G50" s="50">
         <v>300100201</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I50" s="50">
         <v>100</v>
@@ -3779,7 +3782,7 @@
         <v>300100201</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51">
@@ -3790,31 +3793,31 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G51" s="50">
         <v>300100301</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J51" s="50">
         <v>300100301</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52">
@@ -3825,28 +3828,28 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F52" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G52" s="50">
         <v>300200000</v>
       </c>
       <c r="I52" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J52" s="50">
         <v>300200000</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53">
@@ -3857,16 +3860,16 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G53" s="50">
         <v>300200001</v>
@@ -3875,13 +3878,13 @@
         <v>300200000</v>
       </c>
       <c r="I53" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J53" s="50">
         <v>300200001</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54">
@@ -3892,16 +3895,16 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F54" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G54" s="50">
         <v>300200002</v>
@@ -3910,13 +3913,13 @@
         <v>300200000</v>
       </c>
       <c r="I54" s="50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J54" s="50">
         <v>300200002</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55">
@@ -3927,16 +3930,16 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G55" s="50">
         <v>300200003</v>
@@ -3951,7 +3954,7 @@
         <v>300200003</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56">
@@ -3962,16 +3965,16 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F56" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G56" s="50">
         <v>300200004</v>
@@ -3986,7 +3989,7 @@
         <v>300200004</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57">
@@ -3997,31 +4000,31 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G57" s="50">
         <v>300200101</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I57" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J57" s="50">
         <v>300200101</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4032,16 +4035,16 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F58" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G58" s="50">
         <v>300200102</v>
@@ -4056,7 +4059,7 @@
         <v>300200102</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4067,22 +4070,22 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G59" s="50">
         <v>300200201</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I59" s="50">
         <v>100</v>
@@ -4091,7 +4094,7 @@
         <v>300200201</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4102,31 +4105,31 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F60" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G60" s="50">
         <v>300200301</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I60" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J60" s="50">
         <v>300200301</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4137,16 +4140,16 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F61" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G61" s="50">
         <v>300300000</v>
@@ -4155,13 +4158,13 @@
         <v>300200000</v>
       </c>
       <c r="I61" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J61" s="50">
         <v>300300000</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4172,16 +4175,16 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F62" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G62" s="50">
         <v>300300001</v>
@@ -4196,7 +4199,7 @@
         <v>300300001</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4207,16 +4210,16 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G63" s="50">
         <v>300300002</v>
@@ -4231,7 +4234,7 @@
         <v>300300002</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4242,16 +4245,16 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G64" s="50">
         <v>300300003</v>
@@ -4266,7 +4269,7 @@
         <v>300300003</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65">
@@ -4277,16 +4280,16 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G65" s="50">
         <v>300300004</v>
@@ -4301,7 +4304,7 @@
         <v>300300004</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66">
@@ -4312,22 +4315,22 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F66" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G66" s="50">
         <v>300300101</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I66" s="50">
         <v>100</v>
@@ -4336,7 +4339,7 @@
         <v>300300101</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4347,16 +4350,16 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G67" s="50">
         <v>300300102</v>
@@ -4371,7 +4374,7 @@
         <v>300300102</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4382,22 +4385,22 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F68" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G68" s="50">
         <v>300300201</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I68" s="50">
         <v>100</v>
@@ -4406,7 +4409,7 @@
         <v>300300201</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4417,22 +4420,22 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G69" s="50">
         <v>300300301</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I69" s="50" t="s">
         <v>33</v>
@@ -4441,7 +4444,7 @@
         <v>300300301</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4452,16 +4455,16 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F70" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G70" s="50">
         <v>300400000</v>
@@ -4476,7 +4479,7 @@
         <v>300400000</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4487,16 +4490,16 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G71" s="50">
         <v>300400001</v>
@@ -4511,7 +4514,7 @@
         <v>300400001</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4522,16 +4525,16 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F72" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G72" s="50">
         <v>300400002</v>
@@ -4546,7 +4549,7 @@
         <v>300400002</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4557,16 +4560,16 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G73" s="50">
         <v>300400003</v>
@@ -4581,7 +4584,7 @@
         <v>300400003</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4592,16 +4595,16 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F74" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G74" s="50">
         <v>300400004</v>
@@ -4616,7 +4619,7 @@
         <v>300400004</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75">
@@ -4627,16 +4630,16 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F75" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G75" s="50">
         <v>300400005</v>
@@ -4651,7 +4654,7 @@
         <v>300400005</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76">
@@ -4662,22 +4665,22 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F76" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G76" s="50">
         <v>300400101</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
@@ -4686,7 +4689,7 @@
         <v>300400101</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77">
@@ -4697,16 +4700,16 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G77" s="50">
         <v>300400102</v>
@@ -4721,7 +4724,7 @@
         <v>300400102</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4732,22 +4735,22 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G78" s="50">
         <v>300400201</v>
       </c>
       <c r="H78" s="50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I78" s="50">
         <v>100</v>
@@ -4756,7 +4759,7 @@
         <v>300400201</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4767,22 +4770,22 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F79" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G79" s="50">
         <v>300400301</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I79" s="50">
         <v>100</v>
@@ -4791,7 +4794,7 @@
         <v>300400301</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4802,16 +4805,16 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F80" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G80" s="50">
         <v>300500000</v>
@@ -4826,7 +4829,7 @@
         <v>300500000</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4837,16 +4840,16 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F81" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G81" s="50">
         <v>300500001</v>
@@ -4861,7 +4864,7 @@
         <v>300500001</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4872,16 +4875,16 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F82" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G82" s="50">
         <v>300500002</v>
@@ -4896,7 +4899,7 @@
         <v>300500002</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4907,16 +4910,16 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F83" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G83" s="50">
         <v>300500003</v>
@@ -4931,7 +4934,7 @@
         <v>300500003</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="84">
@@ -4942,16 +4945,16 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F84" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G84" s="50">
         <v>300500004</v>
@@ -4966,7 +4969,7 @@
         <v>300500004</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="85">
@@ -4977,22 +4980,22 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F85" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G85" s="50">
         <v>300500101</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
@@ -5001,7 +5004,7 @@
         <v>300500101</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86">
@@ -5012,16 +5015,16 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G86" s="50">
         <v>300500102</v>
@@ -5036,7 +5039,7 @@
         <v>300500102</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87">
@@ -5047,22 +5050,22 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G87" s="50">
         <v>300500201</v>
       </c>
       <c r="H87" s="50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I87" s="50">
         <v>100</v>
@@ -5071,7 +5074,7 @@
         <v>300500201</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="88">
@@ -5082,22 +5085,22 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F88" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G88" s="50">
         <v>300500301</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I88" s="50">
         <v>100</v>
@@ -5106,7 +5109,7 @@
         <v>300500301</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="89">
@@ -5117,16 +5120,16 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F89" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G89" s="50">
         <v>300600000</v>
@@ -5141,7 +5144,7 @@
         <v>300600000</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="90">
@@ -5152,16 +5155,16 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F90" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G90" s="50">
         <v>300600001</v>
@@ -5176,7 +5179,7 @@
         <v>300600001</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="91">
@@ -5187,16 +5190,16 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F91" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G91" s="50">
         <v>300600002</v>
@@ -5211,7 +5214,7 @@
         <v>300600002</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92">
@@ -5222,16 +5225,16 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F92" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G92" s="50">
         <v>300600003</v>
@@ -5246,7 +5249,7 @@
         <v>300600003</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93">
@@ -5257,16 +5260,16 @@
         <v>3</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F93" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G93" s="50">
         <v>300600004</v>
@@ -5281,7 +5284,7 @@
         <v>300600004</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="94">
@@ -5292,16 +5295,16 @@
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D94" s="50">
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F94" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G94" s="50">
         <v>300600005</v>
@@ -5316,7 +5319,7 @@
         <v>300600005</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="95">
@@ -5327,22 +5330,22 @@
         <v>3</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D95" s="50">
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F95" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G95" s="50">
         <v>300600101</v>
       </c>
       <c r="H95" s="50" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I95" s="50">
         <v>100</v>
@@ -5351,7 +5354,7 @@
         <v>300600101</v>
       </c>
       <c r="K95" s="50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="96">
@@ -5362,16 +5365,16 @@
         <v>3</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D96" s="50">
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G96" s="50">
         <v>300600102</v>
@@ -5386,7 +5389,7 @@
         <v>300600102</v>
       </c>
       <c r="K96" s="50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="97">
@@ -5397,22 +5400,22 @@
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D97" s="50">
         <v>1</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F97" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G97" s="50">
         <v>300600201</v>
       </c>
       <c r="H97" s="50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I97" s="50">
         <v>100</v>
@@ -5421,7 +5424,7 @@
         <v>300600201</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98">
@@ -5432,22 +5435,22 @@
         <v>3</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D98" s="50">
         <v>1</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F98" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G98" s="50">
         <v>300600301</v>
       </c>
       <c r="H98" s="50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I98" s="50">
         <v>100</v>
@@ -5456,7 +5459,7 @@
         <v>300600301</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99">
@@ -5467,16 +5470,16 @@
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D99" s="50">
         <v>1</v>
       </c>
       <c r="E99" s="50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F99" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G99" s="50">
         <v>300700000</v>
@@ -5491,7 +5494,7 @@
         <v>300700000</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100">
@@ -5502,16 +5505,16 @@
         <v>3</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D100" s="50">
         <v>1</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F100" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G100" s="50">
         <v>300700001</v>
@@ -5526,7 +5529,7 @@
         <v>300700001</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="101">
@@ -5537,16 +5540,16 @@
         <v>3</v>
       </c>
       <c r="C101" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D101" s="50">
         <v>1</v>
       </c>
       <c r="E101" s="50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F101" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G101" s="50">
         <v>300700002</v>
@@ -5561,7 +5564,7 @@
         <v>300700002</v>
       </c>
       <c r="K101" s="50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102">
@@ -5572,16 +5575,16 @@
         <v>3</v>
       </c>
       <c r="C102" s="50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D102" s="50">
         <v>1</v>
       </c>
       <c r="E102" s="50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F102" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G102" s="50">
         <v>300700003</v>
@@ -5596,7 +5599,7 @@
         <v>300700003</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103">
@@ -5607,16 +5610,16 @@
         <v>3</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D103" s="50">
         <v>1</v>
       </c>
       <c r="E103" s="50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F103" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G103" s="50">
         <v>300700004</v>
@@ -5631,7 +5634,7 @@
         <v>300700004</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="104">
@@ -5642,22 +5645,22 @@
         <v>3</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D104" s="50">
         <v>1</v>
       </c>
       <c r="E104" s="50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F104" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G104" s="50">
         <v>300700101</v>
       </c>
       <c r="H104" s="50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I104" s="50">
         <v>100</v>
@@ -5666,7 +5669,7 @@
         <v>300700101</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105">
@@ -5677,16 +5680,16 @@
         <v>3</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D105" s="50">
         <v>1</v>
       </c>
       <c r="E105" s="50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F105" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G105" s="50">
         <v>300700102</v>
@@ -5701,7 +5704,7 @@
         <v>300700102</v>
       </c>
       <c r="K105" s="50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="106">
@@ -5712,22 +5715,22 @@
         <v>3</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D106" s="50">
         <v>1</v>
       </c>
       <c r="E106" s="50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F106" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G106" s="50">
         <v>300700201</v>
       </c>
       <c r="H106" s="50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I106" s="50">
         <v>100</v>
@@ -5736,7 +5739,7 @@
         <v>300700201</v>
       </c>
       <c r="K106" s="50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="107">
@@ -5747,22 +5750,22 @@
         <v>3</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D107" s="50">
         <v>1</v>
       </c>
       <c r="E107" s="50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F107" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G107" s="50">
         <v>300700301</v>
       </c>
       <c r="H107" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I107" s="50">
         <v>100</v>
@@ -5771,7 +5774,7 @@
         <v>300700301</v>
       </c>
       <c r="K107" s="50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="108">
@@ -5782,28 +5785,28 @@
         <v>1</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D108" s="50">
         <v>1</v>
       </c>
       <c r="E108" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F108" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G108" s="50">
         <v>100500001</v>
       </c>
       <c r="I108" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J108" s="50">
         <v>100500001</v>
       </c>
       <c r="K108" s="50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="286">
   <si>
     <t>id</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>献祭失败保底概率提升</t>
+  </si>
+  <si>
+    <t>100,200,500,1000,1500,2000,2500,3000,3500,5000</t>
   </si>
   <si>
     <t>不同魔物献祭成功率提升</t>
@@ -2449,13 +2452,13 @@
         <v>51</v>
       </c>
       <c r="I12" s="50" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J12" s="50">
         <v>100100004</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -2466,7 +2469,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="50">
         <v>1</v>
@@ -2484,13 +2487,13 @@
         <v>46</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J13" s="50">
         <v>100200001</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -2501,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" s="50">
         <v>1</v>
@@ -2525,7 +2528,7 @@
         <v>100200002</v>
       </c>
       <c r="K14" s="50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2536,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" s="50">
         <v>1</v>
@@ -2551,7 +2554,7 @@
         <v>100200003</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I15" s="50">
         <v>100</v>
@@ -2560,7 +2563,7 @@
         <v>100200003</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -2571,7 +2574,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -2586,16 +2589,16 @@
         <v>100200004</v>
       </c>
       <c r="H16" s="50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I16" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J16" s="50">
         <v>100200004</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -2606,16 +2609,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="50">
         <v>100300001</v>
@@ -2624,13 +2627,13 @@
         <v>46</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J17" s="50">
         <v>100300001</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -2641,31 +2644,31 @@
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="50">
         <v>100300002</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J18" s="50">
         <v>100300002</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -2676,31 +2679,31 @@
         <v>1</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G19" s="50">
         <v>100300003</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J19" s="50">
         <v>100300003</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -2711,31 +2714,31 @@
         <v>1</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E20" s="50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="50">
         <v>100300004</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J20" s="50">
         <v>100300004</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21">
@@ -2746,31 +2749,31 @@
         <v>1</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="50">
         <v>100300005</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J21" s="50">
         <v>100300005</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
@@ -2781,31 +2784,31 @@
         <v>1</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22" s="50">
         <v>10</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" s="50">
         <v>100300006</v>
       </c>
       <c r="H22" s="50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I22" s="50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J22" s="50">
         <v>100300006</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23">
@@ -2816,31 +2819,31 @@
         <v>4</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" s="50">
         <v>9</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" s="50">
         <v>100310112</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J23" s="50">
         <v>100310112</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
@@ -2851,31 +2854,31 @@
         <v>4</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D24" s="50">
         <v>1</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" s="50">
         <v>100310130</v>
       </c>
       <c r="H24" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I24" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J24" s="50">
         <v>100310130</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25">
@@ -2886,16 +2889,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="50">
         <v>1</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G25" s="50">
         <v>100400000</v>
@@ -2904,13 +2907,13 @@
         <v>46</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J25" s="50">
         <v>100400000</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26">
@@ -2921,16 +2924,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" s="50">
         <v>1</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G26" s="50">
         <v>100400001</v>
@@ -2939,13 +2942,13 @@
         <v>100400000</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J26" s="50">
         <v>100400001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27">
@@ -2956,31 +2959,31 @@
         <v>1</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D27" s="50">
         <v>1</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G27" s="50">
         <v>100401000</v>
       </c>
       <c r="H27" s="50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J27" s="50">
         <v>100401000</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28">
@@ -2991,16 +2994,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D28" s="50">
         <v>50</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G28" s="50">
         <v>100401001</v>
@@ -3009,13 +3012,13 @@
         <v>100401000</v>
       </c>
       <c r="I28" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J28" s="50">
         <v>100401001</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29">
@@ -3026,22 +3029,22 @@
         <v>1</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G29" s="50">
         <v>100402000</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I29" s="50">
         <v>1000</v>
@@ -3050,7 +3053,7 @@
         <v>100402000</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30">
@@ -3061,16 +3064,16 @@
         <v>1</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D30" s="50">
         <v>50</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G30" s="50">
         <v>100402001</v>
@@ -3079,13 +3082,13 @@
         <v>100402000</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J30" s="50">
         <v>100402001</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31">
@@ -3096,22 +3099,22 @@
         <v>1</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G31" s="50">
         <v>100403000</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I31" s="50">
         <v>10000</v>
@@ -3120,7 +3123,7 @@
         <v>100403000</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32">
@@ -3131,16 +3134,16 @@
         <v>1</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" s="50">
         <v>50</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F32" s="50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G32" s="50">
         <v>100403001</v>
@@ -3149,13 +3152,13 @@
         <v>100403000</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J32" s="50">
         <v>100403001</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33">
@@ -3172,7 +3175,7 @@
         <v>30</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F33" s="50">
         <v>0</v>
@@ -3181,13 +3184,13 @@
         <v>200000001</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J33" s="50">
         <v>200000001</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
@@ -3198,31 +3201,31 @@
         <v>2</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D34" s="50">
         <v>4</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F34" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G34" s="50">
         <v>200100001</v>
       </c>
       <c r="H34" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I34" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J34" s="50">
         <v>200100001</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35">
@@ -3233,7 +3236,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D35" s="50">
         <v>6</v>
@@ -3248,16 +3251,16 @@
         <v>200200001</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J35" s="50">
         <v>200200001</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36">
@@ -3268,7 +3271,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D36" s="50">
         <v>5</v>
@@ -3277,22 +3280,22 @@
         <v>0</v>
       </c>
       <c r="F36" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G36" s="50">
         <v>200300001</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I36" s="50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J36" s="50">
         <v>200300001</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37">
@@ -3303,13 +3306,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D37" s="50">
         <v>3</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F37" s="50">
         <v>-200</v>
@@ -3318,16 +3321,16 @@
         <v>200400001</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J37" s="50">
         <v>200400001</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38">
@@ -3338,31 +3341,31 @@
         <v>2</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D38" s="50">
         <v>5</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G38" s="50">
         <v>200500001</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I38" s="50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J38" s="50">
         <v>200500001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39">
@@ -3373,31 +3376,31 @@
         <v>2</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D39" s="50">
         <v>3</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G39" s="50">
         <v>200600001</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J39" s="50">
         <v>200600001</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40">
@@ -3408,31 +3411,31 @@
         <v>2</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D40" s="50">
         <v>4</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F40" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G40" s="50">
         <v>200700001</v>
       </c>
       <c r="H40" s="50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I40" s="50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J40" s="50">
         <v>200700001</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41">
@@ -3443,31 +3446,31 @@
         <v>2</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D41" s="50">
         <v>10</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F41" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G41" s="50">
         <v>200800001</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I41" s="50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J41" s="50">
         <v>200800001</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42">
@@ -3478,31 +3481,31 @@
         <v>2</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D42" s="50">
         <v>5</v>
       </c>
       <c r="E42" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F42" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G42" s="50">
         <v>200900001</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I42" s="50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J42" s="50">
         <v>200900001</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43">
@@ -3513,16 +3516,16 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G43" s="50">
         <v>300100000</v>
@@ -3537,7 +3540,7 @@
         <v>300100000</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44">
@@ -3548,16 +3551,16 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F44" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G44" s="50">
         <v>300100001</v>
@@ -3572,7 +3575,7 @@
         <v>300100001</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45">
@@ -3583,16 +3586,16 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G45" s="50">
         <v>300100002</v>
@@ -3607,7 +3610,7 @@
         <v>300100002</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46">
@@ -3618,16 +3621,16 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F46" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G46" s="50">
         <v>300100003</v>
@@ -3642,7 +3645,7 @@
         <v>300100003</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47">
@@ -3653,16 +3656,16 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F47" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G47" s="50">
         <v>300100004</v>
@@ -3677,7 +3680,7 @@
         <v>300100004</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48">
@@ -3688,22 +3691,22 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G48" s="50">
         <v>300100101</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I48" s="50">
         <v>100</v>
@@ -3712,7 +3715,7 @@
         <v>300100101</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49">
@@ -3723,16 +3726,16 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G49" s="50">
         <v>300100102</v>
@@ -3747,7 +3750,7 @@
         <v>300100102</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50">
@@ -3758,22 +3761,22 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F50" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G50" s="50">
         <v>300100201</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I50" s="50">
         <v>100</v>
@@ -3782,7 +3785,7 @@
         <v>300100201</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51">
@@ -3793,31 +3796,31 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G51" s="50">
         <v>300100301</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J51" s="50">
         <v>300100301</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52">
@@ -3828,28 +3831,28 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F52" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G52" s="50">
         <v>300200000</v>
       </c>
       <c r="I52" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J52" s="50">
         <v>300200000</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53">
@@ -3860,16 +3863,16 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G53" s="50">
         <v>300200001</v>
@@ -3878,13 +3881,13 @@
         <v>300200000</v>
       </c>
       <c r="I53" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J53" s="50">
         <v>300200001</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54">
@@ -3895,16 +3898,16 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F54" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G54" s="50">
         <v>300200002</v>
@@ -3913,13 +3916,13 @@
         <v>300200000</v>
       </c>
       <c r="I54" s="50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J54" s="50">
         <v>300200002</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55">
@@ -3930,16 +3933,16 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G55" s="50">
         <v>300200003</v>
@@ -3954,7 +3957,7 @@
         <v>300200003</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56">
@@ -3965,16 +3968,16 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F56" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G56" s="50">
         <v>300200004</v>
@@ -3989,7 +3992,7 @@
         <v>300200004</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57">
@@ -4000,31 +4003,31 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G57" s="50">
         <v>300200101</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I57" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J57" s="50">
         <v>300200101</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4035,16 +4038,16 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F58" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G58" s="50">
         <v>300200102</v>
@@ -4059,7 +4062,7 @@
         <v>300200102</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4070,22 +4073,22 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G59" s="50">
         <v>300200201</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I59" s="50">
         <v>100</v>
@@ -4094,7 +4097,7 @@
         <v>300200201</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4105,31 +4108,31 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F60" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G60" s="50">
         <v>300200301</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I60" s="50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J60" s="50">
         <v>300200301</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4140,16 +4143,16 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F61" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G61" s="50">
         <v>300300000</v>
@@ -4158,13 +4161,13 @@
         <v>300200000</v>
       </c>
       <c r="I61" s="50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J61" s="50">
         <v>300300000</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4175,16 +4178,16 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F62" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G62" s="50">
         <v>300300001</v>
@@ -4199,7 +4202,7 @@
         <v>300300001</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4210,16 +4213,16 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G63" s="50">
         <v>300300002</v>
@@ -4234,7 +4237,7 @@
         <v>300300002</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4245,16 +4248,16 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G64" s="50">
         <v>300300003</v>
@@ -4269,7 +4272,7 @@
         <v>300300003</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65">
@@ -4280,16 +4283,16 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G65" s="50">
         <v>300300004</v>
@@ -4304,7 +4307,7 @@
         <v>300300004</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66">
@@ -4315,22 +4318,22 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F66" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G66" s="50">
         <v>300300101</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I66" s="50">
         <v>100</v>
@@ -4339,7 +4342,7 @@
         <v>300300101</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4350,16 +4353,16 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G67" s="50">
         <v>300300102</v>
@@ -4374,7 +4377,7 @@
         <v>300300102</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4385,22 +4388,22 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F68" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G68" s="50">
         <v>300300201</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I68" s="50">
         <v>100</v>
@@ -4409,7 +4412,7 @@
         <v>300300201</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4420,22 +4423,22 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G69" s="50">
         <v>300300301</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I69" s="50" t="s">
         <v>33</v>
@@ -4444,7 +4447,7 @@
         <v>300300301</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4455,16 +4458,16 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F70" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G70" s="50">
         <v>300400000</v>
@@ -4479,7 +4482,7 @@
         <v>300400000</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4490,16 +4493,16 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G71" s="50">
         <v>300400001</v>
@@ -4514,7 +4517,7 @@
         <v>300400001</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4525,16 +4528,16 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F72" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G72" s="50">
         <v>300400002</v>
@@ -4549,7 +4552,7 @@
         <v>300400002</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4560,16 +4563,16 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G73" s="50">
         <v>300400003</v>
@@ -4584,7 +4587,7 @@
         <v>300400003</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4595,16 +4598,16 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F74" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G74" s="50">
         <v>300400004</v>
@@ -4619,7 +4622,7 @@
         <v>300400004</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75">
@@ -4630,16 +4633,16 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F75" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G75" s="50">
         <v>300400005</v>
@@ -4654,7 +4657,7 @@
         <v>300400005</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="76">
@@ -4665,22 +4668,22 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F76" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G76" s="50">
         <v>300400101</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
@@ -4689,7 +4692,7 @@
         <v>300400101</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77">
@@ -4700,16 +4703,16 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G77" s="50">
         <v>300400102</v>
@@ -4724,7 +4727,7 @@
         <v>300400102</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4735,22 +4738,22 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G78" s="50">
         <v>300400201</v>
       </c>
       <c r="H78" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I78" s="50">
         <v>100</v>
@@ -4759,7 +4762,7 @@
         <v>300400201</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4770,22 +4773,22 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F79" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G79" s="50">
         <v>300400301</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I79" s="50">
         <v>100</v>
@@ -4794,7 +4797,7 @@
         <v>300400301</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4805,16 +4808,16 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F80" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G80" s="50">
         <v>300500000</v>
@@ -4829,7 +4832,7 @@
         <v>300500000</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4840,16 +4843,16 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F81" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G81" s="50">
         <v>300500001</v>
@@ -4864,7 +4867,7 @@
         <v>300500001</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4875,16 +4878,16 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F82" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G82" s="50">
         <v>300500002</v>
@@ -4899,7 +4902,7 @@
         <v>300500002</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4910,16 +4913,16 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F83" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G83" s="50">
         <v>300500003</v>
@@ -4934,7 +4937,7 @@
         <v>300500003</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84">
@@ -4945,16 +4948,16 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F84" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G84" s="50">
         <v>300500004</v>
@@ -4969,7 +4972,7 @@
         <v>300500004</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85">
@@ -4980,22 +4983,22 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F85" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G85" s="50">
         <v>300500101</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
@@ -5004,7 +5007,7 @@
         <v>300500101</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86">
@@ -5015,16 +5018,16 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G86" s="50">
         <v>300500102</v>
@@ -5039,7 +5042,7 @@
         <v>300500102</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87">
@@ -5050,22 +5053,22 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G87" s="50">
         <v>300500201</v>
       </c>
       <c r="H87" s="50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I87" s="50">
         <v>100</v>
@@ -5074,7 +5077,7 @@
         <v>300500201</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="88">
@@ -5085,22 +5088,22 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F88" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G88" s="50">
         <v>300500301</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I88" s="50">
         <v>100</v>
@@ -5109,7 +5112,7 @@
         <v>300500301</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89">
@@ -5120,16 +5123,16 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F89" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G89" s="50">
         <v>300600000</v>
@@ -5144,7 +5147,7 @@
         <v>300600000</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90">
@@ -5155,16 +5158,16 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F90" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G90" s="50">
         <v>300600001</v>
@@ -5179,7 +5182,7 @@
         <v>300600001</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="91">
@@ -5190,16 +5193,16 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F91" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G91" s="50">
         <v>300600002</v>
@@ -5214,7 +5217,7 @@
         <v>300600002</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="92">
@@ -5225,16 +5228,16 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F92" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G92" s="50">
         <v>300600003</v>
@@ -5249,7 +5252,7 @@
         <v>300600003</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93">
@@ -5260,16 +5263,16 @@
         <v>3</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F93" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G93" s="50">
         <v>300600004</v>
@@ -5284,7 +5287,7 @@
         <v>300600004</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94">
@@ -5295,16 +5298,16 @@
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D94" s="50">
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F94" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G94" s="50">
         <v>300600005</v>
@@ -5319,7 +5322,7 @@
         <v>300600005</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="95">
@@ -5330,22 +5333,22 @@
         <v>3</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D95" s="50">
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F95" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G95" s="50">
         <v>300600101</v>
       </c>
       <c r="H95" s="50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I95" s="50">
         <v>100</v>
@@ -5354,7 +5357,7 @@
         <v>300600101</v>
       </c>
       <c r="K95" s="50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96">
@@ -5365,16 +5368,16 @@
         <v>3</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D96" s="50">
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G96" s="50">
         <v>300600102</v>
@@ -5389,7 +5392,7 @@
         <v>300600102</v>
       </c>
       <c r="K96" s="50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="97">
@@ -5400,22 +5403,22 @@
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D97" s="50">
         <v>1</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F97" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G97" s="50">
         <v>300600201</v>
       </c>
       <c r="H97" s="50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I97" s="50">
         <v>100</v>
@@ -5424,7 +5427,7 @@
         <v>300600201</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="98">
@@ -5435,22 +5438,22 @@
         <v>3</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D98" s="50">
         <v>1</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F98" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G98" s="50">
         <v>300600301</v>
       </c>
       <c r="H98" s="50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I98" s="50">
         <v>100</v>
@@ -5459,7 +5462,7 @@
         <v>300600301</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99">
@@ -5470,16 +5473,16 @@
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D99" s="50">
         <v>1</v>
       </c>
       <c r="E99" s="50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F99" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G99" s="50">
         <v>300700000</v>
@@ -5494,7 +5497,7 @@
         <v>300700000</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="100">
@@ -5505,16 +5508,16 @@
         <v>3</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D100" s="50">
         <v>1</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F100" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G100" s="50">
         <v>300700001</v>
@@ -5529,7 +5532,7 @@
         <v>300700001</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101">
@@ -5540,16 +5543,16 @@
         <v>3</v>
       </c>
       <c r="C101" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D101" s="50">
         <v>1</v>
       </c>
       <c r="E101" s="50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F101" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G101" s="50">
         <v>300700002</v>
@@ -5564,7 +5567,7 @@
         <v>300700002</v>
       </c>
       <c r="K101" s="50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102">
@@ -5575,16 +5578,16 @@
         <v>3</v>
       </c>
       <c r="C102" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D102" s="50">
         <v>1</v>
       </c>
       <c r="E102" s="50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F102" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G102" s="50">
         <v>300700003</v>
@@ -5599,7 +5602,7 @@
         <v>300700003</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103">
@@ -5610,16 +5613,16 @@
         <v>3</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D103" s="50">
         <v>1</v>
       </c>
       <c r="E103" s="50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F103" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G103" s="50">
         <v>300700004</v>
@@ -5634,7 +5637,7 @@
         <v>300700004</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="104">
@@ -5645,22 +5648,22 @@
         <v>3</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D104" s="50">
         <v>1</v>
       </c>
       <c r="E104" s="50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F104" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G104" s="50">
         <v>300700101</v>
       </c>
       <c r="H104" s="50" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I104" s="50">
         <v>100</v>
@@ -5669,7 +5672,7 @@
         <v>300700101</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="105">
@@ -5680,16 +5683,16 @@
         <v>3</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D105" s="50">
         <v>1</v>
       </c>
       <c r="E105" s="50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F105" s="50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G105" s="50">
         <v>300700102</v>
@@ -5704,7 +5707,7 @@
         <v>300700102</v>
       </c>
       <c r="K105" s="50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="106">
@@ -5715,22 +5718,22 @@
         <v>3</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D106" s="50">
         <v>1</v>
       </c>
       <c r="E106" s="50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F106" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G106" s="50">
         <v>300700201</v>
       </c>
       <c r="H106" s="50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I106" s="50">
         <v>100</v>
@@ -5739,7 +5742,7 @@
         <v>300700201</v>
       </c>
       <c r="K106" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="107">
@@ -5750,22 +5753,22 @@
         <v>3</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D107" s="50">
         <v>1</v>
       </c>
       <c r="E107" s="50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F107" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G107" s="50">
         <v>300700301</v>
       </c>
       <c r="H107" s="50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I107" s="50">
         <v>100</v>
@@ -5774,7 +5777,7 @@
         <v>300700301</v>
       </c>
       <c r="K107" s="50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="108">
@@ -5785,28 +5788,28 @@
         <v>1</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D108" s="50">
         <v>1</v>
       </c>
       <c r="E108" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F108" s="50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G108" s="50">
         <v>100500001</v>
       </c>
       <c r="I108" s="50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J108" s="50">
         <v>100500001</v>
       </c>
       <c r="K108" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
   <si>
     <t>id</t>
   </si>
@@ -589,6 +589,9 @@
   </si>
   <si>
     <t>-725</t>
+  </si>
+  <si>
+    <t>201</t>
   </si>
   <si>
     <t>解锁职业：烂泥史莱姆</t>
@@ -4090,8 +4093,8 @@
       <c r="H59" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="I59" s="50">
-        <v>100</v>
+      <c r="I59" s="50" t="s">
+        <v>98</v>
       </c>
       <c r="J59" s="50">
         <v>300200201</v>
@@ -4230,8 +4233,8 @@
       <c r="H63" s="50">
         <v>300300000</v>
       </c>
-      <c r="I63" s="50">
-        <v>100</v>
+      <c r="I63" s="50" t="s">
+        <v>98</v>
       </c>
       <c r="J63" s="50">
         <v>300300002</v>
@@ -4257,7 +4260,7 @@
         <v>191</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="G64" s="50">
         <v>300300003</v>
@@ -4265,14 +4268,14 @@
       <c r="H64" s="50">
         <v>300300000</v>
       </c>
-      <c r="I64" s="50">
-        <v>100</v>
+      <c r="I64" s="50" t="s">
+        <v>33</v>
       </c>
       <c r="J64" s="50">
         <v>300300003</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65">
@@ -4283,13 +4286,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>80</v>
@@ -4300,14 +4303,14 @@
       <c r="H65" s="50">
         <v>300300000</v>
       </c>
-      <c r="I65" s="50">
-        <v>100</v>
+      <c r="I65" s="50" t="s">
+        <v>57</v>
       </c>
       <c r="J65" s="50">
         <v>300300004</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66">
@@ -4333,16 +4336,16 @@
         <v>300300101</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="I66" s="50">
-        <v>100</v>
+        <v>197</v>
+      </c>
+      <c r="I66" s="50" t="s">
+        <v>33</v>
       </c>
       <c r="J66" s="50">
         <v>300300101</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4370,14 +4373,14 @@
       <c r="H67" s="50">
         <v>300300101</v>
       </c>
-      <c r="I67" s="50">
-        <v>100</v>
+      <c r="I67" s="50" t="s">
+        <v>57</v>
       </c>
       <c r="J67" s="50">
         <v>300300102</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4394,7 +4397,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>100</v>
@@ -4403,16 +4406,16 @@
         <v>300300201</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>200</v>
-      </c>
-      <c r="I68" s="50">
-        <v>100</v>
+        <v>201</v>
+      </c>
+      <c r="I68" s="50" t="s">
+        <v>98</v>
       </c>
       <c r="J68" s="50">
         <v>300300201</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4438,16 +4441,16 @@
         <v>300300301</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I69" s="50" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="J69" s="50">
         <v>300300301</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4458,13 +4461,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>67</v>
@@ -4482,7 +4485,7 @@
         <v>300400000</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4499,7 +4502,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>80</v>
@@ -4517,7 +4520,7 @@
         <v>300400001</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4528,13 +4531,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>80</v>
@@ -4552,7 +4555,7 @@
         <v>300400002</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4563,13 +4566,13 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>80</v>
@@ -4587,7 +4590,7 @@
         <v>300400003</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4598,13 +4601,13 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>80</v>
@@ -4622,7 +4625,7 @@
         <v>300400004</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="75">
@@ -4639,7 +4642,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>80</v>
@@ -4657,7 +4660,7 @@
         <v>300400005</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76">
@@ -4674,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>91</v>
@@ -4683,7 +4686,7 @@
         <v>300400101</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
@@ -4692,7 +4695,7 @@
         <v>300400101</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77">
@@ -4709,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F77" s="50" t="s">
         <v>94</v>
@@ -4727,7 +4730,7 @@
         <v>300400102</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4738,13 +4741,13 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>100</v>
@@ -4753,7 +4756,7 @@
         <v>300400201</v>
       </c>
       <c r="H78" s="50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I78" s="50">
         <v>100</v>
@@ -4762,7 +4765,7 @@
         <v>300400201</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4779,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>100</v>
@@ -4788,7 +4791,7 @@
         <v>300400301</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I79" s="50">
         <v>100</v>
@@ -4797,7 +4800,7 @@
         <v>300400301</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4808,13 +4811,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>67</v>
@@ -4832,7 +4835,7 @@
         <v>300500000</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4849,7 +4852,7 @@
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>80</v>
@@ -4867,7 +4870,7 @@
         <v>300500001</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4884,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>80</v>
@@ -4902,7 +4905,7 @@
         <v>300500002</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4919,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>80</v>
@@ -4937,7 +4940,7 @@
         <v>300500003</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="84">
@@ -4954,7 +4957,7 @@
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>80</v>
@@ -4972,7 +4975,7 @@
         <v>300500004</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="85">
@@ -4989,7 +4992,7 @@
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>91</v>
@@ -4998,7 +5001,7 @@
         <v>300500101</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
@@ -5007,7 +5010,7 @@
         <v>300500101</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86">
@@ -5024,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>94</v>
@@ -5042,7 +5045,7 @@
         <v>300500102</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="87">
@@ -5053,13 +5056,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F87" s="50" t="s">
         <v>100</v>
@@ -5068,7 +5071,7 @@
         <v>300500201</v>
       </c>
       <c r="H87" s="50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I87" s="50">
         <v>100</v>
@@ -5077,7 +5080,7 @@
         <v>300500201</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="88">
@@ -5094,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>100</v>
@@ -5103,7 +5106,7 @@
         <v>300500301</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I88" s="50">
         <v>100</v>
@@ -5112,7 +5115,7 @@
         <v>300500301</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89">
@@ -5123,13 +5126,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>67</v>
@@ -5147,7 +5150,7 @@
         <v>300600000</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="90">
@@ -5158,13 +5161,13 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>80</v>
@@ -5182,7 +5185,7 @@
         <v>300600001</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91">
@@ -5199,7 +5202,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>80</v>
@@ -5217,7 +5220,7 @@
         <v>300600002</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92">
@@ -5234,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>80</v>
@@ -5252,7 +5255,7 @@
         <v>300600003</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93">
@@ -5269,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F93" s="50" t="s">
         <v>80</v>
@@ -5287,7 +5290,7 @@
         <v>300600004</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="94">
@@ -5304,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F94" s="50" t="s">
         <v>80</v>
@@ -5322,7 +5325,7 @@
         <v>300600005</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="95">
@@ -5339,7 +5342,7 @@
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F95" s="50" t="s">
         <v>91</v>
@@ -5348,7 +5351,7 @@
         <v>300600101</v>
       </c>
       <c r="H95" s="50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I95" s="50">
         <v>100</v>
@@ -5357,7 +5360,7 @@
         <v>300600101</v>
       </c>
       <c r="K95" s="50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="96">
@@ -5374,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F96" s="50" t="s">
         <v>94</v>
@@ -5392,7 +5395,7 @@
         <v>300600102</v>
       </c>
       <c r="K96" s="50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97">
@@ -5403,13 +5406,13 @@
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D97" s="50">
         <v>1</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F97" s="50" t="s">
         <v>100</v>
@@ -5418,7 +5421,7 @@
         <v>300600201</v>
       </c>
       <c r="H97" s="50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I97" s="50">
         <v>100</v>
@@ -5427,7 +5430,7 @@
         <v>300600201</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98">
@@ -5444,7 +5447,7 @@
         <v>1</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F98" s="50" t="s">
         <v>100</v>
@@ -5453,7 +5456,7 @@
         <v>300600301</v>
       </c>
       <c r="H98" s="50" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I98" s="50">
         <v>100</v>
@@ -5462,7 +5465,7 @@
         <v>300600301</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="99">
@@ -5473,13 +5476,13 @@
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D99" s="50">
         <v>1</v>
       </c>
       <c r="E99" s="50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F99" s="50" t="s">
         <v>67</v>
@@ -5497,7 +5500,7 @@
         <v>300700000</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="100">
@@ -5514,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F100" s="50" t="s">
         <v>80</v>
@@ -5532,7 +5535,7 @@
         <v>300700001</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101">
@@ -5549,7 +5552,7 @@
         <v>1</v>
       </c>
       <c r="E101" s="50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F101" s="50" t="s">
         <v>80</v>
@@ -5567,7 +5570,7 @@
         <v>300700002</v>
       </c>
       <c r="K101" s="50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102">
@@ -5584,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="E102" s="50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F102" s="50" t="s">
         <v>80</v>
@@ -5602,7 +5605,7 @@
         <v>300700003</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="103">
@@ -5619,7 +5622,7 @@
         <v>1</v>
       </c>
       <c r="E103" s="50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F103" s="50" t="s">
         <v>80</v>
@@ -5637,7 +5640,7 @@
         <v>300700004</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="104">
@@ -5654,7 +5657,7 @@
         <v>1</v>
       </c>
       <c r="E104" s="50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F104" s="50" t="s">
         <v>91</v>
@@ -5663,7 +5666,7 @@
         <v>300700101</v>
       </c>
       <c r="H104" s="50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I104" s="50">
         <v>100</v>
@@ -5672,7 +5675,7 @@
         <v>300700101</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="105">
@@ -5689,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="E105" s="50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F105" s="50" t="s">
         <v>94</v>
@@ -5707,7 +5710,7 @@
         <v>300700102</v>
       </c>
       <c r="K105" s="50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="106">
@@ -5718,13 +5721,13 @@
         <v>3</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D106" s="50">
         <v>1</v>
       </c>
       <c r="E106" s="50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F106" s="50" t="s">
         <v>100</v>
@@ -5733,7 +5736,7 @@
         <v>300700201</v>
       </c>
       <c r="H106" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I106" s="50">
         <v>100</v>
@@ -5742,7 +5745,7 @@
         <v>300700201</v>
       </c>
       <c r="K106" s="50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="107">
@@ -5759,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="E107" s="50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F107" s="50" t="s">
         <v>100</v>
@@ -5768,7 +5771,7 @@
         <v>300700301</v>
       </c>
       <c r="H107" s="50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I107" s="50">
         <v>100</v>
@@ -5777,7 +5780,7 @@
         <v>300700301</v>
       </c>
       <c r="K107" s="50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="108">
@@ -5788,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D108" s="50">
         <v>1</v>
@@ -5809,7 +5812,7 @@
         <v>100500001</v>
       </c>
       <c r="K108" s="50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -351,7 +351,7 @@
     <t>孕育稀有度：SSR 概率+1%</t>
   </si>
   <si>
-    <t>50,100,150,200,250,300,350,400,450,500,</t>
+    <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000</t>
   </si>
   <si>
     <t>阵容上限+1</t>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="286">
   <si>
     <t>id</t>
   </si>
@@ -417,16 +417,13 @@
     <t>突进冷却</t>
   </si>
   <si>
-    <t>500*1</t>
+    <t>200*1</t>
   </si>
   <si>
     <t>魔王自动拾取魔晶</t>
   </si>
   <si>
     <t>200800001</t>
-  </si>
-  <si>
-    <t>2000*1</t>
   </si>
   <si>
     <t>每次拾取魔晶+1</t>
@@ -3502,13 +3499,13 @@
         <v>136</v>
       </c>
       <c r="I42" s="50" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="J42" s="50">
         <v>200900001</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43">
@@ -3519,7 +3516,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
@@ -3543,7 +3540,7 @@
         <v>300100000</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44">
@@ -3554,13 +3551,13 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="50">
+        <v>1</v>
+      </c>
+      <c r="E44" s="50" t="s">
         <v>141</v>
-      </c>
-      <c r="D44" s="50">
-        <v>1</v>
-      </c>
-      <c r="E44" s="50" t="s">
-        <v>142</v>
       </c>
       <c r="F44" s="50" t="s">
         <v>80</v>
@@ -3578,7 +3575,7 @@
         <v>300100001</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45">
@@ -3589,13 +3586,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="50">
+        <v>1</v>
+      </c>
+      <c r="E45" s="50" t="s">
         <v>144</v>
-      </c>
-      <c r="D45" s="50">
-        <v>1</v>
-      </c>
-      <c r="E45" s="50" t="s">
-        <v>145</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>80</v>
@@ -3613,7 +3610,7 @@
         <v>300100002</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46">
@@ -3624,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" s="50">
+        <v>1</v>
+      </c>
+      <c r="E46" s="50" t="s">
         <v>147</v>
-      </c>
-      <c r="D46" s="50">
-        <v>1</v>
-      </c>
-      <c r="E46" s="50" t="s">
-        <v>148</v>
       </c>
       <c r="F46" s="50" t="s">
         <v>80</v>
@@ -3648,7 +3645,7 @@
         <v>300100003</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47">
@@ -3659,13 +3656,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" s="50">
+        <v>1</v>
+      </c>
+      <c r="E47" s="50" t="s">
         <v>150</v>
-      </c>
-      <c r="D47" s="50">
-        <v>1</v>
-      </c>
-      <c r="E47" s="50" t="s">
-        <v>151</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>80</v>
@@ -3683,7 +3680,7 @@
         <v>300100004</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48">
@@ -3694,7 +3691,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
@@ -3709,7 +3706,7 @@
         <v>300100101</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I48" s="50">
         <v>100</v>
@@ -3718,7 +3715,7 @@
         <v>300100101</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49">
@@ -3729,7 +3726,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
@@ -3753,7 +3750,7 @@
         <v>300100102</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50">
@@ -3764,13 +3761,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>100</v>
@@ -3779,7 +3776,7 @@
         <v>300100201</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I50" s="50">
         <v>100</v>
@@ -3788,7 +3785,7 @@
         <v>300100201</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51">
@@ -3799,7 +3796,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
@@ -3814,7 +3811,7 @@
         <v>300100301</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I51" s="50" t="s">
         <v>98</v>
@@ -3823,7 +3820,7 @@
         <v>300100301</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52">
@@ -3834,7 +3831,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
@@ -3855,7 +3852,7 @@
         <v>300200000</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53">
@@ -3866,16 +3863,16 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="F53" s="50" t="s">
         <v>166</v>
-      </c>
-      <c r="F53" s="50" t="s">
-        <v>167</v>
       </c>
       <c r="G53" s="50">
         <v>300200001</v>
@@ -3890,7 +3887,7 @@
         <v>300200001</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54">
@@ -3901,13 +3898,13 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F54" s="50" t="s">
         <v>80</v>
@@ -3919,13 +3916,13 @@
         <v>300200000</v>
       </c>
       <c r="I54" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J54" s="50">
         <v>300200002</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55">
@@ -3936,13 +3933,13 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F55" s="50" t="s">
         <v>80</v>
@@ -3960,7 +3957,7 @@
         <v>300200003</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56">
@@ -3971,13 +3968,13 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>80</v>
@@ -3995,7 +3992,7 @@
         <v>300200004</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57">
@@ -4006,7 +4003,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
@@ -4021,7 +4018,7 @@
         <v>300200101</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I57" s="50" t="s">
         <v>95</v>
@@ -4030,7 +4027,7 @@
         <v>300200101</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4041,7 +4038,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
@@ -4065,7 +4062,7 @@
         <v>300200102</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4076,7 +4073,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
@@ -4091,7 +4088,7 @@
         <v>300200201</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I59" s="50" t="s">
         <v>98</v>
@@ -4100,7 +4097,7 @@
         <v>300200201</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4111,7 +4108,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
@@ -4126,7 +4123,7 @@
         <v>300200301</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I60" s="50" t="s">
         <v>69</v>
@@ -4135,7 +4132,7 @@
         <v>300200301</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4146,7 +4143,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
@@ -4170,7 +4167,7 @@
         <v>300300000</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4181,13 +4178,13 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D62" s="50">
+        <v>1</v>
+      </c>
+      <c r="E62" s="50" t="s">
         <v>185</v>
-      </c>
-      <c r="D62" s="50">
-        <v>1</v>
-      </c>
-      <c r="E62" s="50" t="s">
-        <v>186</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>80</v>
@@ -4205,7 +4202,7 @@
         <v>300300001</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4216,13 +4213,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" s="50">
+        <v>1</v>
+      </c>
+      <c r="E63" s="50" t="s">
         <v>188</v>
-      </c>
-      <c r="D63" s="50">
-        <v>1</v>
-      </c>
-      <c r="E63" s="50" t="s">
-        <v>189</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>80</v>
@@ -4240,7 +4237,7 @@
         <v>300300002</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4251,16 +4248,16 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="F64" s="50" t="s">
         <v>191</v>
-      </c>
-      <c r="F64" s="50" t="s">
-        <v>192</v>
       </c>
       <c r="G64" s="50">
         <v>300300003</v>
@@ -4275,7 +4272,7 @@
         <v>300300003</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65">
@@ -4286,13 +4283,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" s="50">
+        <v>1</v>
+      </c>
+      <c r="E65" s="50" t="s">
         <v>194</v>
-      </c>
-      <c r="D65" s="50">
-        <v>1</v>
-      </c>
-      <c r="E65" s="50" t="s">
-        <v>195</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>80</v>
@@ -4310,7 +4307,7 @@
         <v>300300004</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66">
@@ -4321,7 +4318,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
@@ -4336,7 +4333,7 @@
         <v>300300101</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I66" s="50" t="s">
         <v>33</v>
@@ -4345,7 +4342,7 @@
         <v>300300101</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4356,7 +4353,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
@@ -4380,7 +4377,7 @@
         <v>300300102</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4391,13 +4388,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>100</v>
@@ -4406,7 +4403,7 @@
         <v>300300201</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I68" s="50" t="s">
         <v>98</v>
@@ -4415,7 +4412,7 @@
         <v>300300201</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4426,7 +4423,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
@@ -4441,7 +4438,7 @@
         <v>300300301</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I69" s="50" t="s">
         <v>98</v>
@@ -4450,7 +4447,7 @@
         <v>300300301</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4461,13 +4458,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="D70" s="50">
+        <v>1</v>
+      </c>
+      <c r="E70" s="50" t="s">
         <v>205</v>
-      </c>
-      <c r="D70" s="50">
-        <v>1</v>
-      </c>
-      <c r="E70" s="50" t="s">
-        <v>206</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>67</v>
@@ -4485,7 +4482,7 @@
         <v>300400000</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4496,13 +4493,13 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>80</v>
@@ -4520,7 +4517,7 @@
         <v>300400001</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4531,13 +4528,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="D72" s="50">
+        <v>1</v>
+      </c>
+      <c r="E72" s="50" t="s">
         <v>210</v>
-      </c>
-      <c r="D72" s="50">
-        <v>1</v>
-      </c>
-      <c r="E72" s="50" t="s">
-        <v>211</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>80</v>
@@ -4555,7 +4552,7 @@
         <v>300400002</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4566,13 +4563,13 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>80</v>
@@ -4590,7 +4587,7 @@
         <v>300400003</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4601,13 +4598,13 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
+        <v>214</v>
+      </c>
+      <c r="D74" s="50">
+        <v>1</v>
+      </c>
+      <c r="E74" s="50" t="s">
         <v>215</v>
-      </c>
-      <c r="D74" s="50">
-        <v>1</v>
-      </c>
-      <c r="E74" s="50" t="s">
-        <v>216</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>80</v>
@@ -4625,7 +4622,7 @@
         <v>300400004</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75">
@@ -4636,13 +4633,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>80</v>
@@ -4660,7 +4657,7 @@
         <v>300400005</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="76">
@@ -4671,13 +4668,13 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>91</v>
@@ -4686,7 +4683,7 @@
         <v>300400101</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
@@ -4695,7 +4692,7 @@
         <v>300400101</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77">
@@ -4706,13 +4703,13 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F77" s="50" t="s">
         <v>94</v>
@@ -4730,7 +4727,7 @@
         <v>300400102</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4741,13 +4738,13 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>100</v>
@@ -4756,7 +4753,7 @@
         <v>300400201</v>
       </c>
       <c r="H78" s="50" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I78" s="50">
         <v>100</v>
@@ -4765,7 +4762,7 @@
         <v>300400201</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4776,13 +4773,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>100</v>
@@ -4791,7 +4788,7 @@
         <v>300400301</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I79" s="50">
         <v>100</v>
@@ -4800,7 +4797,7 @@
         <v>300400301</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4811,13 +4808,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="D80" s="50">
+        <v>1</v>
+      </c>
+      <c r="E80" s="50" t="s">
         <v>227</v>
-      </c>
-      <c r="D80" s="50">
-        <v>1</v>
-      </c>
-      <c r="E80" s="50" t="s">
-        <v>228</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>67</v>
@@ -4835,7 +4832,7 @@
         <v>300500000</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4846,13 +4843,13 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>80</v>
@@ -4870,7 +4867,7 @@
         <v>300500001</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4881,13 +4878,13 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>80</v>
@@ -4905,7 +4902,7 @@
         <v>300500002</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4916,13 +4913,13 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>80</v>
@@ -4940,7 +4937,7 @@
         <v>300500003</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84">
@@ -4951,13 +4948,13 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>80</v>
@@ -4975,7 +4972,7 @@
         <v>300500004</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85">
@@ -4986,13 +4983,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>91</v>
@@ -5001,7 +4998,7 @@
         <v>300500101</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
@@ -5010,7 +5007,7 @@
         <v>300500101</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86">
@@ -5021,13 +5018,13 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>94</v>
@@ -5045,7 +5042,7 @@
         <v>300500102</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87">
@@ -5056,13 +5053,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F87" s="50" t="s">
         <v>100</v>
@@ -5071,7 +5068,7 @@
         <v>300500201</v>
       </c>
       <c r="H87" s="50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I87" s="50">
         <v>100</v>
@@ -5080,7 +5077,7 @@
         <v>300500201</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="88">
@@ -5091,13 +5088,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>100</v>
@@ -5106,7 +5103,7 @@
         <v>300500301</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I88" s="50">
         <v>100</v>
@@ -5115,7 +5112,7 @@
         <v>300500301</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89">
@@ -5126,13 +5123,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="D89" s="50">
+        <v>1</v>
+      </c>
+      <c r="E89" s="50" t="s">
         <v>246</v>
-      </c>
-      <c r="D89" s="50">
-        <v>1</v>
-      </c>
-      <c r="E89" s="50" t="s">
-        <v>247</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>67</v>
@@ -5150,7 +5147,7 @@
         <v>300600000</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90">
@@ -5161,13 +5158,13 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="D90" s="50">
+        <v>1</v>
+      </c>
+      <c r="E90" s="50" t="s">
         <v>249</v>
-      </c>
-      <c r="D90" s="50">
-        <v>1</v>
-      </c>
-      <c r="E90" s="50" t="s">
-        <v>250</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>80</v>
@@ -5185,7 +5182,7 @@
         <v>300600001</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="91">
@@ -5196,13 +5193,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>80</v>
@@ -5220,7 +5217,7 @@
         <v>300600002</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="92">
@@ -5231,13 +5228,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>80</v>
@@ -5255,7 +5252,7 @@
         <v>300600003</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93">
@@ -5266,13 +5263,13 @@
         <v>3</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F93" s="50" t="s">
         <v>80</v>
@@ -5290,7 +5287,7 @@
         <v>300600004</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94">
@@ -5301,13 +5298,13 @@
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D94" s="50">
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F94" s="50" t="s">
         <v>80</v>
@@ -5325,7 +5322,7 @@
         <v>300600005</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="95">
@@ -5336,13 +5333,13 @@
         <v>3</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D95" s="50">
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F95" s="50" t="s">
         <v>91</v>
@@ -5351,7 +5348,7 @@
         <v>300600101</v>
       </c>
       <c r="H95" s="50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I95" s="50">
         <v>100</v>
@@ -5360,7 +5357,7 @@
         <v>300600101</v>
       </c>
       <c r="K95" s="50" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96">
@@ -5371,13 +5368,13 @@
         <v>3</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D96" s="50">
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F96" s="50" t="s">
         <v>94</v>
@@ -5395,7 +5392,7 @@
         <v>300600102</v>
       </c>
       <c r="K96" s="50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="97">
@@ -5406,13 +5403,13 @@
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D97" s="50">
         <v>1</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F97" s="50" t="s">
         <v>100</v>
@@ -5421,7 +5418,7 @@
         <v>300600201</v>
       </c>
       <c r="H97" s="50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I97" s="50">
         <v>100</v>
@@ -5430,7 +5427,7 @@
         <v>300600201</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="98">
@@ -5441,13 +5438,13 @@
         <v>3</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D98" s="50">
         <v>1</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F98" s="50" t="s">
         <v>100</v>
@@ -5456,7 +5453,7 @@
         <v>300600301</v>
       </c>
       <c r="H98" s="50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I98" s="50">
         <v>100</v>
@@ -5465,7 +5462,7 @@
         <v>300600301</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99">
@@ -5476,13 +5473,13 @@
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="D99" s="50">
+        <v>1</v>
+      </c>
+      <c r="E99" s="50" t="s">
         <v>266</v>
-      </c>
-      <c r="D99" s="50">
-        <v>1</v>
-      </c>
-      <c r="E99" s="50" t="s">
-        <v>267</v>
       </c>
       <c r="F99" s="50" t="s">
         <v>67</v>
@@ -5500,7 +5497,7 @@
         <v>300700000</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="100">
@@ -5511,13 +5508,13 @@
         <v>3</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D100" s="50">
         <v>1</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F100" s="50" t="s">
         <v>80</v>
@@ -5535,7 +5532,7 @@
         <v>300700001</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101">
@@ -5546,13 +5543,13 @@
         <v>3</v>
       </c>
       <c r="C101" s="50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D101" s="50">
         <v>1</v>
       </c>
       <c r="E101" s="50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F101" s="50" t="s">
         <v>80</v>
@@ -5570,7 +5567,7 @@
         <v>300700002</v>
       </c>
       <c r="K101" s="50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102">
@@ -5581,13 +5578,13 @@
         <v>3</v>
       </c>
       <c r="C102" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D102" s="50">
         <v>1</v>
       </c>
       <c r="E102" s="50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F102" s="50" t="s">
         <v>80</v>
@@ -5605,7 +5602,7 @@
         <v>300700003</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103">
@@ -5616,13 +5613,13 @@
         <v>3</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D103" s="50">
         <v>1</v>
       </c>
       <c r="E103" s="50" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F103" s="50" t="s">
         <v>80</v>
@@ -5640,7 +5637,7 @@
         <v>300700004</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="104">
@@ -5651,13 +5648,13 @@
         <v>3</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D104" s="50">
         <v>1</v>
       </c>
       <c r="E104" s="50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F104" s="50" t="s">
         <v>91</v>
@@ -5666,7 +5663,7 @@
         <v>300700101</v>
       </c>
       <c r="H104" s="50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I104" s="50">
         <v>100</v>
@@ -5675,7 +5672,7 @@
         <v>300700101</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="105">
@@ -5686,13 +5683,13 @@
         <v>3</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D105" s="50">
         <v>1</v>
       </c>
       <c r="E105" s="50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F105" s="50" t="s">
         <v>94</v>
@@ -5710,7 +5707,7 @@
         <v>300700102</v>
       </c>
       <c r="K105" s="50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="106">
@@ -5721,13 +5718,13 @@
         <v>3</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D106" s="50">
         <v>1</v>
       </c>
       <c r="E106" s="50" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F106" s="50" t="s">
         <v>100</v>
@@ -5736,7 +5733,7 @@
         <v>300700201</v>
       </c>
       <c r="H106" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I106" s="50">
         <v>100</v>
@@ -5745,7 +5742,7 @@
         <v>300700201</v>
       </c>
       <c r="K106" s="50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="107">
@@ -5756,13 +5753,13 @@
         <v>3</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D107" s="50">
         <v>1</v>
       </c>
       <c r="E107" s="50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F107" s="50" t="s">
         <v>100</v>
@@ -5771,7 +5768,7 @@
         <v>300700301</v>
       </c>
       <c r="H107" s="50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I107" s="50">
         <v>100</v>
@@ -5780,7 +5777,7 @@
         <v>300700301</v>
       </c>
       <c r="K107" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="108">
@@ -5791,7 +5788,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D108" s="50">
         <v>1</v>
@@ -5812,7 +5809,7 @@
         <v>100500001</v>
       </c>
       <c r="K108" s="50" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t>id</t>
   </si>
@@ -309,198 +309,192 @@
     <t>100400000</t>
   </si>
   <si>
+    <t>解锁孕育稀有度：R</t>
+  </si>
+  <si>
+    <t>-200</t>
+  </si>
+  <si>
+    <t>100*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：R 概率+1%</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>100401000,100401001,</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：SR</t>
+  </si>
+  <si>
+    <t>1000*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：SR 概率+1%</t>
+  </si>
+  <si>
+    <t>100402000,100402001,</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：SSR</t>
+  </si>
+  <si>
+    <t>10000*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：SSR 概率+1%</t>
+  </si>
+  <si>
+    <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000</t>
+  </si>
+  <si>
+    <t>阵容上限+1</t>
+  </si>
+  <si>
+    <t>ui_research_6</t>
+  </si>
+  <si>
+    <t>200000001</t>
+  </si>
+  <si>
+    <t>100,200,300,400,</t>
+  </si>
+  <si>
+    <t>解锁第二阵容</t>
+  </si>
+  <si>
+    <t>ui_research_60</t>
+  </si>
+  <si>
+    <t>100,500,1000,5000,10000,50000</t>
+  </si>
+  <si>
+    <t>魔晶掉落存在时长+5秒</t>
+  </si>
+  <si>
+    <t>ui_research_61</t>
+  </si>
+  <si>
+    <t>200400001</t>
+  </si>
+  <si>
+    <t>100,500,1000,5000,10000</t>
+  </si>
+  <si>
+    <t>魔王魔力上限+10</t>
+  </si>
+  <si>
+    <t>100,500,1000</t>
+  </si>
+  <si>
+    <t>魔王魔力恢复速度+1/s</t>
+  </si>
+  <si>
+    <t>ui_research_62</t>
+  </si>
+  <si>
+    <t>深渊馈赠刷新次数+1</t>
+  </si>
+  <si>
+    <t>100,1000,10000</t>
+  </si>
+  <si>
+    <t>空格突进</t>
+  </si>
+  <si>
+    <t>200600001</t>
+  </si>
+  <si>
+    <t>200,2000,20000,200000</t>
+  </si>
+  <si>
+    <t>突进冷却</t>
+  </si>
+  <si>
+    <t>200*1</t>
+  </si>
+  <si>
+    <t>魔王自动拾取魔晶</t>
+  </si>
+  <si>
+    <t>200800001</t>
+  </si>
+  <si>
+    <t>每次拾取魔晶+1</t>
+  </si>
+  <si>
+    <t>ui_research_36</t>
+  </si>
+  <si>
+    <t>解锁种族：人类</t>
+  </si>
+  <si>
+    <t>ui_research_43</t>
+  </si>
+  <si>
+    <t>解锁职业：人类战士</t>
+  </si>
+  <si>
+    <t>ui_research_42</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>解锁职业：人类弓箭手</t>
+  </si>
+  <si>
+    <t>ui_research_48</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>解锁职业：人类魔法师（火）</t>
+  </si>
+  <si>
+    <t>ui_research_47</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>解锁职业：人类魔法师（冰）</t>
+  </si>
+  <si>
+    <t>ui_research_33</t>
+  </si>
+  <si>
+    <t>300100001|300100002|300100003|300100004|</t>
+  </si>
+  <si>
+    <t>孕育人类x5</t>
+  </si>
+  <si>
+    <t>ui_research_34</t>
+  </si>
+  <si>
+    <t>孕育人类x10</t>
+  </si>
+  <si>
+    <t>100200001,300100000,</t>
+  </si>
+  <si>
+    <t>可转生为人类</t>
+  </si>
+  <si>
+    <t>ui_research_58</t>
+  </si>
+  <si>
+    <t>300100000,</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>解锁孕育稀有度：R</t>
-  </si>
-  <si>
-    <t>-200</t>
-  </si>
-  <si>
-    <t>100*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：R 概率+1%</t>
-  </si>
-  <si>
-    <t>800</t>
-  </si>
-  <si>
-    <t>100401000,100401001,</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：SR</t>
-  </si>
-  <si>
-    <t>1000*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：SR 概率+1%</t>
-  </si>
-  <si>
-    <t>100402000,100402001,</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：SSR</t>
-  </si>
-  <si>
-    <t>10000*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：SSR 概率+1%</t>
-  </si>
-  <si>
-    <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000</t>
-  </si>
-  <si>
-    <t>阵容上限+1</t>
-  </si>
-  <si>
-    <t>ui_research_6</t>
-  </si>
-  <si>
-    <t>200000001</t>
-  </si>
-  <si>
-    <t>100,200,300,400,</t>
-  </si>
-  <si>
-    <t>解锁第二阵容</t>
-  </si>
-  <si>
-    <t>ui_research_60</t>
-  </si>
-  <si>
-    <t>100,500,1000,5000,10000,50000</t>
-  </si>
-  <si>
-    <t>魔晶掉落存在时长+5秒</t>
-  </si>
-  <si>
-    <t>ui_research_61</t>
-  </si>
-  <si>
-    <t>200400001</t>
-  </si>
-  <si>
-    <t>100,500,1000,5000,10000</t>
-  </si>
-  <si>
-    <t>魔王魔力上限+10</t>
-  </si>
-  <si>
-    <t>100,500,1000</t>
-  </si>
-  <si>
-    <t>魔王魔力恢复速度+1/s</t>
-  </si>
-  <si>
-    <t>ui_research_62</t>
-  </si>
-  <si>
-    <t>深渊馈赠刷新次数+1</t>
-  </si>
-  <si>
-    <t>100,1000,10000</t>
-  </si>
-  <si>
-    <t>空格突进</t>
-  </si>
-  <si>
-    <t>200600001</t>
-  </si>
-  <si>
-    <t>200,2000,20000,200000</t>
-  </si>
-  <si>
-    <t>突进冷却</t>
-  </si>
-  <si>
-    <t>200*1</t>
-  </si>
-  <si>
-    <t>魔王自动拾取魔晶</t>
-  </si>
-  <si>
-    <t>200800001</t>
-  </si>
-  <si>
-    <t>每次拾取魔晶+1</t>
-  </si>
-  <si>
-    <t>ui_research_36</t>
-  </si>
-  <si>
-    <t>解锁种族：人类</t>
-  </si>
-  <si>
-    <t>ui_research_43</t>
-  </si>
-  <si>
-    <t>575</t>
-  </si>
-  <si>
-    <t>解锁职业：人类战士</t>
-  </si>
-  <si>
-    <t>ui_research_42</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>解锁职业：人类弓箭手</t>
-  </si>
-  <si>
-    <t>ui_research_48</t>
-  </si>
-  <si>
-    <t>875</t>
-  </si>
-  <si>
-    <t>解锁职业：人类魔法师（火）</t>
-  </si>
-  <si>
-    <t>ui_research_47</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>解锁职业：人类魔法师（冰）</t>
-  </si>
-  <si>
-    <t>ui_research_33</t>
-  </si>
-  <si>
-    <t>300100001|300100002|300100003|300100004|</t>
-  </si>
-  <si>
-    <t>孕育人类x5</t>
-  </si>
-  <si>
-    <t>ui_research_34</t>
-  </si>
-  <si>
-    <t>孕育人类x10</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>100200001,300100000,</t>
-  </si>
-  <si>
-    <t>可转生为人类</t>
-  </si>
-  <si>
-    <t>ui_research_58</t>
-  </si>
-  <si>
-    <t>300100000,</t>
-  </si>
-  <si>
     <t>奖励-可获取人类装备</t>
   </si>
   <si>
@@ -510,33 +504,18 @@
     <t>解锁种族：骷髅</t>
   </si>
   <si>
-    <t>-223</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
     <t>解锁职业：骷髅战士</t>
   </si>
   <si>
-    <t>-75</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
     <t>解锁职业：骷髅投手</t>
   </si>
   <si>
-    <t>75</t>
-  </si>
-  <si>
     <t>解锁职业：骷髅魔法师（火）</t>
   </si>
   <si>
-    <t>225</t>
-  </si>
-  <si>
     <t>解锁职业：骷髅魔法师（冰）</t>
   </si>
   <si>
@@ -570,7 +549,7 @@
     <t>ui_research_51</t>
   </si>
   <si>
-    <t>-1025</t>
+    <t>-1100</t>
   </si>
   <si>
     <t>解锁职业：守护史莱姆</t>
@@ -579,13 +558,13 @@
     <t>ui_research_54</t>
   </si>
   <si>
-    <t>-875</t>
+    <t>-950</t>
   </si>
   <si>
     <t>解锁职业：自爆史莱姆</t>
   </si>
   <si>
-    <t>-725</t>
+    <t>-650</t>
   </si>
   <si>
     <t>201</t>
@@ -597,9 +576,6 @@
     <t>ui_research_53</t>
   </si>
   <si>
-    <t>-575</t>
-  </si>
-  <si>
     <t>解锁职业：毒液史莱姆</t>
   </si>
   <si>
@@ -610,9 +586,6 @@
   </si>
   <si>
     <t>孕育史莱姆x10</t>
-  </si>
-  <si>
-    <t>-650</t>
   </si>
   <si>
     <t>100200001,300300000,</t>
@@ -2977,13 +2950,13 @@
         <v>97</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="J27" s="50">
         <v>100401000</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
@@ -3000,7 +2973,7 @@
         <v>50</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F28" s="50" t="s">
         <v>94</v>
@@ -3012,13 +2985,13 @@
         <v>100401000</v>
       </c>
       <c r="I28" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J28" s="50">
         <v>100401001</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
@@ -3038,13 +3011,13 @@
         <v>67</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G29" s="50">
         <v>100402000</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I29" s="50">
         <v>1000</v>
@@ -3053,7 +3026,7 @@
         <v>100402000</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30">
@@ -3070,10 +3043,10 @@
         <v>50</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G30" s="50">
         <v>100402001</v>
@@ -3082,13 +3055,13 @@
         <v>100402000</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J30" s="50">
         <v>100402001</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
@@ -3114,7 +3087,7 @@
         <v>100403000</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I31" s="50">
         <v>10000</v>
@@ -3123,7 +3096,7 @@
         <v>100403000</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
@@ -3140,7 +3113,7 @@
         <v>50</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>57</v>
@@ -3152,13 +3125,13 @@
         <v>100403000</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J32" s="50">
         <v>100403001</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33">
@@ -3184,13 +3157,13 @@
         <v>200000001</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J33" s="50">
         <v>200000001</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34">
@@ -3201,13 +3174,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D34" s="50">
         <v>4</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F34" s="50" t="s">
         <v>67</v>
@@ -3216,16 +3189,16 @@
         <v>200100001</v>
       </c>
       <c r="H34" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="I34" s="50" t="s">
         <v>115</v>
-      </c>
-      <c r="I34" s="50" t="s">
-        <v>116</v>
       </c>
       <c r="J34" s="50">
         <v>200100001</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35">
@@ -3236,7 +3209,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D35" s="50">
         <v>6</v>
@@ -3251,16 +3224,16 @@
         <v>200200001</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J35" s="50">
         <v>200200001</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
@@ -3271,7 +3244,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D36" s="50">
         <v>5</v>
@@ -3286,16 +3259,16 @@
         <v>200300001</v>
       </c>
       <c r="H36" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="I36" s="50" t="s">
         <v>122</v>
-      </c>
-      <c r="I36" s="50" t="s">
-        <v>123</v>
       </c>
       <c r="J36" s="50">
         <v>200300001</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37">
@@ -3306,7 +3279,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D37" s="50">
         <v>3</v>
@@ -3321,16 +3294,16 @@
         <v>200400001</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J37" s="50">
         <v>200400001</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
@@ -3341,7 +3314,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D38" s="50">
         <v>5</v>
@@ -3356,16 +3329,16 @@
         <v>200500001</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I38" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J38" s="50">
         <v>200500001</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39">
@@ -3376,13 +3349,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D39" s="50">
         <v>3</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F39" s="50" t="s">
         <v>80</v>
@@ -3391,16 +3364,16 @@
         <v>200600001</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J39" s="50">
         <v>200600001</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40">
@@ -3411,7 +3384,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D40" s="50">
         <v>4</v>
@@ -3426,16 +3399,16 @@
         <v>200700001</v>
       </c>
       <c r="H40" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="I40" s="50" t="s">
         <v>131</v>
-      </c>
-      <c r="I40" s="50" t="s">
-        <v>132</v>
       </c>
       <c r="J40" s="50">
         <v>200700001</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41">
@@ -3446,7 +3419,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D41" s="50">
         <v>10</v>
@@ -3461,16 +3434,16 @@
         <v>200800001</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I41" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J41" s="50">
         <v>200800001</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42">
@@ -3481,7 +3454,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D42" s="50">
         <v>5</v>
@@ -3496,16 +3469,16 @@
         <v>200900001</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I42" s="50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J42" s="50">
         <v>200900001</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43">
@@ -3516,13 +3489,13 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F43" s="50" t="s">
         <v>67</v>
@@ -3540,7 +3513,7 @@
         <v>300100000</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44">
@@ -3551,13 +3524,13 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="F44" s="50" t="s">
         <v>80</v>
@@ -3575,7 +3548,7 @@
         <v>300100001</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45">
@@ -3586,13 +3559,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>80</v>
@@ -3610,7 +3583,7 @@
         <v>300100002</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46">
@@ -3621,13 +3594,13 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F46" s="50" t="s">
         <v>80</v>
@@ -3645,7 +3618,7 @@
         <v>300100003</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47">
@@ -3656,13 +3629,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>80</v>
@@ -3680,7 +3653,7 @@
         <v>300100004</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48">
@@ -3691,13 +3664,13 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F48" s="50" t="s">
         <v>91</v>
@@ -3706,7 +3679,7 @@
         <v>300100101</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I48" s="50">
         <v>100</v>
@@ -3715,7 +3688,7 @@
         <v>300100101</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49">
@@ -3726,13 +3699,13 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F49" s="50" t="s">
         <v>94</v>
@@ -3750,7 +3723,7 @@
         <v>300100102</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50">
@@ -3761,22 +3734,22 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="F50" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G50" s="50">
         <v>300100201</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I50" s="50">
         <v>100</v>
@@ -3785,7 +3758,7 @@
         <v>300100201</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51">
@@ -3796,31 +3769,31 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G51" s="50">
         <v>300100301</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="J51" s="50">
         <v>300100301</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52">
@@ -3831,7 +3804,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
@@ -3852,7 +3825,7 @@
         <v>300200000</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53">
@@ -3863,16 +3836,16 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="G53" s="50">
         <v>300200001</v>
@@ -3887,7 +3860,7 @@
         <v>300200001</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54">
@@ -3898,13 +3871,13 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="F54" s="50" t="s">
         <v>80</v>
@@ -3916,13 +3889,13 @@
         <v>300200000</v>
       </c>
       <c r="I54" s="50" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J54" s="50">
         <v>300200002</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55">
@@ -3933,13 +3906,13 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="F55" s="50" t="s">
         <v>80</v>
@@ -3957,7 +3930,7 @@
         <v>300200003</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56">
@@ -3968,13 +3941,13 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>173</v>
+        <v>28</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>80</v>
@@ -3992,7 +3965,7 @@
         <v>300200004</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57">
@@ -4003,7 +3976,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
@@ -4018,7 +3991,7 @@
         <v>300200101</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="I57" s="50" t="s">
         <v>95</v>
@@ -4027,7 +4000,7 @@
         <v>300200101</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4038,7 +4011,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
@@ -4062,7 +4035,7 @@
         <v>300200102</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4073,7 +4046,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
@@ -4082,22 +4055,22 @@
         <v>77</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G59" s="50">
         <v>300200201</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I59" s="50" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="J59" s="50">
         <v>300200201</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4108,7 +4081,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
@@ -4117,13 +4090,13 @@
         <v>67</v>
       </c>
       <c r="F60" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G60" s="50">
         <v>300200301</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I60" s="50" t="s">
         <v>69</v>
@@ -4132,7 +4105,7 @@
         <v>300200301</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4143,7 +4116,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
@@ -4161,13 +4134,13 @@
         <v>300200000</v>
       </c>
       <c r="I61" s="50" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="J61" s="50">
         <v>300300000</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4178,13 +4151,13 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>80</v>
@@ -4202,7 +4175,7 @@
         <v>300300001</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4213,13 +4186,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>80</v>
@@ -4231,13 +4204,13 @@
         <v>300300000</v>
       </c>
       <c r="I63" s="50" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="J63" s="50">
         <v>300300002</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4248,16 +4221,16 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G64" s="50">
         <v>300300003</v>
@@ -4272,7 +4245,7 @@
         <v>300300003</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="65">
@@ -4283,13 +4256,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>194</v>
+        <v>32</v>
       </c>
       <c r="F65" s="50" t="s">
         <v>80</v>
@@ -4307,7 +4280,7 @@
         <v>300300004</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66">
@@ -4318,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
@@ -4333,7 +4306,7 @@
         <v>300300101</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I66" s="50" t="s">
         <v>33</v>
@@ -4342,7 +4315,7 @@
         <v>300300101</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4353,7 +4326,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
@@ -4377,7 +4350,7 @@
         <v>300300102</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4388,31 +4361,31 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="F68" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G68" s="50">
         <v>300300201</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I68" s="50" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="J68" s="50">
         <v>300300201</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4423,7 +4396,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
@@ -4432,22 +4405,22 @@
         <v>71</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G69" s="50">
         <v>300300301</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="I69" s="50" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="J69" s="50">
         <v>300300301</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4458,13 +4431,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>67</v>
@@ -4482,7 +4455,7 @@
         <v>300400000</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4493,13 +4466,13 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>80</v>
@@ -4517,7 +4490,7 @@
         <v>300400001</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4528,13 +4501,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>80</v>
@@ -4552,7 +4525,7 @@
         <v>300400002</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4563,13 +4536,13 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>80</v>
@@ -4587,7 +4560,7 @@
         <v>300400003</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4598,13 +4571,13 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>80</v>
@@ -4622,7 +4595,7 @@
         <v>300400004</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75">
@@ -4633,13 +4606,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>80</v>
@@ -4657,7 +4630,7 @@
         <v>300400005</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76">
@@ -4668,13 +4641,13 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>91</v>
@@ -4683,7 +4656,7 @@
         <v>300400101</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
@@ -4692,7 +4665,7 @@
         <v>300400101</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77">
@@ -4703,13 +4676,13 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F77" s="50" t="s">
         <v>94</v>
@@ -4727,7 +4700,7 @@
         <v>300400102</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4738,22 +4711,22 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G78" s="50">
         <v>300400201</v>
       </c>
       <c r="H78" s="50" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="I78" s="50">
         <v>100</v>
@@ -4762,7 +4735,7 @@
         <v>300400201</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4773,22 +4746,22 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F79" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G79" s="50">
         <v>300400301</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="I79" s="50">
         <v>100</v>
@@ -4797,7 +4770,7 @@
         <v>300400301</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4808,13 +4781,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>67</v>
@@ -4832,7 +4805,7 @@
         <v>300500000</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4843,13 +4816,13 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>80</v>
@@ -4867,7 +4840,7 @@
         <v>300500001</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4878,13 +4851,13 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>80</v>
@@ -4902,7 +4875,7 @@
         <v>300500002</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4913,13 +4886,13 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>80</v>
@@ -4937,7 +4910,7 @@
         <v>300500003</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
     </row>
     <row r="84">
@@ -4948,13 +4921,13 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>80</v>
@@ -4972,7 +4945,7 @@
         <v>300500004</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
     </row>
     <row r="85">
@@ -4983,13 +4956,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>91</v>
@@ -4998,7 +4971,7 @@
         <v>300500101</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
@@ -5007,7 +4980,7 @@
         <v>300500101</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="86">
@@ -5018,13 +4991,13 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>94</v>
@@ -5042,7 +5015,7 @@
         <v>300500102</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87">
@@ -5053,22 +5026,22 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G87" s="50">
         <v>300500201</v>
       </c>
       <c r="H87" s="50" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="I87" s="50">
         <v>100</v>
@@ -5077,7 +5050,7 @@
         <v>300500201</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
     </row>
     <row r="88">
@@ -5088,22 +5061,22 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="F88" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G88" s="50">
         <v>300500301</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="I88" s="50">
         <v>100</v>
@@ -5112,7 +5085,7 @@
         <v>300500301</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
     </row>
     <row r="89">
@@ -5123,13 +5096,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>67</v>
@@ -5147,7 +5120,7 @@
         <v>300600000</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="90">
@@ -5158,13 +5131,13 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>80</v>
@@ -5182,7 +5155,7 @@
         <v>300600001</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="91">
@@ -5193,13 +5166,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>80</v>
@@ -5217,7 +5190,7 @@
         <v>300600002</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92">
@@ -5228,13 +5201,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>80</v>
@@ -5252,7 +5225,7 @@
         <v>300600003</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93">
@@ -5263,13 +5236,13 @@
         <v>3</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="F93" s="50" t="s">
         <v>80</v>
@@ -5287,7 +5260,7 @@
         <v>300600004</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
     </row>
     <row r="94">
@@ -5298,13 +5271,13 @@
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D94" s="50">
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="F94" s="50" t="s">
         <v>80</v>
@@ -5322,7 +5295,7 @@
         <v>300600005</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
     <row r="95">
@@ -5333,13 +5306,13 @@
         <v>3</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D95" s="50">
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="F95" s="50" t="s">
         <v>91</v>
@@ -5348,7 +5321,7 @@
         <v>300600101</v>
       </c>
       <c r="H95" s="50" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I95" s="50">
         <v>100</v>
@@ -5357,7 +5330,7 @@
         <v>300600101</v>
       </c>
       <c r="K95" s="50" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
     </row>
     <row r="96">
@@ -5368,13 +5341,13 @@
         <v>3</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D96" s="50">
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="F96" s="50" t="s">
         <v>94</v>
@@ -5392,7 +5365,7 @@
         <v>300600102</v>
       </c>
       <c r="K96" s="50" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
     </row>
     <row r="97">
@@ -5403,22 +5376,22 @@
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="D97" s="50">
+        <v>1</v>
+      </c>
+      <c r="E97" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="D97" s="50">
-        <v>1</v>
-      </c>
-      <c r="E97" s="50" t="s">
-        <v>254</v>
-      </c>
       <c r="F97" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G97" s="50">
         <v>300600201</v>
       </c>
       <c r="H97" s="50" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="I97" s="50">
         <v>100</v>
@@ -5427,7 +5400,7 @@
         <v>300600201</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="98">
@@ -5438,22 +5411,22 @@
         <v>3</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D98" s="50">
         <v>1</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="F98" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G98" s="50">
         <v>300600301</v>
       </c>
       <c r="H98" s="50" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="I98" s="50">
         <v>100</v>
@@ -5462,7 +5435,7 @@
         <v>300600301</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="99">
@@ -5473,13 +5446,13 @@
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D99" s="50">
         <v>1</v>
       </c>
       <c r="E99" s="50" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F99" s="50" t="s">
         <v>67</v>
@@ -5497,7 +5470,7 @@
         <v>300700000</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
     </row>
     <row r="100">
@@ -5508,13 +5481,13 @@
         <v>3</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D100" s="50">
         <v>1</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="F100" s="50" t="s">
         <v>80</v>
@@ -5532,7 +5505,7 @@
         <v>300700001</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="101">
@@ -5543,13 +5516,13 @@
         <v>3</v>
       </c>
       <c r="C101" s="50" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D101" s="50">
         <v>1</v>
       </c>
       <c r="E101" s="50" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F101" s="50" t="s">
         <v>80</v>
@@ -5567,7 +5540,7 @@
         <v>300700002</v>
       </c>
       <c r="K101" s="50" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
     </row>
     <row r="102">
@@ -5578,13 +5551,13 @@
         <v>3</v>
       </c>
       <c r="C102" s="50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D102" s="50">
         <v>1</v>
       </c>
       <c r="E102" s="50" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F102" s="50" t="s">
         <v>80</v>
@@ -5602,7 +5575,7 @@
         <v>300700003</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103">
@@ -5613,13 +5586,13 @@
         <v>3</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D103" s="50">
         <v>1</v>
       </c>
       <c r="E103" s="50" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F103" s="50" t="s">
         <v>80</v>
@@ -5637,7 +5610,7 @@
         <v>300700004</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104">
@@ -5648,13 +5621,13 @@
         <v>3</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D104" s="50">
         <v>1</v>
       </c>
       <c r="E104" s="50" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F104" s="50" t="s">
         <v>91</v>
@@ -5663,7 +5636,7 @@
         <v>300700101</v>
       </c>
       <c r="H104" s="50" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="I104" s="50">
         <v>100</v>
@@ -5672,7 +5645,7 @@
         <v>300700101</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="105">
@@ -5683,13 +5656,13 @@
         <v>3</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D105" s="50">
         <v>1</v>
       </c>
       <c r="E105" s="50" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F105" s="50" t="s">
         <v>94</v>
@@ -5707,7 +5680,7 @@
         <v>300700102</v>
       </c>
       <c r="K105" s="50" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
     </row>
     <row r="106">
@@ -5718,22 +5691,22 @@
         <v>3</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D106" s="50">
         <v>1</v>
       </c>
       <c r="E106" s="50" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="F106" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G106" s="50">
         <v>300700201</v>
       </c>
       <c r="H106" s="50" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="I106" s="50">
         <v>100</v>
@@ -5742,7 +5715,7 @@
         <v>300700201</v>
       </c>
       <c r="K106" s="50" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107">
@@ -5753,22 +5726,22 @@
         <v>3</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D107" s="50">
         <v>1</v>
       </c>
       <c r="E107" s="50" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F107" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G107" s="50">
         <v>300700301</v>
       </c>
       <c r="H107" s="50" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="I107" s="50">
         <v>100</v>
@@ -5777,7 +5750,7 @@
         <v>300700301</v>
       </c>
       <c r="K107" s="50" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="108">
@@ -5788,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D108" s="50">
         <v>1</v>
@@ -5809,7 +5782,7 @@
         <v>100500001</v>
       </c>
       <c r="K108" s="50" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
   <si>
     <t>id</t>
   </si>
@@ -267,9 +267,6 @@
     <t>ui_research_11</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>100,400,800,1600,3200,6400,12800,25600,51200,</t>
   </si>
   <si>
@@ -346,6 +343,12 @@
   </si>
   <si>
     <t>孕育稀有度：SSR 概率+1%</t>
+  </si>
+  <si>
+    <t>-6</t>
+  </si>
+  <si>
+    <t>开启魔汁机</t>
   </si>
   <si>
     <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000</t>
@@ -1997,7 +2000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1" style="51"/>
@@ -2806,17 +2809,15 @@
       <c r="G23" s="50">
         <v>100310112</v>
       </c>
-      <c r="H23" s="50" t="s">
+      <c r="H23" s="50"/>
+      <c r="I23" s="50" t="s">
         <v>84</v>
-      </c>
-      <c r="I23" s="50" t="s">
-        <v>85</v>
       </c>
       <c r="J23" s="50">
         <v>100310112</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
@@ -2827,7 +2828,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D24" s="50">
         <v>1</v>
@@ -2842,7 +2843,7 @@
         <v>100310130</v>
       </c>
       <c r="H24" s="50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I24" s="50" t="s">
         <v>80</v>
@@ -2851,7 +2852,7 @@
         <v>100310130</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
@@ -2862,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D25" s="50">
         <v>1</v>
@@ -2871,7 +2872,7 @@
         <v>67</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G25" s="50">
         <v>100400000</v>
@@ -2880,13 +2881,13 @@
         <v>46</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J25" s="50">
         <v>100400000</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26">
@@ -2897,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D26" s="50">
         <v>1</v>
@@ -2906,7 +2907,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G26" s="50">
         <v>100400001</v>
@@ -2915,13 +2916,13 @@
         <v>100400000</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J26" s="50">
         <v>100400001</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27">
@@ -2932,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D27" s="50">
         <v>1</v>
@@ -2941,13 +2942,13 @@
         <v>67</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G27" s="50">
         <v>100401000</v>
       </c>
       <c r="H27" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I27" s="50" t="s">
         <v>80</v>
@@ -2956,7 +2957,7 @@
         <v>100401000</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -2967,16 +2968,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D28" s="50">
         <v>50</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G28" s="50">
         <v>100401001</v>
@@ -2985,13 +2986,13 @@
         <v>100401000</v>
       </c>
       <c r="I28" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J28" s="50">
         <v>100401001</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -3002,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" s="50">
         <v>1</v>
@@ -3011,13 +3012,13 @@
         <v>67</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G29" s="50">
         <v>100402000</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I29" s="50">
         <v>1000</v>
@@ -3026,7 +3027,7 @@
         <v>100402000</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30">
@@ -3037,16 +3038,16 @@
         <v>1</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D30" s="50">
         <v>50</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G30" s="50">
         <v>100402001</v>
@@ -3055,13 +3056,13 @@
         <v>100402000</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J30" s="50">
         <v>100402001</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31">
@@ -3072,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" s="50">
         <v>1</v>
@@ -3087,7 +3088,7 @@
         <v>100403000</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I31" s="50">
         <v>10000</v>
@@ -3096,7 +3097,7 @@
         <v>100403000</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32">
@@ -3107,13 +3108,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" s="50">
         <v>50</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>57</v>
@@ -3125,453 +3126,453 @@
         <v>100403000</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J32" s="50">
         <v>100403001</v>
       </c>
       <c r="K32" s="50" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="51">
+        <v>100600001</v>
+      </c>
+      <c r="B33" s="51">
+        <v>1</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="51">
+        <v>1</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" s="51" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="50">
-        <v>200000001</v>
-      </c>
-      <c r="B33" s="50">
-        <v>2</v>
-      </c>
-      <c r="C33" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="50">
-        <v>30</v>
-      </c>
-      <c r="E33" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F33" s="50">
-        <v>0</v>
-      </c>
-      <c r="G33" s="50">
-        <v>200000001</v>
-      </c>
-      <c r="I33" s="50" t="s">
+      <c r="G33" s="51">
+        <v>100600001</v>
+      </c>
+      <c r="H33" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="I33" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="J33" s="51">
+        <v>100600001</v>
+      </c>
+      <c r="K33" s="51" t="s">
         <v>111</v>
-      </c>
-      <c r="J33" s="50">
-        <v>200000001</v>
-      </c>
-      <c r="K33" s="50" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="50">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="B34" s="50">
         <v>2</v>
       </c>
       <c r="C34" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="50">
+        <v>30</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="50">
+        <v>0</v>
+      </c>
+      <c r="G34" s="50">
+        <v>200000001</v>
+      </c>
+      <c r="I34" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="J34" s="50">
+        <v>200000001</v>
+      </c>
+      <c r="K34" s="50" t="s">
         <v>113</v>
-      </c>
-      <c r="D34" s="50">
-        <v>4</v>
-      </c>
-      <c r="E34" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" s="50">
-        <v>200100001</v>
-      </c>
-      <c r="H34" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="I34" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="J34" s="50">
-        <v>200100001</v>
-      </c>
-      <c r="K34" s="50" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="50">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="B35" s="50">
         <v>2</v>
       </c>
       <c r="C35" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="50">
+        <v>4</v>
+      </c>
+      <c r="E35" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="G35" s="50">
+        <v>200100001</v>
+      </c>
+      <c r="H35" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="I35" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="J35" s="50">
+        <v>200100001</v>
+      </c>
+      <c r="K35" s="50" t="s">
         <v>117</v>
-      </c>
-      <c r="D35" s="50">
-        <v>6</v>
-      </c>
-      <c r="E35" s="50">
-        <v>-200</v>
-      </c>
-      <c r="F35" s="50">
-        <v>-200</v>
-      </c>
-      <c r="G35" s="50">
-        <v>200200001</v>
-      </c>
-      <c r="H35" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="I35" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="J35" s="50">
-        <v>200200001</v>
-      </c>
-      <c r="K35" s="50" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="50">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B36" s="50">
         <v>2</v>
       </c>
       <c r="C36" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="50">
+        <v>6</v>
+      </c>
+      <c r="E36" s="50">
+        <v>-200</v>
+      </c>
+      <c r="F36" s="50">
+        <v>-200</v>
+      </c>
+      <c r="G36" s="50">
+        <v>200200001</v>
+      </c>
+      <c r="H36" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="I36" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="J36" s="50">
+        <v>200200001</v>
+      </c>
+      <c r="K36" s="50" t="s">
         <v>120</v>
-      </c>
-      <c r="D36" s="50">
-        <v>5</v>
-      </c>
-      <c r="E36" s="50">
-        <v>0</v>
-      </c>
-      <c r="F36" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="G36" s="50">
-        <v>200300001</v>
-      </c>
-      <c r="H36" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="I36" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J36" s="50">
-        <v>200300001</v>
-      </c>
-      <c r="K36" s="50" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="50">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B37" s="50">
         <v>2</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D37" s="50">
-        <v>3</v>
-      </c>
-      <c r="E37" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="50">
-        <v>-200</v>
+        <v>5</v>
+      </c>
+      <c r="E37" s="50">
+        <v>0</v>
+      </c>
+      <c r="F37" s="50" t="s">
+        <v>68</v>
       </c>
       <c r="G37" s="50">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="I37" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="J37" s="50">
+        <v>200300001</v>
+      </c>
+      <c r="K37" s="50" t="s">
         <v>124</v>
-      </c>
-      <c r="J37" s="50">
-        <v>200400001</v>
-      </c>
-      <c r="K37" s="50" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="50">
-        <v>200500001</v>
+        <v>200400001</v>
       </c>
       <c r="B38" s="50">
         <v>2</v>
       </c>
       <c r="C38" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" s="50">
+        <v>3</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38" s="50">
+        <v>-200</v>
+      </c>
+      <c r="G38" s="50">
+        <v>200400001</v>
+      </c>
+      <c r="H38" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="I38" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="J38" s="50">
+        <v>200400001</v>
+      </c>
+      <c r="K38" s="50" t="s">
         <v>126</v>
-      </c>
-      <c r="D38" s="50">
-        <v>5</v>
-      </c>
-      <c r="E38" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="F38" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="G38" s="50">
-        <v>200500001</v>
-      </c>
-      <c r="H38" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="I38" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J38" s="50">
-        <v>200500001</v>
-      </c>
-      <c r="K38" s="50" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50">
-        <v>200600001</v>
+        <v>200500001</v>
       </c>
       <c r="B39" s="50">
         <v>2</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D39" s="50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G39" s="50">
-        <v>200600001</v>
+        <v>200500001</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I39" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="J39" s="50">
+        <v>200500001</v>
+      </c>
+      <c r="K39" s="50" t="s">
         <v>128</v>
-      </c>
-      <c r="J39" s="50">
-        <v>200600001</v>
-      </c>
-      <c r="K39" s="50" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="50">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="B40" s="50">
         <v>2</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D40" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="F40" s="50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G40" s="50">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="H40" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="I40" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="J40" s="50">
+        <v>200600001</v>
+      </c>
+      <c r="K40" s="50" t="s">
         <v>130</v>
-      </c>
-      <c r="I40" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="J40" s="50">
-        <v>200700001</v>
-      </c>
-      <c r="K40" s="50" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="50">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="B41" s="50">
         <v>2</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D41" s="50">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41" s="50" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G41" s="50">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="I41" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="J41" s="50">
+        <v>200700001</v>
+      </c>
+      <c r="K41" s="50" t="s">
         <v>133</v>
-      </c>
-      <c r="J41" s="50">
-        <v>200800001</v>
-      </c>
-      <c r="K41" s="50" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="50">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="B42" s="50">
         <v>2</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D42" s="50">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E42" s="50" t="s">
         <v>67</v>
       </c>
       <c r="F42" s="50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G42" s="50">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="H42" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="J42" s="50">
+        <v>200800001</v>
+      </c>
+      <c r="K42" s="50" t="s">
         <v>135</v>
-      </c>
-      <c r="I42" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="J42" s="50">
-        <v>200900001</v>
-      </c>
-      <c r="K42" s="50" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="50">
-        <v>300100000</v>
+        <v>200900001</v>
       </c>
       <c r="B43" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="50">
+        <v>5</v>
+      </c>
+      <c r="E43" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G43" s="50">
+        <v>200900001</v>
+      </c>
+      <c r="H43" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I43" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="J43" s="50">
+        <v>200900001</v>
+      </c>
+      <c r="K43" s="50" t="s">
         <v>137</v>
-      </c>
-      <c r="D43" s="50">
-        <v>1</v>
-      </c>
-      <c r="E43" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="F43" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="G43" s="50">
-        <v>300100000</v>
-      </c>
-      <c r="H43" s="50">
-        <v>300200000</v>
-      </c>
-      <c r="I43" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="J43" s="50">
-        <v>300100000</v>
-      </c>
-      <c r="K43" s="50" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="50">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="B44" s="50">
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="D44" s="50">
+        <v>1</v>
+      </c>
+      <c r="E44" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="G44" s="50">
+        <v>300100000</v>
+      </c>
+      <c r="H44" s="50">
+        <v>300200000</v>
+      </c>
+      <c r="I44" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="J44" s="50">
+        <v>300100000</v>
+      </c>
+      <c r="K44" s="50" t="s">
         <v>139</v>
-      </c>
-      <c r="D44" s="50">
-        <v>1</v>
-      </c>
-      <c r="E44" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="F44" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="G44" s="50">
-        <v>300100001</v>
-      </c>
-      <c r="H44" s="50">
-        <v>300100000</v>
-      </c>
-      <c r="I44" s="50">
-        <v>100</v>
-      </c>
-      <c r="J44" s="50">
-        <v>300100001</v>
-      </c>
-      <c r="K44" s="50" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="50">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="B45" s="50">
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G45" s="50">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="H45" s="50">
         <v>300100000</v>
@@ -3580,33 +3581,33 @@
         <v>100</v>
       </c>
       <c r="J45" s="50">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="50">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="B46" s="50">
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F46" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G46" s="50">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="H46" s="50">
         <v>300100000</v>
@@ -3615,33 +3616,33 @@
         <v>100</v>
       </c>
       <c r="J46" s="50">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="50">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="B47" s="50">
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G47" s="50">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="H47" s="50">
         <v>300100000</v>
@@ -3650,214 +3651,214 @@
         <v>100</v>
       </c>
       <c r="J47" s="50">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="50">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="B48" s="50">
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="F48" s="50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G48" s="50">
-        <v>300100101</v>
-      </c>
-      <c r="H48" s="50" t="s">
-        <v>151</v>
+        <v>300100004</v>
+      </c>
+      <c r="H48" s="50">
+        <v>300100000</v>
       </c>
       <c r="I48" s="50">
         <v>100</v>
       </c>
       <c r="J48" s="50">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="50">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="B49" s="50">
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G49" s="50">
-        <v>300100102</v>
-      </c>
-      <c r="H49" s="50">
         <v>300100101</v>
+      </c>
+      <c r="H49" s="50" t="s">
+        <v>152</v>
       </c>
       <c r="I49" s="50">
         <v>100</v>
       </c>
       <c r="J49" s="50">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="50">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="B50" s="50">
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="F50" s="50" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G50" s="50">
-        <v>300100201</v>
-      </c>
-      <c r="H50" s="50" t="s">
-        <v>155</v>
+        <v>300100102</v>
+      </c>
+      <c r="H50" s="50">
+        <v>300100101</v>
       </c>
       <c r="I50" s="50">
         <v>100</v>
       </c>
       <c r="J50" s="50">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="50">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="B51" s="50">
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" s="50">
+        <v>1</v>
+      </c>
+      <c r="E51" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="F51" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G51" s="50">
+        <v>300100201</v>
+      </c>
+      <c r="H51" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="I51" s="50">
+        <v>100</v>
+      </c>
+      <c r="J51" s="50">
+        <v>300100201</v>
+      </c>
+      <c r="K51" s="50" t="s">
         <v>157</v>
-      </c>
-      <c r="D51" s="50">
-        <v>1</v>
-      </c>
-      <c r="E51" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="F51" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="50">
-        <v>300100301</v>
-      </c>
-      <c r="H51" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="I51" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="J51" s="50">
-        <v>300100301</v>
-      </c>
-      <c r="K51" s="50" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="50">
-        <v>300200000</v>
+        <v>300100301</v>
       </c>
       <c r="B52" s="50">
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D52" s="50">
+        <v>1</v>
+      </c>
+      <c r="E52" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="F52" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G52" s="50">
+        <v>300100301</v>
+      </c>
+      <c r="H52" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="I52" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="J52" s="50">
+        <v>300100301</v>
+      </c>
+      <c r="K52" s="50" t="s">
         <v>161</v>
-      </c>
-      <c r="D52" s="50">
-        <v>1</v>
-      </c>
-      <c r="E52" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F52" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="G52" s="50">
-        <v>300200000</v>
-      </c>
-      <c r="I52" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="J52" s="50">
-        <v>300200000</v>
-      </c>
-      <c r="K52" s="50" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="50">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B53" s="50">
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G53" s="50">
-        <v>300200001</v>
-      </c>
-      <c r="H53" s="50">
         <v>300200000</v>
       </c>
       <c r="I53" s="50" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J53" s="50">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="K53" s="50" t="s">
         <v>163</v>
@@ -3865,69 +3866,69 @@
     </row>
     <row r="54">
       <c r="A54" s="50">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B54" s="50">
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="F54" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G54" s="50">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="H54" s="50">
         <v>300200000</v>
       </c>
       <c r="I54" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="J54" s="50">
+        <v>300200001</v>
+      </c>
+      <c r="K54" s="50" t="s">
         <v>164</v>
-      </c>
-      <c r="J54" s="50">
-        <v>300200002</v>
-      </c>
-      <c r="K54" s="50" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="50">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B55" s="50">
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F55" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G55" s="50">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="H55" s="50">
         <v>300200000</v>
       </c>
       <c r="I55" s="50" t="s">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="J55" s="50">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="K55" s="50" t="s">
         <v>166</v>
@@ -3935,25 +3936,25 @@
     </row>
     <row r="56">
       <c r="A56" s="50">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B56" s="50">
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="F56" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G56" s="50">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="H56" s="50">
         <v>300200000</v>
@@ -3962,7 +3963,7 @@
         <v>33</v>
       </c>
       <c r="J56" s="50">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="K56" s="50" t="s">
         <v>167</v>
@@ -3970,48 +3971,48 @@
     </row>
     <row r="57">
       <c r="A57" s="50">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B57" s="50">
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G57" s="50">
-        <v>300200101</v>
-      </c>
-      <c r="H57" s="50" t="s">
+        <v>300200004</v>
+      </c>
+      <c r="H57" s="50">
+        <v>300200000</v>
+      </c>
+      <c r="I57" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="J57" s="50">
+        <v>300200004</v>
+      </c>
+      <c r="K57" s="50" t="s">
         <v>168</v>
-      </c>
-      <c r="I57" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="J57" s="50">
-        <v>300200101</v>
-      </c>
-      <c r="K57" s="50" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A58" s="50">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B58" s="50">
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
@@ -4020,19 +4021,19 @@
         <v>67</v>
       </c>
       <c r="F58" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G58" s="50">
+        <v>300200101</v>
+      </c>
+      <c r="H58" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="I58" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="G58" s="50">
-        <v>300200102</v>
-      </c>
-      <c r="H58" s="50">
+      <c r="J58" s="50">
         <v>300200101</v>
-      </c>
-      <c r="I58" s="50">
-        <v>100</v>
-      </c>
-      <c r="J58" s="50">
-        <v>300200102</v>
       </c>
       <c r="K58" s="50" t="s">
         <v>170</v>
@@ -4040,293 +4041,293 @@
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A59" s="50">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="B59" s="50">
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G59" s="50">
-        <v>300200201</v>
-      </c>
-      <c r="H59" s="50" t="s">
+        <v>300200102</v>
+      </c>
+      <c r="H59" s="50">
+        <v>300200101</v>
+      </c>
+      <c r="I59" s="50">
+        <v>100</v>
+      </c>
+      <c r="J59" s="50">
+        <v>300200102</v>
+      </c>
+      <c r="K59" s="50" t="s">
         <v>171</v>
-      </c>
-      <c r="I59" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="J59" s="50">
-        <v>300200201</v>
-      </c>
-      <c r="K59" s="50" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A60" s="50">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="B60" s="50">
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F60" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G60" s="50">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="H60" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="I60" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="J60" s="50">
+        <v>300200201</v>
+      </c>
+      <c r="K60" s="50" t="s">
         <v>173</v>
-      </c>
-      <c r="I60" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="J60" s="50">
-        <v>300200301</v>
-      </c>
-      <c r="K60" s="50" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A61" s="50">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="B61" s="50">
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D61" s="50">
+        <v>1</v>
+      </c>
+      <c r="E61" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="F61" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G61" s="50">
+        <v>300200301</v>
+      </c>
+      <c r="H61" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="I61" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="J61" s="50">
+        <v>300200301</v>
+      </c>
+      <c r="K61" s="50" t="s">
         <v>175</v>
-      </c>
-      <c r="D61" s="50">
-        <v>1</v>
-      </c>
-      <c r="E61" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="F61" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="G61" s="50">
-        <v>300300000</v>
-      </c>
-      <c r="H61" s="50">
-        <v>300200000</v>
-      </c>
-      <c r="I61" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="J61" s="50">
-        <v>300300000</v>
-      </c>
-      <c r="K61" s="50" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A62" s="50">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="B62" s="50">
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="D62" s="50">
+        <v>1</v>
+      </c>
+      <c r="E62" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="G62" s="50">
+        <v>300300000</v>
+      </c>
+      <c r="H62" s="50">
+        <v>300200000</v>
+      </c>
+      <c r="I62" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="J62" s="50">
+        <v>300300000</v>
+      </c>
+      <c r="K62" s="50" t="s">
         <v>177</v>
-      </c>
-      <c r="D62" s="50">
-        <v>1</v>
-      </c>
-      <c r="E62" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="F62" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="G62" s="50">
-        <v>300300001</v>
-      </c>
-      <c r="H62" s="50">
-        <v>300300000</v>
-      </c>
-      <c r="I62" s="50">
-        <v>100</v>
-      </c>
-      <c r="J62" s="50">
-        <v>300300001</v>
-      </c>
-      <c r="K62" s="50" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A63" s="50">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="B63" s="50">
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G63" s="50">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="H63" s="50">
         <v>300300000</v>
       </c>
-      <c r="I63" s="50" t="s">
-        <v>159</v>
+      <c r="I63" s="50">
+        <v>100</v>
       </c>
       <c r="J63" s="50">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A64" s="50">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="B64" s="50">
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="G64" s="50">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="H64" s="50">
         <v>300300000</v>
       </c>
       <c r="I64" s="50" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
       <c r="J64" s="50">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="50">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="B65" s="50">
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="G65" s="50">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="H65" s="50">
         <v>300300000</v>
       </c>
       <c r="I65" s="50" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J65" s="50">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="50">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="B66" s="50">
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="F66" s="50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G66" s="50">
-        <v>300300101</v>
-      </c>
-      <c r="H66" s="50" t="s">
+        <v>300300004</v>
+      </c>
+      <c r="H66" s="50">
+        <v>300300000</v>
+      </c>
+      <c r="I66" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="J66" s="50">
+        <v>300300004</v>
+      </c>
+      <c r="K66" s="50" t="s">
         <v>188</v>
-      </c>
-      <c r="I66" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="J66" s="50">
-        <v>300300101</v>
-      </c>
-      <c r="K66" s="50" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A67" s="50">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="B67" s="50">
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
@@ -4335,19 +4336,19 @@
         <v>71</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G67" s="50">
-        <v>300300102</v>
-      </c>
-      <c r="H67" s="50">
         <v>300300101</v>
       </c>
+      <c r="H67" s="50" t="s">
+        <v>189</v>
+      </c>
       <c r="I67" s="50" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J67" s="50">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="K67" s="50" t="s">
         <v>190</v>
@@ -4355,165 +4356,165 @@
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A68" s="50">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="B68" s="50">
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="F68" s="50" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G68" s="50">
-        <v>300300201</v>
-      </c>
-      <c r="H68" s="50" t="s">
+        <v>300300102</v>
+      </c>
+      <c r="H68" s="50">
+        <v>300300101</v>
+      </c>
+      <c r="I68" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="J68" s="50">
+        <v>300300102</v>
+      </c>
+      <c r="K68" s="50" t="s">
         <v>191</v>
-      </c>
-      <c r="I68" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="J68" s="50">
-        <v>300300201</v>
-      </c>
-      <c r="K68" s="50" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A69" s="50">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="B69" s="50">
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G69" s="50">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="H69" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="I69" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="J69" s="50">
+        <v>300300201</v>
+      </c>
+      <c r="K69" s="50" t="s">
         <v>193</v>
-      </c>
-      <c r="I69" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="J69" s="50">
-        <v>300300301</v>
-      </c>
-      <c r="K69" s="50" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A70" s="50">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="B70" s="50">
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D70" s="50">
+        <v>1</v>
+      </c>
+      <c r="E70" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="F70" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G70" s="50">
+        <v>300300301</v>
+      </c>
+      <c r="H70" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="I70" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="J70" s="50">
+        <v>300300301</v>
+      </c>
+      <c r="K70" s="50" t="s">
         <v>195</v>
-      </c>
-      <c r="D70" s="50">
-        <v>1</v>
-      </c>
-      <c r="E70" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="F70" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="G70" s="50">
-        <v>300400000</v>
-      </c>
-      <c r="H70" s="50">
-        <v>300600000</v>
-      </c>
-      <c r="I70" s="50">
-        <v>100</v>
-      </c>
-      <c r="J70" s="50">
-        <v>300400000</v>
-      </c>
-      <c r="K70" s="50" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A71" s="50">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="B71" s="50">
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G71" s="50">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="H71" s="50">
-        <v>300400000</v>
+        <v>300600000</v>
       </c>
       <c r="I71" s="50">
         <v>100</v>
       </c>
       <c r="J71" s="50">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A72" s="50">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="B72" s="50">
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G72" s="50">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="H72" s="50">
         <v>300400000</v>
@@ -4522,33 +4523,33 @@
         <v>100</v>
       </c>
       <c r="J72" s="50">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A73" s="50">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="B73" s="50">
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G73" s="50">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="H73" s="50">
         <v>300400000</v>
@@ -4557,33 +4558,33 @@
         <v>100</v>
       </c>
       <c r="J73" s="50">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
       <c r="A74" s="50">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="B74" s="50">
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G74" s="50">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="H74" s="50">
         <v>300400000</v>
@@ -4592,33 +4593,33 @@
         <v>100</v>
       </c>
       <c r="J74" s="50">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="50">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="B75" s="50">
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G75" s="50">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="H75" s="50">
         <v>300400000</v>
@@ -4627,77 +4628,77 @@
         <v>100</v>
       </c>
       <c r="J75" s="50">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="50">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="B76" s="50">
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F76" s="50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G76" s="50">
-        <v>300400101</v>
-      </c>
-      <c r="H76" s="50" t="s">
-        <v>210</v>
+        <v>300400005</v>
+      </c>
+      <c r="H76" s="50">
+        <v>300400000</v>
       </c>
       <c r="I76" s="50">
         <v>100</v>
       </c>
       <c r="J76" s="50">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="50">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="B77" s="50">
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G77" s="50">
-        <v>300400102</v>
-      </c>
-      <c r="H77" s="50">
         <v>300400101</v>
+      </c>
+      <c r="H77" s="50" t="s">
+        <v>211</v>
       </c>
       <c r="I77" s="50">
         <v>100</v>
       </c>
       <c r="J77" s="50">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="K77" s="50" t="s">
         <v>212</v>
@@ -4705,165 +4706,165 @@
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A78" s="50">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="B78" s="50">
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="F78" s="50" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G78" s="50">
-        <v>300400201</v>
-      </c>
-      <c r="H78" s="50" t="s">
-        <v>213</v>
+        <v>300400102</v>
+      </c>
+      <c r="H78" s="50">
+        <v>300400101</v>
       </c>
       <c r="I78" s="50">
         <v>100</v>
       </c>
       <c r="J78" s="50">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A79" s="50">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="B79" s="50">
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="F79" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G79" s="50">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I79" s="50">
         <v>100</v>
       </c>
       <c r="J79" s="50">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="K79" s="50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A80" s="50">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="B80" s="50">
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="F80" s="50" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="G80" s="50">
-        <v>300500000</v>
-      </c>
-      <c r="H80" s="50">
-        <v>300700000</v>
+        <v>300400301</v>
+      </c>
+      <c r="H80" s="50" t="s">
+        <v>216</v>
       </c>
       <c r="I80" s="50">
         <v>100</v>
       </c>
       <c r="J80" s="50">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A81" s="50">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="B81" s="50">
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F81" s="50" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G81" s="50">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="H81" s="50">
-        <v>300500000</v>
+        <v>300700000</v>
       </c>
       <c r="I81" s="50">
         <v>100</v>
       </c>
       <c r="J81" s="50">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="K81" s="50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A82" s="50">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="B82" s="50">
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G82" s="50">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="H82" s="50">
         <v>300500000</v>
@@ -4872,33 +4873,33 @@
         <v>100</v>
       </c>
       <c r="J82" s="50">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
       <c r="A83" s="50">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="B83" s="50">
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G83" s="50">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="H83" s="50">
         <v>300500000</v>
@@ -4907,33 +4908,33 @@
         <v>100</v>
       </c>
       <c r="J83" s="50">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="50">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="B84" s="50">
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G84" s="50">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="H84" s="50">
         <v>300500000</v>
@@ -4942,77 +4943,77 @@
         <v>100</v>
       </c>
       <c r="J84" s="50">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="50">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="B85" s="50">
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="F85" s="50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G85" s="50">
-        <v>300500101</v>
-      </c>
-      <c r="H85" s="50" t="s">
-        <v>228</v>
+        <v>300500004</v>
+      </c>
+      <c r="H85" s="50">
+        <v>300500000</v>
       </c>
       <c r="I85" s="50">
         <v>100</v>
       </c>
       <c r="J85" s="50">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="50">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="B86" s="50">
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G86" s="50">
-        <v>300500102</v>
-      </c>
-      <c r="H86" s="50">
         <v>300500101</v>
+      </c>
+      <c r="H86" s="50" t="s">
+        <v>229</v>
       </c>
       <c r="I86" s="50">
         <v>100</v>
       </c>
       <c r="J86" s="50">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="K86" s="50" t="s">
         <v>230</v>
@@ -5020,165 +5021,165 @@
     </row>
     <row r="87">
       <c r="A87" s="50">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="B87" s="50">
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>217</v>
+        <v>154</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G87" s="50">
-        <v>300500201</v>
-      </c>
-      <c r="H87" s="50" t="s">
-        <v>232</v>
+        <v>300500102</v>
+      </c>
+      <c r="H87" s="50">
+        <v>300500101</v>
       </c>
       <c r="I87" s="50">
         <v>100</v>
       </c>
       <c r="J87" s="50">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="50">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="B88" s="50">
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="F88" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G88" s="50">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I88" s="50">
         <v>100</v>
       </c>
       <c r="J88" s="50">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="50">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="B89" s="50">
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F89" s="50" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="G89" s="50">
-        <v>300600000</v>
-      </c>
-      <c r="H89" s="50">
-        <v>300300000</v>
+        <v>300500301</v>
+      </c>
+      <c r="H89" s="50" t="s">
+        <v>235</v>
       </c>
       <c r="I89" s="50">
         <v>100</v>
       </c>
       <c r="J89" s="50">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="50">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="B90" s="50">
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F90" s="50" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G90" s="50">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="H90" s="50">
-        <v>300600000</v>
+        <v>300300000</v>
       </c>
       <c r="I90" s="50">
         <v>100</v>
       </c>
       <c r="J90" s="50">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="50">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="B91" s="50">
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G91" s="50">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="H91" s="50">
         <v>300600000</v>
@@ -5187,33 +5188,33 @@
         <v>100</v>
       </c>
       <c r="J91" s="50">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="50">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="B92" s="50">
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G92" s="50">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="H92" s="50">
         <v>300600000</v>
@@ -5222,7 +5223,7 @@
         <v>100</v>
       </c>
       <c r="J92" s="50">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="K92" s="50" t="s">
         <v>244</v>
@@ -5230,25 +5231,25 @@
     </row>
     <row r="93">
       <c r="A93" s="50">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="B93" s="50">
         <v>3</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F93" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G93" s="50">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="H93" s="50">
         <v>300600000</v>
@@ -5257,33 +5258,33 @@
         <v>100</v>
       </c>
       <c r="J93" s="50">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="50">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="B94" s="50">
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D94" s="50">
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F94" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G94" s="50">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="H94" s="50">
         <v>300600000</v>
@@ -5292,77 +5293,77 @@
         <v>100</v>
       </c>
       <c r="J94" s="50">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="50">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="B95" s="50">
         <v>3</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D95" s="50">
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F95" s="50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G95" s="50">
-        <v>300600101</v>
-      </c>
-      <c r="H95" s="50" t="s">
-        <v>249</v>
+        <v>300600005</v>
+      </c>
+      <c r="H95" s="50">
+        <v>300600000</v>
       </c>
       <c r="I95" s="50">
         <v>100</v>
       </c>
       <c r="J95" s="50">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="K95" s="50" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="50">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="B96" s="50">
         <v>3</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D96" s="50">
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G96" s="50">
-        <v>300600102</v>
-      </c>
-      <c r="H96" s="50">
         <v>300600101</v>
+      </c>
+      <c r="H96" s="50" t="s">
+        <v>250</v>
       </c>
       <c r="I96" s="50">
         <v>100</v>
       </c>
       <c r="J96" s="50">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="K96" s="50" t="s">
         <v>251</v>
@@ -5370,165 +5371,165 @@
     </row>
     <row r="97">
       <c r="A97" s="50">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="B97" s="50">
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="D97" s="50">
         <v>1</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F97" s="50" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G97" s="50">
-        <v>300600201</v>
-      </c>
-      <c r="H97" s="50" t="s">
-        <v>252</v>
+        <v>300600102</v>
+      </c>
+      <c r="H97" s="50">
+        <v>300600101</v>
       </c>
       <c r="I97" s="50">
         <v>100</v>
       </c>
       <c r="J97" s="50">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="50">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="B98" s="50">
         <v>3</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="D98" s="50">
         <v>1</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F98" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G98" s="50">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="H98" s="50" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I98" s="50">
         <v>100</v>
       </c>
       <c r="J98" s="50">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="50">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="B99" s="50">
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>256</v>
+        <v>158</v>
       </c>
       <c r="D99" s="50">
         <v>1</v>
       </c>
       <c r="E99" s="50" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="F99" s="50" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="G99" s="50">
-        <v>300700000</v>
-      </c>
-      <c r="H99" s="50">
-        <v>300100000</v>
+        <v>300600301</v>
+      </c>
+      <c r="H99" s="50" t="s">
+        <v>255</v>
       </c>
       <c r="I99" s="50">
         <v>100</v>
       </c>
       <c r="J99" s="50">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="50">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="B100" s="50">
         <v>3</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>139</v>
+        <v>257</v>
       </c>
       <c r="D100" s="50">
         <v>1</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F100" s="50" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G100" s="50">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="H100" s="50">
-        <v>300700000</v>
+        <v>300100000</v>
       </c>
       <c r="I100" s="50">
         <v>100</v>
       </c>
       <c r="J100" s="50">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="50">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="B101" s="50">
         <v>3</v>
       </c>
       <c r="C101" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D101" s="50">
         <v>1</v>
       </c>
       <c r="E101" s="50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F101" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G101" s="50">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="H101" s="50">
         <v>300700000</v>
@@ -5537,33 +5538,33 @@
         <v>100</v>
       </c>
       <c r="J101" s="50">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="K101" s="50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="50">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="B102" s="50">
         <v>3</v>
       </c>
       <c r="C102" s="50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D102" s="50">
         <v>1</v>
       </c>
       <c r="E102" s="50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F102" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G102" s="50">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="H102" s="50">
         <v>300700000</v>
@@ -5572,33 +5573,33 @@
         <v>100</v>
       </c>
       <c r="J102" s="50">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="50">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="B103" s="50">
         <v>3</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D103" s="50">
         <v>1</v>
       </c>
       <c r="E103" s="50" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F103" s="50" t="s">
         <v>80</v>
       </c>
       <c r="G103" s="50">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="H103" s="50">
         <v>300700000</v>
@@ -5607,77 +5608,77 @@
         <v>100</v>
       </c>
       <c r="J103" s="50">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="50">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="B104" s="50">
         <v>3</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D104" s="50">
         <v>1</v>
       </c>
       <c r="E104" s="50" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="F104" s="50" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G104" s="50">
-        <v>300700101</v>
-      </c>
-      <c r="H104" s="50" t="s">
-        <v>267</v>
+        <v>300700004</v>
+      </c>
+      <c r="H104" s="50">
+        <v>300700000</v>
       </c>
       <c r="I104" s="50">
         <v>100</v>
       </c>
       <c r="J104" s="50">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="50">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="B105" s="50">
         <v>3</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D105" s="50">
         <v>1</v>
       </c>
       <c r="E105" s="50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F105" s="50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G105" s="50">
-        <v>300700102</v>
-      </c>
-      <c r="H105" s="50">
         <v>300700101</v>
+      </c>
+      <c r="H105" s="50" t="s">
+        <v>268</v>
       </c>
       <c r="I105" s="50">
         <v>100</v>
       </c>
       <c r="J105" s="50">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="K105" s="50" t="s">
         <v>269</v>
@@ -5685,104 +5686,139 @@
     </row>
     <row r="106">
       <c r="A106" s="50">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="B106" s="50">
         <v>3</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>256</v>
+        <v>154</v>
       </c>
       <c r="D106" s="50">
         <v>1</v>
       </c>
       <c r="E106" s="50" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F106" s="50" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G106" s="50">
-        <v>300700201</v>
-      </c>
-      <c r="H106" s="50" t="s">
-        <v>271</v>
+        <v>300700102</v>
+      </c>
+      <c r="H106" s="50">
+        <v>300700101</v>
       </c>
       <c r="I106" s="50">
         <v>100</v>
       </c>
       <c r="J106" s="50">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="K106" s="50" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="50">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="B107" s="50">
         <v>3</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>157</v>
+        <v>257</v>
       </c>
       <c r="D107" s="50">
         <v>1</v>
       </c>
       <c r="E107" s="50" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="F107" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G107" s="50">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="H107" s="50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I107" s="50">
         <v>100</v>
       </c>
       <c r="J107" s="50">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="K107" s="50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="50">
+        <v>300700301</v>
+      </c>
+      <c r="B108" s="50">
+        <v>3</v>
+      </c>
+      <c r="C108" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D108" s="50">
+        <v>1</v>
+      </c>
+      <c r="E108" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="F108" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G108" s="50">
+        <v>300700301</v>
+      </c>
+      <c r="H108" s="50" t="s">
+        <v>274</v>
+      </c>
+      <c r="I108" s="50">
+        <v>100</v>
+      </c>
+      <c r="J108" s="50">
+        <v>300700301</v>
+      </c>
+      <c r="K108" s="50" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="50">
         <v>100500001</v>
       </c>
-      <c r="B108" s="50">
-        <v>1</v>
-      </c>
-      <c r="C108" s="50" t="s">
-        <v>275</v>
-      </c>
-      <c r="D108" s="50">
-        <v>1</v>
-      </c>
-      <c r="E108" s="50" t="s">
+      <c r="B109" s="50">
+        <v>1</v>
+      </c>
+      <c r="C109" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="D109" s="50">
+        <v>1</v>
+      </c>
+      <c r="E109" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F108" s="50" t="s">
+      <c r="F109" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="G108" s="50">
+      <c r="G109" s="50">
         <v>100500001</v>
       </c>
-      <c r="I108" s="50" t="s">
+      <c r="I109" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="J108" s="50">
+      <c r="J109" s="50">
         <v>100500001</v>
       </c>
-      <c r="K108" s="50" t="s">
-        <v>276</v>
+      <c r="K109" s="50" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -1222,15 +1222,20 @@
       </c>
       <c r="I1" s="50" t="inlineStr">
         <is>
+          <t>pre_data</t>
+        </is>
+      </c>
+      <c r="J1" s="50" t="inlineStr">
+        <is>
           <t>pay_crystal</t>
         </is>
       </c>
-      <c r="J1" s="50" t="inlineStr">
+      <c r="K1" s="50" t="inlineStr">
         <is>
           <t>name[language]</t>
         </is>
       </c>
-      <c r="K1" s="50" t="inlineStr">
+      <c r="L1" s="50" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1284,10 +1289,15 @@
       </c>
       <c r="J2" s="50" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" s="50" t="inlineStr">
+        <is>
           <t>long</t>
         </is>
       </c>
-      <c r="K2" s="50" t="inlineStr">
+      <c r="L2" s="50" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1336,15 +1346,20 @@
       </c>
       <c r="I3" s="50" t="inlineStr">
         <is>
+          <t>前置解锁条件(特殊)</t>
+        </is>
+      </c>
+      <c r="J3" s="50" t="inlineStr">
+        <is>
           <t>需要支付的水晶</t>
         </is>
       </c>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="K3" s="50" t="inlineStr">
         <is>
           <t>名字-中文</t>
         </is>
       </c>
-      <c r="K3" s="50" t="inlineStr">
+      <c r="L3" s="50" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1383,15 +1398,15 @@
           <t>100500001,100401000</t>
         </is>
       </c>
-      <c r="I4" s="50" t="inlineStr">
+      <c r="J4" s="50" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="J4" s="50" t="n">
+      <c r="K4" s="50" t="n">
         <v>100000000</v>
       </c>
-      <c r="K4" s="50" t="inlineStr">
+      <c r="L4" s="50" t="inlineStr">
         <is>
           <t>开启进阶设施</t>
         </is>
@@ -1428,15 +1443,15 @@
       <c r="H5" s="50" t="n">
         <v>100000000</v>
       </c>
-      <c r="I5" s="50" t="inlineStr">
+      <c r="J5" s="50" t="inlineStr">
         <is>
           <t>1000,2000,3000,4000,5000,</t>
         </is>
       </c>
-      <c r="J5" s="50" t="n">
+      <c r="K5" s="50" t="n">
         <v>100000001</v>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="L5" s="50" t="inlineStr">
         <is>
           <t>进阶设施+1</t>
         </is>
@@ -1475,13 +1490,13 @@
           <t>100000001</t>
         </is>
       </c>
-      <c r="I6" s="50" t="n">
+      <c r="J6" s="50" t="n">
         <v>500</v>
       </c>
-      <c r="J6" s="50" t="n">
+      <c r="K6" s="50" t="n">
         <v>100000006</v>
       </c>
-      <c r="K6" s="50" t="inlineStr">
+      <c r="L6" s="50" t="inlineStr">
         <is>
           <t>进阶增益范围预览</t>
         </is>
@@ -1520,15 +1535,15 @@
           <t>100000000</t>
         </is>
       </c>
-      <c r="I7" s="50" t="inlineStr">
+      <c r="J7" s="50" t="inlineStr">
         <is>
           <t>1000,2000,3000,4000,5000,</t>
         </is>
       </c>
-      <c r="J7" s="50" t="n">
+      <c r="K7" s="50" t="n">
         <v>100000007</v>
       </c>
-      <c r="K7" s="50" t="inlineStr">
+      <c r="L7" s="50" t="inlineStr">
         <is>
           <t>进阶魔晶加速倍率+1</t>
         </is>
@@ -1567,15 +1582,15 @@
           <t>100000000</t>
         </is>
       </c>
-      <c r="I8" s="50" t="inlineStr">
+      <c r="J8" s="50" t="inlineStr">
         <is>
           <t>1000,2000,3000,4000,5000,</t>
         </is>
       </c>
-      <c r="J8" s="50" t="n">
+      <c r="K8" s="50" t="n">
         <v>100000008</v>
       </c>
-      <c r="K8" s="50" t="inlineStr">
+      <c r="L8" s="50" t="inlineStr">
         <is>
           <t>进阶素材可选数量+1</t>
         </is>
@@ -1614,15 +1629,15 @@
           <t>100500001</t>
         </is>
       </c>
-      <c r="I9" s="50" t="inlineStr">
+      <c r="J9" s="50" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J9" s="50" t="n">
+      <c r="K9" s="50" t="n">
         <v>100100001</v>
       </c>
-      <c r="K9" s="50" t="inlineStr">
+      <c r="L9" s="50" t="inlineStr">
         <is>
           <t>开启献祭设施</t>
         </is>
@@ -1659,15 +1674,15 @@
       <c r="H10" s="50" t="n">
         <v>100100001</v>
       </c>
-      <c r="I10" s="50" t="inlineStr">
+      <c r="J10" s="50" t="inlineStr">
         <is>
           <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
         </is>
       </c>
-      <c r="J10" s="50" t="n">
+      <c r="K10" s="50" t="n">
         <v>100100002</v>
       </c>
-      <c r="K10" s="50" t="inlineStr">
+      <c r="L10" s="50" t="inlineStr">
         <is>
           <t>献祭祭品数量+1</t>
         </is>
@@ -1706,15 +1721,15 @@
           <t>100100001</t>
         </is>
       </c>
-      <c r="I11" s="50" t="inlineStr">
+      <c r="J11" s="50" t="inlineStr">
         <is>
           <t>100,500,1000,5000,10000,20000,30000,40000,50000,100000</t>
         </is>
       </c>
-      <c r="J11" s="50" t="n">
+      <c r="K11" s="50" t="n">
         <v>100100003</v>
       </c>
-      <c r="K11" s="50" t="inlineStr">
+      <c r="L11" s="50" t="inlineStr">
         <is>
           <t>献祭失败保底概率提升</t>
         </is>
@@ -1753,15 +1768,15 @@
           <t>100100001</t>
         </is>
       </c>
-      <c r="I12" s="50" t="inlineStr">
+      <c r="J12" s="50" t="inlineStr">
         <is>
           <t>100,200,500,1000,1500,2000,2500,3000,3500,5000</t>
         </is>
       </c>
-      <c r="J12" s="50" t="n">
+      <c r="K12" s="50" t="n">
         <v>100100004</v>
       </c>
-      <c r="K12" s="50" t="inlineStr">
+      <c r="L12" s="50" t="inlineStr">
         <is>
           <t>不同魔物献祭成功率提升</t>
         </is>
@@ -1800,15 +1815,15 @@
           <t>100500001</t>
         </is>
       </c>
-      <c r="I13" s="50" t="inlineStr">
+      <c r="J13" s="50" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="K13" s="50" t="n">
         <v>100200001</v>
       </c>
-      <c r="K13" s="50" t="inlineStr">
+      <c r="L13" s="50" t="inlineStr">
         <is>
           <t>开启终焉议会</t>
         </is>
@@ -1845,13 +1860,13 @@
       <c r="H14" s="50" t="n">
         <v>100200001</v>
       </c>
-      <c r="I14" s="50" t="n">
+      <c r="J14" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J14" s="50" t="n">
+      <c r="K14" s="50" t="n">
         <v>100200002</v>
       </c>
-      <c r="K14" s="50" t="inlineStr">
+      <c r="L14" s="50" t="inlineStr">
         <is>
           <t>终焉议会议案：魔物重命名</t>
         </is>
@@ -1890,13 +1905,13 @@
           <t>100200002</t>
         </is>
       </c>
-      <c r="I15" s="50" t="n">
+      <c r="J15" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J15" s="50" t="n">
+      <c r="K15" s="50" t="n">
         <v>100200003</v>
       </c>
-      <c r="K15" s="50" t="inlineStr">
+      <c r="L15" s="50" t="inlineStr">
         <is>
           <t>终焉议会议案：魔王重命名</t>
         </is>
@@ -1935,15 +1950,15 @@
           <t>100200001</t>
         </is>
       </c>
-      <c r="I16" s="50" t="inlineStr">
+      <c r="J16" s="50" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="J16" s="50" t="n">
+      <c r="K16" s="50" t="n">
         <v>100200004</v>
       </c>
-      <c r="K16" s="50" t="inlineStr">
+      <c r="L16" s="50" t="inlineStr">
         <is>
           <t>征服通关获得声望</t>
         </is>
@@ -1984,15 +1999,15 @@
           <t>100500001</t>
         </is>
       </c>
-      <c r="I17" s="50" t="inlineStr">
+      <c r="J17" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J17" s="50" t="n">
+      <c r="K17" s="50" t="n">
         <v>100300001</v>
       </c>
-      <c r="K17" s="50" t="inlineStr">
+      <c r="L17" s="50" t="inlineStr">
         <is>
           <t>开启终焉议会</t>
         </is>
@@ -2033,15 +2048,15 @@
           <t>100300003</t>
         </is>
       </c>
-      <c r="I18" s="50" t="inlineStr">
+      <c r="J18" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J18" s="50" t="n">
+      <c r="K18" s="50" t="n">
         <v>100300002</v>
       </c>
-      <c r="K18" s="50" t="inlineStr">
+      <c r="L18" s="50" t="inlineStr">
         <is>
           <t>传送门详情-线路数量预览</t>
         </is>
@@ -2082,15 +2097,15 @@
           <t>100300001</t>
         </is>
       </c>
-      <c r="I19" s="50" t="inlineStr">
+      <c r="J19" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J19" s="50" t="n">
+      <c r="K19" s="50" t="n">
         <v>100300003</v>
       </c>
-      <c r="K19" s="50" t="inlineStr">
+      <c r="L19" s="50" t="inlineStr">
         <is>
           <t>传送门详情-关卡数量预览</t>
         </is>
@@ -2131,15 +2146,15 @@
           <t>100300003</t>
         </is>
       </c>
-      <c r="I20" s="50" t="inlineStr">
+      <c r="J20" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J20" s="50" t="n">
+      <c r="K20" s="50" t="n">
         <v>100300004</v>
       </c>
-      <c r="K20" s="50" t="inlineStr">
+      <c r="L20" s="50" t="inlineStr">
         <is>
           <t>传送门详情-路径长度预览</t>
         </is>
@@ -2180,15 +2195,15 @@
           <t>100300003</t>
         </is>
       </c>
-      <c r="I21" s="50" t="inlineStr">
+      <c r="J21" s="50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J21" s="50" t="n">
+      <c r="K21" s="50" t="n">
         <v>100300005</v>
       </c>
-      <c r="K21" s="50" t="inlineStr">
+      <c r="L21" s="50" t="inlineStr">
         <is>
           <t>传送门详情-奖励预览</t>
         </is>
@@ -2227,15 +2242,15 @@
           <t>100300001</t>
         </is>
       </c>
-      <c r="I22" s="50" t="inlineStr">
+      <c r="J22" s="50" t="inlineStr">
         <is>
           <t>300*2</t>
         </is>
       </c>
-      <c r="J22" s="50" t="n">
+      <c r="K22" s="50" t="n">
         <v>100300006</v>
       </c>
-      <c r="K22" s="50" t="inlineStr">
+      <c r="L22" s="50" t="inlineStr">
         <is>
           <t>传送门刷新解锁</t>
         </is>
@@ -2254,11 +2269,11 @@
         </is>
       </c>
       <c r="D23" s="50" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E23" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-160</t>
         </is>
       </c>
       <c r="F23" s="50" t="inlineStr">
@@ -2270,30 +2285,30 @@
         <v>100310112</v>
       </c>
       <c r="H23" s="50" t="n"/>
-      <c r="I23" s="50" t="inlineStr">
-        <is>
-          <t>100,400,800,1600,3200,6400,12800,25600,51200,</t>
-        </is>
-      </c>
-      <c r="J23" s="50" t="n">
+      <c r="J23" s="50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K23" s="50" t="n">
         <v>100310112</v>
       </c>
-      <c r="K23" s="50" t="inlineStr">
-        <is>
-          <t>剑与魔法：征服难度+1</t>
+      <c r="L23" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法：征服难度2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50" t="n">
-        <v>100310130</v>
+        <v>100400000</v>
       </c>
       <c r="B24" s="50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C24" s="50" t="inlineStr">
         <is>
-          <t>ui_research_66</t>
+          <t>ui_research_57</t>
         </is>
       </c>
       <c r="D24" s="50" t="n">
@@ -2306,81 +2321,79 @@
       </c>
       <c r="F24" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G24" s="50" t="n">
-        <v>100310130</v>
+        <v>100400000</v>
       </c>
       <c r="H24" s="50" t="inlineStr">
         <is>
-          <t>100310112</t>
-        </is>
-      </c>
-      <c r="I24" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J24" s="50" t="n">
-        <v>100310130</v>
-      </c>
-      <c r="K24" s="50" t="inlineStr">
-        <is>
-          <t>剑与魔法-加快进攻节奏</t>
+          <t>100500001</t>
+        </is>
+      </c>
+      <c r="J24" s="50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K24" s="50" t="n">
+        <v>100400000</v>
+      </c>
+      <c r="L24" s="50" t="inlineStr">
+        <is>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50" t="n">
+        <v>100400001</v>
+      </c>
+      <c r="B25" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_57</t>
+        </is>
+      </c>
+      <c r="D25" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F25" s="50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="G25" s="50" t="n">
+        <v>100400001</v>
+      </c>
+      <c r="H25" s="50" t="n">
         <v>100400000</v>
       </c>
-      <c r="B25" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_57</t>
-        </is>
-      </c>
-      <c r="D25" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="G25" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="H25" s="50" t="inlineStr">
-        <is>
-          <t>100500001</t>
-        </is>
-      </c>
-      <c r="I25" s="50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="K25" s="50" t="inlineStr">
-        <is>
-          <t>开启孕育功能</t>
+      <c r="J25" s="50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K25" s="50" t="n">
+        <v>100400001</v>
+      </c>
+      <c r="L25" s="50" t="inlineStr">
+        <is>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="50" t="n">
-        <v>100400001</v>
+        <v>100401000</v>
       </c>
       <c r="B26" s="50" t="n">
         <v>1</v>
@@ -2395,84 +2408,84 @@
       </c>
       <c r="E26" s="50" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="G26" s="50" t="n">
+        <v>100401000</v>
+      </c>
+      <c r="H26" s="50" t="inlineStr">
+        <is>
+          <t>100400000</t>
+        </is>
+      </c>
+      <c r="J26" s="50" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F26" s="50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="G26" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="H26" s="50" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="I26" s="50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J26" s="50" t="n">
-        <v>100400001</v>
-      </c>
-      <c r="K26" s="50" t="inlineStr">
-        <is>
-          <t>孕育可跳过</t>
+      <c r="K26" s="50" t="n">
+        <v>100401000</v>
+      </c>
+      <c r="L26" s="50" t="inlineStr">
+        <is>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="50" t="n">
+        <v>100401001</v>
+      </c>
+      <c r="B27" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_57</t>
+        </is>
+      </c>
+      <c r="D27" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F27" s="50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="G27" s="50" t="n">
+        <v>100401001</v>
+      </c>
+      <c r="H27" s="50" t="n">
         <v>100401000</v>
       </c>
-      <c r="B27" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_57</t>
-        </is>
-      </c>
-      <c r="D27" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" s="50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="G27" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="H27" s="50" t="inlineStr">
-        <is>
-          <t>100400000</t>
-        </is>
-      </c>
-      <c r="I27" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J27" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="K27" s="50" t="inlineStr">
-        <is>
-          <t>解锁孕育稀有度：R</t>
+      <c r="J27" s="50" t="inlineStr">
+        <is>
+          <t>100*1</t>
+        </is>
+      </c>
+      <c r="K27" s="50" t="n">
+        <v>100401001</v>
+      </c>
+      <c r="L27" s="50" t="inlineStr">
+        <is>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="50" t="n">
-        <v>100401001</v>
+        <v>100402000</v>
       </c>
       <c r="B28" s="50" t="n">
         <v>1</v>
@@ -2483,86 +2496,86 @@
         </is>
       </c>
       <c r="D28" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E28" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F28" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>800</t>
         </is>
       </c>
       <c r="G28" s="50" t="n">
-        <v>100401001</v>
-      </c>
-      <c r="H28" s="50" t="n">
-        <v>100401000</v>
-      </c>
-      <c r="I28" s="50" t="inlineStr">
-        <is>
-          <t>100*1</t>
+        <v>100402000</v>
+      </c>
+      <c r="H28" s="50" t="inlineStr">
+        <is>
+          <t>100401000,100401001,</t>
         </is>
       </c>
       <c r="J28" s="50" t="n">
-        <v>100401001</v>
-      </c>
-      <c r="K28" s="50" t="inlineStr">
-        <is>
-          <t>孕育稀有度：R 概率+1%</t>
+        <v>1000</v>
+      </c>
+      <c r="K28" s="50" t="n">
+        <v>100402000</v>
+      </c>
+      <c r="L28" s="50" t="inlineStr">
+        <is>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="50" t="n">
+        <v>100402001</v>
+      </c>
+      <c r="B29" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_57</t>
+        </is>
+      </c>
+      <c r="D29" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F29" s="50" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="G29" s="50" t="n">
+        <v>100402001</v>
+      </c>
+      <c r="H29" s="50" t="n">
         <v>100402000</v>
       </c>
-      <c r="B29" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_57</t>
-        </is>
-      </c>
-      <c r="D29" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="50" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="G29" s="50" t="n">
-        <v>100402000</v>
-      </c>
-      <c r="H29" s="50" t="inlineStr">
-        <is>
-          <t>100401000,100401001,</t>
-        </is>
-      </c>
-      <c r="I29" s="50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J29" s="50" t="n">
-        <v>100402000</v>
-      </c>
-      <c r="K29" s="50" t="inlineStr">
-        <is>
-          <t>解锁孕育稀有度：SR</t>
+      <c r="J29" s="50" t="inlineStr">
+        <is>
+          <t>1000*1</t>
+        </is>
+      </c>
+      <c r="K29" s="50" t="n">
+        <v>100402001</v>
+      </c>
+      <c r="L29" s="50" t="inlineStr">
+        <is>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="50" t="n">
-        <v>100402001</v>
+        <v>100403000</v>
       </c>
       <c r="B30" s="50" t="n">
         <v>1</v>
@@ -2573,308 +2586,308 @@
         </is>
       </c>
       <c r="D30" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E30" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="G30" s="50" t="n">
-        <v>100402001</v>
-      </c>
-      <c r="H30" s="50" t="n">
-        <v>100402000</v>
-      </c>
-      <c r="I30" s="50" t="inlineStr">
-        <is>
-          <t>1000*1</t>
+        <v>100403000</v>
+      </c>
+      <c r="H30" s="50" t="inlineStr">
+        <is>
+          <t>100402000,100402001,</t>
         </is>
       </c>
       <c r="J30" s="50" t="n">
-        <v>100402001</v>
-      </c>
-      <c r="K30" s="50" t="inlineStr">
-        <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+        <v>10000</v>
+      </c>
+      <c r="K30" s="50" t="n">
+        <v>100403000</v>
+      </c>
+      <c r="L30" s="50" t="inlineStr">
+        <is>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="50" t="n">
+        <v>100403001</v>
+      </c>
+      <c r="B31" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_57</t>
+        </is>
+      </c>
+      <c r="D31" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" s="50" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F31" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G31" s="50" t="n">
+        <v>100403001</v>
+      </c>
+      <c r="H31" s="50" t="n">
         <v>100403000</v>
       </c>
-      <c r="B31" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_57</t>
-        </is>
-      </c>
-      <c r="D31" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" s="50" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="G31" s="50" t="n">
-        <v>100403000</v>
-      </c>
-      <c r="H31" s="50" t="inlineStr">
-        <is>
-          <t>100402000,100402001,</t>
-        </is>
-      </c>
-      <c r="I31" s="50" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J31" s="50" t="n">
-        <v>100403000</v>
-      </c>
-      <c r="K31" s="50" t="inlineStr">
-        <is>
-          <t>解锁孕育稀有度：SSR</t>
+      <c r="J31" s="50" t="inlineStr">
+        <is>
+          <t>10000*1</t>
+        </is>
+      </c>
+      <c r="K31" s="50" t="n">
+        <v>100403001</v>
+      </c>
+      <c r="L31" s="50" t="inlineStr">
+        <is>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="50" t="n">
-        <v>100403001</v>
+        <v>100600001</v>
       </c>
       <c r="B32" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
-          <t>ui_research_57</t>
+          <t>ui_research_65</t>
         </is>
       </c>
       <c r="D32" s="50" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E32" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>-500</t>
         </is>
       </c>
       <c r="F32" s="50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="G32" s="50" t="n">
-        <v>100403001</v>
-      </c>
-      <c r="H32" s="50" t="n">
-        <v>100403000</v>
-      </c>
-      <c r="I32" s="50" t="inlineStr">
-        <is>
-          <t>10000*1</t>
-        </is>
-      </c>
-      <c r="J32" s="50" t="n">
-        <v>100403001</v>
-      </c>
-      <c r="K32" s="50" t="inlineStr">
-        <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+        <v>100600001</v>
+      </c>
+      <c r="H32" s="50" t="inlineStr">
+        <is>
+          <t>100500001</t>
+        </is>
+      </c>
+      <c r="J32" s="50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K32" s="50" t="n">
+        <v>100600001</v>
+      </c>
+      <c r="L32" s="50" t="inlineStr">
+        <is>
+          <t>开启魔汁机</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>100600001</v>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ui_research_65</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-500</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>100600001</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>100500001</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>100600001</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>开启魔汁机</t>
+      <c r="A33" s="50" t="n">
+        <v>200000001</v>
+      </c>
+      <c r="B33" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_5</t>
+        </is>
+      </c>
+      <c r="D33" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="E33" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="50" t="n">
+        <v>200000001</v>
+      </c>
+      <c r="J33" s="50" t="inlineStr">
+        <is>
+          <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000</t>
+        </is>
+      </c>
+      <c r="K33" s="50" t="n">
+        <v>200000001</v>
+      </c>
+      <c r="L33" s="50" t="inlineStr">
+        <is>
+          <t>阵容上限+1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="50" t="n">
-        <v>200000001</v>
+        <v>200100001</v>
       </c>
       <c r="B34" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="50" t="inlineStr">
         <is>
-          <t>ui_research_5</t>
+          <t>ui_research_6</t>
         </is>
       </c>
       <c r="D34" s="50" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E34" s="50" t="inlineStr">
         <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F34" s="50" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="50" t="n">
-        <v>0</v>
-      </c>
       <c r="G34" s="50" t="n">
-        <v>200000001</v>
-      </c>
-      <c r="I34" s="50" t="inlineStr">
-        <is>
-          <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000</t>
-        </is>
-      </c>
-      <c r="J34" s="50" t="n">
-        <v>200000001</v>
-      </c>
-      <c r="K34" s="50" t="inlineStr">
-        <is>
-          <t>阵容上限+1</t>
+        <v>200100001</v>
+      </c>
+      <c r="H34" s="50" t="inlineStr">
+        <is>
+          <t>200000001</t>
+        </is>
+      </c>
+      <c r="J34" s="50" t="inlineStr">
+        <is>
+          <t>100,200,300,400,</t>
+        </is>
+      </c>
+      <c r="K34" s="50" t="n">
+        <v>200100001</v>
+      </c>
+      <c r="L34" s="50" t="inlineStr">
+        <is>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="50" t="n">
-        <v>200100001</v>
+        <v>200200001</v>
       </c>
       <c r="B35" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="50" t="inlineStr">
         <is>
-          <t>ui_research_6</t>
+          <t>ui_research_60</t>
         </is>
       </c>
       <c r="D35" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
-      </c>
-      <c r="F35" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="E35" s="50" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F35" s="50" t="n">
+        <v>-200</v>
       </c>
       <c r="G35" s="50" t="n">
-        <v>200100001</v>
+        <v>200200001</v>
       </c>
       <c r="H35" s="50" t="inlineStr">
         <is>
           <t>200000001</t>
         </is>
       </c>
-      <c r="I35" s="50" t="inlineStr">
-        <is>
-          <t>100,200,300,400,</t>
-        </is>
-      </c>
-      <c r="J35" s="50" t="n">
-        <v>200100001</v>
-      </c>
-      <c r="K35" s="50" t="inlineStr">
-        <is>
-          <t>解锁第二阵容</t>
+      <c r="J35" s="50" t="inlineStr">
+        <is>
+          <t>100,500,1000,5000,10000,50000</t>
+        </is>
+      </c>
+      <c r="K35" s="50" t="n">
+        <v>200200001</v>
+      </c>
+      <c r="L35" s="50" t="inlineStr">
+        <is>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="50" t="n">
-        <v>200200001</v>
+        <v>200300001</v>
       </c>
       <c r="B36" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C36" s="50" t="inlineStr">
         <is>
-          <t>ui_research_60</t>
+          <t>ui_research_61</t>
         </is>
       </c>
       <c r="D36" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" s="50" t="n">
-        <v>-200</v>
-      </c>
-      <c r="F36" s="50" t="n">
-        <v>-200</v>
+        <v>0</v>
+      </c>
+      <c r="F36" s="50" t="inlineStr">
+        <is>
+          <t>-400</t>
+        </is>
       </c>
       <c r="G36" s="50" t="n">
-        <v>200200001</v>
+        <v>200300001</v>
       </c>
       <c r="H36" s="50" t="inlineStr">
         <is>
-          <t>200000001</t>
-        </is>
-      </c>
-      <c r="I36" s="50" t="inlineStr">
-        <is>
-          <t>100,500,1000,5000,10000,50000</t>
-        </is>
-      </c>
-      <c r="J36" s="50" t="n">
-        <v>200200001</v>
-      </c>
-      <c r="K36" s="50" t="inlineStr">
-        <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>200400001</t>
+        </is>
+      </c>
+      <c r="J36" s="50" t="inlineStr">
+        <is>
+          <t>100,500,1000,5000,10000</t>
+        </is>
+      </c>
+      <c r="K36" s="50" t="n">
+        <v>200300001</v>
+      </c>
+      <c r="L36" s="50" t="inlineStr">
+        <is>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="50" t="n">
-        <v>200300001</v>
+        <v>200400001</v>
       </c>
       <c r="B37" s="50" t="n">
         <v>2</v>
@@ -2885,133 +2898,135 @@
         </is>
       </c>
       <c r="D37" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="E37" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="50" t="inlineStr">
-        <is>
-          <t>-400</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E37" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="50" t="n">
+        <v>-200</v>
       </c>
       <c r="G37" s="50" t="n">
-        <v>200300001</v>
+        <v>200400001</v>
       </c>
       <c r="H37" s="50" t="inlineStr">
         <is>
-          <t>200400001</t>
-        </is>
-      </c>
-      <c r="I37" s="50" t="inlineStr">
-        <is>
-          <t>100,500,1000,5000,10000</t>
-        </is>
-      </c>
-      <c r="J37" s="50" t="n">
-        <v>200300001</v>
-      </c>
-      <c r="K37" s="50" t="inlineStr">
-        <is>
-          <t>魔王魔力上限+10</t>
+          <t>200000001</t>
+        </is>
+      </c>
+      <c r="J37" s="50" t="inlineStr">
+        <is>
+          <t>100,500,1000</t>
+        </is>
+      </c>
+      <c r="K37" s="50" t="n">
+        <v>200400001</v>
+      </c>
+      <c r="L37" s="50" t="inlineStr">
+        <is>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="50" t="n">
-        <v>200400001</v>
+        <v>200500001</v>
       </c>
       <c r="B38" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C38" s="50" t="inlineStr">
         <is>
-          <t>ui_research_61</t>
+          <t>ui_research_62</t>
         </is>
       </c>
       <c r="D38" s="50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E38" s="50" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F38" s="50" t="n">
-        <v>-200</v>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F38" s="50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G38" s="50" t="n">
-        <v>200400001</v>
+        <v>200500001</v>
       </c>
       <c r="H38" s="50" t="inlineStr">
         <is>
           <t>200000001</t>
         </is>
       </c>
-      <c r="I38" s="50" t="inlineStr">
-        <is>
-          <t>100,500,1000</t>
-        </is>
-      </c>
-      <c r="J38" s="50" t="n">
-        <v>200400001</v>
-      </c>
-      <c r="K38" s="50" t="inlineStr">
-        <is>
-          <t>魔王魔力恢复速度+1/s</t>
+      <c r="J38" s="50" t="inlineStr">
+        <is>
+          <t>100,500,1000,5000,10000</t>
+        </is>
+      </c>
+      <c r="K38" s="50" t="n">
+        <v>200500001</v>
+      </c>
+      <c r="L38" s="50" t="inlineStr">
+        <is>
+          <t>深渊馈赠刷新次数+1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="50" t="n">
-        <v>200500001</v>
+        <v>200600001</v>
       </c>
       <c r="B39" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
-          <t>ui_research_62</t>
+          <t>ui_research_6</t>
         </is>
       </c>
       <c r="D39" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E39" s="50" t="inlineStr">
         <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="F39" s="50" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F39" s="50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G39" s="50" t="n">
-        <v>200500001</v>
+        <v>200600001</v>
       </c>
       <c r="H39" s="50" t="inlineStr">
         <is>
           <t>200000001</t>
         </is>
       </c>
-      <c r="I39" s="50" t="inlineStr">
-        <is>
-          <t>100,500,1000,5000,10000</t>
-        </is>
-      </c>
-      <c r="J39" s="50" t="n">
-        <v>200500001</v>
-      </c>
-      <c r="K39" s="50" t="inlineStr">
-        <is>
-          <t>深渊馈赠刷新次数+1</t>
+      <c r="J39" s="50" t="inlineStr">
+        <is>
+          <t>100,1000,10000</t>
+        </is>
+      </c>
+      <c r="K39" s="50" t="n">
+        <v>200600001</v>
+      </c>
+      <c r="L39" s="50" t="inlineStr">
+        <is>
+          <t>空格突进</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="50" t="n">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="B40" s="50" t="n">
         <v>2</v>
@@ -3022,90 +3037,90 @@
         </is>
       </c>
       <c r="D40" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="F40" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G40" s="50" t="n">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="H40" s="50" t="inlineStr">
         <is>
-          <t>200000001</t>
-        </is>
-      </c>
-      <c r="I40" s="50" t="inlineStr">
-        <is>
-          <t>100,1000,10000</t>
-        </is>
-      </c>
-      <c r="J40" s="50" t="n">
-        <v>200600001</v>
-      </c>
-      <c r="K40" s="50" t="inlineStr">
-        <is>
-          <t>空格突进</t>
+          <t>200600001</t>
+        </is>
+      </c>
+      <c r="J40" s="50" t="inlineStr">
+        <is>
+          <t>200,2000,20000,200000</t>
+        </is>
+      </c>
+      <c r="K40" s="50" t="n">
+        <v>200700001</v>
+      </c>
+      <c r="L40" s="50" t="inlineStr">
+        <is>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="50" t="n">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="B41" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C41" s="50" t="inlineStr">
         <is>
-          <t>ui_research_6</t>
+          <t>ui_research_60</t>
         </is>
       </c>
       <c r="D41" s="50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E41" s="50" t="inlineStr">
         <is>
-          <t>-400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F41" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G41" s="50" t="n">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="H41" s="50" t="inlineStr">
         <is>
-          <t>200600001</t>
-        </is>
-      </c>
-      <c r="I41" s="50" t="inlineStr">
-        <is>
-          <t>200,2000,20000,200000</t>
-        </is>
-      </c>
-      <c r="J41" s="50" t="n">
-        <v>200700001</v>
-      </c>
-      <c r="K41" s="50" t="inlineStr">
-        <is>
-          <t>突进冷却</t>
+          <t>200000001</t>
+        </is>
+      </c>
+      <c r="J41" s="50" t="inlineStr">
+        <is>
+          <t>200*1</t>
+        </is>
+      </c>
+      <c r="K41" s="50" t="n">
+        <v>200800001</v>
+      </c>
+      <c r="L41" s="50" t="inlineStr">
+        <is>
+          <t>魔王自动拾取魔晶</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="50" t="n">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="B42" s="50" t="n">
         <v>2</v>
@@ -3116,7 +3131,7 @@
         </is>
       </c>
       <c r="D42" s="50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E42" s="50" t="inlineStr">
         <is>
@@ -3125,88 +3140,86 @@
       </c>
       <c r="F42" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G42" s="50" t="n">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="H42" s="50" t="inlineStr">
         <is>
-          <t>200000001</t>
-        </is>
-      </c>
-      <c r="I42" s="50" t="inlineStr">
-        <is>
-          <t>200*1</t>
-        </is>
-      </c>
-      <c r="J42" s="50" t="n">
-        <v>200800001</v>
-      </c>
-      <c r="K42" s="50" t="inlineStr">
-        <is>
-          <t>魔王自动拾取魔晶</t>
+          <t>200800001</t>
+        </is>
+      </c>
+      <c r="J42" s="50" t="inlineStr">
+        <is>
+          <t>1000*1</t>
+        </is>
+      </c>
+      <c r="K42" s="50" t="n">
+        <v>200900001</v>
+      </c>
+      <c r="L42" s="50" t="inlineStr">
+        <is>
+          <t>每次拾取魔晶+1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="50" t="n">
-        <v>200900001</v>
+        <v>300100000</v>
       </c>
       <c r="B43" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" s="50" t="inlineStr">
         <is>
-          <t>ui_research_60</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D43" s="50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E43" s="50" t="inlineStr">
         <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="F43" s="50" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
       <c r="G43" s="50" t="n">
-        <v>200900001</v>
-      </c>
-      <c r="H43" s="50" t="inlineStr">
-        <is>
-          <t>200800001</t>
-        </is>
-      </c>
-      <c r="I43" s="50" t="inlineStr">
-        <is>
-          <t>1000*1</t>
-        </is>
-      </c>
-      <c r="J43" s="50" t="n">
-        <v>200900001</v>
-      </c>
-      <c r="K43" s="50" t="inlineStr">
-        <is>
-          <t>每次拾取魔晶+1</t>
+        <v>300100000</v>
+      </c>
+      <c r="H43" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="J43" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="K43" s="50" t="n">
+        <v>300100000</v>
+      </c>
+      <c r="L43" s="50" t="inlineStr">
+        <is>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="50" t="n">
-        <v>300100000</v>
+        <v>300100001</v>
       </c>
       <c r="B44" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D44" s="50" t="n">
@@ -3214,44 +3227,42 @@
       </c>
       <c r="E44" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>500</t>
         </is>
       </c>
       <c r="F44" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G44" s="50" t="n">
+        <v>300100001</v>
+      </c>
+      <c r="H44" s="50" t="n">
         <v>300100000</v>
       </c>
-      <c r="H44" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I44" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
       <c r="J44" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="K44" s="50" t="inlineStr">
-        <is>
-          <t>解锁种族：人类</t>
+        <v>100</v>
+      </c>
+      <c r="K44" s="50" t="n">
+        <v>300100001</v>
+      </c>
+      <c r="L44" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="50" t="n">
-        <v>300100001</v>
+        <v>300100002</v>
       </c>
       <c r="B45" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C45" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D45" s="50" t="n">
@@ -3259,7 +3270,7 @@
       </c>
       <c r="E45" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F45" s="50" t="inlineStr">
@@ -3268,33 +3279,33 @@
         </is>
       </c>
       <c r="G45" s="50" t="n">
-        <v>300100001</v>
+        <v>300100002</v>
       </c>
       <c r="H45" s="50" t="n">
         <v>300100000</v>
       </c>
-      <c r="I45" s="50" t="n">
+      <c r="J45" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J45" s="50" t="n">
-        <v>300100001</v>
-      </c>
-      <c r="K45" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：人类战士</t>
+      <c r="K45" s="50" t="n">
+        <v>300100002</v>
+      </c>
+      <c r="L45" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="50" t="n">
-        <v>300100002</v>
+        <v>300100003</v>
       </c>
       <c r="B46" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C46" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D46" s="50" t="n">
@@ -3302,7 +3313,7 @@
       </c>
       <c r="E46" s="50" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F46" s="50" t="inlineStr">
@@ -3311,33 +3322,33 @@
         </is>
       </c>
       <c r="G46" s="50" t="n">
-        <v>300100002</v>
+        <v>300100003</v>
       </c>
       <c r="H46" s="50" t="n">
         <v>300100000</v>
       </c>
-      <c r="I46" s="50" t="n">
+      <c r="J46" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J46" s="50" t="n">
-        <v>300100002</v>
-      </c>
-      <c r="K46" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：人类弓箭手</t>
+      <c r="K46" s="50" t="n">
+        <v>300100003</v>
+      </c>
+      <c r="L46" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="50" t="n">
-        <v>300100003</v>
+        <v>300100004</v>
       </c>
       <c r="B47" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C47" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D47" s="50" t="n">
@@ -3345,7 +3356,7 @@
       </c>
       <c r="E47" s="50" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F47" s="50" t="inlineStr">
@@ -3354,33 +3365,33 @@
         </is>
       </c>
       <c r="G47" s="50" t="n">
-        <v>300100003</v>
+        <v>300100004</v>
       </c>
       <c r="H47" s="50" t="n">
         <v>300100000</v>
       </c>
-      <c r="I47" s="50" t="n">
+      <c r="J47" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J47" s="50" t="n">
-        <v>300100003</v>
-      </c>
-      <c r="K47" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：人类魔法师（火）</t>
+      <c r="K47" s="50" t="n">
+        <v>300100004</v>
+      </c>
+      <c r="L47" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="50" t="n">
-        <v>300100004</v>
+        <v>300100101</v>
       </c>
       <c r="B48" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D48" s="50" t="n">
@@ -3388,42 +3399,44 @@
       </c>
       <c r="E48" s="50" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G48" s="50" t="n">
-        <v>300100004</v>
-      </c>
-      <c r="H48" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="I48" s="50" t="n">
+        <v>300100101</v>
+      </c>
+      <c r="H48" s="50" t="inlineStr">
+        <is>
+          <t>300100001|300100002|300100003|300100004|</t>
+        </is>
+      </c>
+      <c r="J48" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J48" s="50" t="n">
-        <v>300100004</v>
-      </c>
-      <c r="K48" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+      <c r="K48" s="50" t="n">
+        <v>300100101</v>
+      </c>
+      <c r="L48" s="50" t="inlineStr">
+        <is>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="50" t="n">
-        <v>300100101</v>
+        <v>300100102</v>
       </c>
       <c r="B49" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D49" s="50" t="n">
@@ -3436,39 +3449,37 @@
       </c>
       <c r="F49" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G49" s="50" t="n">
+        <v>300100102</v>
+      </c>
+      <c r="H49" s="50" t="n">
         <v>300100101</v>
       </c>
-      <c r="H49" s="50" t="inlineStr">
-        <is>
-          <t>300100001|300100002|300100003|300100004|</t>
-        </is>
-      </c>
-      <c r="I49" s="50" t="n">
+      <c r="J49" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J49" s="50" t="n">
-        <v>300100101</v>
-      </c>
-      <c r="K49" s="50" t="inlineStr">
-        <is>
-          <t>孕育人类x5</t>
+      <c r="K49" s="50" t="n">
+        <v>300100102</v>
+      </c>
+      <c r="L49" s="50" t="inlineStr">
+        <is>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="50" t="n">
-        <v>300100102</v>
+        <v>300100201</v>
       </c>
       <c r="B50" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C50" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_36</t>
         </is>
       </c>
       <c r="D50" s="50" t="n">
@@ -3476,42 +3487,44 @@
       </c>
       <c r="E50" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F50" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G50" s="50" t="n">
-        <v>300100102</v>
-      </c>
-      <c r="H50" s="50" t="n">
-        <v>300100101</v>
-      </c>
-      <c r="I50" s="50" t="n">
+        <v>300100201</v>
+      </c>
+      <c r="H50" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300100000,</t>
+        </is>
+      </c>
+      <c r="J50" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J50" s="50" t="n">
-        <v>300100102</v>
-      </c>
-      <c r="K50" s="50" t="inlineStr">
-        <is>
-          <t>孕育人类x10</t>
+      <c r="K50" s="50" t="n">
+        <v>300100201</v>
+      </c>
+      <c r="L50" s="50" t="inlineStr">
+        <is>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="50" t="n">
-        <v>300100201</v>
+        <v>300100301</v>
       </c>
       <c r="B51" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C51" s="50" t="inlineStr">
         <is>
-          <t>ui_research_36</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D51" s="50" t="n">
@@ -3519,7 +3532,7 @@
       </c>
       <c r="E51" s="50" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F51" s="50" t="inlineStr">
@@ -3528,35 +3541,37 @@
         </is>
       </c>
       <c r="G51" s="50" t="n">
-        <v>300100201</v>
+        <v>300100301</v>
       </c>
       <c r="H51" s="50" t="inlineStr">
         <is>
-          <t>100200001,300100000,</t>
-        </is>
-      </c>
-      <c r="I51" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J51" s="50" t="n">
-        <v>300100201</v>
-      </c>
-      <c r="K51" s="50" t="inlineStr">
-        <is>
-          <t>可转生为人类</t>
+          <t>300100000,</t>
+        </is>
+      </c>
+      <c r="J51" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K51" s="50" t="n">
+        <v>300100301</v>
+      </c>
+      <c r="L51" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="50" t="n">
-        <v>300100301</v>
+        <v>300200000</v>
       </c>
       <c r="B52" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C52" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D52" s="50" t="n">
@@ -3564,46 +3579,41 @@
       </c>
       <c r="E52" s="50" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F52" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" s="50" t="n">
-        <v>300100301</v>
-      </c>
-      <c r="H52" s="50" t="inlineStr">
-        <is>
-          <t>300100000,</t>
-        </is>
-      </c>
-      <c r="I52" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J52" s="50" t="n">
-        <v>300100301</v>
-      </c>
-      <c r="K52" s="50" t="inlineStr">
-        <is>
-          <t>奖励-可获取人类装备</t>
+        <v>300200000</v>
+      </c>
+      <c r="J52" s="50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="L52" s="50" t="inlineStr">
+        <is>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="50" t="n">
-        <v>300200000</v>
+        <v>300200001</v>
       </c>
       <c r="B53" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C53" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D53" s="50" t="n">
@@ -3611,41 +3621,44 @@
       </c>
       <c r="E53" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-300</t>
         </is>
       </c>
       <c r="F53" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G53" s="50" t="n">
+        <v>300200001</v>
+      </c>
+      <c r="H53" s="50" t="n">
         <v>300200000</v>
       </c>
-      <c r="I53" s="50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="K53" s="50" t="inlineStr">
-        <is>
-          <t>解锁种族：骷髅</t>
+      <c r="J53" s="50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K53" s="50" t="n">
+        <v>300200001</v>
+      </c>
+      <c r="L53" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="50" t="n">
-        <v>300200001</v>
+        <v>300200002</v>
       </c>
       <c r="B54" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D54" s="50" t="n">
@@ -3653,7 +3666,7 @@
       </c>
       <c r="E54" s="50" t="inlineStr">
         <is>
-          <t>-300</t>
+          <t>-150</t>
         </is>
       </c>
       <c r="F54" s="50" t="inlineStr">
@@ -3662,35 +3675,35 @@
         </is>
       </c>
       <c r="G54" s="50" t="n">
-        <v>300200001</v>
+        <v>300200002</v>
       </c>
       <c r="H54" s="50" t="n">
         <v>300200000</v>
       </c>
-      <c r="I54" s="50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" s="50" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="K54" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：骷髅战士</t>
+      <c r="J54" s="50" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K54" s="50" t="n">
+        <v>300200002</v>
+      </c>
+      <c r="L54" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="50" t="n">
-        <v>300200002</v>
+        <v>300200003</v>
       </c>
       <c r="B55" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C55" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D55" s="50" t="n">
@@ -3698,7 +3711,7 @@
       </c>
       <c r="E55" s="50" t="inlineStr">
         <is>
-          <t>-150</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F55" s="50" t="inlineStr">
@@ -3707,35 +3720,35 @@
         </is>
       </c>
       <c r="G55" s="50" t="n">
-        <v>300200002</v>
+        <v>300200003</v>
       </c>
       <c r="H55" s="50" t="n">
         <v>300200000</v>
       </c>
-      <c r="I55" s="50" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J55" s="50" t="n">
-        <v>300200002</v>
-      </c>
-      <c r="K55" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：骷髅投手</t>
+      <c r="J55" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="K55" s="50" t="n">
+        <v>300200003</v>
+      </c>
+      <c r="L55" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="50" t="n">
-        <v>300200003</v>
+        <v>300200004</v>
       </c>
       <c r="B56" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C56" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D56" s="50" t="n">
@@ -3743,7 +3756,7 @@
       </c>
       <c r="E56" s="50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F56" s="50" t="inlineStr">
@@ -3752,35 +3765,35 @@
         </is>
       </c>
       <c r="G56" s="50" t="n">
-        <v>300200003</v>
+        <v>300200004</v>
       </c>
       <c r="H56" s="50" t="n">
         <v>300200000</v>
       </c>
-      <c r="I56" s="50" t="inlineStr">
+      <c r="J56" s="50" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="J56" s="50" t="n">
-        <v>300200003</v>
-      </c>
-      <c r="K56" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+      <c r="K56" s="50" t="n">
+        <v>300200004</v>
+      </c>
+      <c r="L56" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="50" t="n">
-        <v>300200004</v>
+        <v>300200101</v>
       </c>
       <c r="B57" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C57" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D57" s="50" t="n">
@@ -3788,44 +3801,46 @@
       </c>
       <c r="E57" s="50" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F57" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G57" s="50" t="n">
-        <v>300200004</v>
-      </c>
-      <c r="H57" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I57" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J57" s="50" t="n">
-        <v>300200004</v>
-      </c>
-      <c r="K57" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+        <v>300200101</v>
+      </c>
+      <c r="H57" s="50" t="inlineStr">
+        <is>
+          <t>300200001|300200002|300200003|300200004|</t>
+        </is>
+      </c>
+      <c r="J57" s="50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K57" s="50" t="n">
+        <v>300200101</v>
+      </c>
+      <c r="L57" s="50" t="inlineStr">
+        <is>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51">
       <c r="A58" s="50" t="n">
-        <v>300200101</v>
+        <v>300200102</v>
       </c>
       <c r="B58" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C58" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D58" s="50" t="n">
@@ -3838,41 +3853,37 @@
       </c>
       <c r="F58" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G58" s="50" t="n">
+        <v>300200102</v>
+      </c>
+      <c r="H58" s="50" t="n">
         <v>300200101</v>
       </c>
-      <c r="H58" s="50" t="inlineStr">
-        <is>
-          <t>300200001|300200002|300200003|300200004|</t>
-        </is>
-      </c>
-      <c r="I58" s="50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="J58" s="50" t="n">
-        <v>300200101</v>
-      </c>
-      <c r="K58" s="50" t="inlineStr">
-        <is>
-          <t>孕育骷髅x5</t>
+        <v>100</v>
+      </c>
+      <c r="K58" s="50" t="n">
+        <v>300200102</v>
+      </c>
+      <c r="L58" s="50" t="inlineStr">
+        <is>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51">
       <c r="A59" s="50" t="n">
-        <v>300200102</v>
+        <v>300200201</v>
       </c>
       <c r="B59" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C59" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_35</t>
         </is>
       </c>
       <c r="D59" s="50" t="n">
@@ -3880,42 +3891,46 @@
       </c>
       <c r="E59" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F59" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G59" s="50" t="n">
-        <v>300200102</v>
-      </c>
-      <c r="H59" s="50" t="n">
-        <v>300200101</v>
-      </c>
-      <c r="I59" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J59" s="50" t="n">
-        <v>300200102</v>
-      </c>
-      <c r="K59" s="50" t="inlineStr">
-        <is>
-          <t>孕育骷髅x10</t>
+        <v>300200201</v>
+      </c>
+      <c r="H59" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300200000,</t>
+        </is>
+      </c>
+      <c r="J59" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K59" s="50" t="n">
+        <v>300200201</v>
+      </c>
+      <c r="L59" s="50" t="inlineStr">
+        <is>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51">
       <c r="A60" s="50" t="n">
-        <v>300200201</v>
+        <v>300200301</v>
       </c>
       <c r="B60" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="50" t="inlineStr">
         <is>
-          <t>ui_research_35</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D60" s="50" t="n">
@@ -3923,7 +3938,7 @@
       </c>
       <c r="E60" s="50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F60" s="50" t="inlineStr">
@@ -3932,37 +3947,37 @@
         </is>
       </c>
       <c r="G60" s="50" t="n">
-        <v>300200201</v>
+        <v>300200301</v>
       </c>
       <c r="H60" s="50" t="inlineStr">
         <is>
-          <t>100200001,300200000,</t>
-        </is>
-      </c>
-      <c r="I60" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J60" s="50" t="n">
-        <v>300200201</v>
-      </c>
-      <c r="K60" s="50" t="inlineStr">
-        <is>
-          <t>可转生为骷髅</t>
+          <t>300200000,</t>
+        </is>
+      </c>
+      <c r="J60" s="50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K60" s="50" t="n">
+        <v>300200301</v>
+      </c>
+      <c r="L60" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51">
       <c r="A61" s="50" t="n">
-        <v>300200301</v>
+        <v>300300000</v>
       </c>
       <c r="B61" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C61" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D61" s="50" t="n">
@@ -3970,46 +3985,44 @@
       </c>
       <c r="E61" s="50" t="inlineStr">
         <is>
+          <t>-800</t>
+        </is>
+      </c>
+      <c r="F61" s="50" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F61" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
-      </c>
       <c r="G61" s="50" t="n">
-        <v>300200301</v>
-      </c>
-      <c r="H61" s="50" t="inlineStr">
-        <is>
-          <t>300200000,</t>
-        </is>
-      </c>
-      <c r="I61" s="50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" s="50" t="n">
-        <v>300200301</v>
-      </c>
-      <c r="K61" s="50" t="inlineStr">
-        <is>
-          <t>奖励-可获取骷髅装备</t>
+        <v>300300000</v>
+      </c>
+      <c r="H61" s="50" t="n">
+        <v>300200000</v>
+      </c>
+      <c r="J61" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K61" s="50" t="n">
+        <v>300300000</v>
+      </c>
+      <c r="L61" s="50" t="inlineStr">
+        <is>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51">
       <c r="A62" s="50" t="n">
-        <v>300300000</v>
+        <v>300300001</v>
       </c>
       <c r="B62" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D62" s="50" t="n">
@@ -4017,44 +4030,42 @@
       </c>
       <c r="E62" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-1100</t>
         </is>
       </c>
       <c r="F62" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G62" s="50" t="n">
+        <v>300300001</v>
+      </c>
+      <c r="H62" s="50" t="n">
         <v>300300000</v>
       </c>
-      <c r="H62" s="50" t="n">
-        <v>300200000</v>
-      </c>
-      <c r="I62" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="J62" s="50" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="K62" s="50" t="inlineStr">
-        <is>
-          <t>解锁种族：史莱姆</t>
+        <v>100</v>
+      </c>
+      <c r="K62" s="50" t="n">
+        <v>300300001</v>
+      </c>
+      <c r="L62" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51">
       <c r="A63" s="50" t="n">
-        <v>300300001</v>
+        <v>300300002</v>
       </c>
       <c r="B63" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C63" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_54</t>
         </is>
       </c>
       <c r="D63" s="50" t="n">
@@ -4062,7 +4073,7 @@
       </c>
       <c r="E63" s="50" t="inlineStr">
         <is>
-          <t>-1100</t>
+          <t>-950</t>
         </is>
       </c>
       <c r="F63" s="50" t="inlineStr">
@@ -4071,26 +4082,28 @@
         </is>
       </c>
       <c r="G63" s="50" t="n">
-        <v>300300001</v>
+        <v>300300002</v>
       </c>
       <c r="H63" s="50" t="n">
         <v>300300000</v>
       </c>
-      <c r="I63" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J63" s="50" t="n">
-        <v>300300001</v>
-      </c>
-      <c r="K63" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：守护史莱姆</t>
+      <c r="J63" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K63" s="50" t="n">
+        <v>300300002</v>
+      </c>
+      <c r="L63" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51">
       <c r="A64" s="50" t="n">
-        <v>300300002</v>
+        <v>300300003</v>
       </c>
       <c r="B64" s="50" t="n">
         <v>3</v>
@@ -4105,44 +4118,44 @@
       </c>
       <c r="E64" s="50" t="inlineStr">
         <is>
-          <t>-950</t>
+          <t>-650</t>
         </is>
       </c>
       <c r="F64" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="G64" s="50" t="n">
-        <v>300300002</v>
+        <v>300300003</v>
       </c>
       <c r="H64" s="50" t="n">
         <v>300300000</v>
       </c>
-      <c r="I64" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J64" s="50" t="n">
-        <v>300300002</v>
-      </c>
-      <c r="K64" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：自爆史莱姆</t>
+      <c r="J64" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="K64" s="50" t="n">
+        <v>300300003</v>
+      </c>
+      <c r="L64" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="50" t="n">
-        <v>300300003</v>
+        <v>300300004</v>
       </c>
       <c r="B65" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C65" s="50" t="inlineStr">
         <is>
-          <t>ui_research_54</t>
+          <t>ui_research_53</t>
         </is>
       </c>
       <c r="D65" s="50" t="n">
@@ -4150,44 +4163,44 @@
       </c>
       <c r="E65" s="50" t="inlineStr">
         <is>
-          <t>-650</t>
+          <t>-500</t>
         </is>
       </c>
       <c r="F65" s="50" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G65" s="50" t="n">
-        <v>300300003</v>
+        <v>300300004</v>
       </c>
       <c r="H65" s="50" t="n">
         <v>300300000</v>
       </c>
-      <c r="I65" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J65" s="50" t="n">
-        <v>300300003</v>
-      </c>
-      <c r="K65" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：烂泥史莱姆</t>
+      <c r="J65" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="K65" s="50" t="n">
+        <v>300300004</v>
+      </c>
+      <c r="L65" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="50" t="n">
-        <v>300300004</v>
+        <v>300300101</v>
       </c>
       <c r="B66" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C66" s="50" t="inlineStr">
         <is>
-          <t>ui_research_53</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D66" s="50" t="n">
@@ -4195,44 +4208,46 @@
       </c>
       <c r="E66" s="50" t="inlineStr">
         <is>
-          <t>-500</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F66" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G66" s="50" t="n">
-        <v>300300004</v>
-      </c>
-      <c r="H66" s="50" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="I66" s="50" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J66" s="50" t="n">
-        <v>300300004</v>
-      </c>
-      <c r="K66" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：毒液史莱姆</t>
+        <v>300300101</v>
+      </c>
+      <c r="H66" s="50" t="inlineStr">
+        <is>
+          <t>300300001|300300002|300300003|300300004|</t>
+        </is>
+      </c>
+      <c r="J66" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="K66" s="50" t="n">
+        <v>300300101</v>
+      </c>
+      <c r="L66" s="50" t="inlineStr">
+        <is>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51">
       <c r="A67" s="50" t="n">
-        <v>300300101</v>
+        <v>300300102</v>
       </c>
       <c r="B67" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D67" s="50" t="n">
@@ -4245,41 +4260,39 @@
       </c>
       <c r="F67" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G67" s="50" t="n">
+        <v>300300102</v>
+      </c>
+      <c r="H67" s="50" t="n">
         <v>300300101</v>
       </c>
-      <c r="H67" s="50" t="inlineStr">
-        <is>
-          <t>300300001|300300002|300300003|300300004|</t>
-        </is>
-      </c>
-      <c r="I67" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J67" s="50" t="n">
-        <v>300300101</v>
-      </c>
-      <c r="K67" s="50" t="inlineStr">
-        <is>
-          <t>孕育史莱姆x5</t>
+      <c r="J67" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="K67" s="50" t="n">
+        <v>300300102</v>
+      </c>
+      <c r="L67" s="50" t="inlineStr">
+        <is>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51">
       <c r="A68" s="50" t="n">
-        <v>300300102</v>
+        <v>300300201</v>
       </c>
       <c r="B68" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C68" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_37</t>
         </is>
       </c>
       <c r="D68" s="50" t="n">
@@ -4287,44 +4300,46 @@
       </c>
       <c r="E68" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-650</t>
         </is>
       </c>
       <c r="F68" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G68" s="50" t="n">
-        <v>300300102</v>
-      </c>
-      <c r="H68" s="50" t="n">
-        <v>300300101</v>
-      </c>
-      <c r="I68" s="50" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J68" s="50" t="n">
-        <v>300300102</v>
-      </c>
-      <c r="K68" s="50" t="inlineStr">
-        <is>
-          <t>孕育史莱姆x10</t>
+        <v>300300201</v>
+      </c>
+      <c r="H68" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300300000,</t>
+        </is>
+      </c>
+      <c r="J68" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K68" s="50" t="n">
+        <v>300300201</v>
+      </c>
+      <c r="L68" s="50" t="inlineStr">
+        <is>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51">
       <c r="A69" s="50" t="n">
-        <v>300300201</v>
+        <v>300300301</v>
       </c>
       <c r="B69" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C69" s="50" t="inlineStr">
         <is>
-          <t>ui_research_37</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D69" s="50" t="n">
@@ -4332,7 +4347,7 @@
       </c>
       <c r="E69" s="50" t="inlineStr">
         <is>
-          <t>-650</t>
+          <t>-800</t>
         </is>
       </c>
       <c r="F69" s="50" t="inlineStr">
@@ -4341,37 +4356,37 @@
         </is>
       </c>
       <c r="G69" s="50" t="n">
-        <v>300300201</v>
+        <v>300300301</v>
       </c>
       <c r="H69" s="50" t="inlineStr">
         <is>
-          <t>100200001,300300000,</t>
-        </is>
-      </c>
-      <c r="I69" s="50" t="inlineStr">
+          <t>300300000,</t>
+        </is>
+      </c>
+      <c r="J69" s="50" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="J69" s="50" t="n">
-        <v>300300201</v>
-      </c>
-      <c r="K69" s="50" t="inlineStr">
-        <is>
-          <t>可转生为史莱姆</t>
+      <c r="K69" s="50" t="n">
+        <v>300300301</v>
+      </c>
+      <c r="L69" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51">
       <c r="A70" s="50" t="n">
-        <v>300300301</v>
+        <v>300400000</v>
       </c>
       <c r="B70" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D70" s="50" t="n">
@@ -4379,46 +4394,42 @@
       </c>
       <c r="E70" s="50" t="inlineStr">
         <is>
-          <t>-800</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F70" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G70" s="50" t="n">
-        <v>300300301</v>
-      </c>
-      <c r="H70" s="50" t="inlineStr">
-        <is>
-          <t>300300000,</t>
-        </is>
-      </c>
-      <c r="I70" s="50" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+        <v>300400000</v>
+      </c>
+      <c r="H70" s="50" t="n">
+        <v>300600000</v>
       </c>
       <c r="J70" s="50" t="n">
-        <v>300300301</v>
-      </c>
-      <c r="K70" s="50" t="inlineStr">
-        <is>
-          <t>奖励-可获取史莱姆装备</t>
+        <v>100</v>
+      </c>
+      <c r="K70" s="50" t="n">
+        <v>300400000</v>
+      </c>
+      <c r="L70" s="50" t="inlineStr">
+        <is>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51">
       <c r="A71" s="50" t="n">
-        <v>300400000</v>
+        <v>300400001</v>
       </c>
       <c r="B71" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C71" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D71" s="50" t="n">
@@ -4426,42 +4437,42 @@
       </c>
       <c r="E71" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2700</t>
         </is>
       </c>
       <c r="F71" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G71" s="50" t="n">
+        <v>300400001</v>
+      </c>
+      <c r="H71" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="H71" s="50" t="n">
-        <v>300600000</v>
-      </c>
-      <c r="I71" s="50" t="n">
+      <c r="J71" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J71" s="50" t="n">
-        <v>300400000</v>
-      </c>
-      <c r="K71" s="50" t="inlineStr">
-        <is>
-          <t>解锁种族：魅魔</t>
+      <c r="K71" s="50" t="n">
+        <v>300400001</v>
+      </c>
+      <c r="L71" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51">
       <c r="A72" s="50" t="n">
-        <v>300400001</v>
+        <v>300400002</v>
       </c>
       <c r="B72" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C72" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_45</t>
         </is>
       </c>
       <c r="D72" s="50" t="n">
@@ -4469,7 +4480,7 @@
       </c>
       <c r="E72" s="50" t="inlineStr">
         <is>
-          <t>-2700</t>
+          <t>-2550</t>
         </is>
       </c>
       <c r="F72" s="50" t="inlineStr">
@@ -4478,33 +4489,33 @@
         </is>
       </c>
       <c r="G72" s="50" t="n">
-        <v>300400001</v>
+        <v>300400002</v>
       </c>
       <c r="H72" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="I72" s="50" t="n">
+      <c r="J72" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J72" s="50" t="n">
-        <v>300400001</v>
-      </c>
-      <c r="K72" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：战之魅魔</t>
+      <c r="K72" s="50" t="n">
+        <v>300400002</v>
+      </c>
+      <c r="L72" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51">
       <c r="A73" s="50" t="n">
-        <v>300400002</v>
+        <v>300400003</v>
       </c>
       <c r="B73" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C73" s="50" t="inlineStr">
         <is>
-          <t>ui_research_45</t>
+          <t>ui_research_52</t>
         </is>
       </c>
       <c r="D73" s="50" t="n">
@@ -4512,7 +4523,7 @@
       </c>
       <c r="E73" s="50" t="inlineStr">
         <is>
-          <t>-2550</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F73" s="50" t="inlineStr">
@@ -4521,33 +4532,33 @@
         </is>
       </c>
       <c r="G73" s="50" t="n">
-        <v>300400002</v>
+        <v>300400003</v>
       </c>
       <c r="H73" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="I73" s="50" t="n">
+      <c r="J73" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J73" s="50" t="n">
-        <v>300400002</v>
-      </c>
-      <c r="K73" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：愈之魅魔</t>
+      <c r="K73" s="50" t="n">
+        <v>300400003</v>
+      </c>
+      <c r="L73" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51">
       <c r="A74" s="50" t="n">
-        <v>300400003</v>
+        <v>300400004</v>
       </c>
       <c r="B74" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C74" s="50" t="inlineStr">
         <is>
-          <t>ui_research_52</t>
+          <t>ui_research_49</t>
         </is>
       </c>
       <c r="D74" s="50" t="n">
@@ -4555,7 +4566,7 @@
       </c>
       <c r="E74" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F74" s="50" t="inlineStr">
@@ -4564,33 +4575,33 @@
         </is>
       </c>
       <c r="G74" s="50" t="n">
-        <v>300400003</v>
+        <v>300400004</v>
       </c>
       <c r="H74" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="I74" s="50" t="n">
+      <c r="J74" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J74" s="50" t="n">
-        <v>300400003</v>
-      </c>
-      <c r="K74" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：惑之魅魔</t>
+      <c r="K74" s="50" t="n">
+        <v>300400004</v>
+      </c>
+      <c r="L74" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="50" t="n">
-        <v>300400004</v>
+        <v>300400005</v>
       </c>
       <c r="B75" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C75" s="50" t="inlineStr">
         <is>
-          <t>ui_research_49</t>
+          <t>ui_research_51</t>
         </is>
       </c>
       <c r="D75" s="50" t="n">
@@ -4598,7 +4609,7 @@
       </c>
       <c r="E75" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2100</t>
         </is>
       </c>
       <c r="F75" s="50" t="inlineStr">
@@ -4607,33 +4618,33 @@
         </is>
       </c>
       <c r="G75" s="50" t="n">
-        <v>300400004</v>
+        <v>300400005</v>
       </c>
       <c r="H75" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="I75" s="50" t="n">
+      <c r="J75" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J75" s="50" t="n">
-        <v>300400004</v>
-      </c>
-      <c r="K75" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：奥之魅魔</t>
+      <c r="K75" s="50" t="n">
+        <v>300400005</v>
+      </c>
+      <c r="L75" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="50" t="n">
-        <v>300400005</v>
+        <v>300400101</v>
       </c>
       <c r="B76" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C76" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D76" s="50" t="n">
@@ -4641,42 +4652,44 @@
       </c>
       <c r="E76" s="50" t="inlineStr">
         <is>
-          <t>-2100</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F76" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G76" s="50" t="n">
-        <v>300400005</v>
-      </c>
-      <c r="H76" s="50" t="n">
-        <v>300400000</v>
-      </c>
-      <c r="I76" s="50" t="n">
+        <v>300400101</v>
+      </c>
+      <c r="H76" s="50" t="inlineStr">
+        <is>
+          <t>300400001|300400002|300400003|300400004|300400005|</t>
+        </is>
+      </c>
+      <c r="J76" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J76" s="50" t="n">
-        <v>300400005</v>
-      </c>
-      <c r="K76" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：盾之魅魔</t>
+      <c r="K76" s="50" t="n">
+        <v>300400101</v>
+      </c>
+      <c r="L76" s="50" t="inlineStr">
+        <is>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="50" t="n">
-        <v>300400101</v>
+        <v>300400102</v>
       </c>
       <c r="B77" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C77" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D77" s="50" t="n">
@@ -4689,39 +4702,37 @@
       </c>
       <c r="F77" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G77" s="50" t="n">
+        <v>300400102</v>
+      </c>
+      <c r="H77" s="50" t="n">
         <v>300400101</v>
       </c>
-      <c r="H77" s="50" t="inlineStr">
-        <is>
-          <t>300400001|300400002|300400003|300400004|300400005|</t>
-        </is>
-      </c>
-      <c r="I77" s="50" t="n">
+      <c r="J77" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J77" s="50" t="n">
-        <v>300400101</v>
-      </c>
-      <c r="K77" s="50" t="inlineStr">
-        <is>
-          <t>孕育魅魔x5</t>
+      <c r="K77" s="50" t="n">
+        <v>300400102</v>
+      </c>
+      <c r="L77" s="50" t="inlineStr">
+        <is>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51">
       <c r="A78" s="50" t="n">
-        <v>300400102</v>
+        <v>300400201</v>
       </c>
       <c r="B78" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C78" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D78" s="50" t="n">
@@ -4729,42 +4740,44 @@
       </c>
       <c r="E78" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F78" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G78" s="50" t="n">
-        <v>300400102</v>
-      </c>
-      <c r="H78" s="50" t="n">
-        <v>300400101</v>
-      </c>
-      <c r="I78" s="50" t="n">
+        <v>300400201</v>
+      </c>
+      <c r="H78" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300400000,</t>
+        </is>
+      </c>
+      <c r="J78" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J78" s="50" t="n">
-        <v>300400102</v>
-      </c>
-      <c r="K78" s="50" t="inlineStr">
-        <is>
-          <t>孕育魅魔x10</t>
+      <c r="K78" s="50" t="n">
+        <v>300400201</v>
+      </c>
+      <c r="L78" s="50" t="inlineStr">
+        <is>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51">
       <c r="A79" s="50" t="n">
-        <v>300400201</v>
+        <v>300400301</v>
       </c>
       <c r="B79" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C79" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D79" s="50" t="n">
@@ -4772,7 +4785,7 @@
       </c>
       <c r="E79" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F79" s="50" t="inlineStr">
@@ -4781,35 +4794,35 @@
         </is>
       </c>
       <c r="G79" s="50" t="n">
-        <v>300400201</v>
+        <v>300400301</v>
       </c>
       <c r="H79" s="50" t="inlineStr">
         <is>
-          <t>100200001,300400000,</t>
-        </is>
-      </c>
-      <c r="I79" s="50" t="n">
+          <t>300400000,</t>
+        </is>
+      </c>
+      <c r="J79" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J79" s="50" t="n">
-        <v>300400201</v>
-      </c>
-      <c r="K79" s="50" t="inlineStr">
-        <is>
-          <t>可转生为魅魔</t>
+      <c r="K79" s="50" t="n">
+        <v>300400301</v>
+      </c>
+      <c r="L79" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51">
       <c r="A80" s="50" t="n">
-        <v>300400301</v>
+        <v>300500000</v>
       </c>
       <c r="B80" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C80" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D80" s="50" t="n">
@@ -4817,44 +4830,42 @@
       </c>
       <c r="E80" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F80" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G80" s="50" t="n">
-        <v>300400301</v>
-      </c>
-      <c r="H80" s="50" t="inlineStr">
-        <is>
-          <t>300400000,</t>
-        </is>
-      </c>
-      <c r="I80" s="50" t="n">
+        <v>300500000</v>
+      </c>
+      <c r="H80" s="50" t="n">
+        <v>300700000</v>
+      </c>
+      <c r="J80" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J80" s="50" t="n">
-        <v>300400301</v>
-      </c>
-      <c r="K80" s="50" t="inlineStr">
-        <is>
-          <t>奖励-可获取魅魔装备</t>
+      <c r="K80" s="50" t="n">
+        <v>300500000</v>
+      </c>
+      <c r="L80" s="50" t="inlineStr">
+        <is>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51">
       <c r="A81" s="50" t="n">
-        <v>300500000</v>
+        <v>300500001</v>
       </c>
       <c r="B81" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C81" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D81" s="50" t="n">
@@ -4862,42 +4873,42 @@
       </c>
       <c r="E81" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F81" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G81" s="50" t="n">
+        <v>300500001</v>
+      </c>
+      <c r="H81" s="50" t="n">
         <v>300500000</v>
       </c>
-      <c r="H81" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="I81" s="50" t="n">
+      <c r="J81" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J81" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="K81" s="50" t="inlineStr">
-        <is>
-          <t>解锁种族：牛头人</t>
+      <c r="K81" s="50" t="n">
+        <v>300500001</v>
+      </c>
+      <c r="L81" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51">
       <c r="A82" s="50" t="n">
-        <v>300500001</v>
+        <v>300500002</v>
       </c>
       <c r="B82" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C82" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D82" s="50" t="n">
@@ -4905,7 +4916,7 @@
       </c>
       <c r="E82" s="50" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F82" s="50" t="inlineStr">
@@ -4914,33 +4925,33 @@
         </is>
       </c>
       <c r="G82" s="50" t="n">
-        <v>300500001</v>
+        <v>300500002</v>
       </c>
       <c r="H82" s="50" t="n">
         <v>300500000</v>
       </c>
-      <c r="I82" s="50" t="n">
+      <c r="J82" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J82" s="50" t="n">
-        <v>300500001</v>
-      </c>
-      <c r="K82" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：牛头人战士</t>
+      <c r="K82" s="50" t="n">
+        <v>300500002</v>
+      </c>
+      <c r="L82" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51">
       <c r="A83" s="50" t="n">
-        <v>300500002</v>
+        <v>300500003</v>
       </c>
       <c r="B83" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C83" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D83" s="50" t="n">
@@ -4948,7 +4959,7 @@
       </c>
       <c r="E83" s="50" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F83" s="50" t="inlineStr">
@@ -4957,33 +4968,33 @@
         </is>
       </c>
       <c r="G83" s="50" t="n">
-        <v>300500002</v>
+        <v>300500003</v>
       </c>
       <c r="H83" s="50" t="n">
         <v>300500000</v>
       </c>
-      <c r="I83" s="50" t="n">
+      <c r="J83" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J83" s="50" t="n">
-        <v>300500002</v>
-      </c>
-      <c r="K83" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：牛头人投手</t>
+      <c r="K83" s="50" t="n">
+        <v>300500003</v>
+      </c>
+      <c r="L83" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="50" t="n">
-        <v>300500003</v>
+        <v>300500004</v>
       </c>
       <c r="B84" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C84" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D84" s="50" t="n">
@@ -4991,7 +5002,7 @@
       </c>
       <c r="E84" s="50" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="F84" s="50" t="inlineStr">
@@ -5000,33 +5011,33 @@
         </is>
       </c>
       <c r="G84" s="50" t="n">
-        <v>300500003</v>
+        <v>300500004</v>
       </c>
       <c r="H84" s="50" t="n">
         <v>300500000</v>
       </c>
-      <c r="I84" s="50" t="n">
+      <c r="J84" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J84" s="50" t="n">
-        <v>300500003</v>
-      </c>
-      <c r="K84" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+      <c r="K84" s="50" t="n">
+        <v>300500004</v>
+      </c>
+      <c r="L84" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="50" t="n">
-        <v>300500004</v>
+        <v>300500101</v>
       </c>
       <c r="B85" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C85" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D85" s="50" t="n">
@@ -5034,42 +5045,44 @@
       </c>
       <c r="E85" s="50" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F85" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G85" s="50" t="n">
-        <v>300500004</v>
-      </c>
-      <c r="H85" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="I85" s="50" t="n">
+        <v>300500101</v>
+      </c>
+      <c r="H85" s="50" t="inlineStr">
+        <is>
+          <t>300500001|300500002|300500003|300500004|</t>
+        </is>
+      </c>
+      <c r="J85" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J85" s="50" t="n">
-        <v>300500004</v>
-      </c>
-      <c r="K85" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+      <c r="K85" s="50" t="n">
+        <v>300500101</v>
+      </c>
+      <c r="L85" s="50" t="inlineStr">
+        <is>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="50" t="n">
-        <v>300500101</v>
+        <v>300500102</v>
       </c>
       <c r="B86" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C86" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D86" s="50" t="n">
@@ -5082,39 +5095,37 @@
       </c>
       <c r="F86" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G86" s="50" t="n">
+        <v>300500102</v>
+      </c>
+      <c r="H86" s="50" t="n">
         <v>300500101</v>
       </c>
-      <c r="H86" s="50" t="inlineStr">
-        <is>
-          <t>300500001|300500002|300500003|300500004|</t>
-        </is>
-      </c>
-      <c r="I86" s="50" t="n">
+      <c r="J86" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J86" s="50" t="n">
-        <v>300500101</v>
-      </c>
-      <c r="K86" s="50" t="inlineStr">
-        <is>
-          <t>孕育牛头人x5</t>
+      <c r="K86" s="50" t="n">
+        <v>300500102</v>
+      </c>
+      <c r="L86" s="50" t="inlineStr">
+        <is>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="50" t="n">
-        <v>300500102</v>
+        <v>300500201</v>
       </c>
       <c r="B87" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C87" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D87" s="50" t="n">
@@ -5122,42 +5133,44 @@
       </c>
       <c r="E87" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="F87" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G87" s="50" t="n">
-        <v>300500102</v>
-      </c>
-      <c r="H87" s="50" t="n">
-        <v>300500101</v>
-      </c>
-      <c r="I87" s="50" t="n">
+        <v>300500201</v>
+      </c>
+      <c r="H87" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300500000,</t>
+        </is>
+      </c>
+      <c r="J87" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J87" s="50" t="n">
-        <v>300500102</v>
-      </c>
-      <c r="K87" s="50" t="inlineStr">
-        <is>
-          <t>孕育牛头人x10</t>
+      <c r="K87" s="50" t="n">
+        <v>300500201</v>
+      </c>
+      <c r="L87" s="50" t="inlineStr">
+        <is>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="50" t="n">
-        <v>300500201</v>
+        <v>300500301</v>
       </c>
       <c r="B88" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C88" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D88" s="50" t="n">
@@ -5165,7 +5178,7 @@
       </c>
       <c r="E88" s="50" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F88" s="50" t="inlineStr">
@@ -5174,35 +5187,35 @@
         </is>
       </c>
       <c r="G88" s="50" t="n">
-        <v>300500201</v>
+        <v>300500301</v>
       </c>
       <c r="H88" s="50" t="inlineStr">
         <is>
-          <t>100200001,300500000,</t>
-        </is>
-      </c>
-      <c r="I88" s="50" t="n">
+          <t>300500000,</t>
+        </is>
+      </c>
+      <c r="J88" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J88" s="50" t="n">
-        <v>300500201</v>
-      </c>
-      <c r="K88" s="50" t="inlineStr">
-        <is>
-          <t>可转生为牛头人</t>
+      <c r="K88" s="50" t="n">
+        <v>300500301</v>
+      </c>
+      <c r="L88" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="50" t="n">
-        <v>300500301</v>
+        <v>300600000</v>
       </c>
       <c r="B89" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C89" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D89" s="50" t="n">
@@ -5210,44 +5223,42 @@
       </c>
       <c r="E89" s="50" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F89" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G89" s="50" t="n">
-        <v>300500301</v>
-      </c>
-      <c r="H89" s="50" t="inlineStr">
-        <is>
-          <t>300500000,</t>
-        </is>
-      </c>
-      <c r="I89" s="50" t="n">
+        <v>300600000</v>
+      </c>
+      <c r="H89" s="50" t="n">
+        <v>300300000</v>
+      </c>
+      <c r="J89" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J89" s="50" t="n">
-        <v>300500301</v>
-      </c>
-      <c r="K89" s="50" t="inlineStr">
-        <is>
-          <t>奖励-可获取牛头人装备</t>
+      <c r="K89" s="50" t="n">
+        <v>300600000</v>
+      </c>
+      <c r="L89" s="50" t="inlineStr">
+        <is>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="50" t="n">
-        <v>300600000</v>
+        <v>300600001</v>
       </c>
       <c r="B90" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C90" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_44</t>
         </is>
       </c>
       <c r="D90" s="50" t="n">
@@ -5255,42 +5266,42 @@
       </c>
       <c r="E90" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1900</t>
         </is>
       </c>
       <c r="F90" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G90" s="50" t="n">
+        <v>300600001</v>
+      </c>
+      <c r="H90" s="50" t="n">
         <v>300600000</v>
       </c>
-      <c r="H90" s="50" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="I90" s="50" t="n">
+      <c r="J90" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J90" s="50" t="n">
-        <v>300600000</v>
-      </c>
-      <c r="K90" s="50" t="inlineStr">
-        <is>
-          <t>解锁种族：哥布林</t>
+      <c r="K90" s="50" t="n">
+        <v>300600001</v>
+      </c>
+      <c r="L90" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="50" t="n">
-        <v>300600001</v>
+        <v>300600002</v>
       </c>
       <c r="B91" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C91" s="50" t="inlineStr">
         <is>
-          <t>ui_research_44</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D91" s="50" t="n">
@@ -5298,7 +5309,7 @@
       </c>
       <c r="E91" s="50" t="inlineStr">
         <is>
-          <t>-1900</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="F91" s="50" t="inlineStr">
@@ -5307,33 +5318,33 @@
         </is>
       </c>
       <c r="G91" s="50" t="n">
-        <v>300600001</v>
+        <v>300600002</v>
       </c>
       <c r="H91" s="50" t="n">
         <v>300600000</v>
       </c>
-      <c r="I91" s="50" t="n">
+      <c r="J91" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J91" s="50" t="n">
-        <v>300600001</v>
-      </c>
-      <c r="K91" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：哥布林刺客</t>
+      <c r="K91" s="50" t="n">
+        <v>300600002</v>
+      </c>
+      <c r="L91" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="50" t="n">
-        <v>300600002</v>
+        <v>300600003</v>
       </c>
       <c r="B92" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D92" s="50" t="n">
@@ -5341,7 +5352,7 @@
       </c>
       <c r="E92" s="50" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F92" s="50" t="inlineStr">
@@ -5350,33 +5361,33 @@
         </is>
       </c>
       <c r="G92" s="50" t="n">
-        <v>300600002</v>
+        <v>300600003</v>
       </c>
       <c r="H92" s="50" t="n">
         <v>300600000</v>
       </c>
-      <c r="I92" s="50" t="n">
+      <c r="J92" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J92" s="50" t="n">
-        <v>300600002</v>
-      </c>
-      <c r="K92" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：哥布林弓箭手</t>
+      <c r="K92" s="50" t="n">
+        <v>300600003</v>
+      </c>
+      <c r="L92" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="50" t="n">
-        <v>300600003</v>
+        <v>300600004</v>
       </c>
       <c r="B93" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C93" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D93" s="50" t="n">
@@ -5384,7 +5395,7 @@
       </c>
       <c r="E93" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F93" s="50" t="inlineStr">
@@ -5393,33 +5404,33 @@
         </is>
       </c>
       <c r="G93" s="50" t="n">
-        <v>300600003</v>
+        <v>300600004</v>
       </c>
       <c r="H93" s="50" t="n">
         <v>300600000</v>
       </c>
-      <c r="I93" s="50" t="n">
+      <c r="J93" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J93" s="50" t="n">
-        <v>300600003</v>
-      </c>
-      <c r="K93" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：哥布林敢死队</t>
+      <c r="K93" s="50" t="n">
+        <v>300600004</v>
+      </c>
+      <c r="L93" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="50" t="n">
-        <v>300600004</v>
+        <v>300600005</v>
       </c>
       <c r="B94" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C94" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D94" s="50" t="n">
@@ -5427,7 +5438,7 @@
       </c>
       <c r="E94" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>-1300</t>
         </is>
       </c>
       <c r="F94" s="50" t="inlineStr">
@@ -5436,33 +5447,33 @@
         </is>
       </c>
       <c r="G94" s="50" t="n">
-        <v>300600004</v>
+        <v>300600005</v>
       </c>
       <c r="H94" s="50" t="n">
         <v>300600000</v>
       </c>
-      <c r="I94" s="50" t="n">
+      <c r="J94" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J94" s="50" t="n">
-        <v>300600004</v>
-      </c>
-      <c r="K94" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+      <c r="K94" s="50" t="n">
+        <v>300600005</v>
+      </c>
+      <c r="L94" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="50" t="n">
-        <v>300600005</v>
+        <v>300600101</v>
       </c>
       <c r="B95" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C95" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D95" s="50" t="n">
@@ -5470,42 +5481,44 @@
       </c>
       <c r="E95" s="50" t="inlineStr">
         <is>
-          <t>-1300</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F95" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G95" s="50" t="n">
-        <v>300600005</v>
-      </c>
-      <c r="H95" s="50" t="n">
-        <v>300600000</v>
-      </c>
-      <c r="I95" s="50" t="n">
+        <v>300600101</v>
+      </c>
+      <c r="H95" s="50" t="inlineStr">
+        <is>
+          <t>300600001|300600002|300600003|300600004|</t>
+        </is>
+      </c>
+      <c r="J95" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J95" s="50" t="n">
-        <v>300600005</v>
-      </c>
-      <c r="K95" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+      <c r="K95" s="50" t="n">
+        <v>300600101</v>
+      </c>
+      <c r="L95" s="50" t="inlineStr">
+        <is>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="50" t="n">
-        <v>300600101</v>
+        <v>300600102</v>
       </c>
       <c r="B96" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C96" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D96" s="50" t="n">
@@ -5518,39 +5531,37 @@
       </c>
       <c r="F96" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G96" s="50" t="n">
+        <v>300600102</v>
+      </c>
+      <c r="H96" s="50" t="n">
         <v>300600101</v>
       </c>
-      <c r="H96" s="50" t="inlineStr">
-        <is>
-          <t>300600001|300600002|300600003|300600004|</t>
-        </is>
-      </c>
-      <c r="I96" s="50" t="n">
+      <c r="J96" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J96" s="50" t="n">
-        <v>300600101</v>
-      </c>
-      <c r="K96" s="50" t="inlineStr">
-        <is>
-          <t>孕育哥布林x5</t>
+      <c r="K96" s="50" t="n">
+        <v>300600102</v>
+      </c>
+      <c r="L96" s="50" t="inlineStr">
+        <is>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="50" t="n">
-        <v>300600102</v>
+        <v>300600201</v>
       </c>
       <c r="B97" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C97" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D97" s="50" t="n">
@@ -5558,42 +5569,44 @@
       </c>
       <c r="E97" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>-1450</t>
         </is>
       </c>
       <c r="F97" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G97" s="50" t="n">
-        <v>300600102</v>
-      </c>
-      <c r="H97" s="50" t="n">
-        <v>300600101</v>
-      </c>
-      <c r="I97" s="50" t="n">
+        <v>300600201</v>
+      </c>
+      <c r="H97" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300600000,</t>
+        </is>
+      </c>
+      <c r="J97" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J97" s="50" t="n">
-        <v>300600102</v>
-      </c>
-      <c r="K97" s="50" t="inlineStr">
-        <is>
-          <t>孕育哥布林x10</t>
+      <c r="K97" s="50" t="n">
+        <v>300600201</v>
+      </c>
+      <c r="L97" s="50" t="inlineStr">
+        <is>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="50" t="n">
-        <v>300600201</v>
+        <v>300600301</v>
       </c>
       <c r="B98" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C98" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D98" s="50" t="n">
@@ -5601,7 +5614,7 @@
       </c>
       <c r="E98" s="50" t="inlineStr">
         <is>
-          <t>-1450</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F98" s="50" t="inlineStr">
@@ -5610,35 +5623,35 @@
         </is>
       </c>
       <c r="G98" s="50" t="n">
-        <v>300600201</v>
+        <v>300600301</v>
       </c>
       <c r="H98" s="50" t="inlineStr">
         <is>
-          <t>100200001,300600000,</t>
-        </is>
-      </c>
-      <c r="I98" s="50" t="n">
+          <t>300600000,</t>
+        </is>
+      </c>
+      <c r="J98" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J98" s="50" t="n">
-        <v>300600201</v>
-      </c>
-      <c r="K98" s="50" t="inlineStr">
-        <is>
-          <t>可转生为哥布林</t>
+      <c r="K98" s="50" t="n">
+        <v>300600301</v>
+      </c>
+      <c r="L98" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="50" t="n">
-        <v>300600301</v>
+        <v>300700000</v>
       </c>
       <c r="B99" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C99" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_38</t>
         </is>
       </c>
       <c r="D99" s="50" t="n">
@@ -5646,44 +5659,42 @@
       </c>
       <c r="E99" s="50" t="inlineStr">
         <is>
-          <t>-1600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F99" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G99" s="50" t="n">
-        <v>300600301</v>
-      </c>
-      <c r="H99" s="50" t="inlineStr">
-        <is>
-          <t>300600000,</t>
-        </is>
-      </c>
-      <c r="I99" s="50" t="n">
+        <v>300700000</v>
+      </c>
+      <c r="H99" s="50" t="n">
+        <v>300100000</v>
+      </c>
+      <c r="J99" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J99" s="50" t="n">
-        <v>300600301</v>
-      </c>
-      <c r="K99" s="50" t="inlineStr">
-        <is>
-          <t>奖励-可获取哥布林装备</t>
+      <c r="K99" s="50" t="n">
+        <v>300700000</v>
+      </c>
+      <c r="L99" s="50" t="inlineStr">
+        <is>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="50" t="n">
-        <v>300700000</v>
+        <v>300700001</v>
       </c>
       <c r="B100" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C100" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D100" s="50" t="n">
@@ -5691,42 +5702,42 @@
       </c>
       <c r="E100" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="F100" s="50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G100" s="50" t="n">
+        <v>300700001</v>
+      </c>
+      <c r="H100" s="50" t="n">
         <v>300700000</v>
       </c>
-      <c r="H100" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="I100" s="50" t="n">
+      <c r="J100" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J100" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="K100" s="50" t="inlineStr">
-        <is>
-          <t>解锁种族：兽人</t>
+      <c r="K100" s="50" t="n">
+        <v>300700001</v>
+      </c>
+      <c r="L100" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="50" t="n">
-        <v>300700001</v>
+        <v>300700002</v>
       </c>
       <c r="B101" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C101" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D101" s="50" t="n">
@@ -5734,7 +5745,7 @@
       </c>
       <c r="E101" s="50" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F101" s="50" t="inlineStr">
@@ -5743,33 +5754,33 @@
         </is>
       </c>
       <c r="G101" s="50" t="n">
-        <v>300700001</v>
+        <v>300700002</v>
       </c>
       <c r="H101" s="50" t="n">
         <v>300700000</v>
       </c>
-      <c r="I101" s="50" t="n">
+      <c r="J101" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J101" s="50" t="n">
-        <v>300700001</v>
-      </c>
-      <c r="K101" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：兽人战士</t>
+      <c r="K101" s="50" t="n">
+        <v>300700002</v>
+      </c>
+      <c r="L101" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="50" t="n">
-        <v>300700002</v>
+        <v>300700003</v>
       </c>
       <c r="B102" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C102" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D102" s="50" t="n">
@@ -5777,7 +5788,7 @@
       </c>
       <c r="E102" s="50" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="F102" s="50" t="inlineStr">
@@ -5786,33 +5797,33 @@
         </is>
       </c>
       <c r="G102" s="50" t="n">
-        <v>300700002</v>
+        <v>300700003</v>
       </c>
       <c r="H102" s="50" t="n">
         <v>300700000</v>
       </c>
-      <c r="I102" s="50" t="n">
+      <c r="J102" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J102" s="50" t="n">
-        <v>300700002</v>
-      </c>
-      <c r="K102" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：兽人弓箭手</t>
+      <c r="K102" s="50" t="n">
+        <v>300700003</v>
+      </c>
+      <c r="L102" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="50" t="n">
-        <v>300700003</v>
+        <v>300700004</v>
       </c>
       <c r="B103" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C103" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D103" s="50" t="n">
@@ -5820,7 +5831,7 @@
       </c>
       <c r="E103" s="50" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F103" s="50" t="inlineStr">
@@ -5829,33 +5840,33 @@
         </is>
       </c>
       <c r="G103" s="50" t="n">
-        <v>300700003</v>
+        <v>300700004</v>
       </c>
       <c r="H103" s="50" t="n">
         <v>300700000</v>
       </c>
-      <c r="I103" s="50" t="n">
+      <c r="J103" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J103" s="50" t="n">
-        <v>300700003</v>
-      </c>
-      <c r="K103" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+      <c r="K103" s="50" t="n">
+        <v>300700004</v>
+      </c>
+      <c r="L103" s="50" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="50" t="n">
-        <v>300700004</v>
+        <v>300700101</v>
       </c>
       <c r="B104" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C104" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D104" s="50" t="n">
@@ -5863,42 +5874,44 @@
       </c>
       <c r="E104" s="50" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F104" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G104" s="50" t="n">
-        <v>300700004</v>
-      </c>
-      <c r="H104" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="I104" s="50" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="H104" s="50" t="inlineStr">
+        <is>
+          <t>300700001|300700002|300700003|300700004|</t>
+        </is>
+      </c>
+      <c r="J104" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J104" s="50" t="n">
-        <v>300700004</v>
-      </c>
-      <c r="K104" s="50" t="inlineStr">
-        <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+      <c r="K104" s="50" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="L104" s="50" t="inlineStr">
+        <is>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="50" t="n">
-        <v>300700101</v>
+        <v>300700102</v>
       </c>
       <c r="B105" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C105" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D105" s="50" t="n">
@@ -5911,39 +5924,37 @@
       </c>
       <c r="F105" s="50" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G105" s="50" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="H105" s="50" t="n">
         <v>300700101</v>
       </c>
-      <c r="H105" s="50" t="inlineStr">
-        <is>
-          <t>300700001|300700002|300700003|300700004|</t>
-        </is>
-      </c>
-      <c r="I105" s="50" t="n">
+      <c r="J105" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J105" s="50" t="n">
-        <v>300700101</v>
-      </c>
-      <c r="K105" s="50" t="inlineStr">
-        <is>
-          <t>孕育兽人x5</t>
+      <c r="K105" s="50" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="L105" s="50" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="50" t="n">
-        <v>300700102</v>
+        <v>300700201</v>
       </c>
       <c r="B106" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C106" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_38</t>
         </is>
       </c>
       <c r="D106" s="50" t="n">
@@ -5951,42 +5962,44 @@
       </c>
       <c r="E106" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="F106" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G106" s="50" t="n">
-        <v>300700102</v>
-      </c>
-      <c r="H106" s="50" t="n">
-        <v>300700101</v>
-      </c>
-      <c r="I106" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="H106" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300700000,</t>
+        </is>
+      </c>
+      <c r="J106" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J106" s="50" t="n">
-        <v>300700102</v>
-      </c>
-      <c r="K106" s="50" t="inlineStr">
-        <is>
-          <t>孕育兽人x10</t>
+      <c r="K106" s="50" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="L106" s="50" t="inlineStr">
+        <is>
+          <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="50" t="n">
-        <v>300700201</v>
+        <v>300700301</v>
       </c>
       <c r="B107" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C107" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D107" s="50" t="n">
@@ -5994,7 +6007,7 @@
       </c>
       <c r="E107" s="50" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F107" s="50" t="inlineStr">
@@ -6003,35 +6016,35 @@
         </is>
       </c>
       <c r="G107" s="50" t="n">
-        <v>300700201</v>
+        <v>300700301</v>
       </c>
       <c r="H107" s="50" t="inlineStr">
         <is>
-          <t>100200001,300700000,</t>
-        </is>
-      </c>
-      <c r="I107" s="50" t="n">
+          <t>300700000,</t>
+        </is>
+      </c>
+      <c r="J107" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="J107" s="50" t="n">
-        <v>300700201</v>
-      </c>
-      <c r="K107" s="50" t="inlineStr">
-        <is>
-          <t>可转生兽人</t>
+      <c r="K107" s="50" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="L107" s="50" t="inlineStr">
+        <is>
+          <t>奖励-可获取兽人装备</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="50" t="n">
-        <v>300700301</v>
+        <v>100500001</v>
       </c>
       <c r="B108" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C108" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_18</t>
         </is>
       </c>
       <c r="D108" s="50" t="n">
@@ -6039,132 +6052,1439 @@
       </c>
       <c r="E108" s="50" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F108" s="50" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G108" s="50" t="n">
-        <v>300700301</v>
-      </c>
-      <c r="H108" s="50" t="inlineStr">
-        <is>
-          <t>300700000,</t>
-        </is>
-      </c>
-      <c r="I108" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="J108" s="50" t="n">
-        <v>300700301</v>
-      </c>
-      <c r="K108" s="50" t="inlineStr">
-        <is>
-          <t>奖励-可获取兽人装备</t>
+        <v>100500001</v>
+      </c>
+      <c r="J108" s="50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" s="50" t="n">
+        <v>100500001</v>
+      </c>
+      <c r="L108" s="50" t="inlineStr">
+        <is>
+          <t>开启成就系统</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="50" t="n">
-        <v>100500001</v>
+        <v>100600002</v>
       </c>
       <c r="B109" s="50" t="n">
         <v>1</v>
       </c>
       <c r="C109" s="50" t="inlineStr">
         <is>
-          <t>ui_research_18</t>
+          <t>ui_research_65</t>
         </is>
       </c>
       <c r="D109" s="50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E109" s="50" t="inlineStr">
         <is>
+          <t>-500</t>
+        </is>
+      </c>
+      <c r="F109" s="50" t="inlineStr">
+        <is>
+          <t>-156</t>
+        </is>
+      </c>
+      <c r="G109" s="50" t="n">
+        <v>100600002</v>
+      </c>
+      <c r="H109" s="50" t="inlineStr">
+        <is>
+          <t>100600001</t>
+        </is>
+      </c>
+      <c r="J109" s="50" t="inlineStr">
+        <is>
+          <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
+        </is>
+      </c>
+      <c r="K109" s="50" t="n">
+        <v>100600002</v>
+      </c>
+      <c r="L109" s="50" t="inlineStr">
+        <is>
+          <t>魔汁机投入数量+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="50" t="n">
+        <v>100310113</v>
+      </c>
+      <c r="B110" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C110" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_11</t>
+        </is>
+      </c>
+      <c r="D110" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="50" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="F110" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="G110" s="50" t="n">
+        <v>100310113</v>
+      </c>
+      <c r="H110" s="50" t="inlineStr">
+        <is>
+          <t>100310112</t>
+        </is>
+      </c>
+      <c r="J110" s="50" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K110" s="50" t="n">
+        <v>100310113</v>
+      </c>
+      <c r="L110" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法：征服难度3</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="50" t="n">
+        <v>100310114</v>
+      </c>
+      <c r="B111" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C111" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_11</t>
+        </is>
+      </c>
+      <c r="D111" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="50" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="F111" s="50" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="G111" s="50" t="n">
+        <v>100310114</v>
+      </c>
+      <c r="H111" s="50" t="inlineStr">
+        <is>
+          <t>100310113</t>
+        </is>
+      </c>
+      <c r="J111" s="50" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="K111" s="50" t="n">
+        <v>100310114</v>
+      </c>
+      <c r="L111" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法：征服难度4</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="50" t="n">
+        <v>100310115</v>
+      </c>
+      <c r="B112" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C112" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_11</t>
+        </is>
+      </c>
+      <c r="D112" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="50" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="F112" s="50" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="G112" s="50" t="n">
+        <v>100310115</v>
+      </c>
+      <c r="H112" s="50" t="inlineStr">
+        <is>
+          <t>100310114</t>
+        </is>
+      </c>
+      <c r="J112" s="50" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="K112" s="50" t="n">
+        <v>100310115</v>
+      </c>
+      <c r="L112" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法：征服难度5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="50" t="n">
+        <v>100310116</v>
+      </c>
+      <c r="B113" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C113" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_11</t>
+        </is>
+      </c>
+      <c r="D113" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="50" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="F113" s="50" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="G113" s="50" t="n">
+        <v>100310116</v>
+      </c>
+      <c r="H113" s="50" t="inlineStr">
+        <is>
+          <t>100310115</t>
+        </is>
+      </c>
+      <c r="J113" s="50" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="K113" s="50" t="n">
+        <v>100310116</v>
+      </c>
+      <c r="L113" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法：征服难度6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="50" t="n">
+        <v>100310117</v>
+      </c>
+      <c r="B114" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C114" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_11</t>
+        </is>
+      </c>
+      <c r="D114" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="50" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="F114" s="50" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="G114" s="50" t="n">
+        <v>100310117</v>
+      </c>
+      <c r="H114" s="50" t="inlineStr">
+        <is>
+          <t>100310116</t>
+        </is>
+      </c>
+      <c r="J114" s="50" t="inlineStr">
+        <is>
+          <t>6400</t>
+        </is>
+      </c>
+      <c r="K114" s="50" t="n">
+        <v>100310117</v>
+      </c>
+      <c r="L114" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法：征服难度7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="12" customHeight="1" s="51">
+      <c r="A115" s="50" t="n">
+        <v>100310118</v>
+      </c>
+      <c r="B115" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C115" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_11</t>
+        </is>
+      </c>
+      <c r="D115" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="50" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="F115" s="50" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="G115" s="50" t="n">
+        <v>100310118</v>
+      </c>
+      <c r="H115" s="50" t="inlineStr">
+        <is>
+          <t>100310117</t>
+        </is>
+      </c>
+      <c r="J115" s="50" t="inlineStr">
+        <is>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="K115" s="50" t="n">
+        <v>100310118</v>
+      </c>
+      <c r="L115" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法：征服难度8</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="12" customHeight="1" s="51">
+      <c r="A116" s="50" t="n">
+        <v>100310119</v>
+      </c>
+      <c r="B116" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_11</t>
+        </is>
+      </c>
+      <c r="D116" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="50" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="F116" s="50" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="G116" s="50" t="n">
+        <v>100310119</v>
+      </c>
+      <c r="H116" s="50" t="inlineStr">
+        <is>
+          <t>100310118</t>
+        </is>
+      </c>
+      <c r="J116" s="50" t="inlineStr">
+        <is>
+          <t>25600</t>
+        </is>
+      </c>
+      <c r="K116" s="50" t="n">
+        <v>100310119</v>
+      </c>
+      <c r="L116" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法：征服难度9</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="12" customHeight="1" s="51">
+      <c r="A117" s="50" t="n">
+        <v>100310120</v>
+      </c>
+      <c r="B117" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C117" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_11</t>
+        </is>
+      </c>
+      <c r="D117" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="50" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="F117" s="50" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="G117" s="50" t="n">
+        <v>100310120</v>
+      </c>
+      <c r="H117" s="50" t="inlineStr">
+        <is>
+          <t>100310119</t>
+        </is>
+      </c>
+      <c r="J117" s="50" t="inlineStr">
+        <is>
+          <t>51200</t>
+        </is>
+      </c>
+      <c r="K117" s="50" t="n">
+        <v>100310120</v>
+      </c>
+      <c r="L117" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法：征服难度10</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="12" customHeight="1" s="51">
+      <c r="A118" s="50" t="n">
+        <v>100310131</v>
+      </c>
+      <c r="B118" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C118" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D118" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F118" s="50" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F109" s="50" t="inlineStr">
+      <c r="G118" s="50" t="n">
+        <v>100310131</v>
+      </c>
+      <c r="H118" s="50" t="inlineStr">
+        <is>
+          <t>100310112</t>
+        </is>
+      </c>
+      <c r="I118" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount2:1</t>
+        </is>
+      </c>
+      <c r="J118" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K118" s="50" t="n">
+        <v>100310131</v>
+      </c>
+      <c r="L118" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度2-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="12" customHeight="1" s="51">
+      <c r="A119" s="50" t="n">
+        <v>100310132</v>
+      </c>
+      <c r="B119" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C119" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D119" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F119" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="G119" s="50" t="n">
+        <v>100310132</v>
+      </c>
+      <c r="H119" s="50" t="inlineStr">
+        <is>
+          <t>100310113</t>
+        </is>
+      </c>
+      <c r="I119" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount3:1</t>
+        </is>
+      </c>
+      <c r="J119" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K119" s="50" t="n">
+        <v>100310132</v>
+      </c>
+      <c r="L119" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度3-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="12" customHeight="1" s="51">
+      <c r="A120" s="50" t="n">
+        <v>100310133</v>
+      </c>
+      <c r="B120" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C120" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D120" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F120" s="50" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="G120" s="50" t="n">
+        <v>100310133</v>
+      </c>
+      <c r="H120" s="50" t="inlineStr">
+        <is>
+          <t>100310114</t>
+        </is>
+      </c>
+      <c r="I120" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount4:1</t>
+        </is>
+      </c>
+      <c r="J120" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K120" s="50" t="n">
+        <v>100310133</v>
+      </c>
+      <c r="L120" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度4-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="12" customHeight="1" s="51">
+      <c r="A121" s="50" t="n">
+        <v>100310134</v>
+      </c>
+      <c r="B121" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D121" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F121" s="50" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="G121" s="50" t="n">
+        <v>100310134</v>
+      </c>
+      <c r="H121" s="50" t="inlineStr">
+        <is>
+          <t>100310115</t>
+        </is>
+      </c>
+      <c r="I121" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount5:1</t>
+        </is>
+      </c>
+      <c r="J121" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K121" s="50" t="n">
+        <v>100310134</v>
+      </c>
+      <c r="L121" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度5-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="12" customHeight="1" s="51">
+      <c r="A122" s="50" t="n">
+        <v>100310135</v>
+      </c>
+      <c r="B122" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C122" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D122" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F122" s="50" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="G122" s="50" t="n">
+        <v>100310135</v>
+      </c>
+      <c r="H122" s="50" t="inlineStr">
+        <is>
+          <t>100310116</t>
+        </is>
+      </c>
+      <c r="I122" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount6:1</t>
+        </is>
+      </c>
+      <c r="J122" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K122" s="50" t="n">
+        <v>100310135</v>
+      </c>
+      <c r="L122" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度6-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="12" customHeight="1" s="51">
+      <c r="A123" s="50" t="n">
+        <v>100310136</v>
+      </c>
+      <c r="B123" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C123" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D123" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F123" s="50" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="G123" s="50" t="n">
+        <v>100310136</v>
+      </c>
+      <c r="H123" s="50" t="inlineStr">
+        <is>
+          <t>100310117</t>
+        </is>
+      </c>
+      <c r="I123" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount7:1</t>
+        </is>
+      </c>
+      <c r="J123" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K123" s="50" t="n">
+        <v>100310136</v>
+      </c>
+      <c r="L123" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度7-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="50" t="n">
+        <v>100310137</v>
+      </c>
+      <c r="B124" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C124" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D124" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F124" s="50" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="G124" s="50" t="n">
+        <v>100310137</v>
+      </c>
+      <c r="H124" s="50" t="inlineStr">
+        <is>
+          <t>100310118</t>
+        </is>
+      </c>
+      <c r="I124" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount8:1</t>
+        </is>
+      </c>
+      <c r="J124" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K124" s="50" t="n">
+        <v>100310137</v>
+      </c>
+      <c r="L124" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度8-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="50" t="n">
+        <v>100310138</v>
+      </c>
+      <c r="B125" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C125" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D125" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F125" s="50" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="G125" s="50" t="n">
+        <v>100310138</v>
+      </c>
+      <c r="H125" s="50" t="inlineStr">
+        <is>
+          <t>100310119</t>
+        </is>
+      </c>
+      <c r="I125" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount9:1</t>
+        </is>
+      </c>
+      <c r="J125" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K125" s="50" t="n">
+        <v>100310138</v>
+      </c>
+      <c r="L125" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度9-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="50" t="n">
+        <v>100310139</v>
+      </c>
+      <c r="B126" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D126" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F126" s="50" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="G126" s="50" t="n">
+        <v>100310139</v>
+      </c>
+      <c r="H126" s="50" t="inlineStr">
+        <is>
+          <t>100310120</t>
+        </is>
+      </c>
+      <c r="I126" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount10:1</t>
+        </is>
+      </c>
+      <c r="J126" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K126" s="50" t="n">
+        <v>100310139</v>
+      </c>
+      <c r="L126" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度10-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="50" t="n">
+        <v>100310130</v>
+      </c>
+      <c r="B127" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C127" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_66</t>
+        </is>
+      </c>
+      <c r="D127" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F127" s="50" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="G127" s="50" t="n">
+        <v>100310130</v>
+      </c>
+      <c r="I127" s="50" t="inlineStr">
+        <is>
+          <t>World1ConquerCompleteCount1:1</t>
+        </is>
+      </c>
+      <c r="J127" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K127" s="50" t="n">
+        <v>100310130</v>
+      </c>
+      <c r="L127" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度1-加快进攻节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>100310140</v>
+      </c>
+      <c r="B128" t="n">
+        <v>4</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-160</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>100310140</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>100310130</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>100310140</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度1-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>100310141</v>
+      </c>
+      <c r="B129" t="n">
+        <v>4</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G109" s="50" t="n">
-        <v>100500001</v>
-      </c>
-      <c r="I109" s="50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J109" s="50" t="n">
-        <v>100500001</v>
-      </c>
-      <c r="K109" s="50" t="inlineStr">
-        <is>
-          <t>开启成就系统</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>100600002</v>
-      </c>
-      <c r="B110" t="n">
-        <v>1</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>ui_research_65</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-500</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-156</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
-        <v>100600002</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>100600001</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>100600002</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>魔汁机投入数量+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="12" customHeight="1" s="51"/>
-    <row r="116" ht="12" customHeight="1" s="51"/>
-    <row r="117" ht="12" customHeight="1" s="51"/>
-    <row r="118" ht="12" customHeight="1" s="51"/>
-    <row r="119" ht="12" customHeight="1" s="51"/>
-    <row r="120" ht="12" customHeight="1" s="51"/>
-    <row r="121" ht="12" customHeight="1" s="51"/>
-    <row r="122" ht="12" customHeight="1" s="51"/>
-    <row r="123" ht="12" customHeight="1" s="51"/>
+      <c r="G129" t="n">
+        <v>100310141</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>100310131</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>100310141</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度2-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>100310142</v>
+      </c>
+      <c r="B130" t="n">
+        <v>4</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>100310142</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>100310132</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>100310142</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度3-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>100310143</v>
+      </c>
+      <c r="B131" t="n">
+        <v>4</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>100310143</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>100310133</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>100310143</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度4-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>100310144</v>
+      </c>
+      <c r="B132" t="n">
+        <v>4</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>100310144</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>100310134</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>100310144</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度5-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>100310145</v>
+      </c>
+      <c r="B133" t="n">
+        <v>4</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>100310145</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>100310135</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>100310145</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度6-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>100310146</v>
+      </c>
+      <c r="B134" t="n">
+        <v>4</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>100310146</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>100310136</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>100310146</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度7-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>100310147</v>
+      </c>
+      <c r="B135" t="n">
+        <v>4</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>100310147</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>100310137</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>100310147</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度8-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>100310148</v>
+      </c>
+      <c r="B136" t="n">
+        <v>4</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>100310148</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>100310138</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>100310148</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度9-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>100310149</v>
+      </c>
+      <c r="B137" t="n">
+        <v>4</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>100310149</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>100310139</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>100310149</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度10-2倍速游戏</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -384,19 +384,19 @@
     <t>200400001</t>
   </si>
   <si>
+    <t>50,100,200,500,1000,5000,10000,50000,100000,500000</t>
+  </si>
+  <si>
+    <t>魔王魔力上限+10</t>
+  </si>
+  <si>
+    <t>魔王魔力恢复速度+1/s</t>
+  </si>
+  <si>
+    <t>ui_research_62</t>
+  </si>
+  <si>
     <t>100,500,1000,5000,10000</t>
-  </si>
-  <si>
-    <t>魔王魔力上限+10</t>
-  </si>
-  <si>
-    <t>100,500,1000</t>
-  </si>
-  <si>
-    <t>魔王魔力恢复速度+1/s</t>
-  </si>
-  <si>
-    <t>ui_research_62</t>
   </si>
   <si>
     <t>深渊馈赠刷新次数+1</t>
@@ -3481,8 +3481,8 @@
       <c r="C36" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="D36" s="50">
-        <v>5</v>
+      <c r="D36" s="50" t="s">
+        <v>71</v>
       </c>
       <c r="E36" s="50">
         <v>0</v>
@@ -3516,8 +3516,8 @@
       <c r="C37" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="D37" s="50">
-        <v>3</v>
+      <c r="D37" s="50" t="s">
+        <v>71</v>
       </c>
       <c r="E37" s="50" t="s">
         <v>69</v>
@@ -3532,13 +3532,13 @@
         <v>115</v>
       </c>
       <c r="J37" s="50" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K37" s="50">
         <v>200400001</v>
       </c>
       <c r="L37" s="50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
@@ -3549,7 +3549,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D38" s="50">
         <v>5</v>
@@ -3567,7 +3567,7 @@
         <v>115</v>
       </c>
       <c r="J38" s="50" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K38" s="50">
         <v>200500001</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -7020,660 +7020,754 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
+      <c r="A128" s="50" t="n">
         <v>100310140</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" t="inlineStr">
+      <c r="D128" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" s="50" t="inlineStr">
         <is>
           <t>-160</t>
         </is>
       </c>
-      <c r="G128" t="n">
+      <c r="G128" s="50" t="n">
         <v>100310140</v>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H128" s="50" t="inlineStr">
         <is>
           <t>100310130</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="J128" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K128" t="n">
+      <c r="K128" s="50" t="n">
         <v>100310140</v>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="L128" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度1-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" s="50" t="n">
         <v>100310141</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" t="inlineStr">
+      <c r="D129" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F129" s="50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G129" t="n">
+      <c r="G129" s="50" t="n">
         <v>100310141</v>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H129" s="50" t="inlineStr">
         <is>
           <t>100310131</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="J129" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K129" t="n">
+      <c r="K129" s="50" t="n">
         <v>100310141</v>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="L129" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度2-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
+      <c r="A130" s="50" t="n">
         <v>100310142</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D130" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" t="inlineStr">
+      <c r="D130" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="50" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="G130" t="n">
+      <c r="G130" s="50" t="n">
         <v>100310142</v>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H130" s="50" t="inlineStr">
         <is>
           <t>100310132</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="J130" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K130" t="n">
+      <c r="K130" s="50" t="n">
         <v>100310142</v>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="L130" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度3-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131" s="50" t="n">
         <v>100310143</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" t="inlineStr">
+      <c r="D131" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="50" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="G131" t="n">
+      <c r="G131" s="50" t="n">
         <v>100310143</v>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H131" s="50" t="inlineStr">
         <is>
           <t>100310133</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="J131" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K131" t="n">
+      <c r="K131" s="50" t="n">
         <v>100310143</v>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="L131" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度4-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132" s="50" t="n">
         <v>100310144</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D132" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" t="inlineStr">
+      <c r="D132" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="G132" t="n">
+      <c r="G132" s="50" t="n">
         <v>100310144</v>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H132" s="50" t="inlineStr">
         <is>
           <t>100310134</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="J132" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K132" t="n">
+      <c r="K132" s="50" t="n">
         <v>100310144</v>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="L132" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度5-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133" s="50" t="n">
         <v>100310145</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" t="inlineStr">
+      <c r="D133" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="50" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="G133" t="n">
+      <c r="G133" s="50" t="n">
         <v>100310145</v>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H133" s="50" t="inlineStr">
         <is>
           <t>100310135</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="J133" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K133" t="n">
+      <c r="K133" s="50" t="n">
         <v>100310145</v>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="L133" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度6-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" s="50" t="n">
         <v>100310146</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D134" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" t="inlineStr">
+      <c r="D134" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" s="50" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="G134" t="n">
+      <c r="G134" s="50" t="n">
         <v>100310146</v>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H134" s="50" t="inlineStr">
         <is>
           <t>100310136</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="J134" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K134" t="n">
+      <c r="K134" s="50" t="n">
         <v>100310146</v>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="L134" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度7-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" s="50" t="n">
         <v>100310147</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="inlineStr">
+      <c r="D135" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" s="50" t="inlineStr">
         <is>
           <t>960</t>
         </is>
       </c>
-      <c r="G135" t="n">
+      <c r="G135" s="50" t="n">
         <v>100310147</v>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H135" s="50" t="inlineStr">
         <is>
           <t>100310137</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="J135" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K135" t="n">
+      <c r="K135" s="50" t="n">
         <v>100310147</v>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="L135" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度8-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" s="50" t="n">
         <v>100310148</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C136" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D136" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" t="inlineStr">
+      <c r="D136" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F136" s="50" t="inlineStr">
         <is>
           <t>1120</t>
         </is>
       </c>
-      <c r="G136" t="n">
+      <c r="G136" s="50" t="n">
         <v>100310148</v>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="H136" s="50" t="inlineStr">
         <is>
           <t>100310138</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="J136" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K136" t="n">
+      <c r="K136" s="50" t="n">
         <v>100310148</v>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="L136" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度9-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" s="50" t="n">
         <v>100310149</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C137" s="50" t="inlineStr">
         <is>
           <t>ui_research_94</t>
         </is>
       </c>
-      <c r="D137" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" t="inlineStr">
+      <c r="D137" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="50" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F137" s="50" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="G137" t="n">
+      <c r="G137" s="50" t="n">
         <v>100310149</v>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H137" s="50" t="inlineStr">
         <is>
           <t>100310139</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="J137" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K137" t="n">
+      <c r="K137" s="50" t="n">
         <v>100310149</v>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="L137" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度10-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" s="50" t="n">
         <v>100200005</v>
       </c>
-      <c r="B138" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" t="inlineStr">
+      <c r="B138" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="50" t="inlineStr">
         <is>
           <t>ui_research_59</t>
         </is>
       </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="inlineStr">
+      <c r="D138" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" s="50" t="inlineStr">
         <is>
           <t>-500</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F138" s="50" t="inlineStr">
         <is>
           <t>-500</t>
         </is>
       </c>
-      <c r="G138" t="n">
+      <c r="G138" s="50" t="n">
         <v>100200005</v>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="H138" s="50" t="inlineStr">
         <is>
           <t>100200001</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="J138" s="50" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="K138" t="n">
+      <c r="K138" s="50" t="n">
         <v>100200005</v>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="L138" s="50" t="inlineStr">
         <is>
           <t>终焉议会议案：魔物等级下降</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="50" t="n">
         <v>100200006</v>
       </c>
-      <c r="B139" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" t="inlineStr">
+      <c r="B139" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="50" t="inlineStr">
         <is>
           <t>ui_research_59</t>
         </is>
       </c>
-      <c r="D139" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" t="inlineStr">
+      <c r="D139" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="50" t="inlineStr">
         <is>
           <t>-700</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" s="50" t="inlineStr">
         <is>
           <t>-500</t>
         </is>
       </c>
-      <c r="G139" t="n">
+      <c r="G139" s="50" t="n">
         <v>100200006</v>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H139" s="50" t="inlineStr">
         <is>
           <t>100200005</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J139" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K139" t="n">
+      <c r="K139" s="50" t="n">
         <v>100200006</v>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="L139" s="50" t="inlineStr">
         <is>
           <t>终焉议会议案：魔物等级归0</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140" s="50" t="n">
         <v>100200007</v>
       </c>
-      <c r="B140" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" t="inlineStr">
+      <c r="B140" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="50" t="inlineStr">
         <is>
           <t>ui_research_59</t>
         </is>
       </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="inlineStr">
+      <c r="D140" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="50" t="inlineStr">
         <is>
           <t>-500</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F140" s="50" t="inlineStr">
         <is>
           <t>-700</t>
         </is>
       </c>
-      <c r="G140" t="n">
+      <c r="G140" s="50" t="n">
         <v>100200007</v>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="H140" s="50" t="inlineStr">
         <is>
           <t>100200001</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="J140" s="50" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="K140" t="n">
+      <c r="K140" s="50" t="n">
         <v>100200007</v>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="L140" s="50" t="inlineStr">
         <is>
           <t>终焉议会议案：魔物稀有度下降</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" s="50" t="n">
         <v>100200008</v>
       </c>
-      <c r="B141" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" t="inlineStr">
+      <c r="B141" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="50" t="inlineStr">
         <is>
           <t>ui_research_59</t>
         </is>
       </c>
-      <c r="D141" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" t="inlineStr">
+      <c r="D141" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" s="50" t="inlineStr">
         <is>
           <t>-700</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F141" s="50" t="inlineStr">
         <is>
           <t>-700</t>
         </is>
       </c>
-      <c r="G141" t="n">
+      <c r="G141" s="50" t="n">
         <v>100200008</v>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H141" s="50" t="inlineStr">
         <is>
           <t>100200007</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J141" s="50" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K141" t="n">
+      <c r="K141" s="50" t="n">
         <v>100200008</v>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="L141" s="50" t="inlineStr">
         <is>
           <t>终焉议会议案：魔物稀有度归0</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="50" t="n">
+        <v>100200009</v>
+      </c>
+      <c r="B142" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_59</t>
+        </is>
+      </c>
+      <c r="D142" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="50" t="inlineStr">
+        <is>
+          <t>-500</t>
+        </is>
+      </c>
+      <c r="F142" s="50" t="inlineStr">
+        <is>
+          <t>-900</t>
+        </is>
+      </c>
+      <c r="G142" s="50" t="n">
+        <v>100200009</v>
+      </c>
+      <c r="H142" s="50" t="inlineStr">
+        <is>
+          <t>100200001</t>
+        </is>
+      </c>
+      <c r="J142" s="50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K142" s="50" t="n">
+        <v>100200009</v>
+      </c>
+      <c r="L142" s="50" t="inlineStr">
+        <is>
+          <t>终焉议会议案：想要更多装备！</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>100200010</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ui_research_59</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-700</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-900</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>100200010</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>100200009</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>100200010</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>终焉议会议案：想要更多魔王装备！</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -6406,7 +6406,7 @@
         <v>313</v>
       </c>
       <c r="J118" s="50" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K118" s="50">
         <v>100310131</v>
@@ -6444,7 +6444,7 @@
         <v>315</v>
       </c>
       <c r="J119" s="50" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="K119" s="50">
         <v>100310132</v>
@@ -6815,7 +6815,7 @@
         <v>337</v>
       </c>
       <c r="J129" s="50" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K129" s="50">
         <v>100310141</v>
@@ -6850,7 +6850,7 @@
         <v>339</v>
       </c>
       <c r="J130" s="50" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="K130" s="50">
         <v>100310142</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="368">
   <si>
     <t>id</t>
   </si>
@@ -348,6 +348,9 @@
     <t>-6</t>
   </si>
   <si>
+    <t>10000</t>
+  </si>
+  <si>
     <t>开启魔汁机</t>
   </si>
   <si>
@@ -771,7 +774,7 @@
     <t>解锁职业：哥布林魔法师（冰）</t>
   </si>
   <si>
-    <t>300600001|300600002|300600003|300600004|</t>
+    <t>300600001|300600002|300600003|300600004|300600005</t>
   </si>
   <si>
     <t>孕育哥布林x5</t>
@@ -861,7 +864,7 @@
     <t>100600001</t>
   </si>
   <si>
-    <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,</t>
+    <t>10000,20000,30000,40000,50000,60000,70000,80000,90000,100000,</t>
   </si>
   <si>
     <t>魔汁机投入数量+1</t>
@@ -3402,13 +3405,13 @@
         <v>48</v>
       </c>
       <c r="J32" s="50" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="K32" s="50">
         <v>100600001</v>
       </c>
       <c r="L32" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33">
@@ -3434,13 +3437,13 @@
         <v>200000001</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K33" s="50">
         <v>200000001</v>
       </c>
       <c r="L33" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34">
@@ -3451,7 +3454,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D34" s="50">
         <v>4</v>
@@ -3466,16 +3469,16 @@
         <v>200100001</v>
       </c>
       <c r="H34" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J34" s="50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K34" s="50">
         <v>200100001</v>
       </c>
       <c r="L34" s="50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35">
@@ -3486,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D35" s="50">
         <v>6</v>
@@ -3501,16 +3504,16 @@
         <v>200200001</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J35" s="50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K35" s="50">
         <v>200200001</v>
       </c>
       <c r="L35" s="50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36">
@@ -3521,7 +3524,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D36" s="50" t="s">
         <v>71</v>
@@ -3536,16 +3539,16 @@
         <v>200300001</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J36" s="50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K36" s="50">
         <v>200300001</v>
       </c>
       <c r="L36" s="50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37">
@@ -3556,7 +3559,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D37" s="50" t="s">
         <v>71</v>
@@ -3571,16 +3574,16 @@
         <v>200400001</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J37" s="50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K37" s="50">
         <v>200400001</v>
       </c>
       <c r="L37" s="50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38">
@@ -3591,7 +3594,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D38" s="50">
         <v>5</v>
@@ -3606,16 +3609,16 @@
         <v>200500001</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J38" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K38" s="50">
         <v>200500001</v>
       </c>
       <c r="L38" s="50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39">
@@ -3626,7 +3629,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D39" s="50">
         <v>3</v>
@@ -3641,16 +3644,16 @@
         <v>200600001</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J39" s="50" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K39" s="50">
         <v>200600001</v>
       </c>
       <c r="L39" s="50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
@@ -3661,7 +3664,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D40" s="50">
         <v>4</v>
@@ -3676,16 +3679,16 @@
         <v>200700001</v>
       </c>
       <c r="H40" s="50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J40" s="50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K40" s="50">
         <v>200700001</v>
       </c>
       <c r="L40" s="50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41">
@@ -3696,7 +3699,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D41" s="50">
         <v>10</v>
@@ -3711,16 +3714,16 @@
         <v>200800001</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J41" s="50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K41" s="50">
         <v>200800001</v>
       </c>
       <c r="L41" s="50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42">
@@ -3731,7 +3734,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D42" s="50">
         <v>5</v>
@@ -3746,16 +3749,16 @@
         <v>200900001</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J42" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K42" s="50">
         <v>200900001</v>
       </c>
       <c r="L42" s="50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43">
@@ -3766,7 +3769,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D43" s="50">
         <v>1</v>
@@ -3790,7 +3793,7 @@
         <v>300100000</v>
       </c>
       <c r="L43" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44">
@@ -3801,7 +3804,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D44" s="50">
         <v>1</v>
@@ -3825,7 +3828,7 @@
         <v>300100001</v>
       </c>
       <c r="L44" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45">
@@ -3836,13 +3839,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D45" s="50">
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>82</v>
@@ -3860,7 +3863,7 @@
         <v>300100002</v>
       </c>
       <c r="L45" s="50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46">
@@ -3871,13 +3874,13 @@
         <v>3</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D46" s="50">
         <v>1</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F46" s="50" t="s">
         <v>82</v>
@@ -3895,7 +3898,7 @@
         <v>300100003</v>
       </c>
       <c r="L46" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47">
@@ -3906,13 +3909,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F47" s="50" t="s">
         <v>82</v>
@@ -3930,7 +3933,7 @@
         <v>300100004</v>
       </c>
       <c r="L47" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48">
@@ -3941,7 +3944,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
@@ -3956,7 +3959,7 @@
         <v>300100101</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J48" s="50">
         <v>100</v>
@@ -3965,7 +3968,7 @@
         <v>300100101</v>
       </c>
       <c r="L48" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49">
@@ -3976,7 +3979,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
@@ -4000,7 +4003,7 @@
         <v>300100102</v>
       </c>
       <c r="L49" s="50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50">
@@ -4011,13 +4014,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F50" s="50" t="s">
         <v>97</v>
@@ -4026,7 +4029,7 @@
         <v>300100201</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J50" s="50">
         <v>100</v>
@@ -4035,7 +4038,7 @@
         <v>300100201</v>
       </c>
       <c r="L50" s="50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51">
@@ -4046,7 +4049,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
@@ -4061,16 +4064,16 @@
         <v>300100301</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J51" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K51" s="50">
         <v>300100301</v>
       </c>
       <c r="L51" s="50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52">
@@ -4081,7 +4084,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
@@ -4102,7 +4105,7 @@
         <v>300200000</v>
       </c>
       <c r="L52" s="50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53">
@@ -4113,7 +4116,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
@@ -4131,13 +4134,13 @@
         <v>300200000</v>
       </c>
       <c r="J53" s="50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K53" s="50">
         <v>300200001</v>
       </c>
       <c r="L53" s="50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54">
@@ -4148,7 +4151,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
@@ -4166,13 +4169,13 @@
         <v>300200000</v>
       </c>
       <c r="J54" s="50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K54" s="50">
         <v>300200002</v>
       </c>
       <c r="L54" s="50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55">
@@ -4183,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
@@ -4207,7 +4210,7 @@
         <v>300200003</v>
       </c>
       <c r="L55" s="50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56">
@@ -4218,7 +4221,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
@@ -4242,7 +4245,7 @@
         <v>300200004</v>
       </c>
       <c r="L56" s="50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57">
@@ -4253,7 +4256,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
@@ -4268,7 +4271,7 @@
         <v>300200101</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J57" s="50" t="s">
         <v>93</v>
@@ -4277,7 +4280,7 @@
         <v>300200101</v>
       </c>
       <c r="L57" s="50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4288,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
@@ -4312,7 +4315,7 @@
         <v>300200102</v>
       </c>
       <c r="L58" s="50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4323,7 +4326,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
@@ -4338,16 +4341,16 @@
         <v>300200201</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J59" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K59" s="50">
         <v>300200201</v>
       </c>
       <c r="L59" s="50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4358,7 +4361,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
@@ -4373,7 +4376,7 @@
         <v>300200301</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J60" s="50" t="s">
         <v>71</v>
@@ -4382,7 +4385,7 @@
         <v>300200301</v>
       </c>
       <c r="L60" s="50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4393,7 +4396,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
@@ -4411,13 +4414,13 @@
         <v>300200000</v>
       </c>
       <c r="J61" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K61" s="50">
         <v>300300000</v>
       </c>
       <c r="L61" s="50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4428,13 +4431,13 @@
         <v>3</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>82</v>
@@ -4452,7 +4455,7 @@
         <v>300300001</v>
       </c>
       <c r="L62" s="50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4463,13 +4466,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F63" s="50" t="s">
         <v>82</v>
@@ -4481,13 +4484,13 @@
         <v>300300000</v>
       </c>
       <c r="J63" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K63" s="50">
         <v>300300002</v>
       </c>
       <c r="L63" s="50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4498,16 +4501,16 @@
         <v>3</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F64" s="50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G64" s="50">
         <v>300300003</v>
@@ -4522,7 +4525,7 @@
         <v>300300003</v>
       </c>
       <c r="L64" s="50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65">
@@ -4533,7 +4536,7 @@
         <v>3</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
@@ -4557,7 +4560,7 @@
         <v>300300004</v>
       </c>
       <c r="L65" s="50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66">
@@ -4568,7 +4571,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
@@ -4583,7 +4586,7 @@
         <v>300300101</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J66" s="50" t="s">
         <v>35</v>
@@ -4592,7 +4595,7 @@
         <v>300300101</v>
       </c>
       <c r="L66" s="50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4603,7 +4606,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
@@ -4627,7 +4630,7 @@
         <v>300300102</v>
       </c>
       <c r="L67" s="50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4638,13 +4641,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F68" s="50" t="s">
         <v>97</v>
@@ -4653,16 +4656,16 @@
         <v>300300201</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J68" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K68" s="50">
         <v>300300201</v>
       </c>
       <c r="L68" s="50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4673,7 +4676,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
@@ -4688,16 +4691,16 @@
         <v>300300301</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J69" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K69" s="50">
         <v>300300301</v>
       </c>
       <c r="L69" s="50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4708,13 +4711,13 @@
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D70" s="50">
         <v>1</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F70" s="50" t="s">
         <v>69</v>
@@ -4732,7 +4735,7 @@
         <v>300400000</v>
       </c>
       <c r="L70" s="50" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4743,13 +4746,13 @@
         <v>3</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F71" s="50" t="s">
         <v>82</v>
@@ -4767,7 +4770,7 @@
         <v>300400001</v>
       </c>
       <c r="L71" s="50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4778,13 +4781,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D72" s="50">
         <v>1</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F72" s="50" t="s">
         <v>82</v>
@@ -4802,7 +4805,7 @@
         <v>300400002</v>
       </c>
       <c r="L72" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4813,13 +4816,13 @@
         <v>3</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F73" s="50" t="s">
         <v>82</v>
@@ -4837,7 +4840,7 @@
         <v>300400003</v>
       </c>
       <c r="L73" s="50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4848,13 +4851,13 @@
         <v>3</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D74" s="50">
         <v>1</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>82</v>
@@ -4872,7 +4875,7 @@
         <v>300400004</v>
       </c>
       <c r="L74" s="50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75">
@@ -4883,13 +4886,13 @@
         <v>3</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F75" s="50" t="s">
         <v>82</v>
@@ -4907,7 +4910,7 @@
         <v>300400005</v>
       </c>
       <c r="L75" s="50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="76">
@@ -4918,13 +4921,13 @@
         <v>3</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F76" s="50" t="s">
         <v>89</v>
@@ -4933,7 +4936,7 @@
         <v>300400101</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J76" s="50">
         <v>100</v>
@@ -4942,7 +4945,7 @@
         <v>300400101</v>
       </c>
       <c r="L76" s="50" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77">
@@ -4953,13 +4956,13 @@
         <v>3</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D77" s="50">
         <v>1</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F77" s="50" t="s">
         <v>92</v>
@@ -4977,7 +4980,7 @@
         <v>300400102</v>
       </c>
       <c r="L77" s="50" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -4988,13 +4991,13 @@
         <v>3</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D78" s="50">
         <v>1</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F78" s="50" t="s">
         <v>97</v>
@@ -5003,7 +5006,7 @@
         <v>300400201</v>
       </c>
       <c r="H78" s="50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J78" s="50">
         <v>100</v>
@@ -5012,7 +5015,7 @@
         <v>300400201</v>
       </c>
       <c r="L78" s="50" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5023,13 +5026,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D79" s="50">
         <v>1</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>97</v>
@@ -5038,7 +5041,7 @@
         <v>300400301</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J79" s="50">
         <v>100</v>
@@ -5047,7 +5050,7 @@
         <v>300400301</v>
       </c>
       <c r="L79" s="50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5058,13 +5061,13 @@
         <v>3</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D80" s="50">
         <v>1</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F80" s="50" t="s">
         <v>69</v>
@@ -5082,7 +5085,7 @@
         <v>300500000</v>
       </c>
       <c r="L80" s="50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5093,13 +5096,13 @@
         <v>3</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D81" s="50">
         <v>1</v>
       </c>
       <c r="E81" s="50" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F81" s="50" t="s">
         <v>82</v>
@@ -5117,7 +5120,7 @@
         <v>300500001</v>
       </c>
       <c r="L81" s="50" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5128,13 +5131,13 @@
         <v>3</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D82" s="50">
         <v>1</v>
       </c>
       <c r="E82" s="50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F82" s="50" t="s">
         <v>82</v>
@@ -5152,7 +5155,7 @@
         <v>300500002</v>
       </c>
       <c r="L82" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5163,13 +5166,13 @@
         <v>3</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D83" s="50">
         <v>1</v>
       </c>
       <c r="E83" s="50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F83" s="50" t="s">
         <v>82</v>
@@ -5187,7 +5190,7 @@
         <v>300500003</v>
       </c>
       <c r="L83" s="50" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84">
@@ -5198,13 +5201,13 @@
         <v>3</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D84" s="50">
         <v>1</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>82</v>
@@ -5222,7 +5225,7 @@
         <v>300500004</v>
       </c>
       <c r="L84" s="50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85">
@@ -5233,13 +5236,13 @@
         <v>3</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D85" s="50">
         <v>1</v>
       </c>
       <c r="E85" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F85" s="50" t="s">
         <v>89</v>
@@ -5248,7 +5251,7 @@
         <v>300500101</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J85" s="50">
         <v>100</v>
@@ -5257,7 +5260,7 @@
         <v>300500101</v>
       </c>
       <c r="L85" s="50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86">
@@ -5268,13 +5271,13 @@
         <v>3</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D86" s="50">
         <v>1</v>
       </c>
       <c r="E86" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F86" s="50" t="s">
         <v>92</v>
@@ -5292,7 +5295,7 @@
         <v>300500102</v>
       </c>
       <c r="L86" s="50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87">
@@ -5303,13 +5306,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D87" s="50">
         <v>1</v>
       </c>
       <c r="E87" s="50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F87" s="50" t="s">
         <v>97</v>
@@ -5318,7 +5321,7 @@
         <v>300500201</v>
       </c>
       <c r="H87" s="50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J87" s="50">
         <v>100</v>
@@ -5327,7 +5330,7 @@
         <v>300500201</v>
       </c>
       <c r="L87" s="50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88">
@@ -5338,13 +5341,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D88" s="50">
         <v>1</v>
       </c>
       <c r="E88" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F88" s="50" t="s">
         <v>97</v>
@@ -5353,7 +5356,7 @@
         <v>300500301</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J88" s="50">
         <v>100</v>
@@ -5362,7 +5365,7 @@
         <v>300500301</v>
       </c>
       <c r="L88" s="50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89">
@@ -5373,13 +5376,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>69</v>
@@ -5397,7 +5400,7 @@
         <v>300600000</v>
       </c>
       <c r="L89" s="50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="90">
@@ -5408,13 +5411,13 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
       </c>
       <c r="E90" s="50" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F90" s="50" t="s">
         <v>82</v>
@@ -5432,7 +5435,7 @@
         <v>300600001</v>
       </c>
       <c r="L90" s="50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="91">
@@ -5443,13 +5446,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>82</v>
@@ -5467,7 +5470,7 @@
         <v>300600002</v>
       </c>
       <c r="L91" s="50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="92">
@@ -5478,13 +5481,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>82</v>
@@ -5502,7 +5505,7 @@
         <v>300600003</v>
       </c>
       <c r="L92" s="50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93">
@@ -5513,13 +5516,13 @@
         <v>3</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F93" s="50" t="s">
         <v>82</v>
@@ -5537,7 +5540,7 @@
         <v>300600004</v>
       </c>
       <c r="L93" s="50" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="94">
@@ -5548,13 +5551,13 @@
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D94" s="50">
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F94" s="50" t="s">
         <v>82</v>
@@ -5572,7 +5575,7 @@
         <v>300600005</v>
       </c>
       <c r="L94" s="50" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95">
@@ -5583,13 +5586,13 @@
         <v>3</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D95" s="50">
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F95" s="50" t="s">
         <v>89</v>
@@ -5598,7 +5601,7 @@
         <v>300600101</v>
       </c>
       <c r="H95" s="50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J95" s="50">
         <v>100</v>
@@ -5607,7 +5610,7 @@
         <v>300600101</v>
       </c>
       <c r="L95" s="50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="96">
@@ -5618,13 +5621,13 @@
         <v>3</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D96" s="50">
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F96" s="50" t="s">
         <v>92</v>
@@ -5642,7 +5645,7 @@
         <v>300600102</v>
       </c>
       <c r="L96" s="50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97">
@@ -5653,13 +5656,13 @@
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D97" s="50">
         <v>1</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F97" s="50" t="s">
         <v>97</v>
@@ -5668,7 +5671,7 @@
         <v>300600201</v>
       </c>
       <c r="H97" s="50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J97" s="50">
         <v>100</v>
@@ -5677,7 +5680,7 @@
         <v>300600201</v>
       </c>
       <c r="L97" s="50" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98">
@@ -5688,13 +5691,13 @@
         <v>3</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D98" s="50">
         <v>1</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F98" s="50" t="s">
         <v>97</v>
@@ -5703,7 +5706,7 @@
         <v>300600301</v>
       </c>
       <c r="H98" s="50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J98" s="50">
         <v>100</v>
@@ -5712,7 +5715,7 @@
         <v>300600301</v>
       </c>
       <c r="L98" s="50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="99">
@@ -5723,13 +5726,13 @@
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D99" s="50">
         <v>1</v>
       </c>
       <c r="E99" s="50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F99" s="50" t="s">
         <v>69</v>
@@ -5747,7 +5750,7 @@
         <v>300700000</v>
       </c>
       <c r="L99" s="50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="100">
@@ -5758,13 +5761,13 @@
         <v>3</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D100" s="50">
         <v>1</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F100" s="50" t="s">
         <v>82</v>
@@ -5782,7 +5785,7 @@
         <v>300700001</v>
       </c>
       <c r="L100" s="50" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101">
@@ -5793,13 +5796,13 @@
         <v>3</v>
       </c>
       <c r="C101" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D101" s="50">
         <v>1</v>
       </c>
       <c r="E101" s="50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F101" s="50" t="s">
         <v>82</v>
@@ -5817,7 +5820,7 @@
         <v>300700002</v>
       </c>
       <c r="L101" s="50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="102">
@@ -5828,13 +5831,13 @@
         <v>3</v>
       </c>
       <c r="C102" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D102" s="50">
         <v>1</v>
       </c>
       <c r="E102" s="50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F102" s="50" t="s">
         <v>82</v>
@@ -5852,7 +5855,7 @@
         <v>300700003</v>
       </c>
       <c r="L102" s="50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="103">
@@ -5863,13 +5866,13 @@
         <v>3</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D103" s="50">
         <v>1</v>
       </c>
       <c r="E103" s="50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F103" s="50" t="s">
         <v>82</v>
@@ -5887,7 +5890,7 @@
         <v>300700004</v>
       </c>
       <c r="L103" s="50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104">
@@ -5898,13 +5901,13 @@
         <v>3</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D104" s="50">
         <v>1</v>
       </c>
       <c r="E104" s="50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F104" s="50" t="s">
         <v>89</v>
@@ -5913,7 +5916,7 @@
         <v>300700101</v>
       </c>
       <c r="H104" s="50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J104" s="50">
         <v>100</v>
@@ -5922,7 +5925,7 @@
         <v>300700101</v>
       </c>
       <c r="L104" s="50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105">
@@ -5933,13 +5936,13 @@
         <v>3</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D105" s="50">
         <v>1</v>
       </c>
       <c r="E105" s="50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F105" s="50" t="s">
         <v>92</v>
@@ -5957,7 +5960,7 @@
         <v>300700102</v>
       </c>
       <c r="L105" s="50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="106">
@@ -5968,13 +5971,13 @@
         <v>3</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D106" s="50">
         <v>1</v>
       </c>
       <c r="E106" s="50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F106" s="50" t="s">
         <v>97</v>
@@ -5983,7 +5986,7 @@
         <v>300700201</v>
       </c>
       <c r="H106" s="50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J106" s="50">
         <v>100</v>
@@ -5992,7 +5995,7 @@
         <v>300700201</v>
       </c>
       <c r="L106" s="50" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="107">
@@ -6003,13 +6006,13 @@
         <v>3</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D107" s="50">
         <v>1</v>
       </c>
       <c r="E107" s="50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F107" s="50" t="s">
         <v>97</v>
@@ -6018,7 +6021,7 @@
         <v>300700301</v>
       </c>
       <c r="H107" s="50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J107" s="50">
         <v>100</v>
@@ -6027,7 +6030,7 @@
         <v>300700301</v>
       </c>
       <c r="L107" s="50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="108">
@@ -6038,7 +6041,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D108" s="50">
         <v>1</v>
@@ -6059,7 +6062,7 @@
         <v>100500001</v>
       </c>
       <c r="L108" s="50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="109">
@@ -6079,22 +6082,22 @@
         <v>34</v>
       </c>
       <c r="F109" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G109" s="50">
         <v>100600002</v>
       </c>
       <c r="H109" s="50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J109" s="50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K109" s="50">
         <v>100600002</v>
       </c>
       <c r="L109" s="50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110">
@@ -6114,13 +6117,13 @@
         <v>86</v>
       </c>
       <c r="F110" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G110" s="50">
         <v>100310113</v>
       </c>
       <c r="H110" s="50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J110" s="50" t="s">
         <v>35</v>
@@ -6129,7 +6132,7 @@
         <v>100310113</v>
       </c>
       <c r="L110" s="50" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="111">
@@ -6149,13 +6152,13 @@
         <v>86</v>
       </c>
       <c r="F111" s="50" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G111" s="50">
         <v>100310114</v>
       </c>
       <c r="H111" s="50" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J111" s="50" t="s">
         <v>100</v>
@@ -6164,7 +6167,7 @@
         <v>100310114</v>
       </c>
       <c r="L111" s="50" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="112">
@@ -6184,22 +6187,22 @@
         <v>86</v>
       </c>
       <c r="F112" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G112" s="50">
         <v>100310115</v>
       </c>
       <c r="H112" s="50" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J112" s="50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K112" s="50">
         <v>100310115</v>
       </c>
       <c r="L112" s="50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="113">
@@ -6219,22 +6222,22 @@
         <v>86</v>
       </c>
       <c r="F113" s="50" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G113" s="50">
         <v>100310116</v>
       </c>
       <c r="H113" s="50" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J113" s="50" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K113" s="50">
         <v>100310116</v>
       </c>
       <c r="L113" s="50" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="114">
@@ -6260,16 +6263,16 @@
         <v>100310117</v>
       </c>
       <c r="H114" s="50" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J114" s="50" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K114" s="50">
         <v>100310117</v>
       </c>
       <c r="L114" s="50" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6289,22 +6292,22 @@
         <v>86</v>
       </c>
       <c r="F115" s="50" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G115" s="50">
         <v>100310118</v>
       </c>
       <c r="H115" s="50" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J115" s="50" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K115" s="50">
         <v>100310118</v>
       </c>
       <c r="L115" s="50" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="116" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6324,22 +6327,22 @@
         <v>86</v>
       </c>
       <c r="F116" s="50" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G116" s="50">
         <v>100310119</v>
       </c>
       <c r="H116" s="50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J116" s="50" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K116" s="50">
         <v>100310119</v>
       </c>
       <c r="L116" s="50" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="117" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6359,22 +6362,22 @@
         <v>86</v>
       </c>
       <c r="F117" s="50" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G117" s="50">
         <v>100310120</v>
       </c>
       <c r="H117" s="50" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J117" s="50" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K117" s="50">
         <v>100310120</v>
       </c>
       <c r="L117" s="50" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="118" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6385,13 +6388,13 @@
         <v>4</v>
       </c>
       <c r="C118" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D118" s="50">
         <v>1</v>
       </c>
       <c r="E118" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F118" s="50" t="s">
         <v>69</v>
@@ -6400,10 +6403,10 @@
         <v>100310131</v>
       </c>
       <c r="H118" s="50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I118" s="50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J118" s="50" t="s">
         <v>89</v>
@@ -6412,7 +6415,7 @@
         <v>100310131</v>
       </c>
       <c r="L118" s="50" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="119" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6423,34 +6426,34 @@
         <v>4</v>
       </c>
       <c r="C119" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D119" s="50">
         <v>1</v>
       </c>
       <c r="E119" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F119" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G119" s="50">
         <v>100310132</v>
       </c>
       <c r="H119" s="50" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I119" s="50" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J119" s="50" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K119" s="50">
         <v>100310132</v>
       </c>
       <c r="L119" s="50" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="120" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6461,25 +6464,25 @@
         <v>4</v>
       </c>
       <c r="C120" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D120" s="50">
         <v>1</v>
       </c>
       <c r="E120" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F120" s="50" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G120" s="50">
         <v>100310133</v>
       </c>
       <c r="H120" s="50" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I120" s="50" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J120" s="50" t="s">
         <v>82</v>
@@ -6488,7 +6491,7 @@
         <v>100310133</v>
       </c>
       <c r="L120" s="50" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="121" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6499,25 +6502,25 @@
         <v>4</v>
       </c>
       <c r="C121" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D121" s="50">
         <v>1</v>
       </c>
       <c r="E121" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F121" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G121" s="50">
         <v>100310134</v>
       </c>
       <c r="H121" s="50" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I121" s="50" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J121" s="50" t="s">
         <v>82</v>
@@ -6526,7 +6529,7 @@
         <v>100310134</v>
       </c>
       <c r="L121" s="50" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="122" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6537,25 +6540,25 @@
         <v>4</v>
       </c>
       <c r="C122" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D122" s="50">
         <v>1</v>
       </c>
       <c r="E122" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F122" s="50" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G122" s="50">
         <v>100310135</v>
       </c>
       <c r="H122" s="50" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I122" s="50" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J122" s="50" t="s">
         <v>82</v>
@@ -6564,7 +6567,7 @@
         <v>100310135</v>
       </c>
       <c r="L122" s="50" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="123" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6575,13 +6578,13 @@
         <v>4</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D123" s="50">
         <v>1</v>
       </c>
       <c r="E123" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F123" s="50" t="s">
         <v>100</v>
@@ -6590,10 +6593,10 @@
         <v>100310136</v>
       </c>
       <c r="H123" s="50" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I123" s="50" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J123" s="50" t="s">
         <v>82</v>
@@ -6602,7 +6605,7 @@
         <v>100310136</v>
       </c>
       <c r="L123" s="50" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="124">
@@ -6613,25 +6616,25 @@
         <v>4</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D124" s="50">
         <v>1</v>
       </c>
       <c r="E124" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F124" s="50" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G124" s="50">
         <v>100310137</v>
       </c>
       <c r="H124" s="50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I124" s="50" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J124" s="50" t="s">
         <v>82</v>
@@ -6640,7 +6643,7 @@
         <v>100310137</v>
       </c>
       <c r="L124" s="50" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="125">
@@ -6651,25 +6654,25 @@
         <v>4</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D125" s="50">
         <v>1</v>
       </c>
       <c r="E125" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F125" s="50" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G125" s="50">
         <v>100310138</v>
       </c>
       <c r="H125" s="50" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I125" s="50" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J125" s="50" t="s">
         <v>82</v>
@@ -6678,7 +6681,7 @@
         <v>100310138</v>
       </c>
       <c r="L125" s="50" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="126">
@@ -6689,25 +6692,25 @@
         <v>4</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D126" s="50">
         <v>1</v>
       </c>
       <c r="E126" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F126" s="50" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G126" s="50">
         <v>100310139</v>
       </c>
       <c r="H126" s="50" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I126" s="50" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J126" s="50" t="s">
         <v>82</v>
@@ -6716,7 +6719,7 @@
         <v>100310139</v>
       </c>
       <c r="L126" s="50" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="127">
@@ -6727,13 +6730,13 @@
         <v>4</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D127" s="50">
         <v>1</v>
       </c>
       <c r="E127" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F127" s="50" t="s">
         <v>86</v>
@@ -6742,7 +6745,7 @@
         <v>100310130</v>
       </c>
       <c r="I127" s="50" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J127" s="50" t="s">
         <v>82</v>
@@ -6751,7 +6754,7 @@
         <v>100310130</v>
       </c>
       <c r="L127" s="50" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="128">
@@ -6762,13 +6765,13 @@
         <v>4</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D128" s="50">
         <v>1</v>
       </c>
       <c r="E128" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F128" s="50" t="s">
         <v>86</v>
@@ -6777,7 +6780,7 @@
         <v>100310140</v>
       </c>
       <c r="H128" s="50" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J128" s="50" t="s">
         <v>82</v>
@@ -6786,7 +6789,7 @@
         <v>100310140</v>
       </c>
       <c r="L128" s="50" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="129">
@@ -6797,13 +6800,13 @@
         <v>4</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D129" s="50">
         <v>1</v>
       </c>
       <c r="E129" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F129" s="50" t="s">
         <v>69</v>
@@ -6812,7 +6815,7 @@
         <v>100310141</v>
       </c>
       <c r="H129" s="50" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J129" s="50" t="s">
         <v>89</v>
@@ -6821,7 +6824,7 @@
         <v>100310141</v>
       </c>
       <c r="L129" s="50" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="130">
@@ -6832,31 +6835,31 @@
         <v>4</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D130" s="50">
         <v>1</v>
       </c>
       <c r="E130" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F130" s="50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G130" s="50">
         <v>100310142</v>
       </c>
       <c r="H130" s="50" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J130" s="50" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K130" s="50">
         <v>100310142</v>
       </c>
       <c r="L130" s="50" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="131">
@@ -6867,22 +6870,22 @@
         <v>4</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D131" s="50">
         <v>1</v>
       </c>
       <c r="E131" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F131" s="50" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G131" s="50">
         <v>100310143</v>
       </c>
       <c r="H131" s="50" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J131" s="50" t="s">
         <v>82</v>
@@ -6891,7 +6894,7 @@
         <v>100310143</v>
       </c>
       <c r="L131" s="50" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="132">
@@ -6902,22 +6905,22 @@
         <v>4</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D132" s="50">
         <v>1</v>
       </c>
       <c r="E132" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F132" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G132" s="50">
         <v>100310144</v>
       </c>
       <c r="H132" s="50" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J132" s="50" t="s">
         <v>82</v>
@@ -6926,7 +6929,7 @@
         <v>100310144</v>
       </c>
       <c r="L132" s="50" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="133">
@@ -6937,22 +6940,22 @@
         <v>4</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D133" s="50">
         <v>1</v>
       </c>
       <c r="E133" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F133" s="50" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G133" s="50">
         <v>100310145</v>
       </c>
       <c r="H133" s="50" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J133" s="50" t="s">
         <v>82</v>
@@ -6961,7 +6964,7 @@
         <v>100310145</v>
       </c>
       <c r="L133" s="50" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="134">
@@ -6972,13 +6975,13 @@
         <v>4</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D134" s="50">
         <v>1</v>
       </c>
       <c r="E134" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F134" s="50" t="s">
         <v>100</v>
@@ -6987,7 +6990,7 @@
         <v>100310146</v>
       </c>
       <c r="H134" s="50" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J134" s="50" t="s">
         <v>82</v>
@@ -6996,7 +6999,7 @@
         <v>100310146</v>
       </c>
       <c r="L134" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="135">
@@ -7007,22 +7010,22 @@
         <v>4</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D135" s="50">
         <v>1</v>
       </c>
       <c r="E135" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F135" s="50" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G135" s="50">
         <v>100310147</v>
       </c>
       <c r="H135" s="50" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J135" s="50" t="s">
         <v>82</v>
@@ -7031,7 +7034,7 @@
         <v>100310147</v>
       </c>
       <c r="L135" s="50" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="136">
@@ -7042,22 +7045,22 @@
         <v>4</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D136" s="50">
         <v>1</v>
       </c>
       <c r="E136" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F136" s="50" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G136" s="50">
         <v>100310148</v>
       </c>
       <c r="H136" s="50" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J136" s="50" t="s">
         <v>82</v>
@@ -7066,7 +7069,7 @@
         <v>100310148</v>
       </c>
       <c r="L136" s="50" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="137">
@@ -7077,22 +7080,22 @@
         <v>4</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D137" s="50">
         <v>1</v>
       </c>
       <c r="E137" s="50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F137" s="50" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G137" s="50">
         <v>100310149</v>
       </c>
       <c r="H137" s="50" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J137" s="50" t="s">
         <v>82</v>
@@ -7101,7 +7104,7 @@
         <v>100310149</v>
       </c>
       <c r="L137" s="50" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="138">
@@ -7136,7 +7139,7 @@
         <v>100200005</v>
       </c>
       <c r="L138" s="50" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="139">
@@ -7162,7 +7165,7 @@
         <v>100200006</v>
       </c>
       <c r="H139" s="50" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J139" s="50" t="s">
         <v>82</v>
@@ -7171,7 +7174,7 @@
         <v>100200006</v>
       </c>
       <c r="L139" s="50" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="140">
@@ -7206,7 +7209,7 @@
         <v>100200007</v>
       </c>
       <c r="L140" s="50" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="141">
@@ -7232,7 +7235,7 @@
         <v>100200008</v>
       </c>
       <c r="H141" s="50" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J141" s="50" t="s">
         <v>82</v>
@@ -7241,7 +7244,7 @@
         <v>100200008</v>
       </c>
       <c r="L141" s="50" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="142">
@@ -7261,7 +7264,7 @@
         <v>34</v>
       </c>
       <c r="F142" s="50" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G142" s="50">
         <v>100200009</v>
@@ -7276,7 +7279,7 @@
         <v>100200009</v>
       </c>
       <c r="L142" s="50" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="143">
@@ -7296,13 +7299,13 @@
         <v>38</v>
       </c>
       <c r="F143" s="50" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G143" s="50">
         <v>100200010</v>
       </c>
       <c r="H143" s="50" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J143" s="50" t="s">
         <v>82</v>
@@ -7311,7 +7314,7 @@
         <v>100200010</v>
       </c>
       <c r="L143" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="144">
@@ -7337,7 +7340,7 @@
         <v>201000001</v>
       </c>
       <c r="H144" s="51" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J144" s="51" t="s">
         <v>82</v>
@@ -7346,7 +7349,7 @@
         <v>201000001</v>
       </c>
       <c r="L144" s="51" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
